--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -399,14 +399,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:N157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="5.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,7 +434,31 @@
         <v>PG</v>
       </c>
       <c r="F1" t="str">
-        <v>Tags</v>
+        <v>TG</v>
+      </c>
+      <c r="G1" t="str">
+        <v>EL</v>
+      </c>
+      <c r="H1" t="str">
+        <v>MT</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HMT</v>
+      </c>
+      <c r="J1" t="str">
+        <v>MA</v>
+      </c>
+      <c r="K1" t="str">
+        <v>SCI</v>
+      </c>
+      <c r="L1" t="str">
+        <v>HIST</v>
+      </c>
+      <c r="M1" t="str">
+        <v>GEOG</v>
+      </c>
+      <c r="N1" t="str">
+        <v>LIT</v>
       </c>
     </row>
     <row r="2">
@@ -446,7 +478,31 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT CHINESE</v>
+        <v>TG1</v>
+      </c>
+      <c r="G2" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H2" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I2" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J2" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K2" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L2" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M2" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N2" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="3">
@@ -466,7 +522,31 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G3" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H3" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K3" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L3" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M3" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N3" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="4">
@@ -486,7 +566,31 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G4" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H4" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K4" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L4" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M4" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N4" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="5">
@@ -506,7 +610,31 @@
         <v>3</v>
       </c>
       <c r="F5" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G5" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H5" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K5" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L5" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M5" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N5" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="6">
@@ -526,7 +654,31 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G6" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H6" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K6" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L6" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M6" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N6" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="7">
@@ -546,7 +698,31 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G7" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H7" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K7" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L7" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M7" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N7" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="8">
@@ -566,7 +742,31 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G8" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H8" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K8" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L8" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M8" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N8" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="9">
@@ -586,7 +786,31 @@
         <v>3</v>
       </c>
       <c r="F9" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G9" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H9" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I9" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J9" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K9" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L9" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M9" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N9" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="10">
@@ -606,7 +830,31 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G10" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H10" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K10" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L10" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M10" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N10" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="11">
@@ -626,7 +874,31 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G11" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H11" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K11" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L11" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M11" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N11" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="12">
@@ -646,7 +918,31 @@
         <v>3</v>
       </c>
       <c r="F12" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G12" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H12" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K12" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L12" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M12" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N12" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="13">
@@ -666,7 +962,31 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G13" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H13" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K13" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L13" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M13" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N13" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="14">
@@ -686,7 +1006,31 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G14" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H14" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K14" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L14" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M14" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N14" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="15">
@@ -706,7 +1050,31 @@
         <v>2</v>
       </c>
       <c r="F15" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G15" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H15" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K15" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L15" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M15" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N15" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="16">
@@ -726,7 +1094,31 @@
         <v>3</v>
       </c>
       <c r="F16" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G16" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H16" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I16" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J16" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K16" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L16" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M16" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N16" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="17">
@@ -746,7 +1138,31 @@
         <v>3</v>
       </c>
       <c r="F17" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G17" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H17" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K17" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L17" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M17" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N17" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="18">
@@ -766,7 +1182,31 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G18" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H18" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K18" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L18" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M18" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N18" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="19">
@@ -786,7 +1226,31 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G19" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H19" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K19" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L19" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M19" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N19" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="20">
@@ -806,7 +1270,31 @@
         <v>3</v>
       </c>
       <c r="F20" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G20" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H20" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K20" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L20" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M20" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N20" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="21">
@@ -826,7 +1314,31 @@
         <v>3</v>
       </c>
       <c r="F21" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G21" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H21" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K21" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L21" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M21" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N21" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="22">
@@ -846,7 +1358,31 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G22" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H22" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K22" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L22" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M22" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N22" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="23">
@@ -866,7 +1402,31 @@
         <v>2</v>
       </c>
       <c r="F23" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2 · HMT CHINESE</v>
+        <v>TG2</v>
+      </c>
+      <c r="G23" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H23" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I23" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J23" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K23" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L23" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M23" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N23" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="24">
@@ -886,7 +1446,31 @@
         <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G24" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H24" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K24" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L24" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M24" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N24" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="25">
@@ -906,7 +1490,31 @@
         <v>3</v>
       </c>
       <c r="F25" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G25" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H25" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K25" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L25" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M25" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N25" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="26">
@@ -926,7 +1534,31 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G26" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H26" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K26" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L26" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M26" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N26" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="27">
@@ -946,7 +1578,31 @@
         <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G27" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H27" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K27" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L27" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M27" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N27" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="28">
@@ -966,7 +1622,31 @@
         <v>3</v>
       </c>
       <c r="F28" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G28" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H28" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K28" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L28" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M28" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N28" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="29">
@@ -986,7 +1666,31 @@
         <v>3</v>
       </c>
       <c r="F29" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G29" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H29" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K29" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L29" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M29" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N29" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="30">
@@ -1006,7 +1710,31 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G30" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H30" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I30" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J30" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K30" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L30" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M30" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N30" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="31">
@@ -1026,7 +1754,31 @@
         <v>2</v>
       </c>
       <c r="F31" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G31" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H31" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K31" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L31" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M31" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N31" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="32">
@@ -1046,7 +1798,31 @@
         <v>3</v>
       </c>
       <c r="F32" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G32" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H32" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K32" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L32" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M32" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N32" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="33">
@@ -1066,7 +1842,31 @@
         <v>3</v>
       </c>
       <c r="F33" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G33" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H33" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K33" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L33" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M33" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N33" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="34">
@@ -1086,7 +1886,31 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G34" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H34" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K34" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L34" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M34" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N34" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="35">
@@ -1106,7 +1930,31 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G35" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H35" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K35" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L35" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M35" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N35" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="36">
@@ -1126,7 +1974,31 @@
         <v>3</v>
       </c>
       <c r="F36" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G36" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H36" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K36" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L36" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M36" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N36" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="37">
@@ -1146,7 +2018,31 @@
         <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G37" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H37" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I37" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J37" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K37" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L37" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M37" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N37" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="38">
@@ -1166,7 +2062,31 @@
         <v>1</v>
       </c>
       <c r="F38" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G38" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H38" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K38" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L38" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M38" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N38" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="39">
@@ -1186,7 +2106,31 @@
         <v>2</v>
       </c>
       <c r="F39" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G39" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H39" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K39" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L39" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M39" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N39" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="40">
@@ -1206,7 +2150,31 @@
         <v>3</v>
       </c>
       <c r="F40" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G40" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H40" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K40" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L40" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M40" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N40" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="41">
@@ -1226,7 +2194,31 @@
         <v>3</v>
       </c>
       <c r="F41" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G41" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H41" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K41" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L41" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M41" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N41" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="42">
@@ -1246,7 +2238,31 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G42" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H42" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K42" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L42" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M42" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N42" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="43">
@@ -1266,7 +2282,31 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G43" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H43" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K43" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L43" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M43" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N43" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="44">
@@ -1286,7 +2326,31 @@
         <v>3</v>
       </c>
       <c r="F44" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT CHINESE</v>
+        <v>TG1</v>
+      </c>
+      <c r="G44" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H44" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I44" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J44" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K44" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L44" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M44" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N44" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="45">
@@ -1306,7 +2370,31 @@
         <v>3</v>
       </c>
       <c r="F45" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G45" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H45" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K45" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L45" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M45" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N45" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="46">
@@ -1326,7 +2414,31 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G46" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H46" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K46" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L46" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M46" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N46" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="47">
@@ -1346,7 +2458,31 @@
         <v>2</v>
       </c>
       <c r="F47" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G47" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H47" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K47" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L47" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M47" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N47" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="48">
@@ -1366,7 +2502,31 @@
         <v>3</v>
       </c>
       <c r="F48" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G48" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H48" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K48" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L48" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M48" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N48" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="49">
@@ -1386,7 +2546,31 @@
         <v>3</v>
       </c>
       <c r="F49" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G49" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H49" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K49" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L49" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M49" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N49" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="50">
@@ -1406,7 +2590,31 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G50" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H50" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K50" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L50" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M50" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N50" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="51">
@@ -1426,7 +2634,31 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G51" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H51" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I51" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J51" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K51" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L51" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M51" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N51" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="52">
@@ -1446,7 +2678,31 @@
         <v>3</v>
       </c>
       <c r="F52" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G52" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H52" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K52" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L52" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M52" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N52" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="53">
@@ -1466,7 +2722,31 @@
         <v>3</v>
       </c>
       <c r="F53" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G53" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K53" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L53" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M53" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N53" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="54">
@@ -1486,7 +2766,31 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G54" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H54" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K54" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L54" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M54" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N54" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="55">
@@ -1506,7 +2810,31 @@
         <v>2</v>
       </c>
       <c r="F55" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G55" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H55" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K55" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L55" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M55" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N55" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="56">
@@ -1526,7 +2854,31 @@
         <v>3</v>
       </c>
       <c r="F56" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G56" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H56" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K56" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L56" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M56" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N56" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="57">
@@ -1546,7 +2898,31 @@
         <v>3</v>
       </c>
       <c r="F57" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G57" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H57" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K57" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L57" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M57" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N57" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="58">
@@ -1566,7 +2942,31 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G58" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H58" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I58" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J58" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K58" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L58" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M58" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N58" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="59">
@@ -1586,7 +2986,31 @@
         <v>2</v>
       </c>
       <c r="F59" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G59" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H59" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K59" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L59" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M59" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N59" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="60">
@@ -1606,7 +3030,31 @@
         <v>3</v>
       </c>
       <c r="F60" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G60" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H60" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K60" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L60" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M60" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N60" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="61">
@@ -1626,7 +3074,31 @@
         <v>3</v>
       </c>
       <c r="F61" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G61" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H61" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K61" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L61" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M61" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N61" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="62">
@@ -1646,7 +3118,31 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G62" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H62" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I62" t="str">
+        <v/>
+      </c>
+      <c r="J62" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K62" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L62" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M62" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N62" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="63">
@@ -1666,7 +3162,31 @@
         <v>2</v>
       </c>
       <c r="F63" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G63" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H63" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I63" t="str">
+        <v/>
+      </c>
+      <c r="J63" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K63" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L63" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M63" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N63" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="64">
@@ -1686,7 +3206,31 @@
         <v>3</v>
       </c>
       <c r="F64" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G64" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H64" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I64" t="str">
+        <v/>
+      </c>
+      <c r="J64" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K64" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L64" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M64" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N64" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="65">
@@ -1706,7 +3250,31 @@
         <v>3</v>
       </c>
       <c r="F65" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT CHINESE</v>
+        <v>TG2</v>
+      </c>
+      <c r="G65" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H65" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I65" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J65" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K65" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L65" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M65" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N65" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="66">
@@ -1726,7 +3294,31 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G66" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H66" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I66" t="str">
+        <v/>
+      </c>
+      <c r="J66" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K66" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L66" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M66" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N66" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="67">
@@ -1746,7 +3338,31 @@
         <v>2</v>
       </c>
       <c r="F67" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G67" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H67" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I67" t="str">
+        <v/>
+      </c>
+      <c r="J67" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K67" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L67" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M67" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N67" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="68">
@@ -1766,7 +3382,31 @@
         <v>3</v>
       </c>
       <c r="F68" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G68" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H68" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K68" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L68" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M68" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N68" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="69">
@@ -1786,7 +3426,31 @@
         <v>3</v>
       </c>
       <c r="F69" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G69" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H69" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I69" t="str">
+        <v/>
+      </c>
+      <c r="J69" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K69" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L69" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M69" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N69" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="70">
@@ -1806,7 +3470,31 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G70" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H70" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I70" t="str">
+        <v/>
+      </c>
+      <c r="J70" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K70" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L70" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M70" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N70" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="71">
@@ -1826,7 +3514,31 @@
         <v>2</v>
       </c>
       <c r="F71" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G71" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H71" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I71" t="str">
+        <v/>
+      </c>
+      <c r="J71" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K71" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L71" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M71" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N71" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="72">
@@ -1846,7 +3558,31 @@
         <v>3</v>
       </c>
       <c r="F72" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G72" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H72" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I72" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J72" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K72" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L72" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M72" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N72" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="73">
@@ -1866,7 +3602,31 @@
         <v>3</v>
       </c>
       <c r="F73" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G73" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H73" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I73" t="str">
+        <v/>
+      </c>
+      <c r="J73" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K73" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L73" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M73" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N73" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="74">
@@ -1886,7 +3646,31 @@
         <v>1</v>
       </c>
       <c r="F74" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G74" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H74" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I74" t="str">
+        <v/>
+      </c>
+      <c r="J74" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K74" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L74" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M74" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N74" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="75">
@@ -1906,7 +3690,31 @@
         <v>2</v>
       </c>
       <c r="F75" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G75" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H75" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I75" t="str">
+        <v/>
+      </c>
+      <c r="J75" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K75" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L75" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M75" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N75" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="76">
@@ -1926,7 +3734,31 @@
         <v>3</v>
       </c>
       <c r="F76" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G76" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H76" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I76" t="str">
+        <v/>
+      </c>
+      <c r="J76" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K76" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L76" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M76" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N76" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="77">
@@ -1946,7 +3778,31 @@
         <v>3</v>
       </c>
       <c r="F77" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G77" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H77" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I77" t="str">
+        <v/>
+      </c>
+      <c r="J77" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K77" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L77" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M77" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N77" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="78">
@@ -1966,7 +3822,31 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G78" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H78" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I78" t="str">
+        <v/>
+      </c>
+      <c r="J78" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K78" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L78" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M78" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N78" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="79">
@@ -1986,7 +3866,31 @@
         <v>2</v>
       </c>
       <c r="F79" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G79" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H79" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I79" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J79" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K79" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L79" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M79" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N79" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="80">
@@ -2006,7 +3910,31 @@
         <v>3</v>
       </c>
       <c r="F80" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G80" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H80" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I80" t="str">
+        <v/>
+      </c>
+      <c r="J80" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K80" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L80" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M80" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N80" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="81">
@@ -2026,7 +3954,31 @@
         <v>3</v>
       </c>
       <c r="F81" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G81" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H81" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I81" t="str">
+        <v/>
+      </c>
+      <c r="J81" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K81" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L81" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M81" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N81" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="82">
@@ -2046,7 +3998,31 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G82" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H82" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I82" t="str">
+        <v/>
+      </c>
+      <c r="J82" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K82" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L82" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M82" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N82" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="83">
@@ -2066,7 +4042,31 @@
         <v>2</v>
       </c>
       <c r="F83" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G83" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H83" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I83" t="str">
+        <v/>
+      </c>
+      <c r="J83" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K83" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L83" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M83" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N83" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="84">
@@ -2086,7 +4086,31 @@
         <v>3</v>
       </c>
       <c r="F84" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G84" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H84" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I84" t="str">
+        <v/>
+      </c>
+      <c r="J84" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K84" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L84" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M84" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N84" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="85">
@@ -2106,7 +4130,31 @@
         <v>3</v>
       </c>
       <c r="F85" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G85" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H85" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I85" t="str">
+        <v/>
+      </c>
+      <c r="J85" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K85" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L85" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M85" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N85" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="86">
@@ -2126,7 +4174,31 @@
         <v>1</v>
       </c>
       <c r="F86" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT CHINESE</v>
+        <v>TG1</v>
+      </c>
+      <c r="G86" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H86" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I86" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J86" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K86" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L86" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M86" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N86" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="87">
@@ -2146,7 +4218,31 @@
         <v>2</v>
       </c>
       <c r="F87" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G87" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H87" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I87" t="str">
+        <v/>
+      </c>
+      <c r="J87" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K87" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L87" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M87" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N87" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="88">
@@ -2166,7 +4262,31 @@
         <v>3</v>
       </c>
       <c r="F88" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G88" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H88" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I88" t="str">
+        <v/>
+      </c>
+      <c r="J88" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K88" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L88" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M88" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N88" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="89">
@@ -2186,7 +4306,31 @@
         <v>3</v>
       </c>
       <c r="F89" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G89" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H89" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I89" t="str">
+        <v/>
+      </c>
+      <c r="J89" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K89" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L89" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M89" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N89" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="90">
@@ -2206,7 +4350,31 @@
         <v>1</v>
       </c>
       <c r="F90" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G90" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H90" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I90" t="str">
+        <v/>
+      </c>
+      <c r="J90" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K90" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L90" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M90" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N90" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="91">
@@ -2226,7 +4394,31 @@
         <v>2</v>
       </c>
       <c r="F91" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G91" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H91" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I91" t="str">
+        <v/>
+      </c>
+      <c r="J91" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K91" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L91" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M91" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N91" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="92">
@@ -2246,7 +4438,31 @@
         <v>3</v>
       </c>
       <c r="F92" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G92" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H92" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I92" t="str">
+        <v/>
+      </c>
+      <c r="J92" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K92" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L92" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M92" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N92" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="93">
@@ -2266,7 +4482,31 @@
         <v>3</v>
       </c>
       <c r="F93" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G93" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H93" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I93" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J93" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K93" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L93" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M93" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N93" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="94">
@@ -2286,7 +4526,31 @@
         <v>1</v>
       </c>
       <c r="F94" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G94" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H94" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I94" t="str">
+        <v/>
+      </c>
+      <c r="J94" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K94" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L94" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M94" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N94" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="95">
@@ -2306,7 +4570,31 @@
         <v>2</v>
       </c>
       <c r="F95" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G95" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H95" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I95" t="str">
+        <v/>
+      </c>
+      <c r="J95" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K95" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L95" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M95" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N95" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="96">
@@ -2326,7 +4614,31 @@
         <v>3</v>
       </c>
       <c r="F96" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G96" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H96" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I96" t="str">
+        <v/>
+      </c>
+      <c r="J96" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K96" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L96" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M96" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N96" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="97">
@@ -2346,7 +4658,31 @@
         <v>3</v>
       </c>
       <c r="F97" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G97" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H97" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I97" t="str">
+        <v/>
+      </c>
+      <c r="J97" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K97" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L97" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M97" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N97" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="98">
@@ -2366,7 +4702,31 @@
         <v>1</v>
       </c>
       <c r="F98" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G98" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H98" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K98" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L98" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M98" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N98" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="99">
@@ -2386,7 +4746,31 @@
         <v>2</v>
       </c>
       <c r="F99" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G99" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H99" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K99" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L99" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M99" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N99" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="100">
@@ -2406,7 +4790,31 @@
         <v>3</v>
       </c>
       <c r="F100" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G100" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H100" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I100" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J100" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K100" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L100" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M100" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N100" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="101">
@@ -2426,7 +4834,31 @@
         <v>3</v>
       </c>
       <c r="F101" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G101" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H101" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K101" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L101" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M101" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N101" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="102">
@@ -2446,7 +4878,31 @@
         <v>1</v>
       </c>
       <c r="F102" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G102" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H102" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K102" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L102" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M102" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N102" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="103">
@@ -2466,7 +4922,31 @@
         <v>2</v>
       </c>
       <c r="F103" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G103" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H103" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K103" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L103" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M103" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N103" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="104">
@@ -2486,7 +4966,31 @@
         <v>3</v>
       </c>
       <c r="F104" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G104" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H104" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K104" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L104" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M104" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N104" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="105">
@@ -2506,7 +5010,31 @@
         <v>3</v>
       </c>
       <c r="F105" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G105" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H105" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K105" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L105" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M105" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N105" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="106">
@@ -2526,7 +5054,31 @@
         <v>1</v>
       </c>
       <c r="F106" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G106" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H106" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K106" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L106" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M106" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N106" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="107">
@@ -2546,7 +5098,31 @@
         <v>2</v>
       </c>
       <c r="F107" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2 · HMT CHINESE</v>
+        <v>TG2</v>
+      </c>
+      <c r="G107" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H107" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I107" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J107" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K107" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L107" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M107" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N107" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="108">
@@ -2566,7 +5142,31 @@
         <v>3</v>
       </c>
       <c r="F108" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G108" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H108" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K108" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L108" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M108" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N108" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="109">
@@ -2586,7 +5186,31 @@
         <v>3</v>
       </c>
       <c r="F109" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G109" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H109" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K109" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L109" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M109" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N109" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="110">
@@ -2606,7 +5230,31 @@
         <v>1</v>
       </c>
       <c r="F110" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G110" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H110" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K110" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L110" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M110" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N110" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="111">
@@ -2626,7 +5274,31 @@
         <v>2</v>
       </c>
       <c r="F111" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G111" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H111" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K111" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L111" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M111" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N111" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="112">
@@ -2646,7 +5318,31 @@
         <v>3</v>
       </c>
       <c r="F112" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G112" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H112" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K112" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L112" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M112" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N112" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="113">
@@ -2666,7 +5362,31 @@
         <v>3</v>
       </c>
       <c r="F113" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G113" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H113" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K113" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L113" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M113" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N113" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="114">
@@ -2686,7 +5406,31 @@
         <v>1</v>
       </c>
       <c r="F114" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G114" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H114" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I114" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J114" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K114" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L114" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M114" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N114" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="115">
@@ -2706,7 +5450,31 @@
         <v>2</v>
       </c>
       <c r="F115" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G115" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H115" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K115" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L115" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M115" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N115" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="116">
@@ -2726,7 +5494,31 @@
         <v>3</v>
       </c>
       <c r="F116" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G116" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H116" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K116" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L116" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M116" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N116" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="117">
@@ -2746,7 +5538,31 @@
         <v>3</v>
       </c>
       <c r="F117" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G117" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H117" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K117" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L117" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M117" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N117" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="118">
@@ -2766,7 +5582,31 @@
         <v>1</v>
       </c>
       <c r="F118" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G118" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H118" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K118" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L118" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M118" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N118" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="119">
@@ -2786,7 +5626,31 @@
         <v>2</v>
       </c>
       <c r="F119" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G119" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H119" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K119" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L119" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M119" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N119" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="120">
@@ -2806,7 +5670,31 @@
         <v>3</v>
       </c>
       <c r="F120" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G120" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H120" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K120" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L120" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M120" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N120" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="121">
@@ -2826,7 +5714,31 @@
         <v>3</v>
       </c>
       <c r="F121" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G121" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H121" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I121" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J121" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K121" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L121" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M121" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N121" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="122">
@@ -2846,7 +5758,31 @@
         <v>1</v>
       </c>
       <c r="F122" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G122" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H122" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K122" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L122" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M122" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N122" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="123">
@@ -2866,7 +5802,31 @@
         <v>2</v>
       </c>
       <c r="F123" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G123" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H123" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K123" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L123" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M123" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N123" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="124">
@@ -2886,7 +5846,31 @@
         <v>3</v>
       </c>
       <c r="F124" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G124" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H124" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K124" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L124" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M124" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N124" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="125">
@@ -2906,7 +5890,31 @@
         <v>3</v>
       </c>
       <c r="F125" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G125" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H125" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K125" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L125" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M125" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N125" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="126">
@@ -2926,7 +5934,31 @@
         <v>1</v>
       </c>
       <c r="F126" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G126" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H126" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K126" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L126" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M126" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N126" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="127">
@@ -2946,7 +5978,31 @@
         <v>2</v>
       </c>
       <c r="F127" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G127" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H127" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K127" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L127" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M127" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N127" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="128">
@@ -2966,7 +6022,31 @@
         <v>3</v>
       </c>
       <c r="F128" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT CHINESE</v>
+        <v>TG1</v>
+      </c>
+      <c r="G128" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H128" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I128" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J128" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K128" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L128" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M128" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N128" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="129">
@@ -2986,7 +6066,31 @@
         <v>3</v>
       </c>
       <c r="F129" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G129" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H129" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K129" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L129" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M129" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N129" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="130">
@@ -3006,7 +6110,31 @@
         <v>1</v>
       </c>
       <c r="F130" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G130" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H130" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K130" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L130" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M130" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N130" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="131">
@@ -3026,7 +6154,31 @@
         <v>2</v>
       </c>
       <c r="F131" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G131" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H131" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K131" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L131" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M131" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N131" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="132">
@@ -3046,7 +6198,31 @@
         <v>3</v>
       </c>
       <c r="F132" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G132" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H132" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K132" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L132" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M132" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N132" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="133">
@@ -3066,7 +6242,31 @@
         <v>3</v>
       </c>
       <c r="F133" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G133" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H133" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K133" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L133" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M133" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N133" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="134">
@@ -3086,7 +6286,31 @@
         <v>1</v>
       </c>
       <c r="F134" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G134" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H134" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K134" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L134" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M134" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N134" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="135">
@@ -3106,7 +6330,31 @@
         <v>2</v>
       </c>
       <c r="F135" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2 · HMT MALAY</v>
+        <v>TG2</v>
+      </c>
+      <c r="G135" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H135" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I135" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J135" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K135" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L135" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M135" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N135" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="136">
@@ -3126,7 +6374,31 @@
         <v>3</v>
       </c>
       <c r="F136" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G136" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H136" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K136" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L136" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M136" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N136" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="137">
@@ -3146,7 +6418,31 @@
         <v>3</v>
       </c>
       <c r="F137" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G137" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H137" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K137" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L137" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M137" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N137" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="138">
@@ -3166,7 +6462,31 @@
         <v>1</v>
       </c>
       <c r="F138" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G138" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H138" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K138" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L138" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M138" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N138" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="139">
@@ -3186,7 +6506,31 @@
         <v>2</v>
       </c>
       <c r="F139" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G139" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H139" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I139" t="str">
+        <v/>
+      </c>
+      <c r="J139" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K139" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L139" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M139" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N139" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="140">
@@ -3206,7 +6550,31 @@
         <v>3</v>
       </c>
       <c r="F140" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G140" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H140" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I140" t="str">
+        <v/>
+      </c>
+      <c r="J140" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K140" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L140" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M140" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N140" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="141">
@@ -3226,7 +6594,31 @@
         <v>3</v>
       </c>
       <c r="F141" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G141" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H141" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I141" t="str">
+        <v/>
+      </c>
+      <c r="J141" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K141" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L141" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M141" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N141" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="142">
@@ -3246,7 +6638,31 @@
         <v>1</v>
       </c>
       <c r="F142" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G142" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H142" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I142" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J142" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K142" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L142" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M142" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N142" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="143">
@@ -3266,7 +6682,31 @@
         <v>2</v>
       </c>
       <c r="F143" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G143" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H143" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I143" t="str">
+        <v/>
+      </c>
+      <c r="J143" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K143" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L143" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M143" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N143" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="144">
@@ -3286,7 +6726,31 @@
         <v>3</v>
       </c>
       <c r="F144" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G144" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H144" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I144" t="str">
+        <v/>
+      </c>
+      <c r="J144" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K144" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L144" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M144" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N144" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="145">
@@ -3306,7 +6770,31 @@
         <v>3</v>
       </c>
       <c r="F145" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G145" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H145" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I145" t="str">
+        <v/>
+      </c>
+      <c r="J145" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K145" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L145" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M145" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N145" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="146">
@@ -3326,7 +6814,31 @@
         <v>1</v>
       </c>
       <c r="F146" t="str">
-        <v>TG1 · EL G1 · MT CL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G146" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H146" t="str">
+        <v>CL G1</v>
+      </c>
+      <c r="I146" t="str">
+        <v/>
+      </c>
+      <c r="J146" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K146" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L146" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M146" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N146" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="147">
@@ -3346,7 +6858,31 @@
         <v>2</v>
       </c>
       <c r="F147" t="str">
-        <v>TG2 · EL G2 · MT ML G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G147" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H147" t="str">
+        <v>ML G2</v>
+      </c>
+      <c r="I147" t="str">
+        <v/>
+      </c>
+      <c r="J147" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K147" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L147" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M147" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N147" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="148">
@@ -3366,7 +6902,31 @@
         <v>3</v>
       </c>
       <c r="F148" t="str">
-        <v>TG1 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G148" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H148" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I148" t="str">
+        <v/>
+      </c>
+      <c r="J148" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K148" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L148" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M148" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N148" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="149">
@@ -3386,7 +6946,31 @@
         <v>3</v>
       </c>
       <c r="F149" t="str">
-        <v>TG2 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT CHINESE</v>
+        <v>TG2</v>
+      </c>
+      <c r="G149" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H149" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I149" t="str">
+        <v>CHINESE</v>
+      </c>
+      <c r="J149" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K149" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L149" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M149" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N149" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="150">
@@ -3406,7 +6990,31 @@
         <v>1</v>
       </c>
       <c r="F150" t="str">
-        <v>TG1 · EL G1 · MT ML G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G150" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H150" t="str">
+        <v>ML G1</v>
+      </c>
+      <c r="I150" t="str">
+        <v/>
+      </c>
+      <c r="J150" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K150" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L150" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M150" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N150" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="151">
@@ -3426,7 +7034,31 @@
         <v>2</v>
       </c>
       <c r="F151" t="str">
-        <v>TG2 · EL G2 · MT TL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G151" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H151" t="str">
+        <v>TL G2</v>
+      </c>
+      <c r="I151" t="str">
+        <v/>
+      </c>
+      <c r="J151" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K151" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L151" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M151" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N151" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="152">
@@ -3446,7 +7078,31 @@
         <v>3</v>
       </c>
       <c r="F152" t="str">
-        <v>TG1 · EL G3 · MT CL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG1</v>
+      </c>
+      <c r="G152" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H152" t="str">
+        <v>CL G3</v>
+      </c>
+      <c r="I152" t="str">
+        <v/>
+      </c>
+      <c r="J152" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K152" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L152" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M152" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N152" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="153">
@@ -3466,7 +7122,31 @@
         <v>3</v>
       </c>
       <c r="F153" t="str">
-        <v>TG2 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G153" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H153" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I153" t="str">
+        <v/>
+      </c>
+      <c r="J153" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K153" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L153" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M153" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N153" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="154">
@@ -3486,7 +7166,31 @@
         <v>1</v>
       </c>
       <c r="F154" t="str">
-        <v>TG1 · EL G1 · MT TL G1 · MA G1 · SCI G1 · HIST G1 · GEOG G1 · LIT G1</v>
+        <v>TG1</v>
+      </c>
+      <c r="G154" t="str">
+        <v>EL G1</v>
+      </c>
+      <c r="H154" t="str">
+        <v>TL G1</v>
+      </c>
+      <c r="I154" t="str">
+        <v/>
+      </c>
+      <c r="J154" t="str">
+        <v>MA G1</v>
+      </c>
+      <c r="K154" t="str">
+        <v>SCI G1</v>
+      </c>
+      <c r="L154" t="str">
+        <v>HIST G1</v>
+      </c>
+      <c r="M154" t="str">
+        <v>GEOG G1</v>
+      </c>
+      <c r="N154" t="str">
+        <v>LIT G1</v>
       </c>
     </row>
     <row r="155">
@@ -3506,7 +7210,31 @@
         <v>2</v>
       </c>
       <c r="F155" t="str">
-        <v>TG2 · EL G2 · MT CL G2 · MA G2 · SCI G2 · HIST G2 · GEOG G2 · LIT G2</v>
+        <v>TG2</v>
+      </c>
+      <c r="G155" t="str">
+        <v>EL G2</v>
+      </c>
+      <c r="H155" t="str">
+        <v>CL G2</v>
+      </c>
+      <c r="I155" t="str">
+        <v/>
+      </c>
+      <c r="J155" t="str">
+        <v>MA G2</v>
+      </c>
+      <c r="K155" t="str">
+        <v>SCI G2</v>
+      </c>
+      <c r="L155" t="str">
+        <v>HIST G2</v>
+      </c>
+      <c r="M155" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="N155" t="str">
+        <v>LIT G2</v>
       </c>
     </row>
     <row r="156">
@@ -3526,7 +7254,31 @@
         <v>3</v>
       </c>
       <c r="F156" t="str">
-        <v>TG1 · EL G3 · MT ML G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3 · HMT MALAY</v>
+        <v>TG1</v>
+      </c>
+      <c r="G156" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H156" t="str">
+        <v>ML G3</v>
+      </c>
+      <c r="I156" t="str">
+        <v>MALAY</v>
+      </c>
+      <c r="J156" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K156" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L156" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M156" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N156" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
     <row r="157">
@@ -3546,12 +7298,36 @@
         <v>3</v>
       </c>
       <c r="F157" t="str">
-        <v>TG2 · EL G3 · MT TL G3 · MA G3 · SCI G3 · HIST G3 · GEOG G3 · LIT G3</v>
+        <v>TG2</v>
+      </c>
+      <c r="G157" t="str">
+        <v>EL G3</v>
+      </c>
+      <c r="H157" t="str">
+        <v>TL G3</v>
+      </c>
+      <c r="I157" t="str">
+        <v/>
+      </c>
+      <c r="J157" t="str">
+        <v>MA G3</v>
+      </c>
+      <c r="K157" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="L157" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="M157" t="str">
+        <v>GEOG G3</v>
+      </c>
+      <c r="N157" t="str">
+        <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N157"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Students" sheetId="1" r:id="rId1"/>
     <sheet name="Groups" sheetId="2" r:id="rId2"/>
     <sheet name="Memberships" sheetId="3" r:id="rId3"/>
+    <sheet name="Sources" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -12288,4 +12289,49 @@
     <ignoredError numberStoredAsText="1" sqref="A1:B586"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="40.83203125" customWidth="1"/>
+    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="B1" t="str">
+        <v>FilePattern</v>
+      </c>
+      <c r="C1" t="str">
+        <v>LastFile</v>
+      </c>
+      <c r="D1" t="str">
+        <v>LastImported</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Sec 1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Sec 1 Subject Allocation</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -7335,12 +7335,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:G17"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="24.83203125" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7356,6 +7359,15 @@
       <c r="D1" t="str">
         <v>Teacher</v>
       </c>
+      <c r="E1" t="str">
+        <v>AutoSubject</v>
+      </c>
+      <c r="F1" t="str">
+        <v>AutoValue</v>
+      </c>
+      <c r="G1" t="str">
+        <v>AutoClasses</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -7370,6 +7382,15 @@
       <c r="D2" t="str">
         <v>Mrs Lim Bee Leng</v>
       </c>
+      <c r="E2" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>1R1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -7384,6 +7405,15 @@
       <c r="D3" t="str">
         <v>Mr Rajesh Kumar</v>
       </c>
+      <c r="E3" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>1R1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -7398,6 +7428,15 @@
       <c r="D4" t="str">
         <v>Mr Daniel Tan</v>
       </c>
+      <c r="E4" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>1R2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -7412,6 +7451,15 @@
       <c r="D5" t="str">
         <v>Mdm Halimah Yusof</v>
       </c>
+      <c r="E5" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>1R2</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -7426,6 +7474,15 @@
       <c r="D6" t="str">
         <v>Ms Nur Aisyah</v>
       </c>
+      <c r="E6" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>1R3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -7440,6 +7497,15 @@
       <c r="D7" t="str">
         <v>Ms Serene Goh</v>
       </c>
+      <c r="E7" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>1R3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -7454,6 +7520,15 @@
       <c r="D8" t="str">
         <v>Mrs Grace Chua</v>
       </c>
+      <c r="E8" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>1R4</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -7468,6 +7543,15 @@
       <c r="D9" t="str">
         <v>Mr Alvin Ong</v>
       </c>
+      <c r="E9" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>1R4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -7482,6 +7566,15 @@
       <c r="D10" t="str">
         <v>Mr Marcus Lee</v>
       </c>
+      <c r="E10" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>1R5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -7496,6 +7589,15 @@
       <c r="D11" t="str">
         <v>Mrs Doris Koh</v>
       </c>
+      <c r="E11" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>1R5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -7510,6 +7612,15 @@
       <c r="D12" t="str">
         <v>Mdm Sarimah Bakar</v>
       </c>
+      <c r="E12" t="str">
+        <v>EL</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>1R6</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -7524,6 +7635,15 @@
       <c r="D13" t="str">
         <v>Mr Wei Jie Chan</v>
       </c>
+      <c r="E13" t="str">
+        <v>MA</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>1R6</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -7538,6 +7658,15 @@
       <c r="D14" t="str">
         <v>Dr Sarah Loh</v>
       </c>
+      <c r="E14" t="str">
+        <v>SCI</v>
+      </c>
+      <c r="F14" t="str">
+        <v>SCI G3</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -7552,6 +7681,15 @@
       <c r="D15" t="str">
         <v>Ms Priyanka Nair</v>
       </c>
+      <c r="E15" t="str">
+        <v>HIST</v>
+      </c>
+      <c r="F15" t="str">
+        <v>HIST G3</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -7566,6 +7704,15 @@
       <c r="D16" t="str">
         <v>Mr Kenneth Sim</v>
       </c>
+      <c r="E16" t="str">
+        <v>GEOG</v>
+      </c>
+      <c r="F16" t="str">
+        <v>GEOG G2</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -7580,10 +7727,19 @@
       <c r="D17" t="str">
         <v>Mrs Evelyn Phua</v>
       </c>
+      <c r="E17" t="str">
+        <v>LIT</v>
+      </c>
+      <c r="F17" t="str">
+        <v>LIT G3</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -400,14 +400,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N157"/>
+  <dimension ref="A1:O157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="5.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
@@ -416,6 +416,7 @@
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -435,30 +436,33 @@
         <v>PG</v>
       </c>
       <c r="F1" t="str">
+        <v>Origin</v>
+      </c>
+      <c r="G1" t="str">
         <v>TG</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>EL</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>MT</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>HMT</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>MA</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>SCI</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>HIST</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>GEOG</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>LIT</v>
       </c>
     </row>
@@ -479,30 +483,33 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
+        <v>file</v>
+      </c>
+      <c r="G2" t="str">
         <v>TG1</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -523,30 +530,33 @@
         <v>2</v>
       </c>
       <c r="F3" t="str">
+        <v>file</v>
+      </c>
+      <c r="G3" t="str">
         <v>TG2</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
       <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -567,30 +577,33 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
+        <v>file</v>
+      </c>
+      <c r="G4" t="str">
         <v>TG1</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -611,30 +624,33 @@
         <v>3</v>
       </c>
       <c r="F5" t="str">
+        <v>file</v>
+      </c>
+      <c r="G5" t="str">
         <v>TG2</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
       <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -655,30 +671,33 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
+        <v>file</v>
+      </c>
+      <c r="G6" t="str">
         <v>TG1</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
       <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -699,30 +718,33 @@
         <v>2</v>
       </c>
       <c r="F7" t="str">
+        <v>file</v>
+      </c>
+      <c r="G7" t="str">
         <v>TG2</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -743,30 +765,33 @@
         <v>3</v>
       </c>
       <c r="F8" t="str">
+        <v>file</v>
+      </c>
+      <c r="G8" t="str">
         <v>TG1</v>
       </c>
-      <c r="G8" t="str">
+      <c r="H8" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
       <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -787,30 +812,33 @@
         <v>3</v>
       </c>
       <c r="F9" t="str">
+        <v>file</v>
+      </c>
+      <c r="G9" t="str">
         <v>TG2</v>
       </c>
-      <c r="G9" t="str">
+      <c r="H9" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -831,30 +859,33 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
+        <v>file</v>
+      </c>
+      <c r="G10" t="str">
         <v>TG1</v>
       </c>
-      <c r="G10" t="str">
+      <c r="H10" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
       <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -875,30 +906,33 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
+        <v>file</v>
+      </c>
+      <c r="G11" t="str">
         <v>TG2</v>
       </c>
-      <c r="G11" t="str">
+      <c r="H11" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
       <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -919,30 +953,33 @@
         <v>3</v>
       </c>
       <c r="F12" t="str">
+        <v>file</v>
+      </c>
+      <c r="G12" t="str">
         <v>TG1</v>
       </c>
-      <c r="G12" t="str">
+      <c r="H12" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
       <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -963,30 +1000,33 @@
         <v>3</v>
       </c>
       <c r="F13" t="str">
+        <v>file</v>
+      </c>
+      <c r="G13" t="str">
         <v>TG2</v>
       </c>
-      <c r="G13" t="str">
+      <c r="H13" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
       <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1007,30 +1047,33 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
+        <v>file</v>
+      </c>
+      <c r="G14" t="str">
         <v>TG1</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
       <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1051,30 +1094,33 @@
         <v>2</v>
       </c>
       <c r="F15" t="str">
+        <v>file</v>
+      </c>
+      <c r="G15" t="str">
         <v>TG2</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
       <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1095,30 +1141,33 @@
         <v>3</v>
       </c>
       <c r="F16" t="str">
+        <v>file</v>
+      </c>
+      <c r="G16" t="str">
         <v>TG1</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1139,30 +1188,33 @@
         <v>3</v>
       </c>
       <c r="F17" t="str">
+        <v>file</v>
+      </c>
+      <c r="G17" t="str">
         <v>TG2</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1183,30 +1235,33 @@
         <v>1</v>
       </c>
       <c r="F18" t="str">
+        <v>file</v>
+      </c>
+      <c r="G18" t="str">
         <v>TG1</v>
       </c>
-      <c r="G18" t="str">
+      <c r="H18" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
       <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1227,30 +1282,33 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
+        <v>file</v>
+      </c>
+      <c r="G19" t="str">
         <v>TG2</v>
       </c>
-      <c r="G19" t="str">
+      <c r="H19" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
       <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1271,30 +1329,33 @@
         <v>3</v>
       </c>
       <c r="F20" t="str">
+        <v>file</v>
+      </c>
+      <c r="G20" t="str">
         <v>TG1</v>
       </c>
-      <c r="G20" t="str">
+      <c r="H20" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
       <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1315,30 +1376,33 @@
         <v>3</v>
       </c>
       <c r="F21" t="str">
+        <v>file</v>
+      </c>
+      <c r="G21" t="str">
         <v>TG2</v>
       </c>
-      <c r="G21" t="str">
+      <c r="H21" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
       <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1359,30 +1423,33 @@
         <v>1</v>
       </c>
       <c r="F22" t="str">
+        <v>file</v>
+      </c>
+      <c r="G22" t="str">
         <v>TG1</v>
       </c>
-      <c r="G22" t="str">
+      <c r="H22" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
       <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1403,30 +1470,33 @@
         <v>2</v>
       </c>
       <c r="F23" t="str">
+        <v>file</v>
+      </c>
+      <c r="G23" t="str">
         <v>TG2</v>
       </c>
-      <c r="G23" t="str">
+      <c r="H23" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1447,30 +1517,33 @@
         <v>3</v>
       </c>
       <c r="F24" t="str">
+        <v>file</v>
+      </c>
+      <c r="G24" t="str">
         <v>TG1</v>
       </c>
-      <c r="G24" t="str">
+      <c r="H24" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1491,30 +1564,33 @@
         <v>3</v>
       </c>
       <c r="F25" t="str">
+        <v>file</v>
+      </c>
+      <c r="G25" t="str">
         <v>TG2</v>
       </c>
-      <c r="G25" t="str">
+      <c r="H25" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1535,30 +1611,33 @@
         <v>1</v>
       </c>
       <c r="F26" t="str">
+        <v>file</v>
+      </c>
+      <c r="G26" t="str">
         <v>TG1</v>
       </c>
-      <c r="G26" t="str">
+      <c r="H26" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
       <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1579,30 +1658,33 @@
         <v>2</v>
       </c>
       <c r="F27" t="str">
+        <v>file</v>
+      </c>
+      <c r="G27" t="str">
         <v>TG2</v>
       </c>
-      <c r="G27" t="str">
+      <c r="H27" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
       <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1623,30 +1705,33 @@
         <v>3</v>
       </c>
       <c r="F28" t="str">
+        <v>file</v>
+      </c>
+      <c r="G28" t="str">
         <v>TG1</v>
       </c>
-      <c r="G28" t="str">
+      <c r="H28" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1667,30 +1752,33 @@
         <v>3</v>
       </c>
       <c r="F29" t="str">
+        <v>file</v>
+      </c>
+      <c r="G29" t="str">
         <v>TG2</v>
       </c>
-      <c r="G29" t="str">
+      <c r="H29" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K29" t="str">
+      <c r="L29" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1711,30 +1799,33 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
+        <v>file</v>
+      </c>
+      <c r="G30" t="str">
         <v>TG1</v>
       </c>
-      <c r="G30" t="str">
+      <c r="H30" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1755,30 +1846,33 @@
         <v>2</v>
       </c>
       <c r="F31" t="str">
+        <v>file</v>
+      </c>
+      <c r="G31" t="str">
         <v>TG2</v>
       </c>
-      <c r="G31" t="str">
+      <c r="H31" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I31" t="str">
-        <v/>
-      </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K31" t="str">
+      <c r="L31" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1799,30 +1893,33 @@
         <v>3</v>
       </c>
       <c r="F32" t="str">
+        <v>file</v>
+      </c>
+      <c r="G32" t="str">
         <v>TG1</v>
       </c>
-      <c r="G32" t="str">
+      <c r="H32" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K32" t="str">
+      <c r="L32" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L32" t="str">
+      <c r="M32" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1843,30 +1940,33 @@
         <v>3</v>
       </c>
       <c r="F33" t="str">
+        <v>file</v>
+      </c>
+      <c r="G33" t="str">
         <v>TG2</v>
       </c>
-      <c r="G33" t="str">
+      <c r="H33" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I33" t="str">
-        <v/>
-      </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1887,30 +1987,33 @@
         <v>1</v>
       </c>
       <c r="F34" t="str">
+        <v>file</v>
+      </c>
+      <c r="G34" t="str">
         <v>TG1</v>
       </c>
-      <c r="G34" t="str">
+      <c r="H34" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I34" t="str">
-        <v/>
-      </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1931,30 +2034,33 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
+        <v>file</v>
+      </c>
+      <c r="G35" t="str">
         <v>TG2</v>
       </c>
-      <c r="G35" t="str">
+      <c r="H35" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L35" t="str">
+      <c r="M35" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1975,30 +2081,33 @@
         <v>3</v>
       </c>
       <c r="F36" t="str">
+        <v>file</v>
+      </c>
+      <c r="G36" t="str">
         <v>TG1</v>
       </c>
-      <c r="G36" t="str">
+      <c r="H36" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I36" t="str">
-        <v/>
-      </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K36" t="str">
+      <c r="L36" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L36" t="str">
+      <c r="M36" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2019,30 +2128,33 @@
         <v>3</v>
       </c>
       <c r="F37" t="str">
+        <v>file</v>
+      </c>
+      <c r="G37" t="str">
         <v>TG2</v>
       </c>
-      <c r="G37" t="str">
+      <c r="H37" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H37" t="str">
+      <c r="I37" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J37" t="str">
+      <c r="K37" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2063,30 +2175,33 @@
         <v>1</v>
       </c>
       <c r="F38" t="str">
+        <v>file</v>
+      </c>
+      <c r="G38" t="str">
         <v>TG1</v>
       </c>
-      <c r="G38" t="str">
+      <c r="H38" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I38" t="str">
-        <v/>
-      </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2107,30 +2222,33 @@
         <v>2</v>
       </c>
       <c r="F39" t="str">
+        <v>file</v>
+      </c>
+      <c r="G39" t="str">
         <v>TG2</v>
       </c>
-      <c r="G39" t="str">
+      <c r="H39" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I39" t="str">
-        <v/>
-      </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2151,30 +2269,33 @@
         <v>3</v>
       </c>
       <c r="F40" t="str">
+        <v>file</v>
+      </c>
+      <c r="G40" t="str">
         <v>TG1</v>
       </c>
-      <c r="G40" t="str">
+      <c r="H40" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I40" t="str">
-        <v/>
-      </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2195,30 +2316,33 @@
         <v>3</v>
       </c>
       <c r="F41" t="str">
+        <v>file</v>
+      </c>
+      <c r="G41" t="str">
         <v>TG2</v>
       </c>
-      <c r="G41" t="str">
+      <c r="H41" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H41" t="str">
+      <c r="I41" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
       <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2239,30 +2363,33 @@
         <v>1</v>
       </c>
       <c r="F42" t="str">
+        <v>file</v>
+      </c>
+      <c r="G42" t="str">
         <v>TG1</v>
       </c>
-      <c r="G42" t="str">
+      <c r="H42" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I42" t="str">
-        <v/>
-      </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2283,30 +2410,33 @@
         <v>2</v>
       </c>
       <c r="F43" t="str">
+        <v>file</v>
+      </c>
+      <c r="G43" t="str">
         <v>TG2</v>
       </c>
-      <c r="G43" t="str">
+      <c r="H43" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H43" t="str">
+      <c r="I43" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I43" t="str">
-        <v/>
-      </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2327,30 +2457,33 @@
         <v>3</v>
       </c>
       <c r="F44" t="str">
+        <v>file</v>
+      </c>
+      <c r="G44" t="str">
         <v>TG1</v>
       </c>
-      <c r="G44" t="str">
+      <c r="H44" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2371,30 +2504,33 @@
         <v>3</v>
       </c>
       <c r="F45" t="str">
+        <v>file</v>
+      </c>
+      <c r="G45" t="str">
         <v>TG2</v>
       </c>
-      <c r="G45" t="str">
+      <c r="H45" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H45" t="str">
+      <c r="I45" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L45" t="str">
+      <c r="M45" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2415,30 +2551,33 @@
         <v>1</v>
       </c>
       <c r="F46" t="str">
+        <v>file</v>
+      </c>
+      <c r="G46" t="str">
         <v>TG1</v>
       </c>
-      <c r="G46" t="str">
+      <c r="H46" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H46" t="str">
+      <c r="I46" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2459,30 +2598,33 @@
         <v>2</v>
       </c>
       <c r="F47" t="str">
+        <v>file</v>
+      </c>
+      <c r="G47" t="str">
         <v>TG2</v>
       </c>
-      <c r="G47" t="str">
+      <c r="H47" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H47" t="str">
+      <c r="I47" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I47" t="str">
-        <v/>
-      </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K47" t="str">
+      <c r="L47" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2503,30 +2645,33 @@
         <v>3</v>
       </c>
       <c r="F48" t="str">
+        <v>file</v>
+      </c>
+      <c r="G48" t="str">
         <v>TG1</v>
       </c>
-      <c r="G48" t="str">
+      <c r="H48" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H48" t="str">
+      <c r="I48" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
       <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K48" t="str">
+      <c r="L48" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2547,30 +2692,33 @@
         <v>3</v>
       </c>
       <c r="F49" t="str">
+        <v>file</v>
+      </c>
+      <c r="G49" t="str">
         <v>TG2</v>
       </c>
-      <c r="G49" t="str">
+      <c r="H49" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H49" t="str">
+      <c r="I49" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
-      </c>
       <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K49" t="str">
+      <c r="L49" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2591,30 +2739,33 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
+        <v>file</v>
+      </c>
+      <c r="G50" t="str">
         <v>TG1</v>
       </c>
-      <c r="G50" t="str">
+      <c r="H50" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H50" t="str">
+      <c r="I50" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
       <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K50" t="str">
+      <c r="L50" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2635,30 +2786,33 @@
         <v>2</v>
       </c>
       <c r="F51" t="str">
+        <v>file</v>
+      </c>
+      <c r="G51" t="str">
         <v>TG2</v>
       </c>
-      <c r="G51" t="str">
+      <c r="H51" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H51" t="str">
+      <c r="I51" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2679,30 +2833,33 @@
         <v>3</v>
       </c>
       <c r="F52" t="str">
+        <v>file</v>
+      </c>
+      <c r="G52" t="str">
         <v>TG1</v>
       </c>
-      <c r="G52" t="str">
+      <c r="H52" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H52" t="str">
+      <c r="I52" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I52" t="str">
-        <v/>
-      </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L52" t="str">
+      <c r="M52" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2723,30 +2880,33 @@
         <v>3</v>
       </c>
       <c r="F53" t="str">
+        <v>file</v>
+      </c>
+      <c r="G53" t="str">
         <v>TG2</v>
       </c>
-      <c r="G53" t="str">
+      <c r="H53" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H53" t="str">
+      <c r="I53" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I53" t="str">
-        <v/>
-      </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L53" t="str">
+      <c r="M53" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2767,30 +2927,33 @@
         <v>1</v>
       </c>
       <c r="F54" t="str">
+        <v>file</v>
+      </c>
+      <c r="G54" t="str">
         <v>TG1</v>
       </c>
-      <c r="G54" t="str">
+      <c r="H54" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H54" t="str">
+      <c r="I54" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I54" t="str">
-        <v/>
-      </c>
       <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L54" t="str">
+      <c r="M54" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2811,30 +2974,33 @@
         <v>2</v>
       </c>
       <c r="F55" t="str">
+        <v>file</v>
+      </c>
+      <c r="G55" t="str">
         <v>TG2</v>
       </c>
-      <c r="G55" t="str">
+      <c r="H55" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H55" t="str">
+      <c r="I55" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I55" t="str">
-        <v/>
-      </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2855,30 +3021,33 @@
         <v>3</v>
       </c>
       <c r="F56" t="str">
+        <v>file</v>
+      </c>
+      <c r="G56" t="str">
         <v>TG1</v>
       </c>
-      <c r="G56" t="str">
+      <c r="H56" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H56" t="str">
+      <c r="I56" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I56" t="str">
-        <v/>
-      </c>
       <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2899,30 +3068,33 @@
         <v>3</v>
       </c>
       <c r="F57" t="str">
+        <v>file</v>
+      </c>
+      <c r="G57" t="str">
         <v>TG2</v>
       </c>
-      <c r="G57" t="str">
+      <c r="H57" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H57" t="str">
+      <c r="I57" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I57" t="str">
-        <v/>
-      </c>
       <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2943,30 +3115,33 @@
         <v>1</v>
       </c>
       <c r="F58" t="str">
+        <v>file</v>
+      </c>
+      <c r="G58" t="str">
         <v>TG1</v>
       </c>
-      <c r="G58" t="str">
+      <c r="H58" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H58" t="str">
+      <c r="I58" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I58" t="str">
+      <c r="J58" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2987,30 +3162,33 @@
         <v>2</v>
       </c>
       <c r="F59" t="str">
+        <v>file</v>
+      </c>
+      <c r="G59" t="str">
         <v>TG2</v>
       </c>
-      <c r="G59" t="str">
+      <c r="H59" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H59" t="str">
+      <c r="I59" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I59" t="str">
-        <v/>
-      </c>
       <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3031,30 +3209,33 @@
         <v>3</v>
       </c>
       <c r="F60" t="str">
+        <v>file</v>
+      </c>
+      <c r="G60" t="str">
         <v>TG1</v>
       </c>
-      <c r="G60" t="str">
+      <c r="H60" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H60" t="str">
+      <c r="I60" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
       <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3075,30 +3256,33 @@
         <v>3</v>
       </c>
       <c r="F61" t="str">
+        <v>file</v>
+      </c>
+      <c r="G61" t="str">
         <v>TG2</v>
       </c>
-      <c r="G61" t="str">
+      <c r="H61" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H61" t="str">
+      <c r="I61" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I61" t="str">
-        <v/>
-      </c>
       <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L61" t="str">
+      <c r="M61" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3119,30 +3303,33 @@
         <v>1</v>
       </c>
       <c r="F62" t="str">
+        <v>file</v>
+      </c>
+      <c r="G62" t="str">
         <v>TG1</v>
       </c>
-      <c r="G62" t="str">
+      <c r="H62" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H62" t="str">
+      <c r="I62" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I62" t="str">
-        <v/>
-      </c>
       <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L62" t="str">
+      <c r="M62" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3163,30 +3350,33 @@
         <v>2</v>
       </c>
       <c r="F63" t="str">
+        <v>file</v>
+      </c>
+      <c r="G63" t="str">
         <v>TG2</v>
       </c>
-      <c r="G63" t="str">
+      <c r="H63" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H63" t="str">
+      <c r="I63" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I63" t="str">
-        <v/>
-      </c>
       <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L63" t="str">
+      <c r="M63" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3207,30 +3397,33 @@
         <v>3</v>
       </c>
       <c r="F64" t="str">
+        <v>file</v>
+      </c>
+      <c r="G64" t="str">
         <v>TG1</v>
       </c>
-      <c r="G64" t="str">
+      <c r="H64" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H64" t="str">
+      <c r="I64" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I64" t="str">
-        <v/>
-      </c>
       <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L64" t="str">
+      <c r="M64" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3251,30 +3444,33 @@
         <v>3</v>
       </c>
       <c r="F65" t="str">
+        <v>file</v>
+      </c>
+      <c r="G65" t="str">
         <v>TG2</v>
       </c>
-      <c r="G65" t="str">
+      <c r="H65" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H65" t="str">
+      <c r="I65" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I65" t="str">
+      <c r="J65" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3295,30 +3491,33 @@
         <v>1</v>
       </c>
       <c r="F66" t="str">
+        <v>file</v>
+      </c>
+      <c r="G66" t="str">
         <v>TG1</v>
       </c>
-      <c r="G66" t="str">
+      <c r="H66" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H66" t="str">
+      <c r="I66" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I66" t="str">
-        <v/>
-      </c>
       <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K66" t="str">
+      <c r="L66" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L66" t="str">
+      <c r="M66" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M66" t="str">
+      <c r="N66" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3339,30 +3538,33 @@
         <v>2</v>
       </c>
       <c r="F67" t="str">
+        <v>file</v>
+      </c>
+      <c r="G67" t="str">
         <v>TG2</v>
       </c>
-      <c r="G67" t="str">
+      <c r="H67" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H67" t="str">
+      <c r="I67" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I67" t="str">
-        <v/>
-      </c>
       <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K67" t="str">
+      <c r="L67" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L67" t="str">
+      <c r="M67" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M67" t="str">
+      <c r="N67" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N67" t="str">
+      <c r="O67" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3383,30 +3585,33 @@
         <v>3</v>
       </c>
       <c r="F68" t="str">
+        <v>file</v>
+      </c>
+      <c r="G68" t="str">
         <v>TG1</v>
       </c>
-      <c r="G68" t="str">
+      <c r="H68" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H68" t="str">
+      <c r="I68" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I68" t="str">
-        <v/>
-      </c>
       <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K68" t="str">
+      <c r="L68" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L68" t="str">
+      <c r="M68" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M68" t="str">
+      <c r="N68" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3427,30 +3632,33 @@
         <v>3</v>
       </c>
       <c r="F69" t="str">
+        <v>file</v>
+      </c>
+      <c r="G69" t="str">
         <v>TG2</v>
       </c>
-      <c r="G69" t="str">
+      <c r="H69" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H69" t="str">
+      <c r="I69" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I69" t="str">
-        <v/>
-      </c>
       <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K69" t="str">
+      <c r="L69" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L69" t="str">
+      <c r="M69" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3471,30 +3679,33 @@
         <v>1</v>
       </c>
       <c r="F70" t="str">
+        <v>file</v>
+      </c>
+      <c r="G70" t="str">
         <v>TG1</v>
       </c>
-      <c r="G70" t="str">
+      <c r="H70" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H70" t="str">
+      <c r="I70" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I70" t="str">
-        <v/>
-      </c>
       <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K70" t="str">
+      <c r="L70" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L70" t="str">
+      <c r="M70" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3515,30 +3726,33 @@
         <v>2</v>
       </c>
       <c r="F71" t="str">
+        <v>file</v>
+      </c>
+      <c r="G71" t="str">
         <v>TG2</v>
       </c>
-      <c r="G71" t="str">
+      <c r="H71" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H71" t="str">
+      <c r="I71" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I71" t="str">
-        <v/>
-      </c>
       <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K71" t="str">
+      <c r="L71" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L71" t="str">
+      <c r="M71" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3559,30 +3773,33 @@
         <v>3</v>
       </c>
       <c r="F72" t="str">
+        <v>file</v>
+      </c>
+      <c r="G72" t="str">
         <v>TG1</v>
       </c>
-      <c r="G72" t="str">
+      <c r="H72" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H72" t="str">
+      <c r="I72" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I72" t="str">
+      <c r="J72" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3603,30 +3820,33 @@
         <v>3</v>
       </c>
       <c r="F73" t="str">
+        <v>file</v>
+      </c>
+      <c r="G73" t="str">
         <v>TG2</v>
       </c>
-      <c r="G73" t="str">
+      <c r="H73" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H73" t="str">
+      <c r="I73" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I73" t="str">
-        <v/>
-      </c>
       <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K73" t="str">
+      <c r="L73" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L73" t="str">
+      <c r="M73" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3647,30 +3867,33 @@
         <v>1</v>
       </c>
       <c r="F74" t="str">
+        <v>file</v>
+      </c>
+      <c r="G74" t="str">
         <v>TG1</v>
       </c>
-      <c r="G74" t="str">
+      <c r="H74" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H74" t="str">
+      <c r="I74" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I74" t="str">
-        <v/>
-      </c>
       <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K74" t="str">
+      <c r="L74" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L74" t="str">
+      <c r="M74" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3691,30 +3914,33 @@
         <v>2</v>
       </c>
       <c r="F75" t="str">
+        <v>file</v>
+      </c>
+      <c r="G75" t="str">
         <v>TG2</v>
       </c>
-      <c r="G75" t="str">
+      <c r="H75" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H75" t="str">
+      <c r="I75" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I75" t="str">
-        <v/>
-      </c>
       <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K75" t="str">
+      <c r="L75" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L75" t="str">
+      <c r="M75" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3735,30 +3961,33 @@
         <v>3</v>
       </c>
       <c r="F76" t="str">
+        <v>file</v>
+      </c>
+      <c r="G76" t="str">
         <v>TG1</v>
       </c>
-      <c r="G76" t="str">
+      <c r="H76" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H76" t="str">
+      <c r="I76" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I76" t="str">
-        <v/>
-      </c>
       <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K76" t="str">
+      <c r="L76" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L76" t="str">
+      <c r="M76" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M76" t="str">
+      <c r="N76" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3779,30 +4008,33 @@
         <v>3</v>
       </c>
       <c r="F77" t="str">
+        <v>file</v>
+      </c>
+      <c r="G77" t="str">
         <v>TG2</v>
       </c>
-      <c r="G77" t="str">
+      <c r="H77" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H77" t="str">
+      <c r="I77" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I77" t="str">
-        <v/>
-      </c>
       <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K77" t="str">
+      <c r="L77" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L77" t="str">
+      <c r="M77" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M77" t="str">
+      <c r="N77" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3823,30 +4055,33 @@
         <v>1</v>
       </c>
       <c r="F78" t="str">
+        <v>file</v>
+      </c>
+      <c r="G78" t="str">
         <v>TG1</v>
       </c>
-      <c r="G78" t="str">
+      <c r="H78" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H78" t="str">
+      <c r="I78" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I78" t="str">
-        <v/>
-      </c>
       <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K78" t="str">
+      <c r="L78" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L78" t="str">
+      <c r="M78" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M78" t="str">
+      <c r="N78" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3867,30 +4102,33 @@
         <v>2</v>
       </c>
       <c r="F79" t="str">
+        <v>file</v>
+      </c>
+      <c r="G79" t="str">
         <v>TG2</v>
       </c>
-      <c r="G79" t="str">
+      <c r="H79" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H79" t="str">
+      <c r="I79" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I79" t="str">
+      <c r="J79" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J79" t="str">
+      <c r="K79" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K79" t="str">
+      <c r="L79" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3911,30 +4149,33 @@
         <v>3</v>
       </c>
       <c r="F80" t="str">
+        <v>file</v>
+      </c>
+      <c r="G80" t="str">
         <v>TG1</v>
       </c>
-      <c r="G80" t="str">
+      <c r="H80" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H80" t="str">
+      <c r="I80" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I80" t="str">
-        <v/>
-      </c>
       <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K80" t="str">
+      <c r="L80" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L80" t="str">
+      <c r="M80" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M80" t="str">
+      <c r="N80" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3955,30 +4196,33 @@
         <v>3</v>
       </c>
       <c r="F81" t="str">
+        <v>file</v>
+      </c>
+      <c r="G81" t="str">
         <v>TG2</v>
       </c>
-      <c r="G81" t="str">
+      <c r="H81" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H81" t="str">
+      <c r="I81" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I81" t="str">
-        <v/>
-      </c>
       <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K81" t="str">
+      <c r="L81" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L81" t="str">
+      <c r="M81" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M81" t="str">
+      <c r="N81" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3999,30 +4243,33 @@
         <v>1</v>
       </c>
       <c r="F82" t="str">
+        <v>file</v>
+      </c>
+      <c r="G82" t="str">
         <v>TG1</v>
       </c>
-      <c r="G82" t="str">
+      <c r="H82" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H82" t="str">
+      <c r="I82" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I82" t="str">
-        <v/>
-      </c>
       <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K82" t="str">
+      <c r="L82" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L82" t="str">
+      <c r="M82" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M82" t="str">
+      <c r="N82" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4043,30 +4290,33 @@
         <v>2</v>
       </c>
       <c r="F83" t="str">
+        <v>file</v>
+      </c>
+      <c r="G83" t="str">
         <v>TG2</v>
       </c>
-      <c r="G83" t="str">
+      <c r="H83" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H83" t="str">
+      <c r="I83" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I83" t="str">
-        <v/>
-      </c>
       <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K83" t="str">
+      <c r="L83" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L83" t="str">
+      <c r="M83" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M83" t="str">
+      <c r="N83" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N83" t="str">
+      <c r="O83" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4087,30 +4337,33 @@
         <v>3</v>
       </c>
       <c r="F84" t="str">
+        <v>file</v>
+      </c>
+      <c r="G84" t="str">
         <v>TG1</v>
       </c>
-      <c r="G84" t="str">
+      <c r="H84" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H84" t="str">
+      <c r="I84" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I84" t="str">
-        <v/>
-      </c>
       <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K84" t="str">
+      <c r="L84" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L84" t="str">
+      <c r="M84" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M84" t="str">
+      <c r="N84" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N84" t="str">
+      <c r="O84" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4131,30 +4384,33 @@
         <v>3</v>
       </c>
       <c r="F85" t="str">
+        <v>file</v>
+      </c>
+      <c r="G85" t="str">
         <v>TG2</v>
       </c>
-      <c r="G85" t="str">
+      <c r="H85" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H85" t="str">
+      <c r="I85" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I85" t="str">
-        <v/>
-      </c>
       <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K85" t="str">
+      <c r="L85" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L85" t="str">
+      <c r="M85" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M85" t="str">
+      <c r="N85" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N85" t="str">
+      <c r="O85" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4175,30 +4431,33 @@
         <v>1</v>
       </c>
       <c r="F86" t="str">
+        <v>file</v>
+      </c>
+      <c r="G86" t="str">
         <v>TG1</v>
       </c>
-      <c r="G86" t="str">
+      <c r="H86" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H86" t="str">
+      <c r="I86" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I86" t="str">
+      <c r="J86" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J86" t="str">
+      <c r="K86" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4219,30 +4478,33 @@
         <v>2</v>
       </c>
       <c r="F87" t="str">
+        <v>file</v>
+      </c>
+      <c r="G87" t="str">
         <v>TG2</v>
       </c>
-      <c r="G87" t="str">
+      <c r="H87" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H87" t="str">
+      <c r="I87" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I87" t="str">
-        <v/>
-      </c>
       <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K87" t="str">
+      <c r="L87" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L87" t="str">
+      <c r="M87" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M87" t="str">
+      <c r="N87" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N87" t="str">
+      <c r="O87" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4263,30 +4525,33 @@
         <v>3</v>
       </c>
       <c r="F88" t="str">
+        <v>file</v>
+      </c>
+      <c r="G88" t="str">
         <v>TG1</v>
       </c>
-      <c r="G88" t="str">
+      <c r="H88" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H88" t="str">
+      <c r="I88" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I88" t="str">
-        <v/>
-      </c>
       <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K88" t="str">
+      <c r="L88" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L88" t="str">
+      <c r="M88" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M88" t="str">
+      <c r="N88" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N88" t="str">
+      <c r="O88" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4307,30 +4572,33 @@
         <v>3</v>
       </c>
       <c r="F89" t="str">
+        <v>file</v>
+      </c>
+      <c r="G89" t="str">
         <v>TG2</v>
       </c>
-      <c r="G89" t="str">
+      <c r="H89" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H89" t="str">
+      <c r="I89" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I89" t="str">
-        <v/>
-      </c>
       <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K89" t="str">
+      <c r="L89" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L89" t="str">
+      <c r="M89" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M89" t="str">
+      <c r="N89" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N89" t="str">
+      <c r="O89" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4351,30 +4619,33 @@
         <v>1</v>
       </c>
       <c r="F90" t="str">
+        <v>file</v>
+      </c>
+      <c r="G90" t="str">
         <v>TG1</v>
       </c>
-      <c r="G90" t="str">
+      <c r="H90" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H90" t="str">
+      <c r="I90" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I90" t="str">
-        <v/>
-      </c>
       <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K90" t="str">
+      <c r="L90" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L90" t="str">
+      <c r="M90" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M90" t="str">
+      <c r="N90" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N90" t="str">
+      <c r="O90" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4395,30 +4666,33 @@
         <v>2</v>
       </c>
       <c r="F91" t="str">
+        <v>file</v>
+      </c>
+      <c r="G91" t="str">
         <v>TG2</v>
       </c>
-      <c r="G91" t="str">
+      <c r="H91" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H91" t="str">
+      <c r="I91" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I91" t="str">
-        <v/>
-      </c>
       <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K91" t="str">
+      <c r="L91" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L91" t="str">
+      <c r="M91" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M91" t="str">
+      <c r="N91" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N91" t="str">
+      <c r="O91" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4439,30 +4713,33 @@
         <v>3</v>
       </c>
       <c r="F92" t="str">
+        <v>file</v>
+      </c>
+      <c r="G92" t="str">
         <v>TG1</v>
       </c>
-      <c r="G92" t="str">
+      <c r="H92" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H92" t="str">
+      <c r="I92" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I92" t="str">
-        <v/>
-      </c>
       <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K92" t="str">
+      <c r="L92" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L92" t="str">
+      <c r="M92" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M92" t="str">
+      <c r="N92" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N92" t="str">
+      <c r="O92" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4483,30 +4760,33 @@
         <v>3</v>
       </c>
       <c r="F93" t="str">
+        <v>file</v>
+      </c>
+      <c r="G93" t="str">
         <v>TG2</v>
       </c>
-      <c r="G93" t="str">
+      <c r="H93" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H93" t="str">
+      <c r="I93" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I93" t="str">
+      <c r="J93" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J93" t="str">
+      <c r="K93" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L93" t="str">
+      <c r="M93" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N93" t="str">
+      <c r="O93" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4527,30 +4807,33 @@
         <v>1</v>
       </c>
       <c r="F94" t="str">
+        <v>file</v>
+      </c>
+      <c r="G94" t="str">
         <v>TG1</v>
       </c>
-      <c r="G94" t="str">
+      <c r="H94" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H94" t="str">
+      <c r="I94" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
       <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K94" t="str">
+      <c r="L94" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L94" t="str">
+      <c r="M94" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M94" t="str">
+      <c r="N94" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N94" t="str">
+      <c r="O94" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4571,30 +4854,33 @@
         <v>2</v>
       </c>
       <c r="F95" t="str">
+        <v>file</v>
+      </c>
+      <c r="G95" t="str">
         <v>TG2</v>
       </c>
-      <c r="G95" t="str">
+      <c r="H95" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H95" t="str">
+      <c r="I95" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I95" t="str">
-        <v/>
-      </c>
       <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K95" t="str">
+      <c r="L95" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L95" t="str">
+      <c r="M95" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M95" t="str">
+      <c r="N95" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N95" t="str">
+      <c r="O95" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4615,30 +4901,33 @@
         <v>3</v>
       </c>
       <c r="F96" t="str">
+        <v>file</v>
+      </c>
+      <c r="G96" t="str">
         <v>TG1</v>
       </c>
-      <c r="G96" t="str">
+      <c r="H96" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H96" t="str">
+      <c r="I96" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I96" t="str">
-        <v/>
-      </c>
       <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K96" t="str">
+      <c r="L96" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L96" t="str">
+      <c r="M96" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M96" t="str">
+      <c r="N96" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N96" t="str">
+      <c r="O96" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4659,30 +4948,33 @@
         <v>3</v>
       </c>
       <c r="F97" t="str">
+        <v>file</v>
+      </c>
+      <c r="G97" t="str">
         <v>TG2</v>
       </c>
-      <c r="G97" t="str">
+      <c r="H97" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H97" t="str">
+      <c r="I97" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I97" t="str">
-        <v/>
-      </c>
       <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K97" t="str">
+      <c r="L97" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L97" t="str">
+      <c r="M97" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M97" t="str">
+      <c r="N97" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N97" t="str">
+      <c r="O97" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4703,30 +4995,33 @@
         <v>1</v>
       </c>
       <c r="F98" t="str">
+        <v>file</v>
+      </c>
+      <c r="G98" t="str">
         <v>TG1</v>
       </c>
-      <c r="G98" t="str">
+      <c r="H98" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H98" t="str">
+      <c r="I98" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
       <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K98" t="str">
+      <c r="L98" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L98" t="str">
+      <c r="M98" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M98" t="str">
+      <c r="N98" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N98" t="str">
+      <c r="O98" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4747,30 +5042,33 @@
         <v>2</v>
       </c>
       <c r="F99" t="str">
+        <v>file</v>
+      </c>
+      <c r="G99" t="str">
         <v>TG2</v>
       </c>
-      <c r="G99" t="str">
+      <c r="H99" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H99" t="str">
+      <c r="I99" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
       <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K99" t="str">
+      <c r="L99" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L99" t="str">
+      <c r="M99" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M99" t="str">
+      <c r="N99" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N99" t="str">
+      <c r="O99" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4791,30 +5089,33 @@
         <v>3</v>
       </c>
       <c r="F100" t="str">
+        <v>file</v>
+      </c>
+      <c r="G100" t="str">
         <v>TG1</v>
       </c>
-      <c r="G100" t="str">
+      <c r="H100" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H100" t="str">
+      <c r="I100" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I100" t="str">
+      <c r="J100" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J100" t="str">
+      <c r="K100" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L100" t="str">
+      <c r="M100" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N100" t="str">
+      <c r="O100" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4835,30 +5136,33 @@
         <v>3</v>
       </c>
       <c r="F101" t="str">
+        <v>file</v>
+      </c>
+      <c r="G101" t="str">
         <v>TG2</v>
       </c>
-      <c r="G101" t="str">
+      <c r="H101" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H101" t="str">
+      <c r="I101" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I101" t="str">
-        <v/>
-      </c>
       <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K101" t="str">
+      <c r="L101" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L101" t="str">
+      <c r="M101" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M101" t="str">
+      <c r="N101" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N101" t="str">
+      <c r="O101" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4879,30 +5183,33 @@
         <v>1</v>
       </c>
       <c r="F102" t="str">
+        <v>file</v>
+      </c>
+      <c r="G102" t="str">
         <v>TG1</v>
       </c>
-      <c r="G102" t="str">
+      <c r="H102" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H102" t="str">
+      <c r="I102" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
       <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K102" t="str">
+      <c r="L102" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L102" t="str">
+      <c r="M102" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M102" t="str">
+      <c r="N102" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N102" t="str">
+      <c r="O102" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4923,30 +5230,33 @@
         <v>2</v>
       </c>
       <c r="F103" t="str">
+        <v>file</v>
+      </c>
+      <c r="G103" t="str">
         <v>TG2</v>
       </c>
-      <c r="G103" t="str">
+      <c r="H103" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H103" t="str">
+      <c r="I103" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
       <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K103" t="str">
+      <c r="L103" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L103" t="str">
+      <c r="M103" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M103" t="str">
+      <c r="N103" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N103" t="str">
+      <c r="O103" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4967,30 +5277,33 @@
         <v>3</v>
       </c>
       <c r="F104" t="str">
+        <v>file</v>
+      </c>
+      <c r="G104" t="str">
         <v>TG1</v>
       </c>
-      <c r="G104" t="str">
+      <c r="H104" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H104" t="str">
+      <c r="I104" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
       <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K104" t="str">
+      <c r="L104" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L104" t="str">
+      <c r="M104" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M104" t="str">
+      <c r="N104" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N104" t="str">
+      <c r="O104" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5011,30 +5324,33 @@
         <v>3</v>
       </c>
       <c r="F105" t="str">
+        <v>file</v>
+      </c>
+      <c r="G105" t="str">
         <v>TG2</v>
       </c>
-      <c r="G105" t="str">
+      <c r="H105" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H105" t="str">
+      <c r="I105" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
       <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K105" t="str">
+      <c r="L105" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L105" t="str">
+      <c r="M105" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M105" t="str">
+      <c r="N105" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N105" t="str">
+      <c r="O105" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5055,30 +5371,33 @@
         <v>1</v>
       </c>
       <c r="F106" t="str">
+        <v>file</v>
+      </c>
+      <c r="G106" t="str">
         <v>TG1</v>
       </c>
-      <c r="G106" t="str">
+      <c r="H106" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H106" t="str">
+      <c r="I106" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I106" t="str">
-        <v/>
-      </c>
       <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K106" t="str">
+      <c r="L106" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L106" t="str">
+      <c r="M106" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M106" t="str">
+      <c r="N106" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N106" t="str">
+      <c r="O106" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5099,30 +5418,33 @@
         <v>2</v>
       </c>
       <c r="F107" t="str">
+        <v>file</v>
+      </c>
+      <c r="G107" t="str">
         <v>TG2</v>
       </c>
-      <c r="G107" t="str">
+      <c r="H107" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H107" t="str">
+      <c r="I107" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I107" t="str">
+      <c r="J107" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J107" t="str">
+      <c r="K107" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L107" t="str">
+      <c r="M107" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N107" t="str">
+      <c r="O107" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5143,30 +5465,33 @@
         <v>3</v>
       </c>
       <c r="F108" t="str">
+        <v>file</v>
+      </c>
+      <c r="G108" t="str">
         <v>TG1</v>
       </c>
-      <c r="G108" t="str">
+      <c r="H108" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H108" t="str">
+      <c r="I108" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I108" t="str">
-        <v/>
-      </c>
       <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K108" t="str">
+      <c r="L108" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L108" t="str">
+      <c r="M108" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M108" t="str">
+      <c r="N108" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N108" t="str">
+      <c r="O108" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5187,30 +5512,33 @@
         <v>3</v>
       </c>
       <c r="F109" t="str">
+        <v>file</v>
+      </c>
+      <c r="G109" t="str">
         <v>TG2</v>
       </c>
-      <c r="G109" t="str">
+      <c r="H109" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H109" t="str">
+      <c r="I109" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I109" t="str">
-        <v/>
-      </c>
       <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K109" t="str">
+      <c r="L109" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L109" t="str">
+      <c r="M109" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M109" t="str">
+      <c r="N109" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N109" t="str">
+      <c r="O109" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5231,30 +5559,33 @@
         <v>1</v>
       </c>
       <c r="F110" t="str">
+        <v>file</v>
+      </c>
+      <c r="G110" t="str">
         <v>TG1</v>
       </c>
-      <c r="G110" t="str">
+      <c r="H110" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H110" t="str">
+      <c r="I110" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I110" t="str">
-        <v/>
-      </c>
       <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K110" t="str">
+      <c r="L110" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L110" t="str">
+      <c r="M110" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M110" t="str">
+      <c r="N110" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N110" t="str">
+      <c r="O110" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5275,30 +5606,33 @@
         <v>2</v>
       </c>
       <c r="F111" t="str">
+        <v>file</v>
+      </c>
+      <c r="G111" t="str">
         <v>TG2</v>
       </c>
-      <c r="G111" t="str">
+      <c r="H111" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H111" t="str">
+      <c r="I111" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I111" t="str">
-        <v/>
-      </c>
       <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K111" t="str">
+      <c r="L111" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L111" t="str">
+      <c r="M111" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M111" t="str">
+      <c r="N111" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N111" t="str">
+      <c r="O111" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5319,30 +5653,33 @@
         <v>3</v>
       </c>
       <c r="F112" t="str">
+        <v>file</v>
+      </c>
+      <c r="G112" t="str">
         <v>TG1</v>
       </c>
-      <c r="G112" t="str">
+      <c r="H112" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H112" t="str">
+      <c r="I112" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I112" t="str">
-        <v/>
-      </c>
       <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K112" t="str">
+      <c r="L112" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L112" t="str">
+      <c r="M112" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M112" t="str">
+      <c r="N112" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N112" t="str">
+      <c r="O112" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5363,30 +5700,33 @@
         <v>3</v>
       </c>
       <c r="F113" t="str">
+        <v>file</v>
+      </c>
+      <c r="G113" t="str">
         <v>TG2</v>
       </c>
-      <c r="G113" t="str">
+      <c r="H113" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H113" t="str">
+      <c r="I113" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I113" t="str">
-        <v/>
-      </c>
       <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K113" t="str">
+      <c r="L113" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L113" t="str">
+      <c r="M113" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M113" t="str">
+      <c r="N113" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N113" t="str">
+      <c r="O113" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5407,30 +5747,33 @@
         <v>1</v>
       </c>
       <c r="F114" t="str">
+        <v>file</v>
+      </c>
+      <c r="G114" t="str">
         <v>TG1</v>
       </c>
-      <c r="G114" t="str">
+      <c r="H114" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H114" t="str">
+      <c r="I114" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I114" t="str">
+      <c r="J114" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J114" t="str">
+      <c r="K114" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K114" t="str">
+      <c r="L114" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L114" t="str">
+      <c r="M114" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N114" t="str">
+      <c r="O114" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5451,30 +5794,33 @@
         <v>2</v>
       </c>
       <c r="F115" t="str">
+        <v>file</v>
+      </c>
+      <c r="G115" t="str">
         <v>TG2</v>
       </c>
-      <c r="G115" t="str">
+      <c r="H115" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H115" t="str">
+      <c r="I115" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I115" t="str">
-        <v/>
-      </c>
       <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K115" t="str">
+      <c r="L115" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L115" t="str">
+      <c r="M115" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M115" t="str">
+      <c r="N115" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N115" t="str">
+      <c r="O115" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5495,30 +5841,33 @@
         <v>3</v>
       </c>
       <c r="F116" t="str">
+        <v>file</v>
+      </c>
+      <c r="G116" t="str">
         <v>TG1</v>
       </c>
-      <c r="G116" t="str">
+      <c r="H116" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H116" t="str">
+      <c r="I116" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I116" t="str">
-        <v/>
-      </c>
       <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K116" t="str">
+      <c r="L116" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L116" t="str">
+      <c r="M116" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M116" t="str">
+      <c r="N116" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N116" t="str">
+      <c r="O116" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5539,30 +5888,33 @@
         <v>3</v>
       </c>
       <c r="F117" t="str">
+        <v>file</v>
+      </c>
+      <c r="G117" t="str">
         <v>TG2</v>
       </c>
-      <c r="G117" t="str">
+      <c r="H117" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H117" t="str">
+      <c r="I117" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I117" t="str">
-        <v/>
-      </c>
       <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K117" t="str">
+      <c r="L117" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L117" t="str">
+      <c r="M117" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M117" t="str">
+      <c r="N117" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N117" t="str">
+      <c r="O117" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5583,30 +5935,33 @@
         <v>1</v>
       </c>
       <c r="F118" t="str">
+        <v>file</v>
+      </c>
+      <c r="G118" t="str">
         <v>TG1</v>
       </c>
-      <c r="G118" t="str">
+      <c r="H118" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H118" t="str">
+      <c r="I118" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I118" t="str">
-        <v/>
-      </c>
       <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K118" t="str">
+      <c r="L118" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L118" t="str">
+      <c r="M118" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M118" t="str">
+      <c r="N118" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N118" t="str">
+      <c r="O118" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5627,30 +5982,33 @@
         <v>2</v>
       </c>
       <c r="F119" t="str">
+        <v>file</v>
+      </c>
+      <c r="G119" t="str">
         <v>TG2</v>
       </c>
-      <c r="G119" t="str">
+      <c r="H119" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H119" t="str">
+      <c r="I119" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I119" t="str">
-        <v/>
-      </c>
       <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K119" t="str">
+      <c r="L119" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L119" t="str">
+      <c r="M119" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M119" t="str">
+      <c r="N119" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N119" t="str">
+      <c r="O119" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5671,30 +6029,33 @@
         <v>3</v>
       </c>
       <c r="F120" t="str">
+        <v>file</v>
+      </c>
+      <c r="G120" t="str">
         <v>TG1</v>
       </c>
-      <c r="G120" t="str">
+      <c r="H120" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H120" t="str">
+      <c r="I120" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I120" t="str">
-        <v/>
-      </c>
       <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K120" t="str">
+      <c r="L120" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L120" t="str">
+      <c r="M120" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M120" t="str">
+      <c r="N120" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N120" t="str">
+      <c r="O120" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5715,30 +6076,33 @@
         <v>3</v>
       </c>
       <c r="F121" t="str">
+        <v>file</v>
+      </c>
+      <c r="G121" t="str">
         <v>TG2</v>
       </c>
-      <c r="G121" t="str">
+      <c r="H121" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H121" t="str">
+      <c r="I121" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I121" t="str">
+      <c r="J121" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J121" t="str">
+      <c r="K121" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K121" t="str">
+      <c r="L121" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L121" t="str">
+      <c r="M121" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N121" t="str">
+      <c r="O121" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5759,30 +6123,33 @@
         <v>1</v>
       </c>
       <c r="F122" t="str">
+        <v>file</v>
+      </c>
+      <c r="G122" t="str">
         <v>TG1</v>
       </c>
-      <c r="G122" t="str">
+      <c r="H122" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H122" t="str">
+      <c r="I122" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I122" t="str">
-        <v/>
-      </c>
       <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K122" t="str">
+      <c r="L122" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L122" t="str">
+      <c r="M122" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M122" t="str">
+      <c r="N122" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N122" t="str">
+      <c r="O122" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5803,30 +6170,33 @@
         <v>2</v>
       </c>
       <c r="F123" t="str">
+        <v>file</v>
+      </c>
+      <c r="G123" t="str">
         <v>TG2</v>
       </c>
-      <c r="G123" t="str">
+      <c r="H123" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H123" t="str">
+      <c r="I123" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I123" t="str">
-        <v/>
-      </c>
       <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K123" t="str">
+      <c r="L123" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L123" t="str">
+      <c r="M123" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M123" t="str">
+      <c r="N123" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N123" t="str">
+      <c r="O123" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5847,30 +6217,33 @@
         <v>3</v>
       </c>
       <c r="F124" t="str">
+        <v>file</v>
+      </c>
+      <c r="G124" t="str">
         <v>TG1</v>
       </c>
-      <c r="G124" t="str">
+      <c r="H124" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H124" t="str">
+      <c r="I124" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
       <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K124" t="str">
+      <c r="L124" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L124" t="str">
+      <c r="M124" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M124" t="str">
+      <c r="N124" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N124" t="str">
+      <c r="O124" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5891,30 +6264,33 @@
         <v>3</v>
       </c>
       <c r="F125" t="str">
+        <v>file</v>
+      </c>
+      <c r="G125" t="str">
         <v>TG2</v>
       </c>
-      <c r="G125" t="str">
+      <c r="H125" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H125" t="str">
+      <c r="I125" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I125" t="str">
-        <v/>
-      </c>
       <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K125" t="str">
+      <c r="L125" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L125" t="str">
+      <c r="M125" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M125" t="str">
+      <c r="N125" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N125" t="str">
+      <c r="O125" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5935,30 +6311,33 @@
         <v>1</v>
       </c>
       <c r="F126" t="str">
+        <v>file</v>
+      </c>
+      <c r="G126" t="str">
         <v>TG1</v>
       </c>
-      <c r="G126" t="str">
+      <c r="H126" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H126" t="str">
+      <c r="I126" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I126" t="str">
-        <v/>
-      </c>
       <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K126" t="str">
+      <c r="L126" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L126" t="str">
+      <c r="M126" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M126" t="str">
+      <c r="N126" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N126" t="str">
+      <c r="O126" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5979,30 +6358,33 @@
         <v>2</v>
       </c>
       <c r="F127" t="str">
+        <v>file</v>
+      </c>
+      <c r="G127" t="str">
         <v>TG2</v>
       </c>
-      <c r="G127" t="str">
+      <c r="H127" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H127" t="str">
+      <c r="I127" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I127" t="str">
-        <v/>
-      </c>
       <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K127" t="str">
+      <c r="L127" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L127" t="str">
+      <c r="M127" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M127" t="str">
+      <c r="N127" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N127" t="str">
+      <c r="O127" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6023,30 +6405,33 @@
         <v>3</v>
       </c>
       <c r="F128" t="str">
+        <v>file</v>
+      </c>
+      <c r="G128" t="str">
         <v>TG1</v>
       </c>
-      <c r="G128" t="str">
+      <c r="H128" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H128" t="str">
+      <c r="I128" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I128" t="str">
+      <c r="J128" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J128" t="str">
+      <c r="K128" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K128" t="str">
+      <c r="L128" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L128" t="str">
+      <c r="M128" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N128" t="str">
+      <c r="O128" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6067,30 +6452,33 @@
         <v>3</v>
       </c>
       <c r="F129" t="str">
+        <v>file</v>
+      </c>
+      <c r="G129" t="str">
         <v>TG2</v>
       </c>
-      <c r="G129" t="str">
+      <c r="H129" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H129" t="str">
+      <c r="I129" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I129" t="str">
-        <v/>
-      </c>
       <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K129" t="str">
+      <c r="L129" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L129" t="str">
+      <c r="M129" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M129" t="str">
+      <c r="N129" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N129" t="str">
+      <c r="O129" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6111,30 +6499,33 @@
         <v>1</v>
       </c>
       <c r="F130" t="str">
+        <v>file</v>
+      </c>
+      <c r="G130" t="str">
         <v>TG1</v>
       </c>
-      <c r="G130" t="str">
+      <c r="H130" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H130" t="str">
+      <c r="I130" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I130" t="str">
-        <v/>
-      </c>
       <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K130" t="str">
+      <c r="L130" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L130" t="str">
+      <c r="M130" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M130" t="str">
+      <c r="N130" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N130" t="str">
+      <c r="O130" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6155,30 +6546,33 @@
         <v>2</v>
       </c>
       <c r="F131" t="str">
+        <v>file</v>
+      </c>
+      <c r="G131" t="str">
         <v>TG2</v>
       </c>
-      <c r="G131" t="str">
+      <c r="H131" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H131" t="str">
+      <c r="I131" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I131" t="str">
-        <v/>
-      </c>
       <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K131" t="str">
+      <c r="L131" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L131" t="str">
+      <c r="M131" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M131" t="str">
+      <c r="N131" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N131" t="str">
+      <c r="O131" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6199,30 +6593,33 @@
         <v>3</v>
       </c>
       <c r="F132" t="str">
+        <v>file</v>
+      </c>
+      <c r="G132" t="str">
         <v>TG1</v>
       </c>
-      <c r="G132" t="str">
+      <c r="H132" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H132" t="str">
+      <c r="I132" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I132" t="str">
-        <v/>
-      </c>
       <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K132" t="str">
+      <c r="L132" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L132" t="str">
+      <c r="M132" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M132" t="str">
+      <c r="N132" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N132" t="str">
+      <c r="O132" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6243,30 +6640,33 @@
         <v>3</v>
       </c>
       <c r="F133" t="str">
+        <v>file</v>
+      </c>
+      <c r="G133" t="str">
         <v>TG2</v>
       </c>
-      <c r="G133" t="str">
+      <c r="H133" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H133" t="str">
+      <c r="I133" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I133" t="str">
-        <v/>
-      </c>
       <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K133" t="str">
+      <c r="L133" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L133" t="str">
+      <c r="M133" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M133" t="str">
+      <c r="N133" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N133" t="str">
+      <c r="O133" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6287,30 +6687,33 @@
         <v>1</v>
       </c>
       <c r="F134" t="str">
+        <v>file</v>
+      </c>
+      <c r="G134" t="str">
         <v>TG1</v>
       </c>
-      <c r="G134" t="str">
+      <c r="H134" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H134" t="str">
+      <c r="I134" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I134" t="str">
-        <v/>
-      </c>
       <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K134" t="str">
+      <c r="L134" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L134" t="str">
+      <c r="M134" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M134" t="str">
+      <c r="N134" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N134" t="str">
+      <c r="O134" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6331,30 +6734,33 @@
         <v>2</v>
       </c>
       <c r="F135" t="str">
+        <v>file</v>
+      </c>
+      <c r="G135" t="str">
         <v>TG2</v>
       </c>
-      <c r="G135" t="str">
+      <c r="H135" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H135" t="str">
+      <c r="I135" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I135" t="str">
+      <c r="J135" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J135" t="str">
+      <c r="K135" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K135" t="str">
+      <c r="L135" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L135" t="str">
+      <c r="M135" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N135" t="str">
+      <c r="O135" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6375,30 +6781,33 @@
         <v>3</v>
       </c>
       <c r="F136" t="str">
+        <v>file</v>
+      </c>
+      <c r="G136" t="str">
         <v>TG1</v>
       </c>
-      <c r="G136" t="str">
+      <c r="H136" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H136" t="str">
+      <c r="I136" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I136" t="str">
-        <v/>
-      </c>
       <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K136" t="str">
+      <c r="L136" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L136" t="str">
+      <c r="M136" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M136" t="str">
+      <c r="N136" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N136" t="str">
+      <c r="O136" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6419,30 +6828,33 @@
         <v>3</v>
       </c>
       <c r="F137" t="str">
+        <v>file</v>
+      </c>
+      <c r="G137" t="str">
         <v>TG2</v>
       </c>
-      <c r="G137" t="str">
+      <c r="H137" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H137" t="str">
+      <c r="I137" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I137" t="str">
-        <v/>
-      </c>
       <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K137" t="str">
+      <c r="L137" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L137" t="str">
+      <c r="M137" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M137" t="str">
+      <c r="N137" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N137" t="str">
+      <c r="O137" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6463,30 +6875,33 @@
         <v>1</v>
       </c>
       <c r="F138" t="str">
+        <v>file</v>
+      </c>
+      <c r="G138" t="str">
         <v>TG1</v>
       </c>
-      <c r="G138" t="str">
+      <c r="H138" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H138" t="str">
+      <c r="I138" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I138" t="str">
-        <v/>
-      </c>
       <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K138" t="str">
+      <c r="L138" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L138" t="str">
+      <c r="M138" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M138" t="str">
+      <c r="N138" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N138" t="str">
+      <c r="O138" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6507,30 +6922,33 @@
         <v>2</v>
       </c>
       <c r="F139" t="str">
+        <v>file</v>
+      </c>
+      <c r="G139" t="str">
         <v>TG2</v>
       </c>
-      <c r="G139" t="str">
+      <c r="H139" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H139" t="str">
+      <c r="I139" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I139" t="str">
-        <v/>
-      </c>
       <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K139" t="str">
+      <c r="L139" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L139" t="str">
+      <c r="M139" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M139" t="str">
+      <c r="N139" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N139" t="str">
+      <c r="O139" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6551,30 +6969,33 @@
         <v>3</v>
       </c>
       <c r="F140" t="str">
+        <v>file</v>
+      </c>
+      <c r="G140" t="str">
         <v>TG1</v>
       </c>
-      <c r="G140" t="str">
+      <c r="H140" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H140" t="str">
+      <c r="I140" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I140" t="str">
-        <v/>
-      </c>
       <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K140" t="str">
+      <c r="L140" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L140" t="str">
+      <c r="M140" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M140" t="str">
+      <c r="N140" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N140" t="str">
+      <c r="O140" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6595,30 +7016,33 @@
         <v>3</v>
       </c>
       <c r="F141" t="str">
+        <v>file</v>
+      </c>
+      <c r="G141" t="str">
         <v>TG2</v>
       </c>
-      <c r="G141" t="str">
+      <c r="H141" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H141" t="str">
+      <c r="I141" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I141" t="str">
-        <v/>
-      </c>
       <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K141" t="str">
+      <c r="L141" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L141" t="str">
+      <c r="M141" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M141" t="str">
+      <c r="N141" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N141" t="str">
+      <c r="O141" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6639,30 +7063,33 @@
         <v>1</v>
       </c>
       <c r="F142" t="str">
+        <v>file</v>
+      </c>
+      <c r="G142" t="str">
         <v>TG1</v>
       </c>
-      <c r="G142" t="str">
+      <c r="H142" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H142" t="str">
+      <c r="I142" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I142" t="str">
+      <c r="J142" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J142" t="str">
+      <c r="K142" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K142" t="str">
+      <c r="L142" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L142" t="str">
+      <c r="M142" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N142" t="str">
+      <c r="O142" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6683,30 +7110,33 @@
         <v>2</v>
       </c>
       <c r="F143" t="str">
+        <v>file</v>
+      </c>
+      <c r="G143" t="str">
         <v>TG2</v>
       </c>
-      <c r="G143" t="str">
+      <c r="H143" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H143" t="str">
+      <c r="I143" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I143" t="str">
-        <v/>
-      </c>
       <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K143" t="str">
+      <c r="L143" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L143" t="str">
+      <c r="M143" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M143" t="str">
+      <c r="N143" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N143" t="str">
+      <c r="O143" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6727,30 +7157,33 @@
         <v>3</v>
       </c>
       <c r="F144" t="str">
+        <v>file</v>
+      </c>
+      <c r="G144" t="str">
         <v>TG1</v>
       </c>
-      <c r="G144" t="str">
+      <c r="H144" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H144" t="str">
+      <c r="I144" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I144" t="str">
-        <v/>
-      </c>
       <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K144" t="str">
+      <c r="L144" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L144" t="str">
+      <c r="M144" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M144" t="str">
+      <c r="N144" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N144" t="str">
+      <c r="O144" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6771,30 +7204,33 @@
         <v>3</v>
       </c>
       <c r="F145" t="str">
+        <v>file</v>
+      </c>
+      <c r="G145" t="str">
         <v>TG2</v>
       </c>
-      <c r="G145" t="str">
+      <c r="H145" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H145" t="str">
+      <c r="I145" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I145" t="str">
-        <v/>
-      </c>
       <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K145" t="str">
+      <c r="L145" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L145" t="str">
+      <c r="M145" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M145" t="str">
+      <c r="N145" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N145" t="str">
+      <c r="O145" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6815,30 +7251,33 @@
         <v>1</v>
       </c>
       <c r="F146" t="str">
+        <v>file</v>
+      </c>
+      <c r="G146" t="str">
         <v>TG1</v>
       </c>
-      <c r="G146" t="str">
+      <c r="H146" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H146" t="str">
+      <c r="I146" t="str">
         <v>CL G1</v>
       </c>
-      <c r="I146" t="str">
-        <v/>
-      </c>
       <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K146" t="str">
+      <c r="L146" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L146" t="str">
+      <c r="M146" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M146" t="str">
+      <c r="N146" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N146" t="str">
+      <c r="O146" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6859,30 +7298,33 @@
         <v>2</v>
       </c>
       <c r="F147" t="str">
+        <v>file</v>
+      </c>
+      <c r="G147" t="str">
         <v>TG2</v>
       </c>
-      <c r="G147" t="str">
+      <c r="H147" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H147" t="str">
+      <c r="I147" t="str">
         <v>ML G2</v>
       </c>
-      <c r="I147" t="str">
-        <v/>
-      </c>
       <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K147" t="str">
+      <c r="L147" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L147" t="str">
+      <c r="M147" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M147" t="str">
+      <c r="N147" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N147" t="str">
+      <c r="O147" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6903,30 +7345,33 @@
         <v>3</v>
       </c>
       <c r="F148" t="str">
+        <v>file</v>
+      </c>
+      <c r="G148" t="str">
         <v>TG1</v>
       </c>
-      <c r="G148" t="str">
+      <c r="H148" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H148" t="str">
+      <c r="I148" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I148" t="str">
-        <v/>
-      </c>
       <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K148" t="str">
+      <c r="L148" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L148" t="str">
+      <c r="M148" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M148" t="str">
+      <c r="N148" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N148" t="str">
+      <c r="O148" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6947,30 +7392,33 @@
         <v>3</v>
       </c>
       <c r="F149" t="str">
+        <v>file</v>
+      </c>
+      <c r="G149" t="str">
         <v>TG2</v>
       </c>
-      <c r="G149" t="str">
+      <c r="H149" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H149" t="str">
+      <c r="I149" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I149" t="str">
+      <c r="J149" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="J149" t="str">
+      <c r="K149" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K149" t="str">
+      <c r="L149" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L149" t="str">
+      <c r="M149" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N149" t="str">
+      <c r="O149" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6991,30 +7439,33 @@
         <v>1</v>
       </c>
       <c r="F150" t="str">
+        <v>file</v>
+      </c>
+      <c r="G150" t="str">
         <v>TG1</v>
       </c>
-      <c r="G150" t="str">
+      <c r="H150" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H150" t="str">
+      <c r="I150" t="str">
         <v>ML G1</v>
       </c>
-      <c r="I150" t="str">
-        <v/>
-      </c>
       <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K150" t="str">
+      <c r="L150" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L150" t="str">
+      <c r="M150" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M150" t="str">
+      <c r="N150" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N150" t="str">
+      <c r="O150" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7035,30 +7486,33 @@
         <v>2</v>
       </c>
       <c r="F151" t="str">
+        <v>file</v>
+      </c>
+      <c r="G151" t="str">
         <v>TG2</v>
       </c>
-      <c r="G151" t="str">
+      <c r="H151" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H151" t="str">
+      <c r="I151" t="str">
         <v>TL G2</v>
       </c>
-      <c r="I151" t="str">
-        <v/>
-      </c>
       <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K151" t="str">
+      <c r="L151" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L151" t="str">
+      <c r="M151" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M151" t="str">
+      <c r="N151" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N151" t="str">
+      <c r="O151" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7079,30 +7533,33 @@
         <v>3</v>
       </c>
       <c r="F152" t="str">
+        <v>file</v>
+      </c>
+      <c r="G152" t="str">
         <v>TG1</v>
       </c>
-      <c r="G152" t="str">
+      <c r="H152" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H152" t="str">
+      <c r="I152" t="str">
         <v>CL G3</v>
       </c>
-      <c r="I152" t="str">
-        <v/>
-      </c>
       <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K152" t="str">
+      <c r="L152" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L152" t="str">
+      <c r="M152" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M152" t="str">
+      <c r="N152" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N152" t="str">
+      <c r="O152" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7123,30 +7580,33 @@
         <v>3</v>
       </c>
       <c r="F153" t="str">
+        <v>file</v>
+      </c>
+      <c r="G153" t="str">
         <v>TG2</v>
       </c>
-      <c r="G153" t="str">
+      <c r="H153" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H153" t="str">
+      <c r="I153" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I153" t="str">
-        <v/>
-      </c>
       <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K153" t="str">
+      <c r="L153" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L153" t="str">
+      <c r="M153" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M153" t="str">
+      <c r="N153" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N153" t="str">
+      <c r="O153" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7167,30 +7627,33 @@
         <v>1</v>
       </c>
       <c r="F154" t="str">
+        <v>file</v>
+      </c>
+      <c r="G154" t="str">
         <v>TG1</v>
       </c>
-      <c r="G154" t="str">
+      <c r="H154" t="str">
         <v>EL G1</v>
       </c>
-      <c r="H154" t="str">
+      <c r="I154" t="str">
         <v>TL G1</v>
       </c>
-      <c r="I154" t="str">
-        <v/>
-      </c>
       <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
         <v>MA G1</v>
       </c>
-      <c r="K154" t="str">
+      <c r="L154" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="L154" t="str">
+      <c r="M154" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="M154" t="str">
+      <c r="N154" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="N154" t="str">
+      <c r="O154" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7211,30 +7674,33 @@
         <v>2</v>
       </c>
       <c r="F155" t="str">
+        <v>file</v>
+      </c>
+      <c r="G155" t="str">
         <v>TG2</v>
       </c>
-      <c r="G155" t="str">
+      <c r="H155" t="str">
         <v>EL G2</v>
       </c>
-      <c r="H155" t="str">
+      <c r="I155" t="str">
         <v>CL G2</v>
       </c>
-      <c r="I155" t="str">
-        <v/>
-      </c>
       <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
         <v>MA G2</v>
       </c>
-      <c r="K155" t="str">
+      <c r="L155" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="L155" t="str">
+      <c r="M155" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="M155" t="str">
+      <c r="N155" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="N155" t="str">
+      <c r="O155" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7255,30 +7721,33 @@
         <v>3</v>
       </c>
       <c r="F156" t="str">
+        <v>file</v>
+      </c>
+      <c r="G156" t="str">
         <v>TG1</v>
       </c>
-      <c r="G156" t="str">
+      <c r="H156" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H156" t="str">
+      <c r="I156" t="str">
         <v>ML G3</v>
       </c>
-      <c r="I156" t="str">
+      <c r="J156" t="str">
         <v>MALAY</v>
       </c>
-      <c r="J156" t="str">
+      <c r="K156" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K156" t="str">
+      <c r="L156" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L156" t="str">
+      <c r="M156" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7299,36 +7768,39 @@
         <v>3</v>
       </c>
       <c r="F157" t="str">
+        <v>file</v>
+      </c>
+      <c r="G157" t="str">
         <v>TG2</v>
       </c>
-      <c r="G157" t="str">
+      <c r="H157" t="str">
         <v>EL G3</v>
       </c>
-      <c r="H157" t="str">
+      <c r="I157" t="str">
         <v>TL G3</v>
       </c>
-      <c r="I157" t="str">
-        <v/>
-      </c>
       <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
         <v>MA G3</v>
       </c>
-      <c r="K157" t="str">
+      <c r="L157" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="L157" t="str">
+      <c r="M157" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="M157" t="str">
+      <c r="N157" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="N157" t="str">
+      <c r="O157" t="str">
         <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O157"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -12921,12 +12921,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="22.83203125" customWidth="1"/>
+    <col min="2" max="2" width="42.83203125" customWidth="1"/>
+    <col min="3" max="3" width="30.83203125" customWidth="1"/>
+    <col min="4" max="4" width="42.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12934,12 +12935,15 @@
         <v>Level</v>
       </c>
       <c r="B1" t="str">
+        <v>SourceFile</v>
+      </c>
+      <c r="C1" t="str">
         <v>FilePattern</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>LastFile</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>LastImported</v>
       </c>
     </row>
@@ -12948,18 +12952,21 @@
         <v>Sec 1</v>
       </c>
       <c r="B2" t="str">
+        <v>Sec 1 Subject Allocation_14 Jan.xlsx</v>
+      </c>
+      <c r="C2" t="str">
         <v>Sec 1 Subject Allocation</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
       <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -400,15 +400,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O157"/>
+  <dimension ref="A1:P157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" customWidth="1"/>
-    <col min="6" max="6" width="8.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
@@ -417,6 +417,7 @@
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -430,39 +431,42 @@
         <v>Class</v>
       </c>
       <c r="D1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="E1" t="str">
         <v>Gender</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>PG</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>Origin</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>TG</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>EL</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>MT</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>HMT</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>MA</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>SCI</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>HIST</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>GEOG</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>LIT</v>
       </c>
     </row>
@@ -477,39 +481,42 @@
         <v>1R1</v>
       </c>
       <c r="D2" t="str">
+        <v>1</v>
+      </c>
+      <c r="E2" t="str">
         <v>F</v>
       </c>
-      <c r="E2" t="str">
-        <v>1</v>
-      </c>
       <c r="F2" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G2" t="str">
+        <v>file</v>
+      </c>
+      <c r="H2" t="str">
         <v>TG1</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -524,39 +531,42 @@
         <v>1R1</v>
       </c>
       <c r="D3" t="str">
+        <v>1</v>
+      </c>
+      <c r="E3" t="str">
         <v>M</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>2</v>
       </c>
-      <c r="F3" t="str">
-        <v>file</v>
-      </c>
       <c r="G3" t="str">
+        <v>file</v>
+      </c>
+      <c r="H3" t="str">
         <v>TG2</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -571,39 +581,42 @@
         <v>1R1</v>
       </c>
       <c r="D4" t="str">
+        <v>1</v>
+      </c>
+      <c r="E4" t="str">
         <v>F</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>3</v>
       </c>
-      <c r="F4" t="str">
-        <v>file</v>
-      </c>
       <c r="G4" t="str">
+        <v>file</v>
+      </c>
+      <c r="H4" t="str">
         <v>TG1</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -618,39 +631,42 @@
         <v>1R1</v>
       </c>
       <c r="D5" t="str">
+        <v>1</v>
+      </c>
+      <c r="E5" t="str">
         <v>M</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>3</v>
       </c>
-      <c r="F5" t="str">
-        <v>file</v>
-      </c>
       <c r="G5" t="str">
+        <v>file</v>
+      </c>
+      <c r="H5" t="str">
         <v>TG2</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -665,39 +681,42 @@
         <v>1R1</v>
       </c>
       <c r="D6" t="str">
+        <v>1</v>
+      </c>
+      <c r="E6" t="str">
         <v>F</v>
       </c>
-      <c r="E6" t="str">
-        <v>1</v>
-      </c>
       <c r="F6" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G6" t="str">
+        <v>file</v>
+      </c>
+      <c r="H6" t="str">
         <v>TG1</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -712,39 +731,42 @@
         <v>1R1</v>
       </c>
       <c r="D7" t="str">
+        <v>1</v>
+      </c>
+      <c r="E7" t="str">
         <v>M</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>2</v>
       </c>
-      <c r="F7" t="str">
-        <v>file</v>
-      </c>
       <c r="G7" t="str">
+        <v>file</v>
+      </c>
+      <c r="H7" t="str">
         <v>TG2</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -759,39 +781,42 @@
         <v>1R1</v>
       </c>
       <c r="D8" t="str">
+        <v>1</v>
+      </c>
+      <c r="E8" t="str">
         <v>F</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
         <v>3</v>
       </c>
-      <c r="F8" t="str">
-        <v>file</v>
-      </c>
       <c r="G8" t="str">
+        <v>file</v>
+      </c>
+      <c r="H8" t="str">
         <v>TG1</v>
       </c>
-      <c r="H8" t="str">
+      <c r="I8" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -806,39 +831,42 @@
         <v>1R1</v>
       </c>
       <c r="D9" t="str">
+        <v>1</v>
+      </c>
+      <c r="E9" t="str">
         <v>M</v>
       </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
         <v>3</v>
       </c>
-      <c r="F9" t="str">
-        <v>file</v>
-      </c>
       <c r="G9" t="str">
+        <v>file</v>
+      </c>
+      <c r="H9" t="str">
         <v>TG2</v>
       </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -853,39 +881,42 @@
         <v>1R1</v>
       </c>
       <c r="D10" t="str">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
         <v>F</v>
       </c>
-      <c r="E10" t="str">
-        <v>1</v>
-      </c>
       <c r="F10" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G10" t="str">
+        <v>file</v>
+      </c>
+      <c r="H10" t="str">
         <v>TG1</v>
       </c>
-      <c r="H10" t="str">
+      <c r="I10" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -900,39 +931,42 @@
         <v>1R1</v>
       </c>
       <c r="D11" t="str">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
         <v>M</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
         <v>2</v>
       </c>
-      <c r="F11" t="str">
-        <v>file</v>
-      </c>
       <c r="G11" t="str">
+        <v>file</v>
+      </c>
+      <c r="H11" t="str">
         <v>TG2</v>
       </c>
-      <c r="H11" t="str">
+      <c r="I11" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -947,39 +981,42 @@
         <v>1R1</v>
       </c>
       <c r="D12" t="str">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
         <v>F</v>
       </c>
-      <c r="E12" t="str">
+      <c r="F12" t="str">
         <v>3</v>
       </c>
-      <c r="F12" t="str">
-        <v>file</v>
-      </c>
       <c r="G12" t="str">
+        <v>file</v>
+      </c>
+      <c r="H12" t="str">
         <v>TG1</v>
       </c>
-      <c r="H12" t="str">
+      <c r="I12" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -994,39 +1031,42 @@
         <v>1R1</v>
       </c>
       <c r="D13" t="str">
+        <v>1</v>
+      </c>
+      <c r="E13" t="str">
         <v>M</v>
       </c>
-      <c r="E13" t="str">
+      <c r="F13" t="str">
         <v>3</v>
       </c>
-      <c r="F13" t="str">
-        <v>file</v>
-      </c>
       <c r="G13" t="str">
+        <v>file</v>
+      </c>
+      <c r="H13" t="str">
         <v>TG2</v>
       </c>
-      <c r="H13" t="str">
+      <c r="I13" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1041,39 +1081,42 @@
         <v>1R1</v>
       </c>
       <c r="D14" t="str">
+        <v>1</v>
+      </c>
+      <c r="E14" t="str">
         <v>F</v>
       </c>
-      <c r="E14" t="str">
-        <v>1</v>
-      </c>
       <c r="F14" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G14" t="str">
+        <v>file</v>
+      </c>
+      <c r="H14" t="str">
         <v>TG1</v>
       </c>
-      <c r="H14" t="str">
+      <c r="I14" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1088,39 +1131,42 @@
         <v>1R1</v>
       </c>
       <c r="D15" t="str">
+        <v>1</v>
+      </c>
+      <c r="E15" t="str">
         <v>M</v>
       </c>
-      <c r="E15" t="str">
+      <c r="F15" t="str">
         <v>2</v>
       </c>
-      <c r="F15" t="str">
-        <v>file</v>
-      </c>
       <c r="G15" t="str">
+        <v>file</v>
+      </c>
+      <c r="H15" t="str">
         <v>TG2</v>
       </c>
-      <c r="H15" t="str">
+      <c r="I15" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1135,39 +1181,42 @@
         <v>1R1</v>
       </c>
       <c r="D16" t="str">
+        <v>1</v>
+      </c>
+      <c r="E16" t="str">
         <v>F</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>3</v>
       </c>
-      <c r="F16" t="str">
-        <v>file</v>
-      </c>
       <c r="G16" t="str">
+        <v>file</v>
+      </c>
+      <c r="H16" t="str">
         <v>TG1</v>
       </c>
-      <c r="H16" t="str">
+      <c r="I16" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1182,39 +1231,42 @@
         <v>1R1</v>
       </c>
       <c r="D17" t="str">
+        <v>1</v>
+      </c>
+      <c r="E17" t="str">
         <v>M</v>
       </c>
-      <c r="E17" t="str">
+      <c r="F17" t="str">
         <v>3</v>
       </c>
-      <c r="F17" t="str">
-        <v>file</v>
-      </c>
       <c r="G17" t="str">
+        <v>file</v>
+      </c>
+      <c r="H17" t="str">
         <v>TG2</v>
       </c>
-      <c r="H17" t="str">
+      <c r="I17" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1229,39 +1281,42 @@
         <v>1R1</v>
       </c>
       <c r="D18" t="str">
+        <v>1</v>
+      </c>
+      <c r="E18" t="str">
         <v>F</v>
       </c>
-      <c r="E18" t="str">
-        <v>1</v>
-      </c>
       <c r="F18" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G18" t="str">
+        <v>file</v>
+      </c>
+      <c r="H18" t="str">
         <v>TG1</v>
       </c>
-      <c r="H18" t="str">
+      <c r="I18" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1276,39 +1331,42 @@
         <v>1R1</v>
       </c>
       <c r="D19" t="str">
+        <v>1</v>
+      </c>
+      <c r="E19" t="str">
         <v>M</v>
       </c>
-      <c r="E19" t="str">
+      <c r="F19" t="str">
         <v>2</v>
       </c>
-      <c r="F19" t="str">
-        <v>file</v>
-      </c>
       <c r="G19" t="str">
+        <v>file</v>
+      </c>
+      <c r="H19" t="str">
         <v>TG2</v>
       </c>
-      <c r="H19" t="str">
+      <c r="I19" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1323,39 +1381,42 @@
         <v>1R1</v>
       </c>
       <c r="D20" t="str">
+        <v>1</v>
+      </c>
+      <c r="E20" t="str">
         <v>F</v>
       </c>
-      <c r="E20" t="str">
+      <c r="F20" t="str">
         <v>3</v>
       </c>
-      <c r="F20" t="str">
-        <v>file</v>
-      </c>
       <c r="G20" t="str">
+        <v>file</v>
+      </c>
+      <c r="H20" t="str">
         <v>TG1</v>
       </c>
-      <c r="H20" t="str">
+      <c r="I20" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1370,39 +1431,42 @@
         <v>1R1</v>
       </c>
       <c r="D21" t="str">
+        <v>1</v>
+      </c>
+      <c r="E21" t="str">
         <v>M</v>
       </c>
-      <c r="E21" t="str">
+      <c r="F21" t="str">
         <v>3</v>
       </c>
-      <c r="F21" t="str">
-        <v>file</v>
-      </c>
       <c r="G21" t="str">
+        <v>file</v>
+      </c>
+      <c r="H21" t="str">
         <v>TG2</v>
       </c>
-      <c r="H21" t="str">
+      <c r="I21" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1417,39 +1481,42 @@
         <v>1R1</v>
       </c>
       <c r="D22" t="str">
+        <v>1</v>
+      </c>
+      <c r="E22" t="str">
         <v>F</v>
       </c>
-      <c r="E22" t="str">
-        <v>1</v>
-      </c>
       <c r="F22" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G22" t="str">
+        <v>file</v>
+      </c>
+      <c r="H22" t="str">
         <v>TG1</v>
       </c>
-      <c r="H22" t="str">
+      <c r="I22" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1464,39 +1531,42 @@
         <v>1R1</v>
       </c>
       <c r="D23" t="str">
+        <v>1</v>
+      </c>
+      <c r="E23" t="str">
         <v>M</v>
       </c>
-      <c r="E23" t="str">
+      <c r="F23" t="str">
         <v>2</v>
       </c>
-      <c r="F23" t="str">
-        <v>file</v>
-      </c>
       <c r="G23" t="str">
+        <v>file</v>
+      </c>
+      <c r="H23" t="str">
         <v>TG2</v>
       </c>
-      <c r="H23" t="str">
+      <c r="I23" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1511,39 +1581,42 @@
         <v>1R1</v>
       </c>
       <c r="D24" t="str">
+        <v>1</v>
+      </c>
+      <c r="E24" t="str">
         <v>F</v>
       </c>
-      <c r="E24" t="str">
+      <c r="F24" t="str">
         <v>3</v>
       </c>
-      <c r="F24" t="str">
-        <v>file</v>
-      </c>
       <c r="G24" t="str">
+        <v>file</v>
+      </c>
+      <c r="H24" t="str">
         <v>TG1</v>
       </c>
-      <c r="H24" t="str">
+      <c r="I24" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J24" t="str">
-        <v/>
-      </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1558,39 +1631,42 @@
         <v>1R1</v>
       </c>
       <c r="D25" t="str">
+        <v>1</v>
+      </c>
+      <c r="E25" t="str">
         <v>M</v>
       </c>
-      <c r="E25" t="str">
+      <c r="F25" t="str">
         <v>3</v>
       </c>
-      <c r="F25" t="str">
-        <v>file</v>
-      </c>
       <c r="G25" t="str">
+        <v>file</v>
+      </c>
+      <c r="H25" t="str">
         <v>TG2</v>
       </c>
-      <c r="H25" t="str">
+      <c r="I25" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J25" t="str">
-        <v/>
-      </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1605,39 +1681,42 @@
         <v>1R1</v>
       </c>
       <c r="D26" t="str">
+        <v>1</v>
+      </c>
+      <c r="E26" t="str">
         <v>F</v>
       </c>
-      <c r="E26" t="str">
-        <v>1</v>
-      </c>
       <c r="F26" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G26" t="str">
+        <v>file</v>
+      </c>
+      <c r="H26" t="str">
         <v>TG1</v>
       </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J26" t="str">
-        <v/>
-      </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1652,39 +1731,42 @@
         <v>1R1</v>
       </c>
       <c r="D27" t="str">
+        <v>1</v>
+      </c>
+      <c r="E27" t="str">
         <v>M</v>
       </c>
-      <c r="E27" t="str">
+      <c r="F27" t="str">
         <v>2</v>
       </c>
-      <c r="F27" t="str">
-        <v>file</v>
-      </c>
       <c r="G27" t="str">
+        <v>file</v>
+      </c>
+      <c r="H27" t="str">
         <v>TG2</v>
       </c>
-      <c r="H27" t="str">
+      <c r="I27" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J27" t="str">
-        <v/>
-      </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1699,39 +1781,42 @@
         <v>1R2</v>
       </c>
       <c r="D28" t="str">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
         <v>F</v>
       </c>
-      <c r="E28" t="str">
+      <c r="F28" t="str">
         <v>3</v>
       </c>
-      <c r="F28" t="str">
-        <v>file</v>
-      </c>
       <c r="G28" t="str">
+        <v>file</v>
+      </c>
+      <c r="H28" t="str">
         <v>TG1</v>
       </c>
-      <c r="H28" t="str">
+      <c r="I28" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J28" t="str">
-        <v/>
-      </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1746,39 +1831,42 @@
         <v>1R2</v>
       </c>
       <c r="D29" t="str">
+        <v>1</v>
+      </c>
+      <c r="E29" t="str">
         <v>M</v>
       </c>
-      <c r="E29" t="str">
+      <c r="F29" t="str">
         <v>3</v>
       </c>
-      <c r="F29" t="str">
-        <v>file</v>
-      </c>
       <c r="G29" t="str">
+        <v>file</v>
+      </c>
+      <c r="H29" t="str">
         <v>TG2</v>
       </c>
-      <c r="H29" t="str">
+      <c r="I29" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J29" t="str">
-        <v/>
-      </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1793,39 +1881,42 @@
         <v>1R2</v>
       </c>
       <c r="D30" t="str">
+        <v>1</v>
+      </c>
+      <c r="E30" t="str">
         <v>F</v>
       </c>
-      <c r="E30" t="str">
-        <v>1</v>
-      </c>
       <c r="F30" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G30" t="str">
+        <v>file</v>
+      </c>
+      <c r="H30" t="str">
         <v>TG1</v>
       </c>
-      <c r="H30" t="str">
+      <c r="I30" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1840,39 +1931,42 @@
         <v>1R2</v>
       </c>
       <c r="D31" t="str">
+        <v>1</v>
+      </c>
+      <c r="E31" t="str">
         <v>M</v>
       </c>
-      <c r="E31" t="str">
+      <c r="F31" t="str">
         <v>2</v>
       </c>
-      <c r="F31" t="str">
-        <v>file</v>
-      </c>
       <c r="G31" t="str">
+        <v>file</v>
+      </c>
+      <c r="H31" t="str">
         <v>TG2</v>
       </c>
-      <c r="H31" t="str">
+      <c r="I31" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J31" t="str">
-        <v/>
-      </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1887,39 +1981,42 @@
         <v>1R2</v>
       </c>
       <c r="D32" t="str">
+        <v>1</v>
+      </c>
+      <c r="E32" t="str">
         <v>F</v>
       </c>
-      <c r="E32" t="str">
+      <c r="F32" t="str">
         <v>3</v>
       </c>
-      <c r="F32" t="str">
-        <v>file</v>
-      </c>
       <c r="G32" t="str">
+        <v>file</v>
+      </c>
+      <c r="H32" t="str">
         <v>TG1</v>
       </c>
-      <c r="H32" t="str">
+      <c r="I32" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J32" t="str">
-        <v/>
-      </c>
       <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L32" t="str">
+      <c r="M32" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1934,39 +2031,42 @@
         <v>1R2</v>
       </c>
       <c r="D33" t="str">
+        <v>1</v>
+      </c>
+      <c r="E33" t="str">
         <v>M</v>
       </c>
-      <c r="E33" t="str">
+      <c r="F33" t="str">
         <v>3</v>
       </c>
-      <c r="F33" t="str">
-        <v>file</v>
-      </c>
       <c r="G33" t="str">
+        <v>file</v>
+      </c>
+      <c r="H33" t="str">
         <v>TG2</v>
       </c>
-      <c r="H33" t="str">
+      <c r="I33" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I33" t="str">
+      <c r="J33" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J33" t="str">
-        <v/>
-      </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1981,39 +2081,42 @@
         <v>1R2</v>
       </c>
       <c r="D34" t="str">
+        <v>1</v>
+      </c>
+      <c r="E34" t="str">
         <v>F</v>
       </c>
-      <c r="E34" t="str">
-        <v>1</v>
-      </c>
       <c r="F34" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G34" t="str">
+        <v>file</v>
+      </c>
+      <c r="H34" t="str">
         <v>TG1</v>
       </c>
-      <c r="H34" t="str">
+      <c r="I34" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I34" t="str">
+      <c r="J34" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J34" t="str">
-        <v/>
-      </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2028,39 +2131,42 @@
         <v>1R2</v>
       </c>
       <c r="D35" t="str">
+        <v>1</v>
+      </c>
+      <c r="E35" t="str">
         <v>M</v>
       </c>
-      <c r="E35" t="str">
+      <c r="F35" t="str">
         <v>2</v>
       </c>
-      <c r="F35" t="str">
-        <v>file</v>
-      </c>
       <c r="G35" t="str">
+        <v>file</v>
+      </c>
+      <c r="H35" t="str">
         <v>TG2</v>
       </c>
-      <c r="H35" t="str">
+      <c r="I35" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J35" t="str">
-        <v/>
-      </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L35" t="str">
+      <c r="M35" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2075,39 +2181,42 @@
         <v>1R2</v>
       </c>
       <c r="D36" t="str">
+        <v>1</v>
+      </c>
+      <c r="E36" t="str">
         <v>F</v>
       </c>
-      <c r="E36" t="str">
+      <c r="F36" t="str">
         <v>3</v>
       </c>
-      <c r="F36" t="str">
-        <v>file</v>
-      </c>
       <c r="G36" t="str">
+        <v>file</v>
+      </c>
+      <c r="H36" t="str">
         <v>TG1</v>
       </c>
-      <c r="H36" t="str">
+      <c r="I36" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I36" t="str">
+      <c r="J36" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J36" t="str">
-        <v/>
-      </c>
       <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L36" t="str">
+      <c r="M36" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2122,39 +2231,42 @@
         <v>1R2</v>
       </c>
       <c r="D37" t="str">
+        <v>1</v>
+      </c>
+      <c r="E37" t="str">
         <v>M</v>
       </c>
-      <c r="E37" t="str">
+      <c r="F37" t="str">
         <v>3</v>
       </c>
-      <c r="F37" t="str">
-        <v>file</v>
-      </c>
       <c r="G37" t="str">
+        <v>file</v>
+      </c>
+      <c r="H37" t="str">
         <v>TG2</v>
       </c>
-      <c r="H37" t="str">
+      <c r="I37" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J37" t="str">
+      <c r="K37" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2169,39 +2281,42 @@
         <v>1R2</v>
       </c>
       <c r="D38" t="str">
+        <v>1</v>
+      </c>
+      <c r="E38" t="str">
         <v>F</v>
       </c>
-      <c r="E38" t="str">
-        <v>1</v>
-      </c>
       <c r="F38" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G38" t="str">
+        <v>file</v>
+      </c>
+      <c r="H38" t="str">
         <v>TG1</v>
       </c>
-      <c r="H38" t="str">
+      <c r="I38" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I38" t="str">
+      <c r="J38" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J38" t="str">
-        <v/>
-      </c>
       <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2216,39 +2331,42 @@
         <v>1R2</v>
       </c>
       <c r="D39" t="str">
+        <v>1</v>
+      </c>
+      <c r="E39" t="str">
         <v>M</v>
       </c>
-      <c r="E39" t="str">
+      <c r="F39" t="str">
         <v>2</v>
       </c>
-      <c r="F39" t="str">
-        <v>file</v>
-      </c>
       <c r="G39" t="str">
+        <v>file</v>
+      </c>
+      <c r="H39" t="str">
         <v>TG2</v>
       </c>
-      <c r="H39" t="str">
+      <c r="I39" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I39" t="str">
+      <c r="J39" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J39" t="str">
-        <v/>
-      </c>
       <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2263,39 +2381,42 @@
         <v>1R2</v>
       </c>
       <c r="D40" t="str">
+        <v>1</v>
+      </c>
+      <c r="E40" t="str">
         <v>F</v>
       </c>
-      <c r="E40" t="str">
+      <c r="F40" t="str">
         <v>3</v>
       </c>
-      <c r="F40" t="str">
-        <v>file</v>
-      </c>
       <c r="G40" t="str">
+        <v>file</v>
+      </c>
+      <c r="H40" t="str">
         <v>TG1</v>
       </c>
-      <c r="H40" t="str">
+      <c r="I40" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J40" t="str">
-        <v/>
-      </c>
       <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2310,39 +2431,42 @@
         <v>1R2</v>
       </c>
       <c r="D41" t="str">
+        <v>1</v>
+      </c>
+      <c r="E41" t="str">
         <v>M</v>
       </c>
-      <c r="E41" t="str">
+      <c r="F41" t="str">
         <v>3</v>
       </c>
-      <c r="F41" t="str">
-        <v>file</v>
-      </c>
       <c r="G41" t="str">
+        <v>file</v>
+      </c>
+      <c r="H41" t="str">
         <v>TG2</v>
       </c>
-      <c r="H41" t="str">
+      <c r="I41" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J41" t="str">
-        <v/>
-      </c>
       <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2357,39 +2481,42 @@
         <v>1R2</v>
       </c>
       <c r="D42" t="str">
+        <v>1</v>
+      </c>
+      <c r="E42" t="str">
         <v>F</v>
       </c>
-      <c r="E42" t="str">
-        <v>1</v>
-      </c>
       <c r="F42" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G42" t="str">
+        <v>file</v>
+      </c>
+      <c r="H42" t="str">
         <v>TG1</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I42" t="str">
+      <c r="J42" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J42" t="str">
-        <v/>
-      </c>
       <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2404,39 +2531,42 @@
         <v>1R2</v>
       </c>
       <c r="D43" t="str">
+        <v>1</v>
+      </c>
+      <c r="E43" t="str">
         <v>M</v>
       </c>
-      <c r="E43" t="str">
+      <c r="F43" t="str">
         <v>2</v>
       </c>
-      <c r="F43" t="str">
-        <v>file</v>
-      </c>
       <c r="G43" t="str">
+        <v>file</v>
+      </c>
+      <c r="H43" t="str">
         <v>TG2</v>
       </c>
-      <c r="H43" t="str">
+      <c r="I43" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I43" t="str">
+      <c r="J43" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J43" t="str">
-        <v/>
-      </c>
       <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2451,39 +2581,42 @@
         <v>1R2</v>
       </c>
       <c r="D44" t="str">
+        <v>1</v>
+      </c>
+      <c r="E44" t="str">
         <v>F</v>
       </c>
-      <c r="E44" t="str">
+      <c r="F44" t="str">
         <v>3</v>
       </c>
-      <c r="F44" t="str">
-        <v>file</v>
-      </c>
       <c r="G44" t="str">
+        <v>file</v>
+      </c>
+      <c r="H44" t="str">
         <v>TG1</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2498,39 +2631,42 @@
         <v>1R2</v>
       </c>
       <c r="D45" t="str">
+        <v>1</v>
+      </c>
+      <c r="E45" t="str">
         <v>M</v>
       </c>
-      <c r="E45" t="str">
+      <c r="F45" t="str">
         <v>3</v>
       </c>
-      <c r="F45" t="str">
-        <v>file</v>
-      </c>
       <c r="G45" t="str">
+        <v>file</v>
+      </c>
+      <c r="H45" t="str">
         <v>TG2</v>
       </c>
-      <c r="H45" t="str">
+      <c r="I45" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I45" t="str">
+      <c r="J45" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J45" t="str">
-        <v/>
-      </c>
       <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L45" t="str">
+      <c r="M45" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2545,39 +2681,42 @@
         <v>1R2</v>
       </c>
       <c r="D46" t="str">
+        <v>1</v>
+      </c>
+      <c r="E46" t="str">
         <v>F</v>
       </c>
-      <c r="E46" t="str">
-        <v>1</v>
-      </c>
       <c r="F46" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G46" t="str">
+        <v>file</v>
+      </c>
+      <c r="H46" t="str">
         <v>TG1</v>
       </c>
-      <c r="H46" t="str">
+      <c r="I46" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J46" t="str">
-        <v/>
-      </c>
       <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2592,39 +2731,42 @@
         <v>1R2</v>
       </c>
       <c r="D47" t="str">
+        <v>1</v>
+      </c>
+      <c r="E47" t="str">
         <v>M</v>
       </c>
-      <c r="E47" t="str">
+      <c r="F47" t="str">
         <v>2</v>
       </c>
-      <c r="F47" t="str">
-        <v>file</v>
-      </c>
       <c r="G47" t="str">
+        <v>file</v>
+      </c>
+      <c r="H47" t="str">
         <v>TG2</v>
       </c>
-      <c r="H47" t="str">
+      <c r="I47" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I47" t="str">
+      <c r="J47" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J47" t="str">
-        <v/>
-      </c>
       <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2639,39 +2781,42 @@
         <v>1R2</v>
       </c>
       <c r="D48" t="str">
+        <v>1</v>
+      </c>
+      <c r="E48" t="str">
         <v>F</v>
       </c>
-      <c r="E48" t="str">
+      <c r="F48" t="str">
         <v>3</v>
       </c>
-      <c r="F48" t="str">
-        <v>file</v>
-      </c>
       <c r="G48" t="str">
+        <v>file</v>
+      </c>
+      <c r="H48" t="str">
         <v>TG1</v>
       </c>
-      <c r="H48" t="str">
+      <c r="I48" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I48" t="str">
+      <c r="J48" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J48" t="str">
-        <v/>
-      </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2686,39 +2831,42 @@
         <v>1R2</v>
       </c>
       <c r="D49" t="str">
+        <v>1</v>
+      </c>
+      <c r="E49" t="str">
         <v>M</v>
       </c>
-      <c r="E49" t="str">
+      <c r="F49" t="str">
         <v>3</v>
       </c>
-      <c r="F49" t="str">
-        <v>file</v>
-      </c>
       <c r="G49" t="str">
+        <v>file</v>
+      </c>
+      <c r="H49" t="str">
         <v>TG2</v>
       </c>
-      <c r="H49" t="str">
+      <c r="I49" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I49" t="str">
+      <c r="J49" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J49" t="str">
-        <v/>
-      </c>
       <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2733,39 +2881,42 @@
         <v>1R2</v>
       </c>
       <c r="D50" t="str">
+        <v>1</v>
+      </c>
+      <c r="E50" t="str">
         <v>F</v>
       </c>
-      <c r="E50" t="str">
-        <v>1</v>
-      </c>
       <c r="F50" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G50" t="str">
+        <v>file</v>
+      </c>
+      <c r="H50" t="str">
         <v>TG1</v>
       </c>
-      <c r="H50" t="str">
+      <c r="I50" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I50" t="str">
+      <c r="J50" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
       <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2780,39 +2931,42 @@
         <v>1R2</v>
       </c>
       <c r="D51" t="str">
+        <v>1</v>
+      </c>
+      <c r="E51" t="str">
         <v>M</v>
       </c>
-      <c r="E51" t="str">
+      <c r="F51" t="str">
         <v>2</v>
       </c>
-      <c r="F51" t="str">
-        <v>file</v>
-      </c>
       <c r="G51" t="str">
+        <v>file</v>
+      </c>
+      <c r="H51" t="str">
         <v>TG2</v>
       </c>
-      <c r="H51" t="str">
+      <c r="I51" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2827,39 +2981,42 @@
         <v>1R2</v>
       </c>
       <c r="D52" t="str">
+        <v>1</v>
+      </c>
+      <c r="E52" t="str">
         <v>F</v>
       </c>
-      <c r="E52" t="str">
+      <c r="F52" t="str">
         <v>3</v>
       </c>
-      <c r="F52" t="str">
-        <v>file</v>
-      </c>
       <c r="G52" t="str">
+        <v>file</v>
+      </c>
+      <c r="H52" t="str">
         <v>TG1</v>
       </c>
-      <c r="H52" t="str">
+      <c r="I52" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I52" t="str">
+      <c r="J52" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J52" t="str">
-        <v/>
-      </c>
       <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L52" t="str">
+      <c r="M52" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2874,39 +3031,42 @@
         <v>1R2</v>
       </c>
       <c r="D53" t="str">
+        <v>1</v>
+      </c>
+      <c r="E53" t="str">
         <v>M</v>
       </c>
-      <c r="E53" t="str">
+      <c r="F53" t="str">
         <v>3</v>
       </c>
-      <c r="F53" t="str">
-        <v>file</v>
-      </c>
       <c r="G53" t="str">
+        <v>file</v>
+      </c>
+      <c r="H53" t="str">
         <v>TG2</v>
       </c>
-      <c r="H53" t="str">
+      <c r="I53" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I53" t="str">
+      <c r="J53" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J53" t="str">
-        <v/>
-      </c>
       <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L53" t="str">
+      <c r="M53" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2921,39 +3081,42 @@
         <v>1R3</v>
       </c>
       <c r="D54" t="str">
+        <v>1</v>
+      </c>
+      <c r="E54" t="str">
         <v>F</v>
       </c>
-      <c r="E54" t="str">
-        <v>1</v>
-      </c>
       <c r="F54" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G54" t="str">
+        <v>file</v>
+      </c>
+      <c r="H54" t="str">
         <v>TG1</v>
       </c>
-      <c r="H54" t="str">
+      <c r="I54" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I54" t="str">
+      <c r="J54" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J54" t="str">
-        <v/>
-      </c>
       <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L54" t="str">
+      <c r="M54" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2968,39 +3131,42 @@
         <v>1R3</v>
       </c>
       <c r="D55" t="str">
+        <v>1</v>
+      </c>
+      <c r="E55" t="str">
         <v>M</v>
       </c>
-      <c r="E55" t="str">
+      <c r="F55" t="str">
         <v>2</v>
       </c>
-      <c r="F55" t="str">
-        <v>file</v>
-      </c>
       <c r="G55" t="str">
+        <v>file</v>
+      </c>
+      <c r="H55" t="str">
         <v>TG2</v>
       </c>
-      <c r="H55" t="str">
+      <c r="I55" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I55" t="str">
+      <c r="J55" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J55" t="str">
-        <v/>
-      </c>
       <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3015,39 +3181,42 @@
         <v>1R3</v>
       </c>
       <c r="D56" t="str">
+        <v>1</v>
+      </c>
+      <c r="E56" t="str">
         <v>F</v>
       </c>
-      <c r="E56" t="str">
+      <c r="F56" t="str">
         <v>3</v>
       </c>
-      <c r="F56" t="str">
-        <v>file</v>
-      </c>
       <c r="G56" t="str">
+        <v>file</v>
+      </c>
+      <c r="H56" t="str">
         <v>TG1</v>
       </c>
-      <c r="H56" t="str">
+      <c r="I56" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I56" t="str">
+      <c r="J56" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J56" t="str">
-        <v/>
-      </c>
       <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3062,39 +3231,42 @@
         <v>1R3</v>
       </c>
       <c r="D57" t="str">
+        <v>1</v>
+      </c>
+      <c r="E57" t="str">
         <v>M</v>
       </c>
-      <c r="E57" t="str">
+      <c r="F57" t="str">
         <v>3</v>
       </c>
-      <c r="F57" t="str">
-        <v>file</v>
-      </c>
       <c r="G57" t="str">
+        <v>file</v>
+      </c>
+      <c r="H57" t="str">
         <v>TG2</v>
       </c>
-      <c r="H57" t="str">
+      <c r="I57" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I57" t="str">
+      <c r="J57" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J57" t="str">
-        <v/>
-      </c>
       <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3109,39 +3281,42 @@
         <v>1R3</v>
       </c>
       <c r="D58" t="str">
+        <v>1</v>
+      </c>
+      <c r="E58" t="str">
         <v>F</v>
       </c>
-      <c r="E58" t="str">
-        <v>1</v>
-      </c>
       <c r="F58" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G58" t="str">
+        <v>file</v>
+      </c>
+      <c r="H58" t="str">
         <v>TG1</v>
       </c>
-      <c r="H58" t="str">
+      <c r="I58" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I58" t="str">
+      <c r="J58" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3156,39 +3331,42 @@
         <v>1R3</v>
       </c>
       <c r="D59" t="str">
+        <v>1</v>
+      </c>
+      <c r="E59" t="str">
         <v>M</v>
       </c>
-      <c r="E59" t="str">
+      <c r="F59" t="str">
         <v>2</v>
       </c>
-      <c r="F59" t="str">
-        <v>file</v>
-      </c>
       <c r="G59" t="str">
+        <v>file</v>
+      </c>
+      <c r="H59" t="str">
         <v>TG2</v>
       </c>
-      <c r="H59" t="str">
+      <c r="I59" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I59" t="str">
+      <c r="J59" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J59" t="str">
-        <v/>
-      </c>
       <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3203,39 +3381,42 @@
         <v>1R3</v>
       </c>
       <c r="D60" t="str">
+        <v>1</v>
+      </c>
+      <c r="E60" t="str">
         <v>F</v>
       </c>
-      <c r="E60" t="str">
+      <c r="F60" t="str">
         <v>3</v>
       </c>
-      <c r="F60" t="str">
-        <v>file</v>
-      </c>
       <c r="G60" t="str">
+        <v>file</v>
+      </c>
+      <c r="H60" t="str">
         <v>TG1</v>
       </c>
-      <c r="H60" t="str">
+      <c r="I60" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I60" t="str">
+      <c r="J60" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J60" t="str">
-        <v/>
-      </c>
       <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3250,39 +3431,42 @@
         <v>1R3</v>
       </c>
       <c r="D61" t="str">
+        <v>1</v>
+      </c>
+      <c r="E61" t="str">
         <v>M</v>
       </c>
-      <c r="E61" t="str">
+      <c r="F61" t="str">
         <v>3</v>
       </c>
-      <c r="F61" t="str">
-        <v>file</v>
-      </c>
       <c r="G61" t="str">
+        <v>file</v>
+      </c>
+      <c r="H61" t="str">
         <v>TG2</v>
       </c>
-      <c r="H61" t="str">
+      <c r="I61" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I61" t="str">
+      <c r="J61" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J61" t="str">
-        <v/>
-      </c>
       <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L61" t="str">
+      <c r="M61" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3297,39 +3481,42 @@
         <v>1R3</v>
       </c>
       <c r="D62" t="str">
+        <v>1</v>
+      </c>
+      <c r="E62" t="str">
         <v>F</v>
       </c>
-      <c r="E62" t="str">
-        <v>1</v>
-      </c>
       <c r="F62" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G62" t="str">
+        <v>file</v>
+      </c>
+      <c r="H62" t="str">
         <v>TG1</v>
       </c>
-      <c r="H62" t="str">
+      <c r="I62" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I62" t="str">
+      <c r="J62" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J62" t="str">
-        <v/>
-      </c>
       <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L62" t="str">
+      <c r="M62" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3344,39 +3531,42 @@
         <v>1R3</v>
       </c>
       <c r="D63" t="str">
+        <v>1</v>
+      </c>
+      <c r="E63" t="str">
         <v>M</v>
       </c>
-      <c r="E63" t="str">
+      <c r="F63" t="str">
         <v>2</v>
       </c>
-      <c r="F63" t="str">
-        <v>file</v>
-      </c>
       <c r="G63" t="str">
+        <v>file</v>
+      </c>
+      <c r="H63" t="str">
         <v>TG2</v>
       </c>
-      <c r="H63" t="str">
+      <c r="I63" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I63" t="str">
+      <c r="J63" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J63" t="str">
-        <v/>
-      </c>
       <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L63" t="str">
+      <c r="M63" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3391,39 +3581,42 @@
         <v>1R3</v>
       </c>
       <c r="D64" t="str">
+        <v>1</v>
+      </c>
+      <c r="E64" t="str">
         <v>F</v>
       </c>
-      <c r="E64" t="str">
+      <c r="F64" t="str">
         <v>3</v>
       </c>
-      <c r="F64" t="str">
-        <v>file</v>
-      </c>
       <c r="G64" t="str">
+        <v>file</v>
+      </c>
+      <c r="H64" t="str">
         <v>TG1</v>
       </c>
-      <c r="H64" t="str">
+      <c r="I64" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I64" t="str">
+      <c r="J64" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J64" t="str">
-        <v/>
-      </c>
       <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L64" t="str">
+      <c r="M64" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3438,39 +3631,42 @@
         <v>1R3</v>
       </c>
       <c r="D65" t="str">
+        <v>1</v>
+      </c>
+      <c r="E65" t="str">
         <v>M</v>
       </c>
-      <c r="E65" t="str">
+      <c r="F65" t="str">
         <v>3</v>
       </c>
-      <c r="F65" t="str">
-        <v>file</v>
-      </c>
       <c r="G65" t="str">
+        <v>file</v>
+      </c>
+      <c r="H65" t="str">
         <v>TG2</v>
       </c>
-      <c r="H65" t="str">
+      <c r="I65" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I65" t="str">
+      <c r="J65" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3485,39 +3681,42 @@
         <v>1R3</v>
       </c>
       <c r="D66" t="str">
+        <v>1</v>
+      </c>
+      <c r="E66" t="str">
         <v>F</v>
       </c>
-      <c r="E66" t="str">
-        <v>1</v>
-      </c>
       <c r="F66" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G66" t="str">
+        <v>file</v>
+      </c>
+      <c r="H66" t="str">
         <v>TG1</v>
       </c>
-      <c r="H66" t="str">
+      <c r="I66" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I66" t="str">
+      <c r="J66" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J66" t="str">
-        <v/>
-      </c>
       <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L66" t="str">
+      <c r="M66" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M66" t="str">
+      <c r="N66" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3532,39 +3731,42 @@
         <v>1R3</v>
       </c>
       <c r="D67" t="str">
+        <v>1</v>
+      </c>
+      <c r="E67" t="str">
         <v>M</v>
       </c>
-      <c r="E67" t="str">
+      <c r="F67" t="str">
         <v>2</v>
       </c>
-      <c r="F67" t="str">
-        <v>file</v>
-      </c>
       <c r="G67" t="str">
+        <v>file</v>
+      </c>
+      <c r="H67" t="str">
         <v>TG2</v>
       </c>
-      <c r="H67" t="str">
+      <c r="I67" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I67" t="str">
+      <c r="J67" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J67" t="str">
-        <v/>
-      </c>
       <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L67" t="str">
+      <c r="M67" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M67" t="str">
+      <c r="N67" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N67" t="str">
+      <c r="O67" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3579,39 +3781,42 @@
         <v>1R3</v>
       </c>
       <c r="D68" t="str">
+        <v>1</v>
+      </c>
+      <c r="E68" t="str">
         <v>F</v>
       </c>
-      <c r="E68" t="str">
+      <c r="F68" t="str">
         <v>3</v>
       </c>
-      <c r="F68" t="str">
-        <v>file</v>
-      </c>
       <c r="G68" t="str">
+        <v>file</v>
+      </c>
+      <c r="H68" t="str">
         <v>TG1</v>
       </c>
-      <c r="H68" t="str">
+      <c r="I68" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I68" t="str">
+      <c r="J68" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J68" t="str">
-        <v/>
-      </c>
       <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L68" t="str">
+      <c r="M68" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M68" t="str">
+      <c r="N68" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3626,39 +3831,42 @@
         <v>1R3</v>
       </c>
       <c r="D69" t="str">
+        <v>1</v>
+      </c>
+      <c r="E69" t="str">
         <v>M</v>
       </c>
-      <c r="E69" t="str">
+      <c r="F69" t="str">
         <v>3</v>
       </c>
-      <c r="F69" t="str">
-        <v>file</v>
-      </c>
       <c r="G69" t="str">
+        <v>file</v>
+      </c>
+      <c r="H69" t="str">
         <v>TG2</v>
       </c>
-      <c r="H69" t="str">
+      <c r="I69" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I69" t="str">
+      <c r="J69" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J69" t="str">
-        <v/>
-      </c>
       <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L69" t="str">
+      <c r="M69" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3673,39 +3881,42 @@
         <v>1R3</v>
       </c>
       <c r="D70" t="str">
+        <v>1</v>
+      </c>
+      <c r="E70" t="str">
         <v>F</v>
       </c>
-      <c r="E70" t="str">
-        <v>1</v>
-      </c>
       <c r="F70" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G70" t="str">
+        <v>file</v>
+      </c>
+      <c r="H70" t="str">
         <v>TG1</v>
       </c>
-      <c r="H70" t="str">
+      <c r="I70" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I70" t="str">
+      <c r="J70" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J70" t="str">
-        <v/>
-      </c>
       <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L70" t="str">
+      <c r="M70" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3720,39 +3931,42 @@
         <v>1R3</v>
       </c>
       <c r="D71" t="str">
+        <v>1</v>
+      </c>
+      <c r="E71" t="str">
         <v>M</v>
       </c>
-      <c r="E71" t="str">
+      <c r="F71" t="str">
         <v>2</v>
       </c>
-      <c r="F71" t="str">
-        <v>file</v>
-      </c>
       <c r="G71" t="str">
+        <v>file</v>
+      </c>
+      <c r="H71" t="str">
         <v>TG2</v>
       </c>
-      <c r="H71" t="str">
+      <c r="I71" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I71" t="str">
+      <c r="J71" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J71" t="str">
-        <v/>
-      </c>
       <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L71" t="str">
+      <c r="M71" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3767,39 +3981,42 @@
         <v>1R3</v>
       </c>
       <c r="D72" t="str">
+        <v>1</v>
+      </c>
+      <c r="E72" t="str">
         <v>F</v>
       </c>
-      <c r="E72" t="str">
+      <c r="F72" t="str">
         <v>3</v>
       </c>
-      <c r="F72" t="str">
-        <v>file</v>
-      </c>
       <c r="G72" t="str">
+        <v>file</v>
+      </c>
+      <c r="H72" t="str">
         <v>TG1</v>
       </c>
-      <c r="H72" t="str">
+      <c r="I72" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I72" t="str">
+      <c r="J72" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3814,39 +4031,42 @@
         <v>1R3</v>
       </c>
       <c r="D73" t="str">
+        <v>1</v>
+      </c>
+      <c r="E73" t="str">
         <v>M</v>
       </c>
-      <c r="E73" t="str">
+      <c r="F73" t="str">
         <v>3</v>
       </c>
-      <c r="F73" t="str">
-        <v>file</v>
-      </c>
       <c r="G73" t="str">
+        <v>file</v>
+      </c>
+      <c r="H73" t="str">
         <v>TG2</v>
       </c>
-      <c r="H73" t="str">
+      <c r="I73" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I73" t="str">
+      <c r="J73" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J73" t="str">
-        <v/>
-      </c>
       <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L73" t="str">
+      <c r="M73" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3861,39 +4081,42 @@
         <v>1R3</v>
       </c>
       <c r="D74" t="str">
+        <v>1</v>
+      </c>
+      <c r="E74" t="str">
         <v>F</v>
       </c>
-      <c r="E74" t="str">
-        <v>1</v>
-      </c>
       <c r="F74" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G74" t="str">
+        <v>file</v>
+      </c>
+      <c r="H74" t="str">
         <v>TG1</v>
       </c>
-      <c r="H74" t="str">
+      <c r="I74" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I74" t="str">
+      <c r="J74" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J74" t="str">
-        <v/>
-      </c>
       <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L74" t="str">
+      <c r="M74" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3908,39 +4131,42 @@
         <v>1R3</v>
       </c>
       <c r="D75" t="str">
+        <v>1</v>
+      </c>
+      <c r="E75" t="str">
         <v>M</v>
       </c>
-      <c r="E75" t="str">
+      <c r="F75" t="str">
         <v>2</v>
       </c>
-      <c r="F75" t="str">
-        <v>file</v>
-      </c>
       <c r="G75" t="str">
+        <v>file</v>
+      </c>
+      <c r="H75" t="str">
         <v>TG2</v>
       </c>
-      <c r="H75" t="str">
+      <c r="I75" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I75" t="str">
+      <c r="J75" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J75" t="str">
-        <v/>
-      </c>
       <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L75" t="str">
+      <c r="M75" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3955,39 +4181,42 @@
         <v>1R3</v>
       </c>
       <c r="D76" t="str">
+        <v>1</v>
+      </c>
+      <c r="E76" t="str">
         <v>F</v>
       </c>
-      <c r="E76" t="str">
+      <c r="F76" t="str">
         <v>3</v>
       </c>
-      <c r="F76" t="str">
-        <v>file</v>
-      </c>
       <c r="G76" t="str">
+        <v>file</v>
+      </c>
+      <c r="H76" t="str">
         <v>TG1</v>
       </c>
-      <c r="H76" t="str">
+      <c r="I76" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I76" t="str">
+      <c r="J76" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J76" t="str">
-        <v/>
-      </c>
       <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L76" t="str">
+      <c r="M76" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M76" t="str">
+      <c r="N76" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4002,39 +4231,42 @@
         <v>1R3</v>
       </c>
       <c r="D77" t="str">
+        <v>1</v>
+      </c>
+      <c r="E77" t="str">
         <v>M</v>
       </c>
-      <c r="E77" t="str">
+      <c r="F77" t="str">
         <v>3</v>
       </c>
-      <c r="F77" t="str">
-        <v>file</v>
-      </c>
       <c r="G77" t="str">
+        <v>file</v>
+      </c>
+      <c r="H77" t="str">
         <v>TG2</v>
       </c>
-      <c r="H77" t="str">
+      <c r="I77" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I77" t="str">
+      <c r="J77" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J77" t="str">
-        <v/>
-      </c>
       <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L77" t="str">
+      <c r="M77" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M77" t="str">
+      <c r="N77" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4049,39 +4281,42 @@
         <v>1R3</v>
       </c>
       <c r="D78" t="str">
+        <v>1</v>
+      </c>
+      <c r="E78" t="str">
         <v>F</v>
       </c>
-      <c r="E78" t="str">
-        <v>1</v>
-      </c>
       <c r="F78" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G78" t="str">
+        <v>file</v>
+      </c>
+      <c r="H78" t="str">
         <v>TG1</v>
       </c>
-      <c r="H78" t="str">
+      <c r="I78" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I78" t="str">
+      <c r="J78" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J78" t="str">
-        <v/>
-      </c>
       <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L78" t="str">
+      <c r="M78" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M78" t="str">
+      <c r="N78" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4096,39 +4331,42 @@
         <v>1R3</v>
       </c>
       <c r="D79" t="str">
+        <v>1</v>
+      </c>
+      <c r="E79" t="str">
         <v>M</v>
       </c>
-      <c r="E79" t="str">
+      <c r="F79" t="str">
         <v>2</v>
       </c>
-      <c r="F79" t="str">
-        <v>file</v>
-      </c>
       <c r="G79" t="str">
+        <v>file</v>
+      </c>
+      <c r="H79" t="str">
         <v>TG2</v>
       </c>
-      <c r="H79" t="str">
+      <c r="I79" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I79" t="str">
+      <c r="J79" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J79" t="str">
+      <c r="K79" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K79" t="str">
+      <c r="L79" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4143,39 +4381,42 @@
         <v>1R4</v>
       </c>
       <c r="D80" t="str">
+        <v>1</v>
+      </c>
+      <c r="E80" t="str">
         <v>F</v>
       </c>
-      <c r="E80" t="str">
+      <c r="F80" t="str">
         <v>3</v>
       </c>
-      <c r="F80" t="str">
-        <v>file</v>
-      </c>
       <c r="G80" t="str">
+        <v>file</v>
+      </c>
+      <c r="H80" t="str">
         <v>TG1</v>
       </c>
-      <c r="H80" t="str">
+      <c r="I80" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I80" t="str">
+      <c r="J80" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J80" t="str">
-        <v/>
-      </c>
       <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L80" t="str">
+      <c r="M80" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M80" t="str">
+      <c r="N80" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4190,39 +4431,42 @@
         <v>1R4</v>
       </c>
       <c r="D81" t="str">
+        <v>1</v>
+      </c>
+      <c r="E81" t="str">
         <v>M</v>
       </c>
-      <c r="E81" t="str">
+      <c r="F81" t="str">
         <v>3</v>
       </c>
-      <c r="F81" t="str">
-        <v>file</v>
-      </c>
       <c r="G81" t="str">
+        <v>file</v>
+      </c>
+      <c r="H81" t="str">
         <v>TG2</v>
       </c>
-      <c r="H81" t="str">
+      <c r="I81" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I81" t="str">
+      <c r="J81" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J81" t="str">
-        <v/>
-      </c>
       <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L81" t="str">
+      <c r="M81" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M81" t="str">
+      <c r="N81" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4237,39 +4481,42 @@
         <v>1R4</v>
       </c>
       <c r="D82" t="str">
+        <v>1</v>
+      </c>
+      <c r="E82" t="str">
         <v>F</v>
       </c>
-      <c r="E82" t="str">
-        <v>1</v>
-      </c>
       <c r="F82" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G82" t="str">
+        <v>file</v>
+      </c>
+      <c r="H82" t="str">
         <v>TG1</v>
       </c>
-      <c r="H82" t="str">
+      <c r="I82" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I82" t="str">
+      <c r="J82" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J82" t="str">
-        <v/>
-      </c>
       <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L82" t="str">
+      <c r="M82" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M82" t="str">
+      <c r="N82" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4284,39 +4531,42 @@
         <v>1R4</v>
       </c>
       <c r="D83" t="str">
+        <v>1</v>
+      </c>
+      <c r="E83" t="str">
         <v>M</v>
       </c>
-      <c r="E83" t="str">
+      <c r="F83" t="str">
         <v>2</v>
       </c>
-      <c r="F83" t="str">
-        <v>file</v>
-      </c>
       <c r="G83" t="str">
+        <v>file</v>
+      </c>
+      <c r="H83" t="str">
         <v>TG2</v>
       </c>
-      <c r="H83" t="str">
+      <c r="I83" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I83" t="str">
+      <c r="J83" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J83" t="str">
-        <v/>
-      </c>
       <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L83" t="str">
+      <c r="M83" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M83" t="str">
+      <c r="N83" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N83" t="str">
+      <c r="O83" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4331,39 +4581,42 @@
         <v>1R4</v>
       </c>
       <c r="D84" t="str">
+        <v>1</v>
+      </c>
+      <c r="E84" t="str">
         <v>F</v>
       </c>
-      <c r="E84" t="str">
+      <c r="F84" t="str">
         <v>3</v>
       </c>
-      <c r="F84" t="str">
-        <v>file</v>
-      </c>
       <c r="G84" t="str">
+        <v>file</v>
+      </c>
+      <c r="H84" t="str">
         <v>TG1</v>
       </c>
-      <c r="H84" t="str">
+      <c r="I84" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I84" t="str">
+      <c r="J84" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J84" t="str">
-        <v/>
-      </c>
       <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L84" t="str">
+      <c r="M84" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M84" t="str">
+      <c r="N84" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N84" t="str">
+      <c r="O84" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4378,39 +4631,42 @@
         <v>1R4</v>
       </c>
       <c r="D85" t="str">
+        <v>1</v>
+      </c>
+      <c r="E85" t="str">
         <v>M</v>
       </c>
-      <c r="E85" t="str">
+      <c r="F85" t="str">
         <v>3</v>
       </c>
-      <c r="F85" t="str">
-        <v>file</v>
-      </c>
       <c r="G85" t="str">
+        <v>file</v>
+      </c>
+      <c r="H85" t="str">
         <v>TG2</v>
       </c>
-      <c r="H85" t="str">
+      <c r="I85" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I85" t="str">
+      <c r="J85" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J85" t="str">
-        <v/>
-      </c>
       <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L85" t="str">
+      <c r="M85" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M85" t="str">
+      <c r="N85" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N85" t="str">
+      <c r="O85" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4425,39 +4681,42 @@
         <v>1R4</v>
       </c>
       <c r="D86" t="str">
+        <v>1</v>
+      </c>
+      <c r="E86" t="str">
         <v>F</v>
       </c>
-      <c r="E86" t="str">
-        <v>1</v>
-      </c>
       <c r="F86" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G86" t="str">
+        <v>file</v>
+      </c>
+      <c r="H86" t="str">
         <v>TG1</v>
       </c>
-      <c r="H86" t="str">
+      <c r="I86" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I86" t="str">
+      <c r="J86" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J86" t="str">
+      <c r="K86" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4472,39 +4731,42 @@
         <v>1R4</v>
       </c>
       <c r="D87" t="str">
+        <v>1</v>
+      </c>
+      <c r="E87" t="str">
         <v>M</v>
       </c>
-      <c r="E87" t="str">
+      <c r="F87" t="str">
         <v>2</v>
       </c>
-      <c r="F87" t="str">
-        <v>file</v>
-      </c>
       <c r="G87" t="str">
+        <v>file</v>
+      </c>
+      <c r="H87" t="str">
         <v>TG2</v>
       </c>
-      <c r="H87" t="str">
+      <c r="I87" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I87" t="str">
+      <c r="J87" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J87" t="str">
-        <v/>
-      </c>
       <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L87" t="str">
+      <c r="M87" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M87" t="str">
+      <c r="N87" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N87" t="str">
+      <c r="O87" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4519,39 +4781,42 @@
         <v>1R4</v>
       </c>
       <c r="D88" t="str">
+        <v>1</v>
+      </c>
+      <c r="E88" t="str">
         <v>F</v>
       </c>
-      <c r="E88" t="str">
+      <c r="F88" t="str">
         <v>3</v>
       </c>
-      <c r="F88" t="str">
-        <v>file</v>
-      </c>
       <c r="G88" t="str">
+        <v>file</v>
+      </c>
+      <c r="H88" t="str">
         <v>TG1</v>
       </c>
-      <c r="H88" t="str">
+      <c r="I88" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I88" t="str">
+      <c r="J88" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J88" t="str">
-        <v/>
-      </c>
       <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L88" t="str">
+      <c r="M88" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M88" t="str">
+      <c r="N88" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N88" t="str">
+      <c r="O88" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4566,39 +4831,42 @@
         <v>1R4</v>
       </c>
       <c r="D89" t="str">
+        <v>1</v>
+      </c>
+      <c r="E89" t="str">
         <v>M</v>
       </c>
-      <c r="E89" t="str">
+      <c r="F89" t="str">
         <v>3</v>
       </c>
-      <c r="F89" t="str">
-        <v>file</v>
-      </c>
       <c r="G89" t="str">
+        <v>file</v>
+      </c>
+      <c r="H89" t="str">
         <v>TG2</v>
       </c>
-      <c r="H89" t="str">
+      <c r="I89" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I89" t="str">
+      <c r="J89" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J89" t="str">
-        <v/>
-      </c>
       <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L89" t="str">
+      <c r="M89" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M89" t="str">
+      <c r="N89" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N89" t="str">
+      <c r="O89" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4613,39 +4881,42 @@
         <v>1R4</v>
       </c>
       <c r="D90" t="str">
+        <v>1</v>
+      </c>
+      <c r="E90" t="str">
         <v>F</v>
       </c>
-      <c r="E90" t="str">
-        <v>1</v>
-      </c>
       <c r="F90" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G90" t="str">
+        <v>file</v>
+      </c>
+      <c r="H90" t="str">
         <v>TG1</v>
       </c>
-      <c r="H90" t="str">
+      <c r="I90" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I90" t="str">
+      <c r="J90" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J90" t="str">
-        <v/>
-      </c>
       <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L90" t="str">
+      <c r="M90" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M90" t="str">
+      <c r="N90" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N90" t="str">
+      <c r="O90" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4660,39 +4931,42 @@
         <v>1R4</v>
       </c>
       <c r="D91" t="str">
+        <v>1</v>
+      </c>
+      <c r="E91" t="str">
         <v>M</v>
       </c>
-      <c r="E91" t="str">
+      <c r="F91" t="str">
         <v>2</v>
       </c>
-      <c r="F91" t="str">
-        <v>file</v>
-      </c>
       <c r="G91" t="str">
+        <v>file</v>
+      </c>
+      <c r="H91" t="str">
         <v>TG2</v>
       </c>
-      <c r="H91" t="str">
+      <c r="I91" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I91" t="str">
+      <c r="J91" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J91" t="str">
-        <v/>
-      </c>
       <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L91" t="str">
+      <c r="M91" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M91" t="str">
+      <c r="N91" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N91" t="str">
+      <c r="O91" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O91" t="str">
+      <c r="P91" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4707,39 +4981,42 @@
         <v>1R4</v>
       </c>
       <c r="D92" t="str">
+        <v>1</v>
+      </c>
+      <c r="E92" t="str">
         <v>F</v>
       </c>
-      <c r="E92" t="str">
+      <c r="F92" t="str">
         <v>3</v>
       </c>
-      <c r="F92" t="str">
-        <v>file</v>
-      </c>
       <c r="G92" t="str">
+        <v>file</v>
+      </c>
+      <c r="H92" t="str">
         <v>TG1</v>
       </c>
-      <c r="H92" t="str">
+      <c r="I92" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I92" t="str">
+      <c r="J92" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J92" t="str">
-        <v/>
-      </c>
       <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L92" t="str">
+      <c r="M92" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M92" t="str">
+      <c r="N92" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N92" t="str">
+      <c r="O92" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4754,39 +5031,42 @@
         <v>1R4</v>
       </c>
       <c r="D93" t="str">
+        <v>1</v>
+      </c>
+      <c r="E93" t="str">
         <v>M</v>
       </c>
-      <c r="E93" t="str">
+      <c r="F93" t="str">
         <v>3</v>
       </c>
-      <c r="F93" t="str">
-        <v>file</v>
-      </c>
       <c r="G93" t="str">
+        <v>file</v>
+      </c>
+      <c r="H93" t="str">
         <v>TG2</v>
       </c>
-      <c r="H93" t="str">
+      <c r="I93" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I93" t="str">
+      <c r="J93" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J93" t="str">
+      <c r="K93" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L93" t="str">
+      <c r="M93" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N93" t="str">
+      <c r="O93" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O93" t="str">
+      <c r="P93" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4801,39 +5081,42 @@
         <v>1R4</v>
       </c>
       <c r="D94" t="str">
+        <v>1</v>
+      </c>
+      <c r="E94" t="str">
         <v>F</v>
       </c>
-      <c r="E94" t="str">
-        <v>1</v>
-      </c>
       <c r="F94" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G94" t="str">
+        <v>file</v>
+      </c>
+      <c r="H94" t="str">
         <v>TG1</v>
       </c>
-      <c r="H94" t="str">
+      <c r="I94" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I94" t="str">
+      <c r="J94" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J94" t="str">
-        <v/>
-      </c>
       <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L94" t="str">
+      <c r="M94" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M94" t="str">
+      <c r="N94" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N94" t="str">
+      <c r="O94" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O94" t="str">
+      <c r="P94" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4848,39 +5131,42 @@
         <v>1R4</v>
       </c>
       <c r="D95" t="str">
+        <v>1</v>
+      </c>
+      <c r="E95" t="str">
         <v>M</v>
       </c>
-      <c r="E95" t="str">
+      <c r="F95" t="str">
         <v>2</v>
       </c>
-      <c r="F95" t="str">
-        <v>file</v>
-      </c>
       <c r="G95" t="str">
+        <v>file</v>
+      </c>
+      <c r="H95" t="str">
         <v>TG2</v>
       </c>
-      <c r="H95" t="str">
+      <c r="I95" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I95" t="str">
+      <c r="J95" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J95" t="str">
-        <v/>
-      </c>
       <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L95" t="str">
+      <c r="M95" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M95" t="str">
+      <c r="N95" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N95" t="str">
+      <c r="O95" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O95" t="str">
+      <c r="P95" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4895,39 +5181,42 @@
         <v>1R4</v>
       </c>
       <c r="D96" t="str">
+        <v>1</v>
+      </c>
+      <c r="E96" t="str">
         <v>F</v>
       </c>
-      <c r="E96" t="str">
+      <c r="F96" t="str">
         <v>3</v>
       </c>
-      <c r="F96" t="str">
-        <v>file</v>
-      </c>
       <c r="G96" t="str">
+        <v>file</v>
+      </c>
+      <c r="H96" t="str">
         <v>TG1</v>
       </c>
-      <c r="H96" t="str">
+      <c r="I96" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I96" t="str">
+      <c r="J96" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J96" t="str">
-        <v/>
-      </c>
       <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L96" t="str">
+      <c r="M96" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M96" t="str">
+      <c r="N96" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N96" t="str">
+      <c r="O96" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O96" t="str">
+      <c r="P96" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4942,39 +5231,42 @@
         <v>1R4</v>
       </c>
       <c r="D97" t="str">
+        <v>1</v>
+      </c>
+      <c r="E97" t="str">
         <v>M</v>
       </c>
-      <c r="E97" t="str">
+      <c r="F97" t="str">
         <v>3</v>
       </c>
-      <c r="F97" t="str">
-        <v>file</v>
-      </c>
       <c r="G97" t="str">
+        <v>file</v>
+      </c>
+      <c r="H97" t="str">
         <v>TG2</v>
       </c>
-      <c r="H97" t="str">
+      <c r="I97" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I97" t="str">
+      <c r="J97" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J97" t="str">
-        <v/>
-      </c>
       <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L97" t="str">
+      <c r="M97" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M97" t="str">
+      <c r="N97" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N97" t="str">
+      <c r="O97" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O97" t="str">
+      <c r="P97" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4989,39 +5281,42 @@
         <v>1R4</v>
       </c>
       <c r="D98" t="str">
+        <v>1</v>
+      </c>
+      <c r="E98" t="str">
         <v>F</v>
       </c>
-      <c r="E98" t="str">
-        <v>1</v>
-      </c>
       <c r="F98" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G98" t="str">
+        <v>file</v>
+      </c>
+      <c r="H98" t="str">
         <v>TG1</v>
       </c>
-      <c r="H98" t="str">
+      <c r="I98" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I98" t="str">
+      <c r="J98" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J98" t="str">
-        <v/>
-      </c>
       <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L98" t="str">
+      <c r="M98" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M98" t="str">
+      <c r="N98" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N98" t="str">
+      <c r="O98" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O98" t="str">
+      <c r="P98" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5036,39 +5331,42 @@
         <v>1R4</v>
       </c>
       <c r="D99" t="str">
+        <v>1</v>
+      </c>
+      <c r="E99" t="str">
         <v>M</v>
       </c>
-      <c r="E99" t="str">
+      <c r="F99" t="str">
         <v>2</v>
       </c>
-      <c r="F99" t="str">
-        <v>file</v>
-      </c>
       <c r="G99" t="str">
+        <v>file</v>
+      </c>
+      <c r="H99" t="str">
         <v>TG2</v>
       </c>
-      <c r="H99" t="str">
+      <c r="I99" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I99" t="str">
+      <c r="J99" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J99" t="str">
-        <v/>
-      </c>
       <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L99" t="str">
+      <c r="M99" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M99" t="str">
+      <c r="N99" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N99" t="str">
+      <c r="O99" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O99" t="str">
+      <c r="P99" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5083,39 +5381,42 @@
         <v>1R4</v>
       </c>
       <c r="D100" t="str">
+        <v>1</v>
+      </c>
+      <c r="E100" t="str">
         <v>F</v>
       </c>
-      <c r="E100" t="str">
+      <c r="F100" t="str">
         <v>3</v>
       </c>
-      <c r="F100" t="str">
-        <v>file</v>
-      </c>
       <c r="G100" t="str">
+        <v>file</v>
+      </c>
+      <c r="H100" t="str">
         <v>TG1</v>
       </c>
-      <c r="H100" t="str">
+      <c r="I100" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I100" t="str">
+      <c r="J100" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J100" t="str">
+      <c r="K100" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L100" t="str">
+      <c r="M100" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N100" t="str">
+      <c r="O100" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O100" t="str">
+      <c r="P100" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5130,39 +5431,42 @@
         <v>1R4</v>
       </c>
       <c r="D101" t="str">
+        <v>1</v>
+      </c>
+      <c r="E101" t="str">
         <v>M</v>
       </c>
-      <c r="E101" t="str">
+      <c r="F101" t="str">
         <v>3</v>
       </c>
-      <c r="F101" t="str">
-        <v>file</v>
-      </c>
       <c r="G101" t="str">
+        <v>file</v>
+      </c>
+      <c r="H101" t="str">
         <v>TG2</v>
       </c>
-      <c r="H101" t="str">
+      <c r="I101" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I101" t="str">
+      <c r="J101" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J101" t="str">
-        <v/>
-      </c>
       <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L101" t="str">
+      <c r="M101" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M101" t="str">
+      <c r="N101" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N101" t="str">
+      <c r="O101" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O101" t="str">
+      <c r="P101" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5177,39 +5481,42 @@
         <v>1R4</v>
       </c>
       <c r="D102" t="str">
+        <v>1</v>
+      </c>
+      <c r="E102" t="str">
         <v>F</v>
       </c>
-      <c r="E102" t="str">
-        <v>1</v>
-      </c>
       <c r="F102" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G102" t="str">
+        <v>file</v>
+      </c>
+      <c r="H102" t="str">
         <v>TG1</v>
       </c>
-      <c r="H102" t="str">
+      <c r="I102" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I102" t="str">
+      <c r="J102" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J102" t="str">
-        <v/>
-      </c>
       <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L102" t="str">
+      <c r="M102" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M102" t="str">
+      <c r="N102" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N102" t="str">
+      <c r="O102" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5224,39 +5531,42 @@
         <v>1R4</v>
       </c>
       <c r="D103" t="str">
+        <v>1</v>
+      </c>
+      <c r="E103" t="str">
         <v>M</v>
       </c>
-      <c r="E103" t="str">
+      <c r="F103" t="str">
         <v>2</v>
       </c>
-      <c r="F103" t="str">
-        <v>file</v>
-      </c>
       <c r="G103" t="str">
+        <v>file</v>
+      </c>
+      <c r="H103" t="str">
         <v>TG2</v>
       </c>
-      <c r="H103" t="str">
+      <c r="I103" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I103" t="str">
+      <c r="J103" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J103" t="str">
-        <v/>
-      </c>
       <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L103" t="str">
+      <c r="M103" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M103" t="str">
+      <c r="N103" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N103" t="str">
+      <c r="O103" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O103" t="str">
+      <c r="P103" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5271,39 +5581,42 @@
         <v>1R4</v>
       </c>
       <c r="D104" t="str">
+        <v>1</v>
+      </c>
+      <c r="E104" t="str">
         <v>F</v>
       </c>
-      <c r="E104" t="str">
+      <c r="F104" t="str">
         <v>3</v>
       </c>
-      <c r="F104" t="str">
-        <v>file</v>
-      </c>
       <c r="G104" t="str">
+        <v>file</v>
+      </c>
+      <c r="H104" t="str">
         <v>TG1</v>
       </c>
-      <c r="H104" t="str">
+      <c r="I104" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I104" t="str">
+      <c r="J104" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J104" t="str">
-        <v/>
-      </c>
       <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L104" t="str">
+      <c r="M104" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M104" t="str">
+      <c r="N104" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N104" t="str">
+      <c r="O104" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O104" t="str">
+      <c r="P104" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5318,39 +5631,42 @@
         <v>1R4</v>
       </c>
       <c r="D105" t="str">
+        <v>1</v>
+      </c>
+      <c r="E105" t="str">
         <v>M</v>
       </c>
-      <c r="E105" t="str">
+      <c r="F105" t="str">
         <v>3</v>
       </c>
-      <c r="F105" t="str">
-        <v>file</v>
-      </c>
       <c r="G105" t="str">
+        <v>file</v>
+      </c>
+      <c r="H105" t="str">
         <v>TG2</v>
       </c>
-      <c r="H105" t="str">
+      <c r="I105" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I105" t="str">
+      <c r="J105" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J105" t="str">
-        <v/>
-      </c>
       <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L105" t="str">
+      <c r="M105" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M105" t="str">
+      <c r="N105" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N105" t="str">
+      <c r="O105" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O105" t="str">
+      <c r="P105" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5365,39 +5681,42 @@
         <v>1R5</v>
       </c>
       <c r="D106" t="str">
+        <v>1</v>
+      </c>
+      <c r="E106" t="str">
         <v>F</v>
       </c>
-      <c r="E106" t="str">
-        <v>1</v>
-      </c>
       <c r="F106" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G106" t="str">
+        <v>file</v>
+      </c>
+      <c r="H106" t="str">
         <v>TG1</v>
       </c>
-      <c r="H106" t="str">
+      <c r="I106" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I106" t="str">
+      <c r="J106" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J106" t="str">
-        <v/>
-      </c>
       <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L106" t="str">
+      <c r="M106" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M106" t="str">
+      <c r="N106" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N106" t="str">
+      <c r="O106" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O106" t="str">
+      <c r="P106" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5412,39 +5731,42 @@
         <v>1R5</v>
       </c>
       <c r="D107" t="str">
+        <v>1</v>
+      </c>
+      <c r="E107" t="str">
         <v>M</v>
       </c>
-      <c r="E107" t="str">
+      <c r="F107" t="str">
         <v>2</v>
       </c>
-      <c r="F107" t="str">
-        <v>file</v>
-      </c>
       <c r="G107" t="str">
+        <v>file</v>
+      </c>
+      <c r="H107" t="str">
         <v>TG2</v>
       </c>
-      <c r="H107" t="str">
+      <c r="I107" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I107" t="str">
+      <c r="J107" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J107" t="str">
+      <c r="K107" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L107" t="str">
+      <c r="M107" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N107" t="str">
+      <c r="O107" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O107" t="str">
+      <c r="P107" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5459,39 +5781,42 @@
         <v>1R5</v>
       </c>
       <c r="D108" t="str">
+        <v>1</v>
+      </c>
+      <c r="E108" t="str">
         <v>F</v>
       </c>
-      <c r="E108" t="str">
+      <c r="F108" t="str">
         <v>3</v>
       </c>
-      <c r="F108" t="str">
-        <v>file</v>
-      </c>
       <c r="G108" t="str">
+        <v>file</v>
+      </c>
+      <c r="H108" t="str">
         <v>TG1</v>
       </c>
-      <c r="H108" t="str">
+      <c r="I108" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I108" t="str">
+      <c r="J108" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J108" t="str">
-        <v/>
-      </c>
       <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L108" t="str">
+      <c r="M108" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M108" t="str">
+      <c r="N108" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N108" t="str">
+      <c r="O108" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O108" t="str">
+      <c r="P108" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5506,39 +5831,42 @@
         <v>1R5</v>
       </c>
       <c r="D109" t="str">
+        <v>1</v>
+      </c>
+      <c r="E109" t="str">
         <v>M</v>
       </c>
-      <c r="E109" t="str">
+      <c r="F109" t="str">
         <v>3</v>
       </c>
-      <c r="F109" t="str">
-        <v>file</v>
-      </c>
       <c r="G109" t="str">
+        <v>file</v>
+      </c>
+      <c r="H109" t="str">
         <v>TG2</v>
       </c>
-      <c r="H109" t="str">
+      <c r="I109" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I109" t="str">
+      <c r="J109" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J109" t="str">
-        <v/>
-      </c>
       <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L109" t="str">
+      <c r="M109" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M109" t="str">
+      <c r="N109" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N109" t="str">
+      <c r="O109" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O109" t="str">
+      <c r="P109" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5553,39 +5881,42 @@
         <v>1R5</v>
       </c>
       <c r="D110" t="str">
+        <v>1</v>
+      </c>
+      <c r="E110" t="str">
         <v>F</v>
       </c>
-      <c r="E110" t="str">
-        <v>1</v>
-      </c>
       <c r="F110" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G110" t="str">
+        <v>file</v>
+      </c>
+      <c r="H110" t="str">
         <v>TG1</v>
       </c>
-      <c r="H110" t="str">
+      <c r="I110" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I110" t="str">
+      <c r="J110" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J110" t="str">
-        <v/>
-      </c>
       <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L110" t="str">
+      <c r="M110" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M110" t="str">
+      <c r="N110" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N110" t="str">
+      <c r="O110" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O110" t="str">
+      <c r="P110" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5600,39 +5931,42 @@
         <v>1R5</v>
       </c>
       <c r="D111" t="str">
+        <v>1</v>
+      </c>
+      <c r="E111" t="str">
         <v>M</v>
       </c>
-      <c r="E111" t="str">
+      <c r="F111" t="str">
         <v>2</v>
       </c>
-      <c r="F111" t="str">
-        <v>file</v>
-      </c>
       <c r="G111" t="str">
+        <v>file</v>
+      </c>
+      <c r="H111" t="str">
         <v>TG2</v>
       </c>
-      <c r="H111" t="str">
+      <c r="I111" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I111" t="str">
+      <c r="J111" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J111" t="str">
-        <v/>
-      </c>
       <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L111" t="str">
+      <c r="M111" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M111" t="str">
+      <c r="N111" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N111" t="str">
+      <c r="O111" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O111" t="str">
+      <c r="P111" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5647,39 +5981,42 @@
         <v>1R5</v>
       </c>
       <c r="D112" t="str">
+        <v>1</v>
+      </c>
+      <c r="E112" t="str">
         <v>F</v>
       </c>
-      <c r="E112" t="str">
+      <c r="F112" t="str">
         <v>3</v>
       </c>
-      <c r="F112" t="str">
-        <v>file</v>
-      </c>
       <c r="G112" t="str">
+        <v>file</v>
+      </c>
+      <c r="H112" t="str">
         <v>TG1</v>
       </c>
-      <c r="H112" t="str">
+      <c r="I112" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I112" t="str">
+      <c r="J112" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
       <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L112" t="str">
+      <c r="M112" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M112" t="str">
+      <c r="N112" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N112" t="str">
+      <c r="O112" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O112" t="str">
+      <c r="P112" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5694,39 +6031,42 @@
         <v>1R5</v>
       </c>
       <c r="D113" t="str">
+        <v>1</v>
+      </c>
+      <c r="E113" t="str">
         <v>M</v>
       </c>
-      <c r="E113" t="str">
+      <c r="F113" t="str">
         <v>3</v>
       </c>
-      <c r="F113" t="str">
-        <v>file</v>
-      </c>
       <c r="G113" t="str">
+        <v>file</v>
+      </c>
+      <c r="H113" t="str">
         <v>TG2</v>
       </c>
-      <c r="H113" t="str">
+      <c r="I113" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I113" t="str">
+      <c r="J113" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J113" t="str">
-        <v/>
-      </c>
       <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L113" t="str">
+      <c r="M113" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M113" t="str">
+      <c r="N113" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N113" t="str">
+      <c r="O113" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O113" t="str">
+      <c r="P113" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5741,39 +6081,42 @@
         <v>1R5</v>
       </c>
       <c r="D114" t="str">
+        <v>1</v>
+      </c>
+      <c r="E114" t="str">
         <v>F</v>
       </c>
-      <c r="E114" t="str">
-        <v>1</v>
-      </c>
       <c r="F114" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G114" t="str">
+        <v>file</v>
+      </c>
+      <c r="H114" t="str">
         <v>TG1</v>
       </c>
-      <c r="H114" t="str">
+      <c r="I114" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I114" t="str">
+      <c r="J114" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J114" t="str">
+      <c r="K114" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K114" t="str">
+      <c r="L114" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L114" t="str">
+      <c r="M114" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N114" t="str">
+      <c r="O114" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O114" t="str">
+      <c r="P114" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5788,39 +6131,42 @@
         <v>1R5</v>
       </c>
       <c r="D115" t="str">
+        <v>1</v>
+      </c>
+      <c r="E115" t="str">
         <v>M</v>
       </c>
-      <c r="E115" t="str">
+      <c r="F115" t="str">
         <v>2</v>
       </c>
-      <c r="F115" t="str">
-        <v>file</v>
-      </c>
       <c r="G115" t="str">
+        <v>file</v>
+      </c>
+      <c r="H115" t="str">
         <v>TG2</v>
       </c>
-      <c r="H115" t="str">
+      <c r="I115" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I115" t="str">
+      <c r="J115" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J115" t="str">
-        <v/>
-      </c>
       <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L115" t="str">
+      <c r="M115" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M115" t="str">
+      <c r="N115" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N115" t="str">
+      <c r="O115" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O115" t="str">
+      <c r="P115" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5835,39 +6181,42 @@
         <v>1R5</v>
       </c>
       <c r="D116" t="str">
+        <v>1</v>
+      </c>
+      <c r="E116" t="str">
         <v>F</v>
       </c>
-      <c r="E116" t="str">
+      <c r="F116" t="str">
         <v>3</v>
       </c>
-      <c r="F116" t="str">
-        <v>file</v>
-      </c>
       <c r="G116" t="str">
+        <v>file</v>
+      </c>
+      <c r="H116" t="str">
         <v>TG1</v>
       </c>
-      <c r="H116" t="str">
+      <c r="I116" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I116" t="str">
+      <c r="J116" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J116" t="str">
-        <v/>
-      </c>
       <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L116" t="str">
+      <c r="M116" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M116" t="str">
+      <c r="N116" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N116" t="str">
+      <c r="O116" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O116" t="str">
+      <c r="P116" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5882,39 +6231,42 @@
         <v>1R5</v>
       </c>
       <c r="D117" t="str">
+        <v>1</v>
+      </c>
+      <c r="E117" t="str">
         <v>M</v>
       </c>
-      <c r="E117" t="str">
+      <c r="F117" t="str">
         <v>3</v>
       </c>
-      <c r="F117" t="str">
-        <v>file</v>
-      </c>
       <c r="G117" t="str">
+        <v>file</v>
+      </c>
+      <c r="H117" t="str">
         <v>TG2</v>
       </c>
-      <c r="H117" t="str">
+      <c r="I117" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I117" t="str">
+      <c r="J117" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J117" t="str">
-        <v/>
-      </c>
       <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L117" t="str">
+      <c r="M117" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M117" t="str">
+      <c r="N117" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N117" t="str">
+      <c r="O117" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O117" t="str">
+      <c r="P117" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5929,39 +6281,42 @@
         <v>1R5</v>
       </c>
       <c r="D118" t="str">
+        <v>1</v>
+      </c>
+      <c r="E118" t="str">
         <v>F</v>
       </c>
-      <c r="E118" t="str">
-        <v>1</v>
-      </c>
       <c r="F118" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G118" t="str">
+        <v>file</v>
+      </c>
+      <c r="H118" t="str">
         <v>TG1</v>
       </c>
-      <c r="H118" t="str">
+      <c r="I118" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I118" t="str">
+      <c r="J118" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
       <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L118" t="str">
+      <c r="M118" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M118" t="str">
+      <c r="N118" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N118" t="str">
+      <c r="O118" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O118" t="str">
+      <c r="P118" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5976,39 +6331,42 @@
         <v>1R5</v>
       </c>
       <c r="D119" t="str">
+        <v>1</v>
+      </c>
+      <c r="E119" t="str">
         <v>M</v>
       </c>
-      <c r="E119" t="str">
+      <c r="F119" t="str">
         <v>2</v>
       </c>
-      <c r="F119" t="str">
-        <v>file</v>
-      </c>
       <c r="G119" t="str">
+        <v>file</v>
+      </c>
+      <c r="H119" t="str">
         <v>TG2</v>
       </c>
-      <c r="H119" t="str">
+      <c r="I119" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I119" t="str">
+      <c r="J119" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J119" t="str">
-        <v/>
-      </c>
       <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L119" t="str">
+      <c r="M119" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M119" t="str">
+      <c r="N119" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N119" t="str">
+      <c r="O119" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O119" t="str">
+      <c r="P119" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6023,39 +6381,42 @@
         <v>1R5</v>
       </c>
       <c r="D120" t="str">
+        <v>1</v>
+      </c>
+      <c r="E120" t="str">
         <v>F</v>
       </c>
-      <c r="E120" t="str">
+      <c r="F120" t="str">
         <v>3</v>
       </c>
-      <c r="F120" t="str">
-        <v>file</v>
-      </c>
       <c r="G120" t="str">
+        <v>file</v>
+      </c>
+      <c r="H120" t="str">
         <v>TG1</v>
       </c>
-      <c r="H120" t="str">
+      <c r="I120" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I120" t="str">
+      <c r="J120" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J120" t="str">
-        <v/>
-      </c>
       <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L120" t="str">
+      <c r="M120" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M120" t="str">
+      <c r="N120" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N120" t="str">
+      <c r="O120" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O120" t="str">
+      <c r="P120" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6070,39 +6431,42 @@
         <v>1R5</v>
       </c>
       <c r="D121" t="str">
+        <v>1</v>
+      </c>
+      <c r="E121" t="str">
         <v>M</v>
       </c>
-      <c r="E121" t="str">
+      <c r="F121" t="str">
         <v>3</v>
       </c>
-      <c r="F121" t="str">
-        <v>file</v>
-      </c>
       <c r="G121" t="str">
+        <v>file</v>
+      </c>
+      <c r="H121" t="str">
         <v>TG2</v>
       </c>
-      <c r="H121" t="str">
+      <c r="I121" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I121" t="str">
+      <c r="J121" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J121" t="str">
+      <c r="K121" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K121" t="str">
+      <c r="L121" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L121" t="str">
+      <c r="M121" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N121" t="str">
+      <c r="O121" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O121" t="str">
+      <c r="P121" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6117,39 +6481,42 @@
         <v>1R5</v>
       </c>
       <c r="D122" t="str">
+        <v>1</v>
+      </c>
+      <c r="E122" t="str">
         <v>F</v>
       </c>
-      <c r="E122" t="str">
-        <v>1</v>
-      </c>
       <c r="F122" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G122" t="str">
+        <v>file</v>
+      </c>
+      <c r="H122" t="str">
         <v>TG1</v>
       </c>
-      <c r="H122" t="str">
+      <c r="I122" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I122" t="str">
+      <c r="J122" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J122" t="str">
-        <v/>
-      </c>
       <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L122" t="str">
+      <c r="M122" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M122" t="str">
+      <c r="N122" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N122" t="str">
+      <c r="O122" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O122" t="str">
+      <c r="P122" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6164,39 +6531,42 @@
         <v>1R5</v>
       </c>
       <c r="D123" t="str">
+        <v>1</v>
+      </c>
+      <c r="E123" t="str">
         <v>M</v>
       </c>
-      <c r="E123" t="str">
+      <c r="F123" t="str">
         <v>2</v>
       </c>
-      <c r="F123" t="str">
-        <v>file</v>
-      </c>
       <c r="G123" t="str">
+        <v>file</v>
+      </c>
+      <c r="H123" t="str">
         <v>TG2</v>
       </c>
-      <c r="H123" t="str">
+      <c r="I123" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I123" t="str">
+      <c r="J123" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J123" t="str">
-        <v/>
-      </c>
       <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L123" t="str">
+      <c r="M123" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M123" t="str">
+      <c r="N123" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N123" t="str">
+      <c r="O123" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O123" t="str">
+      <c r="P123" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6211,39 +6581,42 @@
         <v>1R5</v>
       </c>
       <c r="D124" t="str">
+        <v>1</v>
+      </c>
+      <c r="E124" t="str">
         <v>F</v>
       </c>
-      <c r="E124" t="str">
+      <c r="F124" t="str">
         <v>3</v>
       </c>
-      <c r="F124" t="str">
-        <v>file</v>
-      </c>
       <c r="G124" t="str">
+        <v>file</v>
+      </c>
+      <c r="H124" t="str">
         <v>TG1</v>
       </c>
-      <c r="H124" t="str">
+      <c r="I124" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I124" t="str">
+      <c r="J124" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
       <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L124" t="str">
+      <c r="M124" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M124" t="str">
+      <c r="N124" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N124" t="str">
+      <c r="O124" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O124" t="str">
+      <c r="P124" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6258,39 +6631,42 @@
         <v>1R5</v>
       </c>
       <c r="D125" t="str">
+        <v>1</v>
+      </c>
+      <c r="E125" t="str">
         <v>M</v>
       </c>
-      <c r="E125" t="str">
+      <c r="F125" t="str">
         <v>3</v>
       </c>
-      <c r="F125" t="str">
-        <v>file</v>
-      </c>
       <c r="G125" t="str">
+        <v>file</v>
+      </c>
+      <c r="H125" t="str">
         <v>TG2</v>
       </c>
-      <c r="H125" t="str">
+      <c r="I125" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I125" t="str">
+      <c r="J125" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J125" t="str">
-        <v/>
-      </c>
       <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L125" t="str">
+      <c r="M125" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M125" t="str">
+      <c r="N125" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N125" t="str">
+      <c r="O125" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O125" t="str">
+      <c r="P125" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6305,39 +6681,42 @@
         <v>1R5</v>
       </c>
       <c r="D126" t="str">
+        <v>1</v>
+      </c>
+      <c r="E126" t="str">
         <v>F</v>
       </c>
-      <c r="E126" t="str">
-        <v>1</v>
-      </c>
       <c r="F126" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G126" t="str">
+        <v>file</v>
+      </c>
+      <c r="H126" t="str">
         <v>TG1</v>
       </c>
-      <c r="H126" t="str">
+      <c r="I126" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I126" t="str">
+      <c r="J126" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J126" t="str">
-        <v/>
-      </c>
       <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L126" t="str">
+      <c r="M126" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M126" t="str">
+      <c r="N126" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N126" t="str">
+      <c r="O126" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O126" t="str">
+      <c r="P126" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6352,39 +6731,42 @@
         <v>1R5</v>
       </c>
       <c r="D127" t="str">
+        <v>1</v>
+      </c>
+      <c r="E127" t="str">
         <v>M</v>
       </c>
-      <c r="E127" t="str">
+      <c r="F127" t="str">
         <v>2</v>
       </c>
-      <c r="F127" t="str">
-        <v>file</v>
-      </c>
       <c r="G127" t="str">
+        <v>file</v>
+      </c>
+      <c r="H127" t="str">
         <v>TG2</v>
       </c>
-      <c r="H127" t="str">
+      <c r="I127" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I127" t="str">
+      <c r="J127" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J127" t="str">
-        <v/>
-      </c>
       <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L127" t="str">
+      <c r="M127" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M127" t="str">
+      <c r="N127" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N127" t="str">
+      <c r="O127" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O127" t="str">
+      <c r="P127" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6399,39 +6781,42 @@
         <v>1R5</v>
       </c>
       <c r="D128" t="str">
+        <v>1</v>
+      </c>
+      <c r="E128" t="str">
         <v>F</v>
       </c>
-      <c r="E128" t="str">
+      <c r="F128" t="str">
         <v>3</v>
       </c>
-      <c r="F128" t="str">
-        <v>file</v>
-      </c>
       <c r="G128" t="str">
+        <v>file</v>
+      </c>
+      <c r="H128" t="str">
         <v>TG1</v>
       </c>
-      <c r="H128" t="str">
+      <c r="I128" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I128" t="str">
+      <c r="J128" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J128" t="str">
+      <c r="K128" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K128" t="str">
+      <c r="L128" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L128" t="str">
+      <c r="M128" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N128" t="str">
+      <c r="O128" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O128" t="str">
+      <c r="P128" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6446,39 +6831,42 @@
         <v>1R5</v>
       </c>
       <c r="D129" t="str">
+        <v>1</v>
+      </c>
+      <c r="E129" t="str">
         <v>M</v>
       </c>
-      <c r="E129" t="str">
+      <c r="F129" t="str">
         <v>3</v>
       </c>
-      <c r="F129" t="str">
-        <v>file</v>
-      </c>
       <c r="G129" t="str">
+        <v>file</v>
+      </c>
+      <c r="H129" t="str">
         <v>TG2</v>
       </c>
-      <c r="H129" t="str">
+      <c r="I129" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I129" t="str">
+      <c r="J129" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J129" t="str">
-        <v/>
-      </c>
       <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L129" t="str">
+      <c r="M129" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M129" t="str">
+      <c r="N129" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N129" t="str">
+      <c r="O129" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O129" t="str">
+      <c r="P129" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6493,39 +6881,42 @@
         <v>1R5</v>
       </c>
       <c r="D130" t="str">
+        <v>1</v>
+      </c>
+      <c r="E130" t="str">
         <v>F</v>
       </c>
-      <c r="E130" t="str">
-        <v>1</v>
-      </c>
       <c r="F130" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G130" t="str">
+        <v>file</v>
+      </c>
+      <c r="H130" t="str">
         <v>TG1</v>
       </c>
-      <c r="H130" t="str">
+      <c r="I130" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I130" t="str">
+      <c r="J130" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J130" t="str">
-        <v/>
-      </c>
       <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L130" t="str">
+      <c r="M130" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M130" t="str">
+      <c r="N130" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N130" t="str">
+      <c r="O130" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O130" t="str">
+      <c r="P130" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6540,39 +6931,42 @@
         <v>1R5</v>
       </c>
       <c r="D131" t="str">
+        <v>1</v>
+      </c>
+      <c r="E131" t="str">
         <v>M</v>
       </c>
-      <c r="E131" t="str">
+      <c r="F131" t="str">
         <v>2</v>
       </c>
-      <c r="F131" t="str">
-        <v>file</v>
-      </c>
       <c r="G131" t="str">
+        <v>file</v>
+      </c>
+      <c r="H131" t="str">
         <v>TG2</v>
       </c>
-      <c r="H131" t="str">
+      <c r="I131" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I131" t="str">
+      <c r="J131" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J131" t="str">
-        <v/>
-      </c>
       <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L131" t="str">
+      <c r="M131" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M131" t="str">
+      <c r="N131" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N131" t="str">
+      <c r="O131" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O131" t="str">
+      <c r="P131" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6587,39 +6981,42 @@
         <v>1R6</v>
       </c>
       <c r="D132" t="str">
+        <v>1</v>
+      </c>
+      <c r="E132" t="str">
         <v>F</v>
       </c>
-      <c r="E132" t="str">
+      <c r="F132" t="str">
         <v>3</v>
       </c>
-      <c r="F132" t="str">
-        <v>file</v>
-      </c>
       <c r="G132" t="str">
+        <v>file</v>
+      </c>
+      <c r="H132" t="str">
         <v>TG1</v>
       </c>
-      <c r="H132" t="str">
+      <c r="I132" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I132" t="str">
+      <c r="J132" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J132" t="str">
-        <v/>
-      </c>
       <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L132" t="str">
+      <c r="M132" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M132" t="str">
+      <c r="N132" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N132" t="str">
+      <c r="O132" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O132" t="str">
+      <c r="P132" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6634,39 +7031,42 @@
         <v>1R6</v>
       </c>
       <c r="D133" t="str">
+        <v>1</v>
+      </c>
+      <c r="E133" t="str">
         <v>M</v>
       </c>
-      <c r="E133" t="str">
+      <c r="F133" t="str">
         <v>3</v>
       </c>
-      <c r="F133" t="str">
-        <v>file</v>
-      </c>
       <c r="G133" t="str">
+        <v>file</v>
+      </c>
+      <c r="H133" t="str">
         <v>TG2</v>
       </c>
-      <c r="H133" t="str">
+      <c r="I133" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I133" t="str">
+      <c r="J133" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J133" t="str">
-        <v/>
-      </c>
       <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L133" t="str">
+      <c r="M133" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M133" t="str">
+      <c r="N133" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N133" t="str">
+      <c r="O133" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O133" t="str">
+      <c r="P133" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6681,39 +7081,42 @@
         <v>1R6</v>
       </c>
       <c r="D134" t="str">
+        <v>1</v>
+      </c>
+      <c r="E134" t="str">
         <v>F</v>
       </c>
-      <c r="E134" t="str">
-        <v>1</v>
-      </c>
       <c r="F134" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G134" t="str">
+        <v>file</v>
+      </c>
+      <c r="H134" t="str">
         <v>TG1</v>
       </c>
-      <c r="H134" t="str">
+      <c r="I134" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I134" t="str">
+      <c r="J134" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J134" t="str">
-        <v/>
-      </c>
       <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L134" t="str">
+      <c r="M134" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M134" t="str">
+      <c r="N134" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N134" t="str">
+      <c r="O134" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O134" t="str">
+      <c r="P134" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6728,39 +7131,42 @@
         <v>1R6</v>
       </c>
       <c r="D135" t="str">
+        <v>1</v>
+      </c>
+      <c r="E135" t="str">
         <v>M</v>
       </c>
-      <c r="E135" t="str">
+      <c r="F135" t="str">
         <v>2</v>
       </c>
-      <c r="F135" t="str">
-        <v>file</v>
-      </c>
       <c r="G135" t="str">
+        <v>file</v>
+      </c>
+      <c r="H135" t="str">
         <v>TG2</v>
       </c>
-      <c r="H135" t="str">
+      <c r="I135" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I135" t="str">
+      <c r="J135" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J135" t="str">
+      <c r="K135" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K135" t="str">
+      <c r="L135" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L135" t="str">
+      <c r="M135" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N135" t="str">
+      <c r="O135" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O135" t="str">
+      <c r="P135" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6775,39 +7181,42 @@
         <v>1R6</v>
       </c>
       <c r="D136" t="str">
+        <v>1</v>
+      </c>
+      <c r="E136" t="str">
         <v>F</v>
       </c>
-      <c r="E136" t="str">
+      <c r="F136" t="str">
         <v>3</v>
       </c>
-      <c r="F136" t="str">
-        <v>file</v>
-      </c>
       <c r="G136" t="str">
+        <v>file</v>
+      </c>
+      <c r="H136" t="str">
         <v>TG1</v>
       </c>
-      <c r="H136" t="str">
+      <c r="I136" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I136" t="str">
+      <c r="J136" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J136" t="str">
-        <v/>
-      </c>
       <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L136" t="str">
+      <c r="M136" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M136" t="str">
+      <c r="N136" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N136" t="str">
+      <c r="O136" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O136" t="str">
+      <c r="P136" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6822,39 +7231,42 @@
         <v>1R6</v>
       </c>
       <c r="D137" t="str">
+        <v>1</v>
+      </c>
+      <c r="E137" t="str">
         <v>M</v>
       </c>
-      <c r="E137" t="str">
+      <c r="F137" t="str">
         <v>3</v>
       </c>
-      <c r="F137" t="str">
-        <v>file</v>
-      </c>
       <c r="G137" t="str">
+        <v>file</v>
+      </c>
+      <c r="H137" t="str">
         <v>TG2</v>
       </c>
-      <c r="H137" t="str">
+      <c r="I137" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I137" t="str">
+      <c r="J137" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J137" t="str">
-        <v/>
-      </c>
       <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L137" t="str">
+      <c r="M137" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M137" t="str">
+      <c r="N137" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N137" t="str">
+      <c r="O137" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O137" t="str">
+      <c r="P137" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6869,39 +7281,42 @@
         <v>1R6</v>
       </c>
       <c r="D138" t="str">
+        <v>1</v>
+      </c>
+      <c r="E138" t="str">
         <v>F</v>
       </c>
-      <c r="E138" t="str">
-        <v>1</v>
-      </c>
       <c r="F138" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G138" t="str">
+        <v>file</v>
+      </c>
+      <c r="H138" t="str">
         <v>TG1</v>
       </c>
-      <c r="H138" t="str">
+      <c r="I138" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I138" t="str">
+      <c r="J138" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J138" t="str">
-        <v/>
-      </c>
       <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L138" t="str">
+      <c r="M138" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M138" t="str">
+      <c r="N138" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N138" t="str">
+      <c r="O138" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O138" t="str">
+      <c r="P138" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6916,39 +7331,42 @@
         <v>1R6</v>
       </c>
       <c r="D139" t="str">
+        <v>1</v>
+      </c>
+      <c r="E139" t="str">
         <v>M</v>
       </c>
-      <c r="E139" t="str">
+      <c r="F139" t="str">
         <v>2</v>
       </c>
-      <c r="F139" t="str">
-        <v>file</v>
-      </c>
       <c r="G139" t="str">
+        <v>file</v>
+      </c>
+      <c r="H139" t="str">
         <v>TG2</v>
       </c>
-      <c r="H139" t="str">
+      <c r="I139" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I139" t="str">
+      <c r="J139" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J139" t="str">
-        <v/>
-      </c>
       <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L139" t="str">
+      <c r="M139" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M139" t="str">
+      <c r="N139" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N139" t="str">
+      <c r="O139" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O139" t="str">
+      <c r="P139" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6963,39 +7381,42 @@
         <v>1R6</v>
       </c>
       <c r="D140" t="str">
+        <v>1</v>
+      </c>
+      <c r="E140" t="str">
         <v>F</v>
       </c>
-      <c r="E140" t="str">
+      <c r="F140" t="str">
         <v>3</v>
       </c>
-      <c r="F140" t="str">
-        <v>file</v>
-      </c>
       <c r="G140" t="str">
+        <v>file</v>
+      </c>
+      <c r="H140" t="str">
         <v>TG1</v>
       </c>
-      <c r="H140" t="str">
+      <c r="I140" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I140" t="str">
+      <c r="J140" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J140" t="str">
-        <v/>
-      </c>
       <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L140" t="str">
+      <c r="M140" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M140" t="str">
+      <c r="N140" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N140" t="str">
+      <c r="O140" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O140" t="str">
+      <c r="P140" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7010,39 +7431,42 @@
         <v>1R6</v>
       </c>
       <c r="D141" t="str">
+        <v>1</v>
+      </c>
+      <c r="E141" t="str">
         <v>M</v>
       </c>
-      <c r="E141" t="str">
+      <c r="F141" t="str">
         <v>3</v>
       </c>
-      <c r="F141" t="str">
-        <v>file</v>
-      </c>
       <c r="G141" t="str">
+        <v>file</v>
+      </c>
+      <c r="H141" t="str">
         <v>TG2</v>
       </c>
-      <c r="H141" t="str">
+      <c r="I141" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I141" t="str">
+      <c r="J141" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J141" t="str">
-        <v/>
-      </c>
       <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L141" t="str">
+      <c r="M141" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M141" t="str">
+      <c r="N141" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N141" t="str">
+      <c r="O141" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O141" t="str">
+      <c r="P141" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7057,39 +7481,42 @@
         <v>1R6</v>
       </c>
       <c r="D142" t="str">
+        <v>1</v>
+      </c>
+      <c r="E142" t="str">
         <v>F</v>
       </c>
-      <c r="E142" t="str">
-        <v>1</v>
-      </c>
       <c r="F142" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G142" t="str">
+        <v>file</v>
+      </c>
+      <c r="H142" t="str">
         <v>TG1</v>
       </c>
-      <c r="H142" t="str">
+      <c r="I142" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I142" t="str">
+      <c r="J142" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J142" t="str">
+      <c r="K142" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K142" t="str">
+      <c r="L142" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L142" t="str">
+      <c r="M142" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N142" t="str">
+      <c r="O142" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O142" t="str">
+      <c r="P142" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7104,39 +7531,42 @@
         <v>1R6</v>
       </c>
       <c r="D143" t="str">
+        <v>1</v>
+      </c>
+      <c r="E143" t="str">
         <v>M</v>
       </c>
-      <c r="E143" t="str">
+      <c r="F143" t="str">
         <v>2</v>
       </c>
-      <c r="F143" t="str">
-        <v>file</v>
-      </c>
       <c r="G143" t="str">
+        <v>file</v>
+      </c>
+      <c r="H143" t="str">
         <v>TG2</v>
       </c>
-      <c r="H143" t="str">
+      <c r="I143" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I143" t="str">
+      <c r="J143" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J143" t="str">
-        <v/>
-      </c>
       <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L143" t="str">
+      <c r="M143" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M143" t="str">
+      <c r="N143" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N143" t="str">
+      <c r="O143" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O143" t="str">
+      <c r="P143" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7151,39 +7581,42 @@
         <v>1R6</v>
       </c>
       <c r="D144" t="str">
+        <v>1</v>
+      </c>
+      <c r="E144" t="str">
         <v>F</v>
       </c>
-      <c r="E144" t="str">
+      <c r="F144" t="str">
         <v>3</v>
       </c>
-      <c r="F144" t="str">
-        <v>file</v>
-      </c>
       <c r="G144" t="str">
+        <v>file</v>
+      </c>
+      <c r="H144" t="str">
         <v>TG1</v>
       </c>
-      <c r="H144" t="str">
+      <c r="I144" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I144" t="str">
+      <c r="J144" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J144" t="str">
-        <v/>
-      </c>
       <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L144" t="str">
+      <c r="M144" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M144" t="str">
+      <c r="N144" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N144" t="str">
+      <c r="O144" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O144" t="str">
+      <c r="P144" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7198,39 +7631,42 @@
         <v>1R6</v>
       </c>
       <c r="D145" t="str">
+        <v>1</v>
+      </c>
+      <c r="E145" t="str">
         <v>M</v>
       </c>
-      <c r="E145" t="str">
+      <c r="F145" t="str">
         <v>3</v>
       </c>
-      <c r="F145" t="str">
-        <v>file</v>
-      </c>
       <c r="G145" t="str">
+        <v>file</v>
+      </c>
+      <c r="H145" t="str">
         <v>TG2</v>
       </c>
-      <c r="H145" t="str">
+      <c r="I145" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I145" t="str">
+      <c r="J145" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J145" t="str">
-        <v/>
-      </c>
       <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L145" t="str">
+      <c r="M145" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M145" t="str">
+      <c r="N145" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N145" t="str">
+      <c r="O145" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O145" t="str">
+      <c r="P145" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7245,39 +7681,42 @@
         <v>1R6</v>
       </c>
       <c r="D146" t="str">
+        <v>1</v>
+      </c>
+      <c r="E146" t="str">
         <v>F</v>
       </c>
-      <c r="E146" t="str">
-        <v>1</v>
-      </c>
       <c r="F146" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G146" t="str">
+        <v>file</v>
+      </c>
+      <c r="H146" t="str">
         <v>TG1</v>
       </c>
-      <c r="H146" t="str">
+      <c r="I146" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I146" t="str">
+      <c r="J146" t="str">
         <v>CL G1</v>
       </c>
-      <c r="J146" t="str">
-        <v/>
-      </c>
       <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L146" t="str">
+      <c r="M146" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M146" t="str">
+      <c r="N146" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N146" t="str">
+      <c r="O146" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O146" t="str">
+      <c r="P146" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7292,39 +7731,42 @@
         <v>1R6</v>
       </c>
       <c r="D147" t="str">
+        <v>1</v>
+      </c>
+      <c r="E147" t="str">
         <v>M</v>
       </c>
-      <c r="E147" t="str">
+      <c r="F147" t="str">
         <v>2</v>
       </c>
-      <c r="F147" t="str">
-        <v>file</v>
-      </c>
       <c r="G147" t="str">
+        <v>file</v>
+      </c>
+      <c r="H147" t="str">
         <v>TG2</v>
       </c>
-      <c r="H147" t="str">
+      <c r="I147" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I147" t="str">
+      <c r="J147" t="str">
         <v>ML G2</v>
       </c>
-      <c r="J147" t="str">
-        <v/>
-      </c>
       <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L147" t="str">
+      <c r="M147" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M147" t="str">
+      <c r="N147" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N147" t="str">
+      <c r="O147" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O147" t="str">
+      <c r="P147" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7339,39 +7781,42 @@
         <v>1R6</v>
       </c>
       <c r="D148" t="str">
+        <v>1</v>
+      </c>
+      <c r="E148" t="str">
         <v>F</v>
       </c>
-      <c r="E148" t="str">
+      <c r="F148" t="str">
         <v>3</v>
       </c>
-      <c r="F148" t="str">
-        <v>file</v>
-      </c>
       <c r="G148" t="str">
+        <v>file</v>
+      </c>
+      <c r="H148" t="str">
         <v>TG1</v>
       </c>
-      <c r="H148" t="str">
+      <c r="I148" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I148" t="str">
+      <c r="J148" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J148" t="str">
-        <v/>
-      </c>
       <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L148" t="str">
+      <c r="M148" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M148" t="str">
+      <c r="N148" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N148" t="str">
+      <c r="O148" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O148" t="str">
+      <c r="P148" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7386,39 +7831,42 @@
         <v>1R6</v>
       </c>
       <c r="D149" t="str">
+        <v>1</v>
+      </c>
+      <c r="E149" t="str">
         <v>M</v>
       </c>
-      <c r="E149" t="str">
+      <c r="F149" t="str">
         <v>3</v>
       </c>
-      <c r="F149" t="str">
-        <v>file</v>
-      </c>
       <c r="G149" t="str">
+        <v>file</v>
+      </c>
+      <c r="H149" t="str">
         <v>TG2</v>
       </c>
-      <c r="H149" t="str">
+      <c r="I149" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I149" t="str">
+      <c r="J149" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J149" t="str">
+      <c r="K149" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="K149" t="str">
+      <c r="L149" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L149" t="str">
+      <c r="M149" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N149" t="str">
+      <c r="O149" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O149" t="str">
+      <c r="P149" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7433,39 +7881,42 @@
         <v>1R6</v>
       </c>
       <c r="D150" t="str">
+        <v>1</v>
+      </c>
+      <c r="E150" t="str">
         <v>F</v>
       </c>
-      <c r="E150" t="str">
-        <v>1</v>
-      </c>
       <c r="F150" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G150" t="str">
+        <v>file</v>
+      </c>
+      <c r="H150" t="str">
         <v>TG1</v>
       </c>
-      <c r="H150" t="str">
+      <c r="I150" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I150" t="str">
+      <c r="J150" t="str">
         <v>ML G1</v>
       </c>
-      <c r="J150" t="str">
-        <v/>
-      </c>
       <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L150" t="str">
+      <c r="M150" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M150" t="str">
+      <c r="N150" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N150" t="str">
+      <c r="O150" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O150" t="str">
+      <c r="P150" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7480,39 +7931,42 @@
         <v>1R6</v>
       </c>
       <c r="D151" t="str">
+        <v>1</v>
+      </c>
+      <c r="E151" t="str">
         <v>M</v>
       </c>
-      <c r="E151" t="str">
+      <c r="F151" t="str">
         <v>2</v>
       </c>
-      <c r="F151" t="str">
-        <v>file</v>
-      </c>
       <c r="G151" t="str">
+        <v>file</v>
+      </c>
+      <c r="H151" t="str">
         <v>TG2</v>
       </c>
-      <c r="H151" t="str">
+      <c r="I151" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I151" t="str">
+      <c r="J151" t="str">
         <v>TL G2</v>
       </c>
-      <c r="J151" t="str">
-        <v/>
-      </c>
       <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L151" t="str">
+      <c r="M151" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M151" t="str">
+      <c r="N151" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N151" t="str">
+      <c r="O151" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O151" t="str">
+      <c r="P151" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7527,39 +7981,42 @@
         <v>1R6</v>
       </c>
       <c r="D152" t="str">
+        <v>1</v>
+      </c>
+      <c r="E152" t="str">
         <v>F</v>
       </c>
-      <c r="E152" t="str">
+      <c r="F152" t="str">
         <v>3</v>
       </c>
-      <c r="F152" t="str">
-        <v>file</v>
-      </c>
       <c r="G152" t="str">
+        <v>file</v>
+      </c>
+      <c r="H152" t="str">
         <v>TG1</v>
       </c>
-      <c r="H152" t="str">
+      <c r="I152" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I152" t="str">
+      <c r="J152" t="str">
         <v>CL G3</v>
       </c>
-      <c r="J152" t="str">
-        <v/>
-      </c>
       <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L152" t="str">
+      <c r="M152" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M152" t="str">
+      <c r="N152" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N152" t="str">
+      <c r="O152" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O152" t="str">
+      <c r="P152" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7574,39 +8031,42 @@
         <v>1R6</v>
       </c>
       <c r="D153" t="str">
+        <v>1</v>
+      </c>
+      <c r="E153" t="str">
         <v>M</v>
       </c>
-      <c r="E153" t="str">
+      <c r="F153" t="str">
         <v>3</v>
       </c>
-      <c r="F153" t="str">
-        <v>file</v>
-      </c>
       <c r="G153" t="str">
+        <v>file</v>
+      </c>
+      <c r="H153" t="str">
         <v>TG2</v>
       </c>
-      <c r="H153" t="str">
+      <c r="I153" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I153" t="str">
+      <c r="J153" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J153" t="str">
-        <v/>
-      </c>
       <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L153" t="str">
+      <c r="M153" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M153" t="str">
+      <c r="N153" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N153" t="str">
+      <c r="O153" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O153" t="str">
+      <c r="P153" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7621,39 +8081,42 @@
         <v>1R6</v>
       </c>
       <c r="D154" t="str">
+        <v>1</v>
+      </c>
+      <c r="E154" t="str">
         <v>F</v>
       </c>
-      <c r="E154" t="str">
-        <v>1</v>
-      </c>
       <c r="F154" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="G154" t="str">
+        <v>file</v>
+      </c>
+      <c r="H154" t="str">
         <v>TG1</v>
       </c>
-      <c r="H154" t="str">
+      <c r="I154" t="str">
         <v>EL G1</v>
       </c>
-      <c r="I154" t="str">
+      <c r="J154" t="str">
         <v>TL G1</v>
       </c>
-      <c r="J154" t="str">
-        <v/>
-      </c>
       <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154" t="str">
         <v>MA G1</v>
       </c>
-      <c r="L154" t="str">
+      <c r="M154" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="M154" t="str">
+      <c r="N154" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="N154" t="str">
+      <c r="O154" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="O154" t="str">
+      <c r="P154" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7668,39 +8131,42 @@
         <v>1R6</v>
       </c>
       <c r="D155" t="str">
+        <v>1</v>
+      </c>
+      <c r="E155" t="str">
         <v>M</v>
       </c>
-      <c r="E155" t="str">
+      <c r="F155" t="str">
         <v>2</v>
       </c>
-      <c r="F155" t="str">
-        <v>file</v>
-      </c>
       <c r="G155" t="str">
+        <v>file</v>
+      </c>
+      <c r="H155" t="str">
         <v>TG2</v>
       </c>
-      <c r="H155" t="str">
+      <c r="I155" t="str">
         <v>EL G2</v>
       </c>
-      <c r="I155" t="str">
+      <c r="J155" t="str">
         <v>CL G2</v>
       </c>
-      <c r="J155" t="str">
-        <v/>
-      </c>
       <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
         <v>MA G2</v>
       </c>
-      <c r="L155" t="str">
+      <c r="M155" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="M155" t="str">
+      <c r="N155" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="N155" t="str">
+      <c r="O155" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="O155" t="str">
+      <c r="P155" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7715,39 +8181,42 @@
         <v>1R6</v>
       </c>
       <c r="D156" t="str">
+        <v>1</v>
+      </c>
+      <c r="E156" t="str">
         <v>F</v>
       </c>
-      <c r="E156" t="str">
+      <c r="F156" t="str">
         <v>3</v>
       </c>
-      <c r="F156" t="str">
-        <v>file</v>
-      </c>
       <c r="G156" t="str">
+        <v>file</v>
+      </c>
+      <c r="H156" t="str">
         <v>TG1</v>
       </c>
-      <c r="H156" t="str">
+      <c r="I156" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I156" t="str">
+      <c r="J156" t="str">
         <v>ML G3</v>
       </c>
-      <c r="J156" t="str">
+      <c r="K156" t="str">
         <v>MALAY</v>
       </c>
-      <c r="K156" t="str">
+      <c r="L156" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L156" t="str">
+      <c r="M156" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O156" t="str">
+      <c r="P156" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7762,60 +8231,65 @@
         <v>1R6</v>
       </c>
       <c r="D157" t="str">
+        <v>1</v>
+      </c>
+      <c r="E157" t="str">
         <v>M</v>
       </c>
-      <c r="E157" t="str">
+      <c r="F157" t="str">
         <v>3</v>
       </c>
-      <c r="F157" t="str">
-        <v>file</v>
-      </c>
       <c r="G157" t="str">
+        <v>file</v>
+      </c>
+      <c r="H157" t="str">
         <v>TG2</v>
       </c>
-      <c r="H157" t="str">
+      <c r="I157" t="str">
         <v>EL G3</v>
       </c>
-      <c r="I157" t="str">
+      <c r="J157" t="str">
         <v>TL G3</v>
       </c>
-      <c r="J157" t="str">
-        <v/>
-      </c>
       <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
         <v>MA G3</v>
       </c>
-      <c r="L157" t="str">
+      <c r="M157" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="M157" t="str">
+      <c r="N157" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="N157" t="str">
+      <c r="O157" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="O157" t="str">
+      <c r="P157" t="str">
         <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P157"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:I17"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="24.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="5" max="5" width="6.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7829,15 +8303,21 @@
         <v>Subject</v>
       </c>
       <c r="D1" t="str">
-        <v>Teacher</v>
+        <v>Teachers</v>
       </c>
       <c r="E1" t="str">
+        <v>Level</v>
+      </c>
+      <c r="F1" t="str">
         <v>AutoSubject</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>AutoValue</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
+        <v>AutoPG</v>
+      </c>
+      <c r="I1" t="str">
         <v>AutoClasses</v>
       </c>
     </row>
@@ -7855,12 +8335,18 @@
         <v>Mrs Lim Bee Leng</v>
       </c>
       <c r="E2" t="str">
+        <v>1</v>
+      </c>
+      <c r="F2" t="str">
         <v>EL</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
       <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -7878,12 +8364,18 @@
         <v>Mr Rajesh Kumar</v>
       </c>
       <c r="E3" t="str">
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
         <v>MA</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
       <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -7901,12 +8393,18 @@
         <v>Mr Daniel Tan</v>
       </c>
       <c r="E4" t="str">
+        <v>1</v>
+      </c>
+      <c r="F4" t="str">
         <v>EL</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
       <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -7924,12 +8422,18 @@
         <v>Mdm Halimah Yusof</v>
       </c>
       <c r="E5" t="str">
+        <v>1</v>
+      </c>
+      <c r="F5" t="str">
         <v>MA</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
       <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -7947,12 +8451,18 @@
         <v>Ms Nur Aisyah</v>
       </c>
       <c r="E6" t="str">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
         <v>EL</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
       <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -7970,12 +8480,18 @@
         <v>Ms Serene Goh</v>
       </c>
       <c r="E7" t="str">
+        <v>1</v>
+      </c>
+      <c r="F7" t="str">
         <v>MA</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
       <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -7993,12 +8509,18 @@
         <v>Mrs Grace Chua</v>
       </c>
       <c r="E8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F8" t="str">
         <v>EL</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
       <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -8016,12 +8538,18 @@
         <v>Mr Alvin Ong</v>
       </c>
       <c r="E9" t="str">
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
         <v>MA</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
       <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -8039,12 +8567,18 @@
         <v>Mr Marcus Lee</v>
       </c>
       <c r="E10" t="str">
+        <v>1</v>
+      </c>
+      <c r="F10" t="str">
         <v>EL</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
       <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -8062,12 +8596,18 @@
         <v>Mrs Doris Koh</v>
       </c>
       <c r="E11" t="str">
+        <v>1</v>
+      </c>
+      <c r="F11" t="str">
         <v>MA</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
       <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -8085,12 +8625,18 @@
         <v>Mdm Sarimah Bakar</v>
       </c>
       <c r="E12" t="str">
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
         <v>EL</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
       <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -8108,12 +8654,18 @@
         <v>Mr Wei Jie Chan</v>
       </c>
       <c r="E13" t="str">
+        <v>1</v>
+      </c>
+      <c r="F13" t="str">
         <v>MA</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
       <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -8128,15 +8680,21 @@
         <v>Science</v>
       </c>
       <c r="D14" t="str">
-        <v>Dr Sarah Loh</v>
+        <v>Dr Sarah Loh ; Mr Benjamin Teo</v>
       </c>
       <c r="E14" t="str">
+        <v>1</v>
+      </c>
+      <c r="F14" t="str">
         <v>SCI</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="G14" t="str">
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v/>
       </c>
     </row>
@@ -8154,12 +8712,18 @@
         <v>Ms Priyanka Nair</v>
       </c>
       <c r="E15" t="str">
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
         <v>HIST</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="G15" t="str">
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v/>
       </c>
     </row>
@@ -8177,12 +8741,18 @@
         <v>Mr Kenneth Sim</v>
       </c>
       <c r="E16" t="str">
+        <v>1</v>
+      </c>
+      <c r="F16" t="str">
         <v>GEOG</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="G16" t="str">
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v/>
       </c>
     </row>
@@ -8200,18 +8770,24 @@
         <v>Mrs Evelyn Phua</v>
       </c>
       <c r="E17" t="str">
+        <v>1</v>
+      </c>
+      <c r="F17" t="str">
         <v>LIT</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>LIT G3</v>
       </c>
-      <c r="G17" t="str">
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -8285,9 +8285,9 @@
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
     <col min="3" max="3" width="18.83203125" customWidth="1"/>
     <col min="4" max="4" width="34.83203125" customWidth="1"/>
-    <col min="5" max="5" width="6.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="8.83203125" customWidth="1"/>
     <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
@@ -8309,10 +8309,10 @@
         <v>Level</v>
       </c>
       <c r="F1" t="str">
-        <v>AutoSubject</v>
+        <v>AutoMatch</v>
       </c>
       <c r="G1" t="str">
-        <v>AutoValue</v>
+        <v>AutoLevel</v>
       </c>
       <c r="H1" t="str">
         <v>AutoPG</v>
@@ -8338,10 +8338,10 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H2" t="str">
         <v/>
@@ -8367,10 +8367,10 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
         <v/>
@@ -8396,10 +8396,10 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H4" t="str">
         <v/>
@@ -8425,10 +8425,10 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H5" t="str">
         <v/>
@@ -8454,10 +8454,10 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H6" t="str">
         <v/>
@@ -8483,10 +8483,10 @@
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H7" t="str">
         <v/>
@@ -8512,10 +8512,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H8" t="str">
         <v/>
@@ -8541,10 +8541,10 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H9" t="str">
         <v/>
@@ -8570,10 +8570,10 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H10" t="str">
         <v/>
@@ -8599,10 +8599,10 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -8628,10 +8628,10 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>EL</v>
+        <v>EL=</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -8657,10 +8657,10 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>MA</v>
+        <v>MA=</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -8686,10 +8686,10 @@
         <v>1</v>
       </c>
       <c r="F14" t="str">
-        <v>SCI</v>
+        <v>SCI=SCI G3</v>
       </c>
       <c r="G14" t="str">
-        <v>SCI G3</v>
+        <v>1</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -8715,10 +8715,10 @@
         <v>1</v>
       </c>
       <c r="F15" t="str">
-        <v>HIST</v>
+        <v>HIST=HIST G3</v>
       </c>
       <c r="G15" t="str">
-        <v>HIST G3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -8744,10 +8744,10 @@
         <v>1</v>
       </c>
       <c r="F16" t="str">
-        <v>GEOG</v>
+        <v>GEOG=GEOG G2</v>
       </c>
       <c r="G16" t="str">
-        <v>GEOG G2</v>
+        <v>1</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -8773,10 +8773,10 @@
         <v>1</v>
       </c>
       <c r="F17" t="str">
-        <v>LIT</v>
+        <v>LIT=LIT G3</v>
       </c>
       <c r="G17" t="str">
-        <v>LIT G3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -13497,13 +13497,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" customWidth="1"/>
     <col min="3" max="3" width="30.83203125" customWidth="1"/>
     <col min="4" max="4" width="42.83203125" customWidth="1"/>
     <col min="5" max="5" width="22.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13522,6 +13523,9 @@
       <c r="E1" t="str">
         <v>LastImported</v>
       </c>
+      <c r="F1" t="str">
+        <v>Mapping</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -13539,10 +13543,13 @@
       <c r="E2" t="str">
         <v/>
       </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -6,7 +6,8 @@
     <sheet name="Students" sheetId="1" r:id="rId1"/>
     <sheet name="Groups" sheetId="2" r:id="rId2"/>
     <sheet name="Memberships" sheetId="3" r:id="rId3"/>
-    <sheet name="Sources" sheetId="4" r:id="rId4"/>
+    <sheet name="Teachers" sheetId="4" r:id="rId4"/>
+    <sheet name="Sources" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -8279,7 +8280,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:H17"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -8287,9 +8288,8 @@
     <col min="4" max="4" width="34.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8312,12 +8312,9 @@
         <v>AutoMatch</v>
       </c>
       <c r="G1" t="str">
-        <v>AutoLevel</v>
+        <v>AutoPG</v>
       </c>
       <c r="H1" t="str">
-        <v>AutoPG</v>
-      </c>
-      <c r="I1" t="str">
         <v>AutoClasses</v>
       </c>
     </row>
@@ -8341,12 +8338,9 @@
         <v>EL=</v>
       </c>
       <c r="G2" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -8370,12 +8364,9 @@
         <v>MA=</v>
       </c>
       <c r="G3" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -8399,12 +8390,9 @@
         <v>EL=</v>
       </c>
       <c r="G4" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -8428,12 +8416,9 @@
         <v>MA=</v>
       </c>
       <c r="G5" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -8457,12 +8442,9 @@
         <v>EL=</v>
       </c>
       <c r="G6" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -8486,12 +8468,9 @@
         <v>MA=</v>
       </c>
       <c r="G7" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -8515,12 +8494,9 @@
         <v>EL=</v>
       </c>
       <c r="G8" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -8544,12 +8520,9 @@
         <v>MA=</v>
       </c>
       <c r="G9" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -8573,12 +8546,9 @@
         <v>EL=</v>
       </c>
       <c r="G10" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -8602,12 +8572,9 @@
         <v>MA=</v>
       </c>
       <c r="G11" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -8631,12 +8598,9 @@
         <v>EL=</v>
       </c>
       <c r="G12" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -8660,12 +8624,9 @@
         <v>MA=</v>
       </c>
       <c r="G13" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -8689,12 +8650,9 @@
         <v>SCI=SCI G3</v>
       </c>
       <c r="G14" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
         <v/>
       </c>
     </row>
@@ -8718,12 +8676,9 @@
         <v>HIST=HIST G3</v>
       </c>
       <c r="G15" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
         <v/>
       </c>
     </row>
@@ -8747,12 +8702,9 @@
         <v>GEOG=GEOG G2</v>
       </c>
       <c r="G16" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
         <v/>
       </c>
     </row>
@@ -8776,18 +8728,15 @@
         <v>LIT=LIT G3</v>
       </c>
       <c r="G17" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13497,6 +13446,110 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A18"/>
+  <cols>
+    <col min="1" max="1" width="34.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Name</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Dr Sarah Loh</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Mdm Halimah Yusof</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Mdm Sarimah Bakar</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Mr Alvin Ong</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Mr Benjamin Teo</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Mr Daniel Tan</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Mr Kenneth Sim</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Mr Marcus Lee</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Mr Rajesh Kumar</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Mr Wei Jie Chan</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Mrs Doris Koh</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Mrs Evelyn Phua</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Mrs Grace Chua</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Mrs Lim Bee Leng</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Ms Nur Aisyah</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Ms Priyanka Nair</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Ms Serene Goh</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A18"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P157"/>
+  <dimension ref="A1:Q157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -410,7 +410,7 @@
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="28.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
@@ -419,6 +419,7 @@
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -444,30 +445,33 @@
         <v>Origin</v>
       </c>
       <c r="H1" t="str">
+        <v>SourceName</v>
+      </c>
+      <c r="I1" t="str">
         <v>TG</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>EL</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>MT</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>HMT</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>MA</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>SCI</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>HIST</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>GEOG</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>LIT</v>
       </c>
     </row>
@@ -494,30 +498,33 @@
         <v>file</v>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>TG1</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -544,30 +551,33 @@
         <v>file</v>
       </c>
       <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>TG2</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -594,30 +604,33 @@
         <v>file</v>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>TG1</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
       <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M4" t="str">
+      <c r="N4" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -644,30 +657,33 @@
         <v>file</v>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>TG2</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -694,30 +710,33 @@
         <v>file</v>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>TG1</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
       <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -744,30 +763,33 @@
         <v>file</v>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>TG2</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -794,30 +816,33 @@
         <v>file</v>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>TG1</v>
       </c>
-      <c r="I8" t="str">
+      <c r="J8" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J8" t="str">
+      <c r="K8" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
       <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M8" t="str">
+      <c r="N8" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -844,30 +869,33 @@
         <v>file</v>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>TG2</v>
       </c>
-      <c r="I9" t="str">
+      <c r="J9" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J9" t="str">
+      <c r="K9" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -894,30 +922,33 @@
         <v>file</v>
       </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>TG1</v>
       </c>
-      <c r="I10" t="str">
+      <c r="J10" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J10" t="str">
+      <c r="K10" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
       <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M10" t="str">
+      <c r="N10" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -944,30 +975,33 @@
         <v>file</v>
       </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>TG2</v>
       </c>
-      <c r="I11" t="str">
+      <c r="J11" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J11" t="str">
+      <c r="K11" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M11" t="str">
+      <c r="N11" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -994,30 +1028,33 @@
         <v>file</v>
       </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>TG1</v>
       </c>
-      <c r="I12" t="str">
+      <c r="J12" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J12" t="str">
+      <c r="K12" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M12" t="str">
+      <c r="N12" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1044,30 +1081,33 @@
         <v>file</v>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>TG2</v>
       </c>
-      <c r="I13" t="str">
+      <c r="J13" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J13" t="str">
+      <c r="K13" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
       <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M13" t="str">
+      <c r="N13" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1094,30 +1134,33 @@
         <v>file</v>
       </c>
       <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v>TG1</v>
       </c>
-      <c r="I14" t="str">
+      <c r="J14" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J14" t="str">
+      <c r="K14" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
       <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M14" t="str">
+      <c r="N14" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1144,30 +1187,33 @@
         <v>file</v>
       </c>
       <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
         <v>TG2</v>
       </c>
-      <c r="I15" t="str">
+      <c r="J15" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J15" t="str">
+      <c r="K15" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
       <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M15" t="str">
+      <c r="N15" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1194,30 +1240,33 @@
         <v>file</v>
       </c>
       <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
         <v>TG1</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J16" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K16" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1244,30 +1293,33 @@
         <v>file</v>
       </c>
       <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
         <v>TG2</v>
       </c>
-      <c r="I17" t="str">
+      <c r="J17" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J17" t="str">
+      <c r="K17" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
       <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M17" t="str">
+      <c r="N17" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1294,30 +1346,33 @@
         <v>file</v>
       </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>TG1</v>
       </c>
-      <c r="I18" t="str">
+      <c r="J18" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J18" t="str">
+      <c r="K18" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
       <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M18" t="str">
+      <c r="N18" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1344,30 +1399,33 @@
         <v>file</v>
       </c>
       <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>TG2</v>
       </c>
-      <c r="I19" t="str">
+      <c r="J19" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J19" t="str">
+      <c r="K19" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
       <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M19" t="str">
+      <c r="N19" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1394,30 +1452,33 @@
         <v>file</v>
       </c>
       <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>TG1</v>
       </c>
-      <c r="I20" t="str">
+      <c r="J20" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J20" t="str">
+      <c r="K20" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
       <c r="L20" t="str">
+        <v/>
+      </c>
+      <c r="M20" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M20" t="str">
+      <c r="N20" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1444,30 +1505,33 @@
         <v>file</v>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>TG2</v>
       </c>
-      <c r="I21" t="str">
+      <c r="J21" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J21" t="str">
+      <c r="K21" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
       <c r="L21" t="str">
+        <v/>
+      </c>
+      <c r="M21" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M21" t="str">
+      <c r="N21" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Q21" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1494,30 +1558,33 @@
         <v>file</v>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>TG1</v>
       </c>
-      <c r="I22" t="str">
+      <c r="J22" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J22" t="str">
+      <c r="K22" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
       <c r="L22" t="str">
+        <v/>
+      </c>
+      <c r="M22" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M22" t="str">
+      <c r="N22" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Q22" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1544,30 +1611,33 @@
         <v>file</v>
       </c>
       <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
         <v>TG2</v>
       </c>
-      <c r="I23" t="str">
+      <c r="J23" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J23" t="str">
+      <c r="K23" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Q23" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1594,30 +1664,33 @@
         <v>file</v>
       </c>
       <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>TG1</v>
       </c>
-      <c r="I24" t="str">
+      <c r="J24" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J24" t="str">
+      <c r="K24" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
       <c r="L24" t="str">
+        <v/>
+      </c>
+      <c r="M24" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M24" t="str">
+      <c r="N24" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Q24" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1644,30 +1717,33 @@
         <v>file</v>
       </c>
       <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>TG2</v>
       </c>
-      <c r="I25" t="str">
+      <c r="J25" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J25" t="str">
+      <c r="K25" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
       <c r="L25" t="str">
+        <v/>
+      </c>
+      <c r="M25" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M25" t="str">
+      <c r="N25" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q25" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1694,30 +1770,33 @@
         <v>file</v>
       </c>
       <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
         <v>TG1</v>
       </c>
-      <c r="I26" t="str">
+      <c r="J26" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J26" t="str">
+      <c r="K26" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
       <c r="L26" t="str">
+        <v/>
+      </c>
+      <c r="M26" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M26" t="str">
+      <c r="N26" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Q26" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1744,30 +1823,33 @@
         <v>file</v>
       </c>
       <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
         <v>TG2</v>
       </c>
-      <c r="I27" t="str">
+      <c r="J27" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J27" t="str">
+      <c r="K27" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
       <c r="L27" t="str">
+        <v/>
+      </c>
+      <c r="M27" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M27" t="str">
+      <c r="N27" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1794,30 +1876,33 @@
         <v>file</v>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>TG1</v>
       </c>
-      <c r="I28" t="str">
+      <c r="J28" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J28" t="str">
+      <c r="K28" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
       <c r="L28" t="str">
+        <v/>
+      </c>
+      <c r="M28" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M28" t="str">
+      <c r="N28" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Q28" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1844,30 +1929,33 @@
         <v>file</v>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <v>TG2</v>
       </c>
-      <c r="I29" t="str">
+      <c r="J29" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J29" t="str">
+      <c r="K29" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
       <c r="L29" t="str">
+        <v/>
+      </c>
+      <c r="M29" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M29" t="str">
+      <c r="N29" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Q29" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1894,30 +1982,33 @@
         <v>file</v>
       </c>
       <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
         <v>TG1</v>
       </c>
-      <c r="I30" t="str">
+      <c r="J30" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J30" t="str">
+      <c r="K30" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1944,30 +2035,33 @@
         <v>file</v>
       </c>
       <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
         <v>TG2</v>
       </c>
-      <c r="I31" t="str">
+      <c r="J31" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J31" t="str">
+      <c r="K31" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
       <c r="L31" t="str">
+        <v/>
+      </c>
+      <c r="M31" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M31" t="str">
+      <c r="N31" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1994,30 +2088,33 @@
         <v>file</v>
       </c>
       <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
         <v>TG1</v>
       </c>
-      <c r="I32" t="str">
+      <c r="J32" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J32" t="str">
+      <c r="K32" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
       <c r="L32" t="str">
+        <v/>
+      </c>
+      <c r="M32" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M32" t="str">
+      <c r="N32" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P32" t="str">
+      <c r="Q32" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2044,30 +2141,33 @@
         <v>file</v>
       </c>
       <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
         <v>TG2</v>
       </c>
-      <c r="I33" t="str">
+      <c r="J33" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J33" t="str">
+      <c r="K33" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K33" t="str">
-        <v/>
-      </c>
       <c r="L33" t="str">
+        <v/>
+      </c>
+      <c r="M33" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M33" t="str">
+      <c r="N33" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P33" t="str">
+      <c r="Q33" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2094,30 +2194,33 @@
         <v>file</v>
       </c>
       <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
         <v>TG1</v>
       </c>
-      <c r="I34" t="str">
+      <c r="J34" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J34" t="str">
+      <c r="K34" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K34" t="str">
-        <v/>
-      </c>
       <c r="L34" t="str">
+        <v/>
+      </c>
+      <c r="M34" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M34" t="str">
+      <c r="N34" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P34" t="str">
+      <c r="Q34" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2144,30 +2247,33 @@
         <v>file</v>
       </c>
       <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
         <v>TG2</v>
       </c>
-      <c r="I35" t="str">
+      <c r="J35" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J35" t="str">
+      <c r="K35" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
       <c r="L35" t="str">
+        <v/>
+      </c>
+      <c r="M35" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M35" t="str">
+      <c r="N35" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2194,30 +2300,33 @@
         <v>file</v>
       </c>
       <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
         <v>TG1</v>
       </c>
-      <c r="I36" t="str">
+      <c r="J36" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J36" t="str">
+      <c r="K36" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K36" t="str">
-        <v/>
-      </c>
       <c r="L36" t="str">
+        <v/>
+      </c>
+      <c r="M36" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M36" t="str">
+      <c r="N36" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P36" t="str">
+      <c r="Q36" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2244,30 +2353,33 @@
         <v>file</v>
       </c>
       <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
         <v>TG2</v>
       </c>
-      <c r="I37" t="str">
+      <c r="J37" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J37" t="str">
+      <c r="K37" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P37" t="str">
+      <c r="Q37" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2294,30 +2406,33 @@
         <v>file</v>
       </c>
       <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
         <v>TG1</v>
       </c>
-      <c r="I38" t="str">
+      <c r="J38" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J38" t="str">
+      <c r="K38" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
       <c r="L38" t="str">
+        <v/>
+      </c>
+      <c r="M38" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M38" t="str">
+      <c r="N38" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P38" t="str">
+      <c r="Q38" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2344,30 +2459,33 @@
         <v>file</v>
       </c>
       <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
         <v>TG2</v>
       </c>
-      <c r="I39" t="str">
+      <c r="J39" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J39" t="str">
+      <c r="K39" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K39" t="str">
-        <v/>
-      </c>
       <c r="L39" t="str">
+        <v/>
+      </c>
+      <c r="M39" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2394,30 +2512,33 @@
         <v>file</v>
       </c>
       <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
         <v>TG1</v>
       </c>
-      <c r="I40" t="str">
+      <c r="J40" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J40" t="str">
+      <c r="K40" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
       <c r="L40" t="str">
+        <v/>
+      </c>
+      <c r="M40" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M40" t="str">
+      <c r="N40" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P40" t="str">
+      <c r="Q40" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2444,30 +2565,33 @@
         <v>file</v>
       </c>
       <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
         <v>TG2</v>
       </c>
-      <c r="I41" t="str">
+      <c r="J41" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J41" t="str">
+      <c r="K41" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
       <c r="L41" t="str">
+        <v/>
+      </c>
+      <c r="M41" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M41" t="str">
+      <c r="N41" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2494,30 +2618,33 @@
         <v>file</v>
       </c>
       <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
         <v>TG1</v>
       </c>
-      <c r="I42" t="str">
+      <c r="J42" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J42" t="str">
+      <c r="K42" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
       <c r="L42" t="str">
+        <v/>
+      </c>
+      <c r="M42" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M42" t="str">
+      <c r="N42" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P42" t="str">
+      <c r="Q42" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2544,30 +2671,33 @@
         <v>file</v>
       </c>
       <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
         <v>TG2</v>
       </c>
-      <c r="I43" t="str">
+      <c r="J43" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J43" t="str">
+      <c r="K43" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K43" t="str">
-        <v/>
-      </c>
       <c r="L43" t="str">
+        <v/>
+      </c>
+      <c r="M43" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M43" t="str">
+      <c r="N43" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P43" t="str">
+      <c r="Q43" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2594,30 +2724,33 @@
         <v>file</v>
       </c>
       <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
         <v>TG1</v>
       </c>
-      <c r="I44" t="str">
+      <c r="J44" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J44" t="str">
+      <c r="K44" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P44" t="str">
+      <c r="Q44" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2644,30 +2777,33 @@
         <v>file</v>
       </c>
       <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
         <v>TG2</v>
       </c>
-      <c r="I45" t="str">
+      <c r="J45" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J45" t="str">
+      <c r="K45" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
       <c r="L45" t="str">
+        <v/>
+      </c>
+      <c r="M45" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M45" t="str">
+      <c r="N45" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P45" t="str">
+      <c r="Q45" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2694,30 +2830,33 @@
         <v>file</v>
       </c>
       <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
         <v>TG1</v>
       </c>
-      <c r="I46" t="str">
+      <c r="J46" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J46" t="str">
+      <c r="K46" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
       <c r="L46" t="str">
+        <v/>
+      </c>
+      <c r="M46" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M46" t="str">
+      <c r="N46" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P46" t="str">
+      <c r="Q46" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2744,30 +2883,33 @@
         <v>file</v>
       </c>
       <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
         <v>TG2</v>
       </c>
-      <c r="I47" t="str">
+      <c r="J47" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J47" t="str">
+      <c r="K47" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
       <c r="L47" t="str">
+        <v/>
+      </c>
+      <c r="M47" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M47" t="str">
+      <c r="N47" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P47" t="str">
+      <c r="Q47" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2794,30 +2936,33 @@
         <v>file</v>
       </c>
       <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
         <v>TG1</v>
       </c>
-      <c r="I48" t="str">
+      <c r="J48" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J48" t="str">
+      <c r="K48" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
       <c r="L48" t="str">
+        <v/>
+      </c>
+      <c r="M48" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M48" t="str">
+      <c r="N48" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P48" t="str">
+      <c r="Q48" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2844,30 +2989,33 @@
         <v>file</v>
       </c>
       <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
         <v>TG2</v>
       </c>
-      <c r="I49" t="str">
+      <c r="J49" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J49" t="str">
+      <c r="K49" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K49" t="str">
-        <v/>
-      </c>
       <c r="L49" t="str">
+        <v/>
+      </c>
+      <c r="M49" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M49" t="str">
+      <c r="N49" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P49" t="str">
+      <c r="Q49" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2894,30 +3042,33 @@
         <v>file</v>
       </c>
       <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
         <v>TG1</v>
       </c>
-      <c r="I50" t="str">
+      <c r="J50" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J50" t="str">
+      <c r="K50" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
       <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M50" t="str">
+      <c r="N50" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P50" t="str">
+      <c r="Q50" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2944,30 +3095,33 @@
         <v>file</v>
       </c>
       <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
         <v>TG2</v>
       </c>
-      <c r="I51" t="str">
+      <c r="J51" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J51" t="str">
+      <c r="K51" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P51" t="str">
+      <c r="Q51" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2994,30 +3148,33 @@
         <v>file</v>
       </c>
       <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
         <v>TG1</v>
       </c>
-      <c r="I52" t="str">
+      <c r="J52" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J52" t="str">
+      <c r="K52" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K52" t="str">
-        <v/>
-      </c>
       <c r="L52" t="str">
+        <v/>
+      </c>
+      <c r="M52" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M52" t="str">
+      <c r="N52" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P52" t="str">
+      <c r="Q52" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3044,30 +3201,33 @@
         <v>file</v>
       </c>
       <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
         <v>TG2</v>
       </c>
-      <c r="I53" t="str">
+      <c r="J53" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J53" t="str">
+      <c r="K53" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K53" t="str">
-        <v/>
-      </c>
       <c r="L53" t="str">
+        <v/>
+      </c>
+      <c r="M53" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M53" t="str">
+      <c r="N53" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P53" t="str">
+      <c r="Q53" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3094,30 +3254,33 @@
         <v>file</v>
       </c>
       <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
         <v>TG1</v>
       </c>
-      <c r="I54" t="str">
+      <c r="J54" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J54" t="str">
+      <c r="K54" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K54" t="str">
-        <v/>
-      </c>
       <c r="L54" t="str">
+        <v/>
+      </c>
+      <c r="M54" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M54" t="str">
+      <c r="N54" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P54" t="str">
+      <c r="Q54" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3144,30 +3307,33 @@
         <v>file</v>
       </c>
       <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
         <v>TG2</v>
       </c>
-      <c r="I55" t="str">
+      <c r="J55" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J55" t="str">
+      <c r="K55" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K55" t="str">
-        <v/>
-      </c>
       <c r="L55" t="str">
+        <v/>
+      </c>
+      <c r="M55" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M55" t="str">
+      <c r="N55" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P55" t="str">
+      <c r="Q55" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3194,30 +3360,33 @@
         <v>file</v>
       </c>
       <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
         <v>TG1</v>
       </c>
-      <c r="I56" t="str">
+      <c r="J56" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J56" t="str">
+      <c r="K56" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K56" t="str">
-        <v/>
-      </c>
       <c r="L56" t="str">
+        <v/>
+      </c>
+      <c r="M56" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M56" t="str">
+      <c r="N56" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P56" t="str">
+      <c r="Q56" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3244,30 +3413,33 @@
         <v>file</v>
       </c>
       <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
         <v>TG2</v>
       </c>
-      <c r="I57" t="str">
+      <c r="J57" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J57" t="str">
+      <c r="K57" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K57" t="str">
-        <v/>
-      </c>
       <c r="L57" t="str">
+        <v/>
+      </c>
+      <c r="M57" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M57" t="str">
+      <c r="N57" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3294,30 +3466,33 @@
         <v>file</v>
       </c>
       <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
         <v>TG1</v>
       </c>
-      <c r="I58" t="str">
+      <c r="J58" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J58" t="str">
+      <c r="K58" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3344,30 +3519,33 @@
         <v>file</v>
       </c>
       <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
         <v>TG2</v>
       </c>
-      <c r="I59" t="str">
+      <c r="J59" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J59" t="str">
+      <c r="K59" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K59" t="str">
-        <v/>
-      </c>
       <c r="L59" t="str">
+        <v/>
+      </c>
+      <c r="M59" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M59" t="str">
+      <c r="N59" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3394,30 +3572,33 @@
         <v>file</v>
       </c>
       <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
         <v>TG1</v>
       </c>
-      <c r="I60" t="str">
+      <c r="J60" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J60" t="str">
+      <c r="K60" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K60" t="str">
-        <v/>
-      </c>
       <c r="L60" t="str">
+        <v/>
+      </c>
+      <c r="M60" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M60" t="str">
+      <c r="N60" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3444,30 +3625,33 @@
         <v>file</v>
       </c>
       <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
         <v>TG2</v>
       </c>
-      <c r="I61" t="str">
+      <c r="J61" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J61" t="str">
+      <c r="K61" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K61" t="str">
-        <v/>
-      </c>
       <c r="L61" t="str">
+        <v/>
+      </c>
+      <c r="M61" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M61" t="str">
+      <c r="N61" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3494,30 +3678,33 @@
         <v>file</v>
       </c>
       <c r="H62" t="str">
+        <v/>
+      </c>
+      <c r="I62" t="str">
         <v>TG1</v>
       </c>
-      <c r="I62" t="str">
+      <c r="J62" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J62" t="str">
+      <c r="K62" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K62" t="str">
-        <v/>
-      </c>
       <c r="L62" t="str">
+        <v/>
+      </c>
+      <c r="M62" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M62" t="str">
+      <c r="N62" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P62" t="str">
+      <c r="Q62" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3544,30 +3731,33 @@
         <v>file</v>
       </c>
       <c r="H63" t="str">
+        <v/>
+      </c>
+      <c r="I63" t="str">
         <v>TG2</v>
       </c>
-      <c r="I63" t="str">
+      <c r="J63" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J63" t="str">
+      <c r="K63" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K63" t="str">
-        <v/>
-      </c>
       <c r="L63" t="str">
+        <v/>
+      </c>
+      <c r="M63" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M63" t="str">
+      <c r="N63" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P63" t="str">
+      <c r="Q63" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3594,30 +3784,33 @@
         <v>file</v>
       </c>
       <c r="H64" t="str">
+        <v/>
+      </c>
+      <c r="I64" t="str">
         <v>TG1</v>
       </c>
-      <c r="I64" t="str">
+      <c r="J64" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J64" t="str">
+      <c r="K64" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K64" t="str">
-        <v/>
-      </c>
       <c r="L64" t="str">
+        <v/>
+      </c>
+      <c r="M64" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M64" t="str">
+      <c r="N64" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P64" t="str">
+      <c r="Q64" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3644,30 +3837,33 @@
         <v>file</v>
       </c>
       <c r="H65" t="str">
+        <v/>
+      </c>
+      <c r="I65" t="str">
         <v>TG2</v>
       </c>
-      <c r="I65" t="str">
+      <c r="J65" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J65" t="str">
+      <c r="K65" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P65" t="str">
+      <c r="Q65" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3694,30 +3890,33 @@
         <v>file</v>
       </c>
       <c r="H66" t="str">
+        <v/>
+      </c>
+      <c r="I66" t="str">
         <v>TG1</v>
       </c>
-      <c r="I66" t="str">
+      <c r="J66" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J66" t="str">
+      <c r="K66" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K66" t="str">
-        <v/>
-      </c>
       <c r="L66" t="str">
+        <v/>
+      </c>
+      <c r="M66" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M66" t="str">
+      <c r="N66" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P66" t="str">
+      <c r="Q66" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3744,30 +3943,33 @@
         <v>file</v>
       </c>
       <c r="H67" t="str">
+        <v/>
+      </c>
+      <c r="I67" t="str">
         <v>TG2</v>
       </c>
-      <c r="I67" t="str">
+      <c r="J67" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J67" t="str">
+      <c r="K67" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K67" t="str">
-        <v/>
-      </c>
       <c r="L67" t="str">
+        <v/>
+      </c>
+      <c r="M67" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M67" t="str">
+      <c r="N67" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N67" t="str">
+      <c r="O67" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P67" t="str">
+      <c r="Q67" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3794,30 +3996,33 @@
         <v>file</v>
       </c>
       <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
         <v>TG1</v>
       </c>
-      <c r="I68" t="str">
+      <c r="J68" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J68" t="str">
+      <c r="K68" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K68" t="str">
-        <v/>
-      </c>
       <c r="L68" t="str">
+        <v/>
+      </c>
+      <c r="M68" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M68" t="str">
+      <c r="N68" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P68" t="str">
+      <c r="Q68" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3844,30 +4049,33 @@
         <v>file</v>
       </c>
       <c r="H69" t="str">
+        <v/>
+      </c>
+      <c r="I69" t="str">
         <v>TG2</v>
       </c>
-      <c r="I69" t="str">
+      <c r="J69" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J69" t="str">
+      <c r="K69" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K69" t="str">
-        <v/>
-      </c>
       <c r="L69" t="str">
+        <v/>
+      </c>
+      <c r="M69" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M69" t="str">
+      <c r="N69" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P69" t="str">
+      <c r="Q69" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3894,30 +4102,33 @@
         <v>file</v>
       </c>
       <c r="H70" t="str">
+        <v/>
+      </c>
+      <c r="I70" t="str">
         <v>TG1</v>
       </c>
-      <c r="I70" t="str">
+      <c r="J70" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J70" t="str">
+      <c r="K70" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K70" t="str">
-        <v/>
-      </c>
       <c r="L70" t="str">
+        <v/>
+      </c>
+      <c r="M70" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M70" t="str">
+      <c r="N70" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P70" t="str">
+      <c r="Q70" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3944,30 +4155,33 @@
         <v>file</v>
       </c>
       <c r="H71" t="str">
+        <v/>
+      </c>
+      <c r="I71" t="str">
         <v>TG2</v>
       </c>
-      <c r="I71" t="str">
+      <c r="J71" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J71" t="str">
+      <c r="K71" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K71" t="str">
-        <v/>
-      </c>
       <c r="L71" t="str">
+        <v/>
+      </c>
+      <c r="M71" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M71" t="str">
+      <c r="N71" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P71" t="str">
+      <c r="Q71" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3994,30 +4208,33 @@
         <v>file</v>
       </c>
       <c r="H72" t="str">
+        <v/>
+      </c>
+      <c r="I72" t="str">
         <v>TG1</v>
       </c>
-      <c r="I72" t="str">
+      <c r="J72" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J72" t="str">
+      <c r="K72" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P72" t="str">
+      <c r="Q72" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4044,30 +4261,33 @@
         <v>file</v>
       </c>
       <c r="H73" t="str">
+        <v/>
+      </c>
+      <c r="I73" t="str">
         <v>TG2</v>
       </c>
-      <c r="I73" t="str">
+      <c r="J73" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J73" t="str">
+      <c r="K73" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K73" t="str">
-        <v/>
-      </c>
       <c r="L73" t="str">
+        <v/>
+      </c>
+      <c r="M73" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M73" t="str">
+      <c r="N73" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P73" t="str">
+      <c r="Q73" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4094,30 +4314,33 @@
         <v>file</v>
       </c>
       <c r="H74" t="str">
+        <v/>
+      </c>
+      <c r="I74" t="str">
         <v>TG1</v>
       </c>
-      <c r="I74" t="str">
+      <c r="J74" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J74" t="str">
+      <c r="K74" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K74" t="str">
-        <v/>
-      </c>
       <c r="L74" t="str">
+        <v/>
+      </c>
+      <c r="M74" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M74" t="str">
+      <c r="N74" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P74" t="str">
+      <c r="Q74" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4144,30 +4367,33 @@
         <v>file</v>
       </c>
       <c r="H75" t="str">
+        <v/>
+      </c>
+      <c r="I75" t="str">
         <v>TG2</v>
       </c>
-      <c r="I75" t="str">
+      <c r="J75" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J75" t="str">
+      <c r="K75" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K75" t="str">
-        <v/>
-      </c>
       <c r="L75" t="str">
+        <v/>
+      </c>
+      <c r="M75" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M75" t="str">
+      <c r="N75" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P75" t="str">
+      <c r="Q75" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4194,30 +4420,33 @@
         <v>file</v>
       </c>
       <c r="H76" t="str">
+        <v/>
+      </c>
+      <c r="I76" t="str">
         <v>TG1</v>
       </c>
-      <c r="I76" t="str">
+      <c r="J76" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J76" t="str">
+      <c r="K76" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K76" t="str">
-        <v/>
-      </c>
       <c r="L76" t="str">
+        <v/>
+      </c>
+      <c r="M76" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M76" t="str">
+      <c r="N76" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P76" t="str">
+      <c r="Q76" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4244,30 +4473,33 @@
         <v>file</v>
       </c>
       <c r="H77" t="str">
+        <v/>
+      </c>
+      <c r="I77" t="str">
         <v>TG2</v>
       </c>
-      <c r="I77" t="str">
+      <c r="J77" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J77" t="str">
+      <c r="K77" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K77" t="str">
-        <v/>
-      </c>
       <c r="L77" t="str">
+        <v/>
+      </c>
+      <c r="M77" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M77" t="str">
+      <c r="N77" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P77" t="str">
+      <c r="Q77" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4294,30 +4526,33 @@
         <v>file</v>
       </c>
       <c r="H78" t="str">
+        <v/>
+      </c>
+      <c r="I78" t="str">
         <v>TG1</v>
       </c>
-      <c r="I78" t="str">
+      <c r="J78" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J78" t="str">
+      <c r="K78" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K78" t="str">
-        <v/>
-      </c>
       <c r="L78" t="str">
+        <v/>
+      </c>
+      <c r="M78" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M78" t="str">
+      <c r="N78" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P78" t="str">
+      <c r="Q78" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4344,30 +4579,33 @@
         <v>file</v>
       </c>
       <c r="H79" t="str">
+        <v/>
+      </c>
+      <c r="I79" t="str">
         <v>TG2</v>
       </c>
-      <c r="I79" t="str">
+      <c r="J79" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J79" t="str">
+      <c r="K79" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K79" t="str">
+      <c r="L79" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P79" t="str">
+      <c r="Q79" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4394,30 +4632,33 @@
         <v>file</v>
       </c>
       <c r="H80" t="str">
+        <v/>
+      </c>
+      <c r="I80" t="str">
         <v>TG1</v>
       </c>
-      <c r="I80" t="str">
+      <c r="J80" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J80" t="str">
+      <c r="K80" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K80" t="str">
-        <v/>
-      </c>
       <c r="L80" t="str">
+        <v/>
+      </c>
+      <c r="M80" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M80" t="str">
+      <c r="N80" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P80" t="str">
+      <c r="Q80" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4444,30 +4685,33 @@
         <v>file</v>
       </c>
       <c r="H81" t="str">
+        <v/>
+      </c>
+      <c r="I81" t="str">
         <v>TG2</v>
       </c>
-      <c r="I81" t="str">
+      <c r="J81" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J81" t="str">
+      <c r="K81" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K81" t="str">
-        <v/>
-      </c>
       <c r="L81" t="str">
+        <v/>
+      </c>
+      <c r="M81" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M81" t="str">
+      <c r="N81" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P81" t="str">
+      <c r="Q81" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4494,30 +4738,33 @@
         <v>file</v>
       </c>
       <c r="H82" t="str">
+        <v/>
+      </c>
+      <c r="I82" t="str">
         <v>TG1</v>
       </c>
-      <c r="I82" t="str">
+      <c r="J82" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J82" t="str">
+      <c r="K82" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K82" t="str">
-        <v/>
-      </c>
       <c r="L82" t="str">
+        <v/>
+      </c>
+      <c r="M82" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M82" t="str">
+      <c r="N82" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P82" t="str">
+      <c r="Q82" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4544,30 +4791,33 @@
         <v>file</v>
       </c>
       <c r="H83" t="str">
+        <v/>
+      </c>
+      <c r="I83" t="str">
         <v>TG2</v>
       </c>
-      <c r="I83" t="str">
+      <c r="J83" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J83" t="str">
+      <c r="K83" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K83" t="str">
-        <v/>
-      </c>
       <c r="L83" t="str">
+        <v/>
+      </c>
+      <c r="M83" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M83" t="str">
+      <c r="N83" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N83" t="str">
+      <c r="O83" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P83" t="str">
+      <c r="Q83" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4594,30 +4844,33 @@
         <v>file</v>
       </c>
       <c r="H84" t="str">
+        <v/>
+      </c>
+      <c r="I84" t="str">
         <v>TG1</v>
       </c>
-      <c r="I84" t="str">
+      <c r="J84" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J84" t="str">
+      <c r="K84" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K84" t="str">
-        <v/>
-      </c>
       <c r="L84" t="str">
+        <v/>
+      </c>
+      <c r="M84" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M84" t="str">
+      <c r="N84" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N84" t="str">
+      <c r="O84" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P84" t="str">
+      <c r="Q84" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4644,30 +4897,33 @@
         <v>file</v>
       </c>
       <c r="H85" t="str">
+        <v/>
+      </c>
+      <c r="I85" t="str">
         <v>TG2</v>
       </c>
-      <c r="I85" t="str">
+      <c r="J85" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J85" t="str">
+      <c r="K85" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K85" t="str">
-        <v/>
-      </c>
       <c r="L85" t="str">
+        <v/>
+      </c>
+      <c r="M85" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M85" t="str">
+      <c r="N85" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N85" t="str">
+      <c r="O85" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P85" t="str">
+      <c r="Q85" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4694,30 +4950,33 @@
         <v>file</v>
       </c>
       <c r="H86" t="str">
+        <v/>
+      </c>
+      <c r="I86" t="str">
         <v>TG1</v>
       </c>
-      <c r="I86" t="str">
+      <c r="J86" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J86" t="str">
+      <c r="K86" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P86" t="str">
+      <c r="Q86" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4744,30 +5003,33 @@
         <v>file</v>
       </c>
       <c r="H87" t="str">
+        <v/>
+      </c>
+      <c r="I87" t="str">
         <v>TG2</v>
       </c>
-      <c r="I87" t="str">
+      <c r="J87" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J87" t="str">
+      <c r="K87" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K87" t="str">
-        <v/>
-      </c>
       <c r="L87" t="str">
+        <v/>
+      </c>
+      <c r="M87" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M87" t="str">
+      <c r="N87" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N87" t="str">
+      <c r="O87" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P87" t="str">
+      <c r="Q87" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4794,30 +5056,33 @@
         <v>file</v>
       </c>
       <c r="H88" t="str">
+        <v/>
+      </c>
+      <c r="I88" t="str">
         <v>TG1</v>
       </c>
-      <c r="I88" t="str">
+      <c r="J88" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J88" t="str">
+      <c r="K88" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K88" t="str">
-        <v/>
-      </c>
       <c r="L88" t="str">
+        <v/>
+      </c>
+      <c r="M88" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M88" t="str">
+      <c r="N88" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N88" t="str">
+      <c r="O88" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P88" t="str">
+      <c r="Q88" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4844,30 +5109,33 @@
         <v>file</v>
       </c>
       <c r="H89" t="str">
+        <v/>
+      </c>
+      <c r="I89" t="str">
         <v>TG2</v>
       </c>
-      <c r="I89" t="str">
+      <c r="J89" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J89" t="str">
+      <c r="K89" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K89" t="str">
-        <v/>
-      </c>
       <c r="L89" t="str">
+        <v/>
+      </c>
+      <c r="M89" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M89" t="str">
+      <c r="N89" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N89" t="str">
+      <c r="O89" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P89" t="str">
+      <c r="Q89" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4894,30 +5162,33 @@
         <v>file</v>
       </c>
       <c r="H90" t="str">
+        <v/>
+      </c>
+      <c r="I90" t="str">
         <v>TG1</v>
       </c>
-      <c r="I90" t="str">
+      <c r="J90" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J90" t="str">
+      <c r="K90" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K90" t="str">
-        <v/>
-      </c>
       <c r="L90" t="str">
+        <v/>
+      </c>
+      <c r="M90" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M90" t="str">
+      <c r="N90" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N90" t="str">
+      <c r="O90" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P90" t="str">
+      <c r="Q90" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4944,30 +5215,33 @@
         <v>file</v>
       </c>
       <c r="H91" t="str">
+        <v/>
+      </c>
+      <c r="I91" t="str">
         <v>TG2</v>
       </c>
-      <c r="I91" t="str">
+      <c r="J91" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J91" t="str">
+      <c r="K91" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K91" t="str">
-        <v/>
-      </c>
       <c r="L91" t="str">
+        <v/>
+      </c>
+      <c r="M91" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M91" t="str">
+      <c r="N91" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N91" t="str">
+      <c r="O91" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O91" t="str">
+      <c r="P91" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P91" t="str">
+      <c r="Q91" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4994,30 +5268,33 @@
         <v>file</v>
       </c>
       <c r="H92" t="str">
+        <v/>
+      </c>
+      <c r="I92" t="str">
         <v>TG1</v>
       </c>
-      <c r="I92" t="str">
+      <c r="J92" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J92" t="str">
+      <c r="K92" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K92" t="str">
-        <v/>
-      </c>
       <c r="L92" t="str">
+        <v/>
+      </c>
+      <c r="M92" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M92" t="str">
+      <c r="N92" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N92" t="str">
+      <c r="O92" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P92" t="str">
+      <c r="Q92" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5044,30 +5321,33 @@
         <v>file</v>
       </c>
       <c r="H93" t="str">
+        <v/>
+      </c>
+      <c r="I93" t="str">
         <v>TG2</v>
       </c>
-      <c r="I93" t="str">
+      <c r="J93" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J93" t="str">
+      <c r="K93" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L93" t="str">
+      <c r="M93" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N93" t="str">
+      <c r="O93" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O93" t="str">
+      <c r="P93" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P93" t="str">
+      <c r="Q93" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5094,30 +5374,33 @@
         <v>file</v>
       </c>
       <c r="H94" t="str">
+        <v/>
+      </c>
+      <c r="I94" t="str">
         <v>TG1</v>
       </c>
-      <c r="I94" t="str">
+      <c r="J94" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J94" t="str">
+      <c r="K94" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K94" t="str">
-        <v/>
-      </c>
       <c r="L94" t="str">
+        <v/>
+      </c>
+      <c r="M94" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M94" t="str">
+      <c r="N94" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N94" t="str">
+      <c r="O94" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O94" t="str">
+      <c r="P94" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P94" t="str">
+      <c r="Q94" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5144,30 +5427,33 @@
         <v>file</v>
       </c>
       <c r="H95" t="str">
+        <v/>
+      </c>
+      <c r="I95" t="str">
         <v>TG2</v>
       </c>
-      <c r="I95" t="str">
+      <c r="J95" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J95" t="str">
+      <c r="K95" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K95" t="str">
-        <v/>
-      </c>
       <c r="L95" t="str">
+        <v/>
+      </c>
+      <c r="M95" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M95" t="str">
+      <c r="N95" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N95" t="str">
+      <c r="O95" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O95" t="str">
+      <c r="P95" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P95" t="str">
+      <c r="Q95" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5194,30 +5480,33 @@
         <v>file</v>
       </c>
       <c r="H96" t="str">
+        <v/>
+      </c>
+      <c r="I96" t="str">
         <v>TG1</v>
       </c>
-      <c r="I96" t="str">
+      <c r="J96" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J96" t="str">
+      <c r="K96" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K96" t="str">
-        <v/>
-      </c>
       <c r="L96" t="str">
+        <v/>
+      </c>
+      <c r="M96" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M96" t="str">
+      <c r="N96" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N96" t="str">
+      <c r="O96" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O96" t="str">
+      <c r="P96" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P96" t="str">
+      <c r="Q96" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5244,30 +5533,33 @@
         <v>file</v>
       </c>
       <c r="H97" t="str">
+        <v/>
+      </c>
+      <c r="I97" t="str">
         <v>TG2</v>
       </c>
-      <c r="I97" t="str">
+      <c r="J97" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J97" t="str">
+      <c r="K97" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K97" t="str">
-        <v/>
-      </c>
       <c r="L97" t="str">
+        <v/>
+      </c>
+      <c r="M97" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M97" t="str">
+      <c r="N97" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N97" t="str">
+      <c r="O97" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O97" t="str">
+      <c r="P97" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P97" t="str">
+      <c r="Q97" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5294,30 +5586,33 @@
         <v>file</v>
       </c>
       <c r="H98" t="str">
+        <v/>
+      </c>
+      <c r="I98" t="str">
         <v>TG1</v>
       </c>
-      <c r="I98" t="str">
+      <c r="J98" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J98" t="str">
+      <c r="K98" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K98" t="str">
-        <v/>
-      </c>
       <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M98" t="str">
+      <c r="N98" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N98" t="str">
+      <c r="O98" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O98" t="str">
+      <c r="P98" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P98" t="str">
+      <c r="Q98" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5344,30 +5639,33 @@
         <v>file</v>
       </c>
       <c r="H99" t="str">
+        <v/>
+      </c>
+      <c r="I99" t="str">
         <v>TG2</v>
       </c>
-      <c r="I99" t="str">
+      <c r="J99" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J99" t="str">
+      <c r="K99" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K99" t="str">
-        <v/>
-      </c>
       <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M99" t="str">
+      <c r="N99" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N99" t="str">
+      <c r="O99" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O99" t="str">
+      <c r="P99" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P99" t="str">
+      <c r="Q99" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5394,30 +5692,33 @@
         <v>file</v>
       </c>
       <c r="H100" t="str">
+        <v/>
+      </c>
+      <c r="I100" t="str">
         <v>TG1</v>
       </c>
-      <c r="I100" t="str">
+      <c r="J100" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J100" t="str">
+      <c r="K100" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L100" t="str">
+      <c r="M100" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N100" t="str">
+      <c r="O100" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O100" t="str">
+      <c r="P100" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P100" t="str">
+      <c r="Q100" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5444,30 +5745,33 @@
         <v>file</v>
       </c>
       <c r="H101" t="str">
+        <v/>
+      </c>
+      <c r="I101" t="str">
         <v>TG2</v>
       </c>
-      <c r="I101" t="str">
+      <c r="J101" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J101" t="str">
+      <c r="K101" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K101" t="str">
-        <v/>
-      </c>
       <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M101" t="str">
+      <c r="N101" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N101" t="str">
+      <c r="O101" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O101" t="str">
+      <c r="P101" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P101" t="str">
+      <c r="Q101" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5494,30 +5798,33 @@
         <v>file</v>
       </c>
       <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
         <v>TG1</v>
       </c>
-      <c r="I102" t="str">
+      <c r="J102" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J102" t="str">
+      <c r="K102" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
       <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M102" t="str">
+      <c r="N102" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N102" t="str">
+      <c r="O102" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P102" t="str">
+      <c r="Q102" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5544,30 +5851,33 @@
         <v>file</v>
       </c>
       <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
         <v>TG2</v>
       </c>
-      <c r="I103" t="str">
+      <c r="J103" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J103" t="str">
+      <c r="K103" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K103" t="str">
-        <v/>
-      </c>
       <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M103" t="str">
+      <c r="N103" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N103" t="str">
+      <c r="O103" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O103" t="str">
+      <c r="P103" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P103" t="str">
+      <c r="Q103" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5594,30 +5904,33 @@
         <v>file</v>
       </c>
       <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
         <v>TG1</v>
       </c>
-      <c r="I104" t="str">
+      <c r="J104" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J104" t="str">
+      <c r="K104" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K104" t="str">
-        <v/>
-      </c>
       <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M104" t="str">
+      <c r="N104" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N104" t="str">
+      <c r="O104" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O104" t="str">
+      <c r="P104" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P104" t="str">
+      <c r="Q104" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5644,30 +5957,33 @@
         <v>file</v>
       </c>
       <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
         <v>TG2</v>
       </c>
-      <c r="I105" t="str">
+      <c r="J105" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J105" t="str">
+      <c r="K105" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K105" t="str">
-        <v/>
-      </c>
       <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M105" t="str">
+      <c r="N105" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N105" t="str">
+      <c r="O105" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O105" t="str">
+      <c r="P105" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P105" t="str">
+      <c r="Q105" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5694,30 +6010,33 @@
         <v>file</v>
       </c>
       <c r="H106" t="str">
+        <v/>
+      </c>
+      <c r="I106" t="str">
         <v>TG1</v>
       </c>
-      <c r="I106" t="str">
+      <c r="J106" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J106" t="str">
+      <c r="K106" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K106" t="str">
-        <v/>
-      </c>
       <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M106" t="str">
+      <c r="N106" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N106" t="str">
+      <c r="O106" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O106" t="str">
+      <c r="P106" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P106" t="str">
+      <c r="Q106" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5744,30 +6063,33 @@
         <v>file</v>
       </c>
       <c r="H107" t="str">
+        <v/>
+      </c>
+      <c r="I107" t="str">
         <v>TG2</v>
       </c>
-      <c r="I107" t="str">
+      <c r="J107" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J107" t="str">
+      <c r="K107" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L107" t="str">
+      <c r="M107" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N107" t="str">
+      <c r="O107" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O107" t="str">
+      <c r="P107" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P107" t="str">
+      <c r="Q107" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5794,30 +6116,33 @@
         <v>file</v>
       </c>
       <c r="H108" t="str">
+        <v/>
+      </c>
+      <c r="I108" t="str">
         <v>TG1</v>
       </c>
-      <c r="I108" t="str">
+      <c r="J108" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J108" t="str">
+      <c r="K108" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K108" t="str">
-        <v/>
-      </c>
       <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M108" t="str">
+      <c r="N108" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N108" t="str">
+      <c r="O108" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O108" t="str">
+      <c r="P108" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P108" t="str">
+      <c r="Q108" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5844,30 +6169,33 @@
         <v>file</v>
       </c>
       <c r="H109" t="str">
+        <v/>
+      </c>
+      <c r="I109" t="str">
         <v>TG2</v>
       </c>
-      <c r="I109" t="str">
+      <c r="J109" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J109" t="str">
+      <c r="K109" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K109" t="str">
-        <v/>
-      </c>
       <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M109" t="str">
+      <c r="N109" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N109" t="str">
+      <c r="O109" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O109" t="str">
+      <c r="P109" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P109" t="str">
+      <c r="Q109" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5894,30 +6222,33 @@
         <v>file</v>
       </c>
       <c r="H110" t="str">
+        <v/>
+      </c>
+      <c r="I110" t="str">
         <v>TG1</v>
       </c>
-      <c r="I110" t="str">
+      <c r="J110" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J110" t="str">
+      <c r="K110" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K110" t="str">
-        <v/>
-      </c>
       <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M110" t="str">
+      <c r="N110" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N110" t="str">
+      <c r="O110" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O110" t="str">
+      <c r="P110" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P110" t="str">
+      <c r="Q110" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5944,30 +6275,33 @@
         <v>file</v>
       </c>
       <c r="H111" t="str">
+        <v/>
+      </c>
+      <c r="I111" t="str">
         <v>TG2</v>
       </c>
-      <c r="I111" t="str">
+      <c r="J111" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J111" t="str">
+      <c r="K111" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K111" t="str">
-        <v/>
-      </c>
       <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M111" t="str">
+      <c r="N111" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N111" t="str">
+      <c r="O111" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O111" t="str">
+      <c r="P111" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P111" t="str">
+      <c r="Q111" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5994,30 +6328,33 @@
         <v>file</v>
       </c>
       <c r="H112" t="str">
+        <v/>
+      </c>
+      <c r="I112" t="str">
         <v>TG1</v>
       </c>
-      <c r="I112" t="str">
+      <c r="J112" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J112" t="str">
+      <c r="K112" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K112" t="str">
-        <v/>
-      </c>
       <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M112" t="str">
+      <c r="N112" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N112" t="str">
+      <c r="O112" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O112" t="str">
+      <c r="P112" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P112" t="str">
+      <c r="Q112" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6044,30 +6381,33 @@
         <v>file</v>
       </c>
       <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
         <v>TG2</v>
       </c>
-      <c r="I113" t="str">
+      <c r="J113" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J113" t="str">
+      <c r="K113" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K113" t="str">
-        <v/>
-      </c>
       <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M113" t="str">
+      <c r="N113" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N113" t="str">
+      <c r="O113" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O113" t="str">
+      <c r="P113" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P113" t="str">
+      <c r="Q113" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6094,30 +6434,33 @@
         <v>file</v>
       </c>
       <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
         <v>TG1</v>
       </c>
-      <c r="I114" t="str">
+      <c r="J114" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J114" t="str">
+      <c r="K114" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K114" t="str">
+      <c r="L114" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L114" t="str">
+      <c r="M114" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N114" t="str">
+      <c r="O114" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O114" t="str">
+      <c r="P114" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P114" t="str">
+      <c r="Q114" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6144,30 +6487,33 @@
         <v>file</v>
       </c>
       <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
         <v>TG2</v>
       </c>
-      <c r="I115" t="str">
+      <c r="J115" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J115" t="str">
+      <c r="K115" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K115" t="str">
-        <v/>
-      </c>
       <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M115" t="str">
+      <c r="N115" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N115" t="str">
+      <c r="O115" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O115" t="str">
+      <c r="P115" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P115" t="str">
+      <c r="Q115" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6194,30 +6540,33 @@
         <v>file</v>
       </c>
       <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
         <v>TG1</v>
       </c>
-      <c r="I116" t="str">
+      <c r="J116" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J116" t="str">
+      <c r="K116" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K116" t="str">
-        <v/>
-      </c>
       <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M116" t="str">
+      <c r="N116" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N116" t="str">
+      <c r="O116" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O116" t="str">
+      <c r="P116" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P116" t="str">
+      <c r="Q116" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6244,30 +6593,33 @@
         <v>file</v>
       </c>
       <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
         <v>TG2</v>
       </c>
-      <c r="I117" t="str">
+      <c r="J117" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J117" t="str">
+      <c r="K117" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K117" t="str">
-        <v/>
-      </c>
       <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M117" t="str">
+      <c r="N117" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N117" t="str">
+      <c r="O117" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O117" t="str">
+      <c r="P117" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P117" t="str">
+      <c r="Q117" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6294,30 +6646,33 @@
         <v>file</v>
       </c>
       <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
         <v>TG1</v>
       </c>
-      <c r="I118" t="str">
+      <c r="J118" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J118" t="str">
+      <c r="K118" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K118" t="str">
-        <v/>
-      </c>
       <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M118" t="str">
+      <c r="N118" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N118" t="str">
+      <c r="O118" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O118" t="str">
+      <c r="P118" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P118" t="str">
+      <c r="Q118" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6344,30 +6699,33 @@
         <v>file</v>
       </c>
       <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
         <v>TG2</v>
       </c>
-      <c r="I119" t="str">
+      <c r="J119" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J119" t="str">
+      <c r="K119" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K119" t="str">
-        <v/>
-      </c>
       <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M119" t="str">
+      <c r="N119" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N119" t="str">
+      <c r="O119" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O119" t="str">
+      <c r="P119" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P119" t="str">
+      <c r="Q119" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6394,30 +6752,33 @@
         <v>file</v>
       </c>
       <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
         <v>TG1</v>
       </c>
-      <c r="I120" t="str">
+      <c r="J120" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J120" t="str">
+      <c r="K120" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K120" t="str">
-        <v/>
-      </c>
       <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M120" t="str">
+      <c r="N120" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N120" t="str">
+      <c r="O120" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O120" t="str">
+      <c r="P120" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P120" t="str">
+      <c r="Q120" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6444,30 +6805,33 @@
         <v>file</v>
       </c>
       <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
         <v>TG2</v>
       </c>
-      <c r="I121" t="str">
+      <c r="J121" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J121" t="str">
+      <c r="K121" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K121" t="str">
+      <c r="L121" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L121" t="str">
+      <c r="M121" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N121" t="str">
+      <c r="O121" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O121" t="str">
+      <c r="P121" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P121" t="str">
+      <c r="Q121" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6494,30 +6858,33 @@
         <v>file</v>
       </c>
       <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
         <v>TG1</v>
       </c>
-      <c r="I122" t="str">
+      <c r="J122" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J122" t="str">
+      <c r="K122" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K122" t="str">
-        <v/>
-      </c>
       <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M122" t="str">
+      <c r="N122" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N122" t="str">
+      <c r="O122" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O122" t="str">
+      <c r="P122" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P122" t="str">
+      <c r="Q122" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6544,30 +6911,33 @@
         <v>file</v>
       </c>
       <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
         <v>TG2</v>
       </c>
-      <c r="I123" t="str">
+      <c r="J123" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J123" t="str">
+      <c r="K123" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K123" t="str">
-        <v/>
-      </c>
       <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M123" t="str">
+      <c r="N123" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N123" t="str">
+      <c r="O123" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O123" t="str">
+      <c r="P123" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P123" t="str">
+      <c r="Q123" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6594,30 +6964,33 @@
         <v>file</v>
       </c>
       <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
         <v>TG1</v>
       </c>
-      <c r="I124" t="str">
+      <c r="J124" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J124" t="str">
+      <c r="K124" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K124" t="str">
-        <v/>
-      </c>
       <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M124" t="str">
+      <c r="N124" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N124" t="str">
+      <c r="O124" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O124" t="str">
+      <c r="P124" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P124" t="str">
+      <c r="Q124" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6644,30 +7017,33 @@
         <v>file</v>
       </c>
       <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
         <v>TG2</v>
       </c>
-      <c r="I125" t="str">
+      <c r="J125" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J125" t="str">
+      <c r="K125" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K125" t="str">
-        <v/>
-      </c>
       <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M125" t="str">
+      <c r="N125" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N125" t="str">
+      <c r="O125" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O125" t="str">
+      <c r="P125" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P125" t="str">
+      <c r="Q125" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6694,30 +7070,33 @@
         <v>file</v>
       </c>
       <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
         <v>TG1</v>
       </c>
-      <c r="I126" t="str">
+      <c r="J126" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J126" t="str">
+      <c r="K126" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K126" t="str">
-        <v/>
-      </c>
       <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M126" t="str">
+      <c r="N126" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N126" t="str">
+      <c r="O126" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O126" t="str">
+      <c r="P126" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P126" t="str">
+      <c r="Q126" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6744,30 +7123,33 @@
         <v>file</v>
       </c>
       <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
         <v>TG2</v>
       </c>
-      <c r="I127" t="str">
+      <c r="J127" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J127" t="str">
+      <c r="K127" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K127" t="str">
-        <v/>
-      </c>
       <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M127" t="str">
+      <c r="N127" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N127" t="str">
+      <c r="O127" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O127" t="str">
+      <c r="P127" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P127" t="str">
+      <c r="Q127" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6794,30 +7176,33 @@
         <v>file</v>
       </c>
       <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
         <v>TG1</v>
       </c>
-      <c r="I128" t="str">
+      <c r="J128" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J128" t="str">
+      <c r="K128" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K128" t="str">
+      <c r="L128" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L128" t="str">
+      <c r="M128" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N128" t="str">
+      <c r="O128" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O128" t="str">
+      <c r="P128" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P128" t="str">
+      <c r="Q128" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6844,30 +7229,33 @@
         <v>file</v>
       </c>
       <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
         <v>TG2</v>
       </c>
-      <c r="I129" t="str">
+      <c r="J129" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J129" t="str">
+      <c r="K129" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K129" t="str">
-        <v/>
-      </c>
       <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M129" t="str">
+      <c r="N129" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N129" t="str">
+      <c r="O129" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O129" t="str">
+      <c r="P129" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P129" t="str">
+      <c r="Q129" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6894,30 +7282,33 @@
         <v>file</v>
       </c>
       <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
         <v>TG1</v>
       </c>
-      <c r="I130" t="str">
+      <c r="J130" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J130" t="str">
+      <c r="K130" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K130" t="str">
-        <v/>
-      </c>
       <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M130" t="str">
+      <c r="N130" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N130" t="str">
+      <c r="O130" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O130" t="str">
+      <c r="P130" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P130" t="str">
+      <c r="Q130" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6944,30 +7335,33 @@
         <v>file</v>
       </c>
       <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
         <v>TG2</v>
       </c>
-      <c r="I131" t="str">
+      <c r="J131" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J131" t="str">
+      <c r="K131" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K131" t="str">
-        <v/>
-      </c>
       <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M131" t="str">
+      <c r="N131" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N131" t="str">
+      <c r="O131" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O131" t="str">
+      <c r="P131" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P131" t="str">
+      <c r="Q131" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6994,30 +7388,33 @@
         <v>file</v>
       </c>
       <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
         <v>TG1</v>
       </c>
-      <c r="I132" t="str">
+      <c r="J132" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J132" t="str">
+      <c r="K132" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K132" t="str">
-        <v/>
-      </c>
       <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M132" t="str">
+      <c r="N132" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N132" t="str">
+      <c r="O132" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O132" t="str">
+      <c r="P132" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P132" t="str">
+      <c r="Q132" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7044,30 +7441,33 @@
         <v>file</v>
       </c>
       <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
         <v>TG2</v>
       </c>
-      <c r="I133" t="str">
+      <c r="J133" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J133" t="str">
+      <c r="K133" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K133" t="str">
-        <v/>
-      </c>
       <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M133" t="str">
+      <c r="N133" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N133" t="str">
+      <c r="O133" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O133" t="str">
+      <c r="P133" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P133" t="str">
+      <c r="Q133" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7094,30 +7494,33 @@
         <v>file</v>
       </c>
       <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
         <v>TG1</v>
       </c>
-      <c r="I134" t="str">
+      <c r="J134" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J134" t="str">
+      <c r="K134" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K134" t="str">
-        <v/>
-      </c>
       <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M134" t="str">
+      <c r="N134" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N134" t="str">
+      <c r="O134" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O134" t="str">
+      <c r="P134" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P134" t="str">
+      <c r="Q134" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7144,30 +7547,33 @@
         <v>file</v>
       </c>
       <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
         <v>TG2</v>
       </c>
-      <c r="I135" t="str">
+      <c r="J135" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J135" t="str">
+      <c r="K135" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K135" t="str">
+      <c r="L135" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L135" t="str">
+      <c r="M135" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N135" t="str">
+      <c r="O135" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O135" t="str">
+      <c r="P135" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P135" t="str">
+      <c r="Q135" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7194,30 +7600,33 @@
         <v>file</v>
       </c>
       <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
         <v>TG1</v>
       </c>
-      <c r="I136" t="str">
+      <c r="J136" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J136" t="str">
+      <c r="K136" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K136" t="str">
-        <v/>
-      </c>
       <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M136" t="str">
+      <c r="N136" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N136" t="str">
+      <c r="O136" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O136" t="str">
+      <c r="P136" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P136" t="str">
+      <c r="Q136" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7244,30 +7653,33 @@
         <v>file</v>
       </c>
       <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
         <v>TG2</v>
       </c>
-      <c r="I137" t="str">
+      <c r="J137" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J137" t="str">
+      <c r="K137" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K137" t="str">
-        <v/>
-      </c>
       <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M137" t="str">
+      <c r="N137" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N137" t="str">
+      <c r="O137" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O137" t="str">
+      <c r="P137" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P137" t="str">
+      <c r="Q137" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7294,30 +7706,33 @@
         <v>file</v>
       </c>
       <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
         <v>TG1</v>
       </c>
-      <c r="I138" t="str">
+      <c r="J138" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J138" t="str">
+      <c r="K138" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K138" t="str">
-        <v/>
-      </c>
       <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M138" t="str">
+      <c r="N138" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N138" t="str">
+      <c r="O138" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O138" t="str">
+      <c r="P138" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P138" t="str">
+      <c r="Q138" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7344,30 +7759,33 @@
         <v>file</v>
       </c>
       <c r="H139" t="str">
+        <v/>
+      </c>
+      <c r="I139" t="str">
         <v>TG2</v>
       </c>
-      <c r="I139" t="str">
+      <c r="J139" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J139" t="str">
+      <c r="K139" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K139" t="str">
-        <v/>
-      </c>
       <c r="L139" t="str">
+        <v/>
+      </c>
+      <c r="M139" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M139" t="str">
+      <c r="N139" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N139" t="str">
+      <c r="O139" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O139" t="str">
+      <c r="P139" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P139" t="str">
+      <c r="Q139" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7394,30 +7812,33 @@
         <v>file</v>
       </c>
       <c r="H140" t="str">
+        <v/>
+      </c>
+      <c r="I140" t="str">
         <v>TG1</v>
       </c>
-      <c r="I140" t="str">
+      <c r="J140" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J140" t="str">
+      <c r="K140" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K140" t="str">
-        <v/>
-      </c>
       <c r="L140" t="str">
+        <v/>
+      </c>
+      <c r="M140" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M140" t="str">
+      <c r="N140" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N140" t="str">
+      <c r="O140" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O140" t="str">
+      <c r="P140" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P140" t="str">
+      <c r="Q140" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7444,30 +7865,33 @@
         <v>file</v>
       </c>
       <c r="H141" t="str">
+        <v/>
+      </c>
+      <c r="I141" t="str">
         <v>TG2</v>
       </c>
-      <c r="I141" t="str">
+      <c r="J141" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J141" t="str">
+      <c r="K141" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K141" t="str">
-        <v/>
-      </c>
       <c r="L141" t="str">
+        <v/>
+      </c>
+      <c r="M141" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M141" t="str">
+      <c r="N141" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N141" t="str">
+      <c r="O141" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O141" t="str">
+      <c r="P141" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P141" t="str">
+      <c r="Q141" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7494,30 +7918,33 @@
         <v>file</v>
       </c>
       <c r="H142" t="str">
+        <v/>
+      </c>
+      <c r="I142" t="str">
         <v>TG1</v>
       </c>
-      <c r="I142" t="str">
+      <c r="J142" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J142" t="str">
+      <c r="K142" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K142" t="str">
+      <c r="L142" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L142" t="str">
+      <c r="M142" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N142" t="str">
+      <c r="O142" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O142" t="str">
+      <c r="P142" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P142" t="str">
+      <c r="Q142" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7544,30 +7971,33 @@
         <v>file</v>
       </c>
       <c r="H143" t="str">
+        <v/>
+      </c>
+      <c r="I143" t="str">
         <v>TG2</v>
       </c>
-      <c r="I143" t="str">
+      <c r="J143" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J143" t="str">
+      <c r="K143" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K143" t="str">
-        <v/>
-      </c>
       <c r="L143" t="str">
+        <v/>
+      </c>
+      <c r="M143" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M143" t="str">
+      <c r="N143" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N143" t="str">
+      <c r="O143" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O143" t="str">
+      <c r="P143" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P143" t="str">
+      <c r="Q143" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7594,30 +8024,33 @@
         <v>file</v>
       </c>
       <c r="H144" t="str">
+        <v/>
+      </c>
+      <c r="I144" t="str">
         <v>TG1</v>
       </c>
-      <c r="I144" t="str">
+      <c r="J144" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J144" t="str">
+      <c r="K144" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K144" t="str">
-        <v/>
-      </c>
       <c r="L144" t="str">
+        <v/>
+      </c>
+      <c r="M144" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M144" t="str">
+      <c r="N144" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N144" t="str">
+      <c r="O144" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O144" t="str">
+      <c r="P144" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P144" t="str">
+      <c r="Q144" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7644,30 +8077,33 @@
         <v>file</v>
       </c>
       <c r="H145" t="str">
+        <v/>
+      </c>
+      <c r="I145" t="str">
         <v>TG2</v>
       </c>
-      <c r="I145" t="str">
+      <c r="J145" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J145" t="str">
+      <c r="K145" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K145" t="str">
-        <v/>
-      </c>
       <c r="L145" t="str">
+        <v/>
+      </c>
+      <c r="M145" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M145" t="str">
+      <c r="N145" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N145" t="str">
+      <c r="O145" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O145" t="str">
+      <c r="P145" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P145" t="str">
+      <c r="Q145" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7694,30 +8130,33 @@
         <v>file</v>
       </c>
       <c r="H146" t="str">
+        <v/>
+      </c>
+      <c r="I146" t="str">
         <v>TG1</v>
       </c>
-      <c r="I146" t="str">
+      <c r="J146" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J146" t="str">
+      <c r="K146" t="str">
         <v>CL G1</v>
       </c>
-      <c r="K146" t="str">
-        <v/>
-      </c>
       <c r="L146" t="str">
+        <v/>
+      </c>
+      <c r="M146" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M146" t="str">
+      <c r="N146" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N146" t="str">
+      <c r="O146" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O146" t="str">
+      <c r="P146" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P146" t="str">
+      <c r="Q146" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7744,30 +8183,33 @@
         <v>file</v>
       </c>
       <c r="H147" t="str">
+        <v/>
+      </c>
+      <c r="I147" t="str">
         <v>TG2</v>
       </c>
-      <c r="I147" t="str">
+      <c r="J147" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J147" t="str">
+      <c r="K147" t="str">
         <v>ML G2</v>
       </c>
-      <c r="K147" t="str">
-        <v/>
-      </c>
       <c r="L147" t="str">
+        <v/>
+      </c>
+      <c r="M147" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M147" t="str">
+      <c r="N147" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N147" t="str">
+      <c r="O147" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O147" t="str">
+      <c r="P147" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P147" t="str">
+      <c r="Q147" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7794,30 +8236,33 @@
         <v>file</v>
       </c>
       <c r="H148" t="str">
+        <v/>
+      </c>
+      <c r="I148" t="str">
         <v>TG1</v>
       </c>
-      <c r="I148" t="str">
+      <c r="J148" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J148" t="str">
+      <c r="K148" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K148" t="str">
-        <v/>
-      </c>
       <c r="L148" t="str">
+        <v/>
+      </c>
+      <c r="M148" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M148" t="str">
+      <c r="N148" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N148" t="str">
+      <c r="O148" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O148" t="str">
+      <c r="P148" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P148" t="str">
+      <c r="Q148" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7844,30 +8289,33 @@
         <v>file</v>
       </c>
       <c r="H149" t="str">
+        <v/>
+      </c>
+      <c r="I149" t="str">
         <v>TG2</v>
       </c>
-      <c r="I149" t="str">
+      <c r="J149" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J149" t="str">
+      <c r="K149" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K149" t="str">
+      <c r="L149" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="L149" t="str">
+      <c r="M149" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N149" t="str">
+      <c r="O149" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O149" t="str">
+      <c r="P149" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P149" t="str">
+      <c r="Q149" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7894,30 +8342,33 @@
         <v>file</v>
       </c>
       <c r="H150" t="str">
+        <v/>
+      </c>
+      <c r="I150" t="str">
         <v>TG1</v>
       </c>
-      <c r="I150" t="str">
+      <c r="J150" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J150" t="str">
+      <c r="K150" t="str">
         <v>ML G1</v>
       </c>
-      <c r="K150" t="str">
-        <v/>
-      </c>
       <c r="L150" t="str">
+        <v/>
+      </c>
+      <c r="M150" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M150" t="str">
+      <c r="N150" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N150" t="str">
+      <c r="O150" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O150" t="str">
+      <c r="P150" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P150" t="str">
+      <c r="Q150" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7944,30 +8395,33 @@
         <v>file</v>
       </c>
       <c r="H151" t="str">
+        <v/>
+      </c>
+      <c r="I151" t="str">
         <v>TG2</v>
       </c>
-      <c r="I151" t="str">
+      <c r="J151" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J151" t="str">
+      <c r="K151" t="str">
         <v>TL G2</v>
       </c>
-      <c r="K151" t="str">
-        <v/>
-      </c>
       <c r="L151" t="str">
+        <v/>
+      </c>
+      <c r="M151" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M151" t="str">
+      <c r="N151" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N151" t="str">
+      <c r="O151" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O151" t="str">
+      <c r="P151" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P151" t="str">
+      <c r="Q151" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7994,30 +8448,33 @@
         <v>file</v>
       </c>
       <c r="H152" t="str">
+        <v/>
+      </c>
+      <c r="I152" t="str">
         <v>TG1</v>
       </c>
-      <c r="I152" t="str">
+      <c r="J152" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J152" t="str">
+      <c r="K152" t="str">
         <v>CL G3</v>
       </c>
-      <c r="K152" t="str">
-        <v/>
-      </c>
       <c r="L152" t="str">
+        <v/>
+      </c>
+      <c r="M152" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M152" t="str">
+      <c r="N152" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N152" t="str">
+      <c r="O152" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O152" t="str">
+      <c r="P152" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P152" t="str">
+      <c r="Q152" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8044,30 +8501,33 @@
         <v>file</v>
       </c>
       <c r="H153" t="str">
+        <v/>
+      </c>
+      <c r="I153" t="str">
         <v>TG2</v>
       </c>
-      <c r="I153" t="str">
+      <c r="J153" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J153" t="str">
+      <c r="K153" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K153" t="str">
-        <v/>
-      </c>
       <c r="L153" t="str">
+        <v/>
+      </c>
+      <c r="M153" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M153" t="str">
+      <c r="N153" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N153" t="str">
+      <c r="O153" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O153" t="str">
+      <c r="P153" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P153" t="str">
+      <c r="Q153" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8094,30 +8554,33 @@
         <v>file</v>
       </c>
       <c r="H154" t="str">
+        <v/>
+      </c>
+      <c r="I154" t="str">
         <v>TG1</v>
       </c>
-      <c r="I154" t="str">
+      <c r="J154" t="str">
         <v>EL G1</v>
       </c>
-      <c r="J154" t="str">
+      <c r="K154" t="str">
         <v>TL G1</v>
       </c>
-      <c r="K154" t="str">
-        <v/>
-      </c>
       <c r="L154" t="str">
+        <v/>
+      </c>
+      <c r="M154" t="str">
         <v>MA G1</v>
       </c>
-      <c r="M154" t="str">
+      <c r="N154" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="N154" t="str">
+      <c r="O154" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="O154" t="str">
+      <c r="P154" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="P154" t="str">
+      <c r="Q154" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8144,30 +8607,33 @@
         <v>file</v>
       </c>
       <c r="H155" t="str">
+        <v/>
+      </c>
+      <c r="I155" t="str">
         <v>TG2</v>
       </c>
-      <c r="I155" t="str">
+      <c r="J155" t="str">
         <v>EL G2</v>
       </c>
-      <c r="J155" t="str">
+      <c r="K155" t="str">
         <v>CL G2</v>
       </c>
-      <c r="K155" t="str">
-        <v/>
-      </c>
       <c r="L155" t="str">
+        <v/>
+      </c>
+      <c r="M155" t="str">
         <v>MA G2</v>
       </c>
-      <c r="M155" t="str">
+      <c r="N155" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="N155" t="str">
+      <c r="O155" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="O155" t="str">
+      <c r="P155" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="P155" t="str">
+      <c r="Q155" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8194,30 +8660,33 @@
         <v>file</v>
       </c>
       <c r="H156" t="str">
+        <v/>
+      </c>
+      <c r="I156" t="str">
         <v>TG1</v>
       </c>
-      <c r="I156" t="str">
+      <c r="J156" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J156" t="str">
+      <c r="K156" t="str">
         <v>ML G3</v>
       </c>
-      <c r="K156" t="str">
+      <c r="L156" t="str">
         <v>MALAY</v>
       </c>
-      <c r="L156" t="str">
+      <c r="M156" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O156" t="str">
+      <c r="P156" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P156" t="str">
+      <c r="Q156" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8244,36 +8713,39 @@
         <v>file</v>
       </c>
       <c r="H157" t="str">
+        <v/>
+      </c>
+      <c r="I157" t="str">
         <v>TG2</v>
       </c>
-      <c r="I157" t="str">
+      <c r="J157" t="str">
         <v>EL G3</v>
       </c>
-      <c r="J157" t="str">
+      <c r="K157" t="str">
         <v>TL G3</v>
       </c>
-      <c r="K157" t="str">
-        <v/>
-      </c>
       <c r="L157" t="str">
+        <v/>
+      </c>
+      <c r="M157" t="str">
         <v>MA G3</v>
       </c>
-      <c r="M157" t="str">
+      <c r="N157" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="N157" t="str">
+      <c r="O157" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="O157" t="str">
+      <c r="P157" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="P157" t="str">
+      <c r="Q157" t="str">
         <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q157"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -409,9 +409,9 @@
     <col min="4" max="4" width="6.83203125" customWidth="1"/>
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="5.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="28.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="6.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
+    <col min="9" max="9" width="28.83203125" customWidth="1"/>
     <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
@@ -442,13 +442,13 @@
         <v>PG</v>
       </c>
       <c r="G1" t="str">
+        <v>TG</v>
+      </c>
+      <c r="H1" t="str">
         <v>Origin</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>SourceName</v>
-      </c>
-      <c r="I1" t="str">
-        <v>TG</v>
       </c>
       <c r="J1" t="str">
         <v>EL</v>
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I2" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v>EL G1</v>
@@ -548,13 +548,13 @@
         <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I3" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J3" t="str">
         <v>EL G2</v>
@@ -601,13 +601,13 @@
         <v>3</v>
       </c>
       <c r="G4" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I4" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J4" t="str">
         <v>EL G3</v>
@@ -654,13 +654,13 @@
         <v>3</v>
       </c>
       <c r="G5" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I5" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J5" t="str">
         <v>EL G3</v>
@@ -707,13 +707,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I6" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J6" t="str">
         <v>EL G1</v>
@@ -760,13 +760,13 @@
         <v>2</v>
       </c>
       <c r="G7" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I7" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J7" t="str">
         <v>EL G2</v>
@@ -813,13 +813,13 @@
         <v>3</v>
       </c>
       <c r="G8" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I8" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J8" t="str">
         <v>EL G3</v>
@@ -866,13 +866,13 @@
         <v>3</v>
       </c>
       <c r="G9" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I9" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J9" t="str">
         <v>EL G3</v>
@@ -919,13 +919,13 @@
         <v>1</v>
       </c>
       <c r="G10" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I10" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J10" t="str">
         <v>EL G1</v>
@@ -972,13 +972,13 @@
         <v>2</v>
       </c>
       <c r="G11" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I11" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J11" t="str">
         <v>EL G2</v>
@@ -1025,13 +1025,13 @@
         <v>3</v>
       </c>
       <c r="G12" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I12" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J12" t="str">
         <v>EL G3</v>
@@ -1078,13 +1078,13 @@
         <v>3</v>
       </c>
       <c r="G13" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H13" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I13" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J13" t="str">
         <v>EL G3</v>
@@ -1131,13 +1131,13 @@
         <v>1</v>
       </c>
       <c r="G14" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I14" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J14" t="str">
         <v>EL G1</v>
@@ -1184,13 +1184,13 @@
         <v>2</v>
       </c>
       <c r="G15" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H15" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I15" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J15" t="str">
         <v>EL G2</v>
@@ -1237,13 +1237,13 @@
         <v>3</v>
       </c>
       <c r="G16" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I16" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J16" t="str">
         <v>EL G3</v>
@@ -1290,13 +1290,13 @@
         <v>3</v>
       </c>
       <c r="G17" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H17" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I17" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J17" t="str">
         <v>EL G3</v>
@@ -1343,13 +1343,13 @@
         <v>1</v>
       </c>
       <c r="G18" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H18" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I18" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J18" t="str">
         <v>EL G1</v>
@@ -1396,13 +1396,13 @@
         <v>2</v>
       </c>
       <c r="G19" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H19" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I19" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J19" t="str">
         <v>EL G2</v>
@@ -1449,13 +1449,13 @@
         <v>3</v>
       </c>
       <c r="G20" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H20" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I20" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J20" t="str">
         <v>EL G3</v>
@@ -1502,13 +1502,13 @@
         <v>3</v>
       </c>
       <c r="G21" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H21" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I21" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J21" t="str">
         <v>EL G3</v>
@@ -1555,13 +1555,13 @@
         <v>1</v>
       </c>
       <c r="G22" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I22" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J22" t="str">
         <v>EL G1</v>
@@ -1608,13 +1608,13 @@
         <v>2</v>
       </c>
       <c r="G23" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H23" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I23" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J23" t="str">
         <v>EL G2</v>
@@ -1661,13 +1661,13 @@
         <v>3</v>
       </c>
       <c r="G24" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H24" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I24" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J24" t="str">
         <v>EL G3</v>
@@ -1714,13 +1714,13 @@
         <v>3</v>
       </c>
       <c r="G25" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H25" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I25" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J25" t="str">
         <v>EL G3</v>
@@ -1767,13 +1767,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I26" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J26" t="str">
         <v>EL G1</v>
@@ -1820,13 +1820,13 @@
         <v>2</v>
       </c>
       <c r="G27" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H27" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I27" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J27" t="str">
         <v>EL G2</v>
@@ -1873,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="G28" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H28" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I28" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J28" t="str">
         <v>EL G3</v>
@@ -1926,13 +1926,13 @@
         <v>3</v>
       </c>
       <c r="G29" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H29" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I29" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J29" t="str">
         <v>EL G3</v>
@@ -1979,13 +1979,13 @@
         <v>1</v>
       </c>
       <c r="G30" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H30" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I30" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J30" t="str">
         <v>EL G1</v>
@@ -2032,13 +2032,13 @@
         <v>2</v>
       </c>
       <c r="G31" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H31" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I31" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J31" t="str">
         <v>EL G2</v>
@@ -2085,13 +2085,13 @@
         <v>3</v>
       </c>
       <c r="G32" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H32" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I32" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J32" t="str">
         <v>EL G3</v>
@@ -2138,13 +2138,13 @@
         <v>3</v>
       </c>
       <c r="G33" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H33" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I33" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J33" t="str">
         <v>EL G3</v>
@@ -2191,13 +2191,13 @@
         <v>1</v>
       </c>
       <c r="G34" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H34" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I34" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J34" t="str">
         <v>EL G1</v>
@@ -2244,13 +2244,13 @@
         <v>2</v>
       </c>
       <c r="G35" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H35" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I35" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J35" t="str">
         <v>EL G2</v>
@@ -2297,13 +2297,13 @@
         <v>3</v>
       </c>
       <c r="G36" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I36" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J36" t="str">
         <v>EL G3</v>
@@ -2350,13 +2350,13 @@
         <v>3</v>
       </c>
       <c r="G37" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H37" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I37" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J37" t="str">
         <v>EL G3</v>
@@ -2403,13 +2403,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H38" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I38" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J38" t="str">
         <v>EL G1</v>
@@ -2456,13 +2456,13 @@
         <v>2</v>
       </c>
       <c r="G39" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H39" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I39" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J39" t="str">
         <v>EL G2</v>
@@ -2509,13 +2509,13 @@
         <v>3</v>
       </c>
       <c r="G40" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H40" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I40" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J40" t="str">
         <v>EL G3</v>
@@ -2562,13 +2562,13 @@
         <v>3</v>
       </c>
       <c r="G41" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H41" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I41" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J41" t="str">
         <v>EL G3</v>
@@ -2615,13 +2615,13 @@
         <v>1</v>
       </c>
       <c r="G42" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H42" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I42" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J42" t="str">
         <v>EL G1</v>
@@ -2668,13 +2668,13 @@
         <v>2</v>
       </c>
       <c r="G43" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H43" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I43" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J43" t="str">
         <v>EL G2</v>
@@ -2721,13 +2721,13 @@
         <v>3</v>
       </c>
       <c r="G44" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H44" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I44" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J44" t="str">
         <v>EL G3</v>
@@ -2774,13 +2774,13 @@
         <v>3</v>
       </c>
       <c r="G45" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H45" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I45" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J45" t="str">
         <v>EL G3</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="G46" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H46" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I46" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J46" t="str">
         <v>EL G1</v>
@@ -2880,13 +2880,13 @@
         <v>2</v>
       </c>
       <c r="G47" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H47" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I47" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J47" t="str">
         <v>EL G2</v>
@@ -2933,13 +2933,13 @@
         <v>3</v>
       </c>
       <c r="G48" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H48" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I48" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J48" t="str">
         <v>EL G3</v>
@@ -2986,13 +2986,13 @@
         <v>3</v>
       </c>
       <c r="G49" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H49" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I49" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J49" t="str">
         <v>EL G3</v>
@@ -3039,13 +3039,13 @@
         <v>1</v>
       </c>
       <c r="G50" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H50" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I50" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J50" t="str">
         <v>EL G1</v>
@@ -3092,13 +3092,13 @@
         <v>2</v>
       </c>
       <c r="G51" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H51" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I51" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J51" t="str">
         <v>EL G2</v>
@@ -3145,13 +3145,13 @@
         <v>3</v>
       </c>
       <c r="G52" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H52" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I52" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J52" t="str">
         <v>EL G3</v>
@@ -3198,13 +3198,13 @@
         <v>3</v>
       </c>
       <c r="G53" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H53" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I53" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J53" t="str">
         <v>EL G3</v>
@@ -3251,13 +3251,13 @@
         <v>1</v>
       </c>
       <c r="G54" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H54" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I54" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J54" t="str">
         <v>EL G1</v>
@@ -3304,13 +3304,13 @@
         <v>2</v>
       </c>
       <c r="G55" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H55" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I55" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J55" t="str">
         <v>EL G2</v>
@@ -3357,13 +3357,13 @@
         <v>3</v>
       </c>
       <c r="G56" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H56" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I56" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J56" t="str">
         <v>EL G3</v>
@@ -3410,13 +3410,13 @@
         <v>3</v>
       </c>
       <c r="G57" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H57" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I57" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J57" t="str">
         <v>EL G3</v>
@@ -3463,13 +3463,13 @@
         <v>1</v>
       </c>
       <c r="G58" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H58" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I58" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J58" t="str">
         <v>EL G1</v>
@@ -3516,13 +3516,13 @@
         <v>2</v>
       </c>
       <c r="G59" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H59" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I59" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J59" t="str">
         <v>EL G2</v>
@@ -3569,13 +3569,13 @@
         <v>3</v>
       </c>
       <c r="G60" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H60" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I60" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J60" t="str">
         <v>EL G3</v>
@@ -3622,13 +3622,13 @@
         <v>3</v>
       </c>
       <c r="G61" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H61" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I61" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J61" t="str">
         <v>EL G3</v>
@@ -3675,13 +3675,13 @@
         <v>1</v>
       </c>
       <c r="G62" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H62" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I62" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J62" t="str">
         <v>EL G1</v>
@@ -3728,13 +3728,13 @@
         <v>2</v>
       </c>
       <c r="G63" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H63" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I63" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J63" t="str">
         <v>EL G2</v>
@@ -3781,13 +3781,13 @@
         <v>3</v>
       </c>
       <c r="G64" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I64" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J64" t="str">
         <v>EL G3</v>
@@ -3834,13 +3834,13 @@
         <v>3</v>
       </c>
       <c r="G65" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H65" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I65" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J65" t="str">
         <v>EL G3</v>
@@ -3887,13 +3887,13 @@
         <v>1</v>
       </c>
       <c r="G66" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I66" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J66" t="str">
         <v>EL G1</v>
@@ -3940,13 +3940,13 @@
         <v>2</v>
       </c>
       <c r="G67" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H67" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I67" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J67" t="str">
         <v>EL G2</v>
@@ -3993,13 +3993,13 @@
         <v>3</v>
       </c>
       <c r="G68" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H68" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I68" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J68" t="str">
         <v>EL G3</v>
@@ -4046,13 +4046,13 @@
         <v>3</v>
       </c>
       <c r="G69" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H69" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I69" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J69" t="str">
         <v>EL G3</v>
@@ -4099,13 +4099,13 @@
         <v>1</v>
       </c>
       <c r="G70" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H70" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I70" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J70" t="str">
         <v>EL G1</v>
@@ -4152,13 +4152,13 @@
         <v>2</v>
       </c>
       <c r="G71" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H71" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I71" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J71" t="str">
         <v>EL G2</v>
@@ -4205,13 +4205,13 @@
         <v>3</v>
       </c>
       <c r="G72" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H72" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I72" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J72" t="str">
         <v>EL G3</v>
@@ -4258,13 +4258,13 @@
         <v>3</v>
       </c>
       <c r="G73" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H73" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I73" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J73" t="str">
         <v>EL G3</v>
@@ -4311,13 +4311,13 @@
         <v>1</v>
       </c>
       <c r="G74" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H74" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I74" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J74" t="str">
         <v>EL G1</v>
@@ -4364,13 +4364,13 @@
         <v>2</v>
       </c>
       <c r="G75" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H75" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I75" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J75" t="str">
         <v>EL G2</v>
@@ -4417,13 +4417,13 @@
         <v>3</v>
       </c>
       <c r="G76" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H76" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I76" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J76" t="str">
         <v>EL G3</v>
@@ -4470,13 +4470,13 @@
         <v>3</v>
       </c>
       <c r="G77" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H77" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I77" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J77" t="str">
         <v>EL G3</v>
@@ -4523,13 +4523,13 @@
         <v>1</v>
       </c>
       <c r="G78" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H78" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I78" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J78" t="str">
         <v>EL G1</v>
@@ -4576,13 +4576,13 @@
         <v>2</v>
       </c>
       <c r="G79" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H79" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I79" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J79" t="str">
         <v>EL G2</v>
@@ -4629,13 +4629,13 @@
         <v>3</v>
       </c>
       <c r="G80" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H80" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I80" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J80" t="str">
         <v>EL G3</v>
@@ -4682,13 +4682,13 @@
         <v>3</v>
       </c>
       <c r="G81" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H81" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I81" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J81" t="str">
         <v>EL G3</v>
@@ -4735,13 +4735,13 @@
         <v>1</v>
       </c>
       <c r="G82" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H82" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I82" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J82" t="str">
         <v>EL G1</v>
@@ -4788,13 +4788,13 @@
         <v>2</v>
       </c>
       <c r="G83" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H83" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I83" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J83" t="str">
         <v>EL G2</v>
@@ -4841,13 +4841,13 @@
         <v>3</v>
       </c>
       <c r="G84" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H84" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I84" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J84" t="str">
         <v>EL G3</v>
@@ -4894,13 +4894,13 @@
         <v>3</v>
       </c>
       <c r="G85" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H85" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I85" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J85" t="str">
         <v>EL G3</v>
@@ -4947,13 +4947,13 @@
         <v>1</v>
       </c>
       <c r="G86" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H86" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I86" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J86" t="str">
         <v>EL G1</v>
@@ -5000,13 +5000,13 @@
         <v>2</v>
       </c>
       <c r="G87" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H87" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I87" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J87" t="str">
         <v>EL G2</v>
@@ -5053,13 +5053,13 @@
         <v>3</v>
       </c>
       <c r="G88" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H88" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I88" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J88" t="str">
         <v>EL G3</v>
@@ -5106,13 +5106,13 @@
         <v>3</v>
       </c>
       <c r="G89" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H89" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I89" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J89" t="str">
         <v>EL G3</v>
@@ -5159,13 +5159,13 @@
         <v>1</v>
       </c>
       <c r="G90" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H90" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I90" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J90" t="str">
         <v>EL G1</v>
@@ -5212,13 +5212,13 @@
         <v>2</v>
       </c>
       <c r="G91" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H91" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I91" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J91" t="str">
         <v>EL G2</v>
@@ -5265,13 +5265,13 @@
         <v>3</v>
       </c>
       <c r="G92" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H92" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I92" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J92" t="str">
         <v>EL G3</v>
@@ -5318,13 +5318,13 @@
         <v>3</v>
       </c>
       <c r="G93" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H93" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I93" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J93" t="str">
         <v>EL G3</v>
@@ -5371,13 +5371,13 @@
         <v>1</v>
       </c>
       <c r="G94" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H94" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I94" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J94" t="str">
         <v>EL G1</v>
@@ -5424,13 +5424,13 @@
         <v>2</v>
       </c>
       <c r="G95" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H95" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I95" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J95" t="str">
         <v>EL G2</v>
@@ -5477,13 +5477,13 @@
         <v>3</v>
       </c>
       <c r="G96" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H96" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I96" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J96" t="str">
         <v>EL G3</v>
@@ -5530,13 +5530,13 @@
         <v>3</v>
       </c>
       <c r="G97" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H97" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I97" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J97" t="str">
         <v>EL G3</v>
@@ -5583,13 +5583,13 @@
         <v>1</v>
       </c>
       <c r="G98" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H98" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I98" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J98" t="str">
         <v>EL G1</v>
@@ -5636,13 +5636,13 @@
         <v>2</v>
       </c>
       <c r="G99" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H99" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I99" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J99" t="str">
         <v>EL G2</v>
@@ -5689,13 +5689,13 @@
         <v>3</v>
       </c>
       <c r="G100" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H100" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I100" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J100" t="str">
         <v>EL G3</v>
@@ -5742,13 +5742,13 @@
         <v>3</v>
       </c>
       <c r="G101" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H101" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I101" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J101" t="str">
         <v>EL G3</v>
@@ -5795,13 +5795,13 @@
         <v>1</v>
       </c>
       <c r="G102" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H102" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I102" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J102" t="str">
         <v>EL G1</v>
@@ -5848,13 +5848,13 @@
         <v>2</v>
       </c>
       <c r="G103" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H103" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I103" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J103" t="str">
         <v>EL G2</v>
@@ -5901,13 +5901,13 @@
         <v>3</v>
       </c>
       <c r="G104" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H104" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I104" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J104" t="str">
         <v>EL G3</v>
@@ -5954,13 +5954,13 @@
         <v>3</v>
       </c>
       <c r="G105" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H105" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I105" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J105" t="str">
         <v>EL G3</v>
@@ -6007,13 +6007,13 @@
         <v>1</v>
       </c>
       <c r="G106" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H106" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I106" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J106" t="str">
         <v>EL G1</v>
@@ -6060,13 +6060,13 @@
         <v>2</v>
       </c>
       <c r="G107" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H107" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I107" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J107" t="str">
         <v>EL G2</v>
@@ -6113,13 +6113,13 @@
         <v>3</v>
       </c>
       <c r="G108" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H108" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I108" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J108" t="str">
         <v>EL G3</v>
@@ -6166,13 +6166,13 @@
         <v>3</v>
       </c>
       <c r="G109" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H109" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I109" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J109" t="str">
         <v>EL G3</v>
@@ -6219,13 +6219,13 @@
         <v>1</v>
       </c>
       <c r="G110" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H110" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I110" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J110" t="str">
         <v>EL G1</v>
@@ -6272,13 +6272,13 @@
         <v>2</v>
       </c>
       <c r="G111" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H111" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I111" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J111" t="str">
         <v>EL G2</v>
@@ -6325,13 +6325,13 @@
         <v>3</v>
       </c>
       <c r="G112" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H112" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I112" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J112" t="str">
         <v>EL G3</v>
@@ -6378,13 +6378,13 @@
         <v>3</v>
       </c>
       <c r="G113" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H113" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I113" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J113" t="str">
         <v>EL G3</v>
@@ -6431,13 +6431,13 @@
         <v>1</v>
       </c>
       <c r="G114" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H114" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I114" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J114" t="str">
         <v>EL G1</v>
@@ -6484,13 +6484,13 @@
         <v>2</v>
       </c>
       <c r="G115" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H115" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I115" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J115" t="str">
         <v>EL G2</v>
@@ -6537,13 +6537,13 @@
         <v>3</v>
       </c>
       <c r="G116" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H116" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I116" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J116" t="str">
         <v>EL G3</v>
@@ -6590,13 +6590,13 @@
         <v>3</v>
       </c>
       <c r="G117" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H117" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I117" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J117" t="str">
         <v>EL G3</v>
@@ -6643,13 +6643,13 @@
         <v>1</v>
       </c>
       <c r="G118" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H118" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I118" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J118" t="str">
         <v>EL G1</v>
@@ -6696,13 +6696,13 @@
         <v>2</v>
       </c>
       <c r="G119" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H119" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I119" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J119" t="str">
         <v>EL G2</v>
@@ -6749,13 +6749,13 @@
         <v>3</v>
       </c>
       <c r="G120" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H120" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I120" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J120" t="str">
         <v>EL G3</v>
@@ -6802,13 +6802,13 @@
         <v>3</v>
       </c>
       <c r="G121" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H121" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I121" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J121" t="str">
         <v>EL G3</v>
@@ -6855,13 +6855,13 @@
         <v>1</v>
       </c>
       <c r="G122" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H122" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I122" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J122" t="str">
         <v>EL G1</v>
@@ -6908,13 +6908,13 @@
         <v>2</v>
       </c>
       <c r="G123" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H123" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I123" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J123" t="str">
         <v>EL G2</v>
@@ -6961,13 +6961,13 @@
         <v>3</v>
       </c>
       <c r="G124" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H124" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I124" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J124" t="str">
         <v>EL G3</v>
@@ -7014,13 +7014,13 @@
         <v>3</v>
       </c>
       <c r="G125" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H125" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I125" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J125" t="str">
         <v>EL G3</v>
@@ -7067,13 +7067,13 @@
         <v>1</v>
       </c>
       <c r="G126" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H126" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I126" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J126" t="str">
         <v>EL G1</v>
@@ -7120,13 +7120,13 @@
         <v>2</v>
       </c>
       <c r="G127" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H127" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I127" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J127" t="str">
         <v>EL G2</v>
@@ -7173,13 +7173,13 @@
         <v>3</v>
       </c>
       <c r="G128" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H128" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I128" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J128" t="str">
         <v>EL G3</v>
@@ -7226,13 +7226,13 @@
         <v>3</v>
       </c>
       <c r="G129" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H129" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I129" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J129" t="str">
         <v>EL G3</v>
@@ -7279,13 +7279,13 @@
         <v>1</v>
       </c>
       <c r="G130" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H130" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I130" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J130" t="str">
         <v>EL G1</v>
@@ -7332,13 +7332,13 @@
         <v>2</v>
       </c>
       <c r="G131" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H131" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I131" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J131" t="str">
         <v>EL G2</v>
@@ -7385,13 +7385,13 @@
         <v>3</v>
       </c>
       <c r="G132" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H132" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I132" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J132" t="str">
         <v>EL G3</v>
@@ -7438,13 +7438,13 @@
         <v>3</v>
       </c>
       <c r="G133" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H133" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I133" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J133" t="str">
         <v>EL G3</v>
@@ -7491,13 +7491,13 @@
         <v>1</v>
       </c>
       <c r="G134" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H134" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I134" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J134" t="str">
         <v>EL G1</v>
@@ -7544,13 +7544,13 @@
         <v>2</v>
       </c>
       <c r="G135" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H135" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I135" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J135" t="str">
         <v>EL G2</v>
@@ -7597,13 +7597,13 @@
         <v>3</v>
       </c>
       <c r="G136" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H136" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I136" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J136" t="str">
         <v>EL G3</v>
@@ -7650,13 +7650,13 @@
         <v>3</v>
       </c>
       <c r="G137" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H137" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I137" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J137" t="str">
         <v>EL G3</v>
@@ -7703,13 +7703,13 @@
         <v>1</v>
       </c>
       <c r="G138" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H138" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I138" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J138" t="str">
         <v>EL G1</v>
@@ -7756,13 +7756,13 @@
         <v>2</v>
       </c>
       <c r="G139" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H139" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I139" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J139" t="str">
         <v>EL G2</v>
@@ -7809,13 +7809,13 @@
         <v>3</v>
       </c>
       <c r="G140" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H140" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I140" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J140" t="str">
         <v>EL G3</v>
@@ -7862,13 +7862,13 @@
         <v>3</v>
       </c>
       <c r="G141" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H141" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I141" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J141" t="str">
         <v>EL G3</v>
@@ -7915,13 +7915,13 @@
         <v>1</v>
       </c>
       <c r="G142" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H142" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I142" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J142" t="str">
         <v>EL G1</v>
@@ -7968,13 +7968,13 @@
         <v>2</v>
       </c>
       <c r="G143" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H143" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I143" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J143" t="str">
         <v>EL G2</v>
@@ -8021,13 +8021,13 @@
         <v>3</v>
       </c>
       <c r="G144" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H144" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I144" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J144" t="str">
         <v>EL G3</v>
@@ -8074,13 +8074,13 @@
         <v>3</v>
       </c>
       <c r="G145" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H145" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I145" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J145" t="str">
         <v>EL G3</v>
@@ -8127,13 +8127,13 @@
         <v>1</v>
       </c>
       <c r="G146" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H146" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I146" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J146" t="str">
         <v>EL G1</v>
@@ -8180,13 +8180,13 @@
         <v>2</v>
       </c>
       <c r="G147" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H147" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I147" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J147" t="str">
         <v>EL G2</v>
@@ -8233,13 +8233,13 @@
         <v>3</v>
       </c>
       <c r="G148" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H148" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I148" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J148" t="str">
         <v>EL G3</v>
@@ -8286,13 +8286,13 @@
         <v>3</v>
       </c>
       <c r="G149" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H149" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I149" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J149" t="str">
         <v>EL G3</v>
@@ -8339,13 +8339,13 @@
         <v>1</v>
       </c>
       <c r="G150" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H150" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I150" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J150" t="str">
         <v>EL G1</v>
@@ -8392,13 +8392,13 @@
         <v>2</v>
       </c>
       <c r="G151" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H151" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I151" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J151" t="str">
         <v>EL G2</v>
@@ -8445,13 +8445,13 @@
         <v>3</v>
       </c>
       <c r="G152" t="str">
-        <v>file</v>
+        <v>SG1</v>
       </c>
       <c r="H152" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I152" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J152" t="str">
         <v>EL G3</v>
@@ -8498,13 +8498,13 @@
         <v>3</v>
       </c>
       <c r="G153" t="str">
-        <v>file</v>
+        <v>SG2</v>
       </c>
       <c r="H153" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I153" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J153" t="str">
         <v>EL G3</v>
@@ -8551,13 +8551,13 @@
         <v>1</v>
       </c>
       <c r="G154" t="str">
-        <v>file</v>
+        <v>SG3</v>
       </c>
       <c r="H154" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I154" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J154" t="str">
         <v>EL G1</v>
@@ -8604,13 +8604,13 @@
         <v>2</v>
       </c>
       <c r="G155" t="str">
-        <v>file</v>
+        <v>SG4</v>
       </c>
       <c r="H155" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I155" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J155" t="str">
         <v>EL G2</v>
@@ -8657,13 +8657,13 @@
         <v>3</v>
       </c>
       <c r="G156" t="str">
-        <v>file</v>
+        <v>SG5</v>
       </c>
       <c r="H156" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I156" t="str">
-        <v>TG1</v>
+        <v/>
       </c>
       <c r="J156" t="str">
         <v>EL G3</v>
@@ -8710,13 +8710,13 @@
         <v>3</v>
       </c>
       <c r="G157" t="str">
-        <v>file</v>
+        <v>SG6</v>
       </c>
       <c r="H157" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="I157" t="str">
-        <v>TG2</v>
+        <v/>
       </c>
       <c r="J157" t="str">
         <v>EL G3</v>
@@ -8752,7 +8752,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="24.83203125" customWidth="1"/>
@@ -8761,7 +8761,8 @@
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
     <col min="6" max="6" width="40.83203125" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8787,6 +8788,9 @@
         <v>AutoPG</v>
       </c>
       <c r="H1" t="str">
+        <v>AutoTG</v>
+      </c>
+      <c r="I1" t="str">
         <v>AutoClasses</v>
       </c>
     </row>
@@ -8813,6 +8817,9 @@
         <v/>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -8839,6 +8846,9 @@
         <v/>
       </c>
       <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>1R1</v>
       </c>
     </row>
@@ -8865,6 +8875,9 @@
         <v/>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -8891,6 +8904,9 @@
         <v/>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>1R2</v>
       </c>
     </row>
@@ -8917,6 +8933,9 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -8943,6 +8962,9 @@
         <v/>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>1R3</v>
       </c>
     </row>
@@ -8969,6 +8991,9 @@
         <v/>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -8995,6 +9020,9 @@
         <v/>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>1R4</v>
       </c>
     </row>
@@ -9021,6 +9049,9 @@
         <v/>
       </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -9047,6 +9078,9 @@
         <v/>
       </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>1R5</v>
       </c>
     </row>
@@ -9073,6 +9107,9 @@
         <v/>
       </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -9099,6 +9136,9 @@
         <v/>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>1R6</v>
       </c>
     </row>
@@ -9127,6 +9167,9 @@
       <c r="H14" t="str">
         <v/>
       </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -9153,6 +9196,9 @@
       <c r="H15" t="str">
         <v/>
       </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -9179,6 +9225,9 @@
       <c r="H16" t="str">
         <v/>
       </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -9205,10 +9254,13 @@
       <c r="H17" t="str">
         <v/>
       </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I17"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q157"/>
+  <dimension ref="A1:R157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -410,9 +410,9 @@
     <col min="5" max="5" width="8.83203125" customWidth="1"/>
     <col min="6" max="6" width="5.83203125" customWidth="1"/>
     <col min="7" max="7" width="6.83203125" customWidth="1"/>
-    <col min="8" max="8" width="8.83203125" customWidth="1"/>
-    <col min="9" max="9" width="28.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="5.83203125" customWidth="1"/>
+    <col min="9" max="9" width="8.83203125" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
@@ -420,6 +420,7 @@
     <col min="15" max="15" width="12.83203125" customWidth="1"/>
     <col min="16" max="16" width="12.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,33 +446,36 @@
         <v>TG</v>
       </c>
       <c r="H1" t="str">
+        <v>SN</v>
+      </c>
+      <c r="I1" t="str">
         <v>Origin</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>SourceName</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>EL</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>MT</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>HMT</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>MA</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>SCI</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>HIST</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>GEOG</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>LIT</v>
       </c>
     </row>
@@ -498,33 +502,36 @@
         <v>SG1</v>
       </c>
       <c r="H2" t="str">
-        <v>file</v>
+        <v>1</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -551,33 +558,36 @@
         <v>SG2</v>
       </c>
       <c r="H3" t="str">
-        <v>file</v>
+        <v>2</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
       <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -604,33 +614,36 @@
         <v>SG3</v>
       </c>
       <c r="H4" t="str">
-        <v>file</v>
+        <v>3</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
       <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N4" t="str">
+      <c r="O4" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -657,33 +670,36 @@
         <v>SG4</v>
       </c>
       <c r="H5" t="str">
-        <v>file</v>
+        <v>4</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
       <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N5" t="str">
+      <c r="O5" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -710,33 +726,36 @@
         <v>SG5</v>
       </c>
       <c r="H6" t="str">
-        <v>file</v>
+        <v>5</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K6" t="str">
+      <c r="L6" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
       <c r="M6" t="str">
+        <v/>
+      </c>
+      <c r="N6" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N6" t="str">
+      <c r="O6" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -763,33 +782,36 @@
         <v>SG6</v>
       </c>
       <c r="H7" t="str">
-        <v>file</v>
+        <v>6</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
       <c r="M7" t="str">
+        <v/>
+      </c>
+      <c r="N7" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N7" t="str">
+      <c r="O7" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -816,33 +838,36 @@
         <v>SG1</v>
       </c>
       <c r="H8" t="str">
-        <v>file</v>
+        <v>7</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
       <c r="M8" t="str">
+        <v/>
+      </c>
+      <c r="N8" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N8" t="str">
+      <c r="O8" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -869,33 +894,36 @@
         <v>SG2</v>
       </c>
       <c r="H9" t="str">
-        <v>file</v>
+        <v>8</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K9" t="str">
+      <c r="L9" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -922,33 +950,36 @@
         <v>SG3</v>
       </c>
       <c r="H10" t="str">
-        <v>file</v>
+        <v>9</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K10" t="str">
+      <c r="L10" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
       <c r="M10" t="str">
+        <v/>
+      </c>
+      <c r="N10" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N10" t="str">
+      <c r="O10" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -975,33 +1006,36 @@
         <v>SG4</v>
       </c>
       <c r="H11" t="str">
-        <v>file</v>
+        <v>10</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K11" t="str">
+      <c r="L11" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
       <c r="M11" t="str">
+        <v/>
+      </c>
+      <c r="N11" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N11" t="str">
+      <c r="O11" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1028,33 +1062,36 @@
         <v>SG5</v>
       </c>
       <c r="H12" t="str">
-        <v>file</v>
+        <v>11</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K12" t="str">
+      <c r="L12" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
       <c r="M12" t="str">
+        <v/>
+      </c>
+      <c r="N12" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N12" t="str">
+      <c r="O12" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="R12" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1081,33 +1118,36 @@
         <v>SG6</v>
       </c>
       <c r="H13" t="str">
-        <v>file</v>
+        <v>12</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K13" t="str">
+      <c r="L13" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
       <c r="M13" t="str">
+        <v/>
+      </c>
+      <c r="N13" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N13" t="str">
+      <c r="O13" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1134,33 +1174,36 @@
         <v>SG1</v>
       </c>
       <c r="H14" t="str">
-        <v>file</v>
+        <v>13</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K14" t="str">
+      <c r="L14" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
       <c r="M14" t="str">
+        <v/>
+      </c>
+      <c r="N14" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N14" t="str">
+      <c r="O14" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="R14" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1187,33 +1230,36 @@
         <v>SG2</v>
       </c>
       <c r="H15" t="str">
-        <v>file</v>
+        <v>14</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K15" t="str">
+      <c r="L15" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
       <c r="M15" t="str">
+        <v/>
+      </c>
+      <c r="N15" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N15" t="str">
+      <c r="O15" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="R15" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1240,33 +1286,36 @@
         <v>SG3</v>
       </c>
       <c r="H16" t="str">
-        <v>file</v>
+        <v>15</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K16" t="str">
+      <c r="L16" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="R16" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1293,33 +1342,36 @@
         <v>SG4</v>
       </c>
       <c r="H17" t="str">
-        <v>file</v>
+        <v>16</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K17" t="str">
+      <c r="L17" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
       <c r="M17" t="str">
+        <v/>
+      </c>
+      <c r="N17" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N17" t="str">
+      <c r="O17" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="R17" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1346,33 +1398,36 @@
         <v>SG5</v>
       </c>
       <c r="H18" t="str">
-        <v>file</v>
+        <v>17</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K18" t="str">
+      <c r="L18" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
       <c r="M18" t="str">
+        <v/>
+      </c>
+      <c r="N18" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N18" t="str">
+      <c r="O18" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="R18" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1399,33 +1454,36 @@
         <v>SG6</v>
       </c>
       <c r="H19" t="str">
-        <v>file</v>
+        <v>18</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K19" t="str">
+      <c r="L19" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
       <c r="M19" t="str">
+        <v/>
+      </c>
+      <c r="N19" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N19" t="str">
+      <c r="O19" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="R19" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1452,33 +1510,36 @@
         <v>SG1</v>
       </c>
       <c r="H20" t="str">
-        <v>file</v>
+        <v>19</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K20" t="str">
+      <c r="L20" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
       <c r="M20" t="str">
+        <v/>
+      </c>
+      <c r="N20" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N20" t="str">
+      <c r="O20" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="R20" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1505,33 +1566,36 @@
         <v>SG2</v>
       </c>
       <c r="H21" t="str">
-        <v>file</v>
+        <v>20</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K21" t="str">
+      <c r="L21" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L21" t="str">
-        <v/>
-      </c>
       <c r="M21" t="str">
+        <v/>
+      </c>
+      <c r="N21" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N21" t="str">
+      <c r="O21" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Q21" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="R21" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1558,33 +1622,36 @@
         <v>SG3</v>
       </c>
       <c r="H22" t="str">
-        <v>file</v>
+        <v>21</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K22" t="str">
+      <c r="L22" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L22" t="str">
-        <v/>
-      </c>
       <c r="M22" t="str">
+        <v/>
+      </c>
+      <c r="N22" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N22" t="str">
+      <c r="O22" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Q22" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="R22" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1611,33 +1678,36 @@
         <v>SG4</v>
       </c>
       <c r="H23" t="str">
-        <v>file</v>
+        <v>22</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K23" t="str">
+      <c r="L23" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Q23" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="R23" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1664,33 +1734,36 @@
         <v>SG5</v>
       </c>
       <c r="H24" t="str">
-        <v>file</v>
+        <v>23</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K24" t="str">
+      <c r="L24" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L24" t="str">
-        <v/>
-      </c>
       <c r="M24" t="str">
+        <v/>
+      </c>
+      <c r="N24" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N24" t="str">
+      <c r="O24" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Q24" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="R24" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1717,33 +1790,36 @@
         <v>SG6</v>
       </c>
       <c r="H25" t="str">
-        <v>file</v>
+        <v>24</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K25" t="str">
+      <c r="L25" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L25" t="str">
-        <v/>
-      </c>
       <c r="M25" t="str">
+        <v/>
+      </c>
+      <c r="N25" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N25" t="str">
+      <c r="O25" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q25" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="R25" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1770,33 +1846,36 @@
         <v>SG1</v>
       </c>
       <c r="H26" t="str">
-        <v>file</v>
+        <v>25</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K26" t="str">
+      <c r="L26" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L26" t="str">
-        <v/>
-      </c>
       <c r="M26" t="str">
+        <v/>
+      </c>
+      <c r="N26" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N26" t="str">
+      <c r="O26" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Q26" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="R26" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1823,33 +1902,36 @@
         <v>SG2</v>
       </c>
       <c r="H27" t="str">
-        <v>file</v>
+        <v>26</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K27" t="str">
+      <c r="L27" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L27" t="str">
-        <v/>
-      </c>
       <c r="M27" t="str">
+        <v/>
+      </c>
+      <c r="N27" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N27" t="str">
+      <c r="O27" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="R27" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1876,33 +1958,36 @@
         <v>SG3</v>
       </c>
       <c r="H28" t="str">
-        <v>file</v>
+        <v>27</v>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K28" t="str">
+      <c r="L28" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L28" t="str">
-        <v/>
-      </c>
       <c r="M28" t="str">
+        <v/>
+      </c>
+      <c r="N28" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N28" t="str">
+      <c r="O28" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Q28" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="R28" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1929,33 +2014,36 @@
         <v>SG4</v>
       </c>
       <c r="H29" t="str">
-        <v>file</v>
+        <v>28</v>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K29" t="str">
+      <c r="L29" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L29" t="str">
-        <v/>
-      </c>
       <c r="M29" t="str">
+        <v/>
+      </c>
+      <c r="N29" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N29" t="str">
+      <c r="O29" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Q29" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="R29" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1982,33 +2070,36 @@
         <v>SG5</v>
       </c>
       <c r="H30" t="str">
-        <v>file</v>
+        <v>29</v>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K30" t="str">
+      <c r="L30" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="R30" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2035,33 +2126,36 @@
         <v>SG6</v>
       </c>
       <c r="H31" t="str">
-        <v>file</v>
+        <v>30</v>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K31" t="str">
+      <c r="L31" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L31" t="str">
-        <v/>
-      </c>
       <c r="M31" t="str">
+        <v/>
+      </c>
+      <c r="N31" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N31" t="str">
+      <c r="O31" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="R31" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2088,33 +2182,36 @@
         <v>SG1</v>
       </c>
       <c r="H32" t="str">
-        <v>file</v>
+        <v>31</v>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K32" t="str">
+      <c r="L32" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
       <c r="M32" t="str">
+        <v/>
+      </c>
+      <c r="N32" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N32" t="str">
+      <c r="O32" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P32" t="str">
+      <c r="Q32" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="R32" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2141,33 +2238,36 @@
         <v>SG2</v>
       </c>
       <c r="H33" t="str">
-        <v>file</v>
+        <v>32</v>
       </c>
       <c r="I33" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K33" t="str">
+      <c r="L33" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L33" t="str">
-        <v/>
-      </c>
       <c r="M33" t="str">
+        <v/>
+      </c>
+      <c r="N33" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N33" t="str">
+      <c r="O33" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P33" t="str">
+      <c r="Q33" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="R33" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2194,33 +2294,36 @@
         <v>SG3</v>
       </c>
       <c r="H34" t="str">
-        <v>file</v>
+        <v>33</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K34" t="str">
+      <c r="L34" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L34" t="str">
-        <v/>
-      </c>
       <c r="M34" t="str">
+        <v/>
+      </c>
+      <c r="N34" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N34" t="str">
+      <c r="O34" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P34" t="str">
+      <c r="Q34" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q34" t="str">
+      <c r="R34" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2247,33 +2350,36 @@
         <v>SG4</v>
       </c>
       <c r="H35" t="str">
-        <v>file</v>
+        <v>34</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K35" t="str">
+      <c r="L35" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L35" t="str">
-        <v/>
-      </c>
       <c r="M35" t="str">
+        <v/>
+      </c>
+      <c r="N35" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N35" t="str">
+      <c r="O35" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q35" t="str">
+      <c r="R35" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2300,33 +2406,36 @@
         <v>SG5</v>
       </c>
       <c r="H36" t="str">
-        <v>file</v>
+        <v>35</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K36" t="str">
+      <c r="L36" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L36" t="str">
-        <v/>
-      </c>
       <c r="M36" t="str">
+        <v/>
+      </c>
+      <c r="N36" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N36" t="str">
+      <c r="O36" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P36" t="str">
+      <c r="Q36" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q36" t="str">
+      <c r="R36" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2353,33 +2462,36 @@
         <v>SG6</v>
       </c>
       <c r="H37" t="str">
-        <v>file</v>
+        <v>36</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K37" t="str">
+      <c r="L37" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P37" t="str">
+      <c r="Q37" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q37" t="str">
+      <c r="R37" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2406,33 +2518,36 @@
         <v>SG1</v>
       </c>
       <c r="H38" t="str">
-        <v>file</v>
+        <v>37</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K38" t="str">
+      <c r="L38" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L38" t="str">
-        <v/>
-      </c>
       <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N38" t="str">
+      <c r="O38" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P38" t="str">
+      <c r="Q38" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="R38" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2459,33 +2574,36 @@
         <v>SG2</v>
       </c>
       <c r="H39" t="str">
-        <v>file</v>
+        <v>38</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K39" t="str">
+      <c r="L39" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L39" t="str">
-        <v/>
-      </c>
       <c r="M39" t="str">
+        <v/>
+      </c>
+      <c r="N39" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N39" t="str">
+      <c r="O39" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="R39" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2512,33 +2630,36 @@
         <v>SG3</v>
       </c>
       <c r="H40" t="str">
-        <v>file</v>
+        <v>39</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K40" t="str">
+      <c r="L40" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L40" t="str">
-        <v/>
-      </c>
       <c r="M40" t="str">
+        <v/>
+      </c>
+      <c r="N40" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N40" t="str">
+      <c r="O40" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P40" t="str">
+      <c r="Q40" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q40" t="str">
+      <c r="R40" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2565,33 +2686,36 @@
         <v>SG4</v>
       </c>
       <c r="H41" t="str">
-        <v>file</v>
+        <v>40</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K41" t="str">
+      <c r="L41" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
       <c r="M41" t="str">
+        <v/>
+      </c>
+      <c r="N41" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N41" t="str">
+      <c r="O41" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q41" t="str">
+      <c r="R41" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2618,33 +2742,36 @@
         <v>SG5</v>
       </c>
       <c r="H42" t="str">
-        <v>file</v>
+        <v>41</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K42" t="str">
+      <c r="L42" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L42" t="str">
-        <v/>
-      </c>
       <c r="M42" t="str">
+        <v/>
+      </c>
+      <c r="N42" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N42" t="str">
+      <c r="O42" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P42" t="str">
+      <c r="Q42" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q42" t="str">
+      <c r="R42" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2671,33 +2798,36 @@
         <v>SG6</v>
       </c>
       <c r="H43" t="str">
-        <v>file</v>
+        <v>42</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K43" t="str">
+      <c r="L43" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L43" t="str">
-        <v/>
-      </c>
       <c r="M43" t="str">
+        <v/>
+      </c>
+      <c r="N43" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N43" t="str">
+      <c r="O43" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P43" t="str">
+      <c r="Q43" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q43" t="str">
+      <c r="R43" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2724,33 +2854,36 @@
         <v>SG1</v>
       </c>
       <c r="H44" t="str">
-        <v>file</v>
+        <v>43</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K44" t="str">
+      <c r="L44" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P44" t="str">
+      <c r="Q44" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q44" t="str">
+      <c r="R44" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2777,33 +2910,36 @@
         <v>SG2</v>
       </c>
       <c r="H45" t="str">
-        <v>file</v>
+        <v>44</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J45" t="str">
+        <v/>
+      </c>
+      <c r="K45" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K45" t="str">
+      <c r="L45" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
       <c r="M45" t="str">
+        <v/>
+      </c>
+      <c r="N45" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N45" t="str">
+      <c r="O45" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P45" t="str">
+      <c r="Q45" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q45" t="str">
+      <c r="R45" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2830,33 +2966,36 @@
         <v>SG3</v>
       </c>
       <c r="H46" t="str">
-        <v>file</v>
+        <v>45</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J46" t="str">
+        <v/>
+      </c>
+      <c r="K46" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K46" t="str">
+      <c r="L46" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
       <c r="M46" t="str">
+        <v/>
+      </c>
+      <c r="N46" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N46" t="str">
+      <c r="O46" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P46" t="str">
+      <c r="Q46" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q46" t="str">
+      <c r="R46" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2883,33 +3022,36 @@
         <v>SG4</v>
       </c>
       <c r="H47" t="str">
-        <v>file</v>
+        <v>46</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J47" t="str">
+        <v/>
+      </c>
+      <c r="K47" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K47" t="str">
+      <c r="L47" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L47" t="str">
-        <v/>
-      </c>
       <c r="M47" t="str">
+        <v/>
+      </c>
+      <c r="N47" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N47" t="str">
+      <c r="O47" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P47" t="str">
+      <c r="Q47" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q47" t="str">
+      <c r="R47" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2936,33 +3078,36 @@
         <v>SG5</v>
       </c>
       <c r="H48" t="str">
-        <v>file</v>
+        <v>47</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J48" t="str">
+        <v/>
+      </c>
+      <c r="K48" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K48" t="str">
+      <c r="L48" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L48" t="str">
-        <v/>
-      </c>
       <c r="M48" t="str">
+        <v/>
+      </c>
+      <c r="N48" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N48" t="str">
+      <c r="O48" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P48" t="str">
+      <c r="Q48" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q48" t="str">
+      <c r="R48" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2989,33 +3134,36 @@
         <v>SG6</v>
       </c>
       <c r="H49" t="str">
-        <v>file</v>
+        <v>48</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J49" t="str">
+        <v/>
+      </c>
+      <c r="K49" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K49" t="str">
+      <c r="L49" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L49" t="str">
-        <v/>
-      </c>
       <c r="M49" t="str">
+        <v/>
+      </c>
+      <c r="N49" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N49" t="str">
+      <c r="O49" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P49" t="str">
+      <c r="Q49" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q49" t="str">
+      <c r="R49" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3042,33 +3190,36 @@
         <v>SG1</v>
       </c>
       <c r="H50" t="str">
-        <v>file</v>
+        <v>49</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K50" t="str">
+      <c r="L50" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
       <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N50" t="str">
+      <c r="O50" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P50" t="str">
+      <c r="Q50" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="R50" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3095,33 +3246,36 @@
         <v>SG2</v>
       </c>
       <c r="H51" t="str">
-        <v>file</v>
+        <v>50</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J51" t="str">
+        <v/>
+      </c>
+      <c r="K51" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K51" t="str">
+      <c r="L51" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P51" t="str">
+      <c r="Q51" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q51" t="str">
+      <c r="R51" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3148,33 +3302,36 @@
         <v>SG3</v>
       </c>
       <c r="H52" t="str">
-        <v>file</v>
+        <v>51</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J52" t="str">
+        <v/>
+      </c>
+      <c r="K52" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K52" t="str">
+      <c r="L52" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L52" t="str">
-        <v/>
-      </c>
       <c r="M52" t="str">
+        <v/>
+      </c>
+      <c r="N52" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N52" t="str">
+      <c r="O52" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P52" t="str">
+      <c r="Q52" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q52" t="str">
+      <c r="R52" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3201,33 +3358,36 @@
         <v>SG4</v>
       </c>
       <c r="H53" t="str">
-        <v>file</v>
+        <v>52</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J53" t="str">
+        <v/>
+      </c>
+      <c r="K53" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K53" t="str">
+      <c r="L53" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L53" t="str">
-        <v/>
-      </c>
       <c r="M53" t="str">
+        <v/>
+      </c>
+      <c r="N53" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N53" t="str">
+      <c r="O53" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P53" t="str">
+      <c r="Q53" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q53" t="str">
+      <c r="R53" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3254,33 +3414,36 @@
         <v>SG5</v>
       </c>
       <c r="H54" t="str">
-        <v>file</v>
+        <v>53</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J54" t="str">
+        <v/>
+      </c>
+      <c r="K54" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K54" t="str">
+      <c r="L54" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L54" t="str">
-        <v/>
-      </c>
       <c r="M54" t="str">
+        <v/>
+      </c>
+      <c r="N54" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N54" t="str">
+      <c r="O54" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P54" t="str">
+      <c r="Q54" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q54" t="str">
+      <c r="R54" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3307,33 +3470,36 @@
         <v>SG6</v>
       </c>
       <c r="H55" t="str">
-        <v>file</v>
+        <v>54</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J55" t="str">
+        <v/>
+      </c>
+      <c r="K55" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K55" t="str">
+      <c r="L55" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L55" t="str">
-        <v/>
-      </c>
       <c r="M55" t="str">
+        <v/>
+      </c>
+      <c r="N55" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N55" t="str">
+      <c r="O55" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P55" t="str">
+      <c r="Q55" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q55" t="str">
+      <c r="R55" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3360,33 +3526,36 @@
         <v>SG1</v>
       </c>
       <c r="H56" t="str">
-        <v>file</v>
+        <v>55</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J56" t="str">
+        <v/>
+      </c>
+      <c r="K56" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K56" t="str">
+      <c r="L56" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L56" t="str">
-        <v/>
-      </c>
       <c r="M56" t="str">
+        <v/>
+      </c>
+      <c r="N56" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N56" t="str">
+      <c r="O56" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P56" t="str">
+      <c r="Q56" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q56" t="str">
+      <c r="R56" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3413,33 +3582,36 @@
         <v>SG2</v>
       </c>
       <c r="H57" t="str">
-        <v>file</v>
+        <v>56</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J57" t="str">
+        <v/>
+      </c>
+      <c r="K57" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K57" t="str">
+      <c r="L57" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L57" t="str">
-        <v/>
-      </c>
       <c r="M57" t="str">
+        <v/>
+      </c>
+      <c r="N57" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N57" t="str">
+      <c r="O57" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q57" t="str">
+      <c r="R57" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3466,33 +3638,36 @@
         <v>SG3</v>
       </c>
       <c r="H58" t="str">
-        <v>file</v>
+        <v>57</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J58" t="str">
+        <v/>
+      </c>
+      <c r="K58" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K58" t="str">
+      <c r="L58" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q58" t="str">
+      <c r="R58" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3519,33 +3694,36 @@
         <v>SG4</v>
       </c>
       <c r="H59" t="str">
-        <v>file</v>
+        <v>58</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J59" t="str">
+        <v/>
+      </c>
+      <c r="K59" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K59" t="str">
+      <c r="L59" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L59" t="str">
-        <v/>
-      </c>
       <c r="M59" t="str">
+        <v/>
+      </c>
+      <c r="N59" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N59" t="str">
+      <c r="O59" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q59" t="str">
+      <c r="R59" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3572,33 +3750,36 @@
         <v>SG5</v>
       </c>
       <c r="H60" t="str">
-        <v>file</v>
+        <v>59</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J60" t="str">
+        <v/>
+      </c>
+      <c r="K60" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K60" t="str">
+      <c r="L60" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L60" t="str">
-        <v/>
-      </c>
       <c r="M60" t="str">
+        <v/>
+      </c>
+      <c r="N60" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N60" t="str">
+      <c r="O60" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="R60" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3625,33 +3806,36 @@
         <v>SG6</v>
       </c>
       <c r="H61" t="str">
-        <v>file</v>
+        <v>60</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J61" t="str">
+        <v/>
+      </c>
+      <c r="K61" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K61" t="str">
+      <c r="L61" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L61" t="str">
-        <v/>
-      </c>
       <c r="M61" t="str">
+        <v/>
+      </c>
+      <c r="N61" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N61" t="str">
+      <c r="O61" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q61" t="str">
+      <c r="R61" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3678,33 +3862,36 @@
         <v>SG1</v>
       </c>
       <c r="H62" t="str">
-        <v>file</v>
+        <v>61</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J62" t="str">
+        <v/>
+      </c>
+      <c r="K62" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K62" t="str">
+      <c r="L62" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L62" t="str">
-        <v/>
-      </c>
       <c r="M62" t="str">
+        <v/>
+      </c>
+      <c r="N62" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N62" t="str">
+      <c r="O62" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P62" t="str">
+      <c r="Q62" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q62" t="str">
+      <c r="R62" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3731,33 +3918,36 @@
         <v>SG2</v>
       </c>
       <c r="H63" t="str">
-        <v>file</v>
+        <v>62</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J63" t="str">
+        <v/>
+      </c>
+      <c r="K63" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K63" t="str">
+      <c r="L63" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L63" t="str">
-        <v/>
-      </c>
       <c r="M63" t="str">
+        <v/>
+      </c>
+      <c r="N63" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N63" t="str">
+      <c r="O63" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P63" t="str">
+      <c r="Q63" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q63" t="str">
+      <c r="R63" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3784,33 +3974,36 @@
         <v>SG3</v>
       </c>
       <c r="H64" t="str">
-        <v>file</v>
+        <v>63</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J64" t="str">
+        <v/>
+      </c>
+      <c r="K64" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K64" t="str">
+      <c r="L64" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L64" t="str">
-        <v/>
-      </c>
       <c r="M64" t="str">
+        <v/>
+      </c>
+      <c r="N64" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N64" t="str">
+      <c r="O64" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P64" t="str">
+      <c r="Q64" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q64" t="str">
+      <c r="R64" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3837,33 +4030,36 @@
         <v>SG4</v>
       </c>
       <c r="H65" t="str">
-        <v>file</v>
+        <v>64</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J65" t="str">
+        <v/>
+      </c>
+      <c r="K65" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K65" t="str">
+      <c r="L65" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P65" t="str">
+      <c r="Q65" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q65" t="str">
+      <c r="R65" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3890,33 +4086,36 @@
         <v>SG5</v>
       </c>
       <c r="H66" t="str">
-        <v>file</v>
+        <v>65</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J66" t="str">
+        <v/>
+      </c>
+      <c r="K66" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K66" t="str">
+      <c r="L66" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L66" t="str">
-        <v/>
-      </c>
       <c r="M66" t="str">
+        <v/>
+      </c>
+      <c r="N66" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N66" t="str">
+      <c r="O66" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P66" t="str">
+      <c r="Q66" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q66" t="str">
+      <c r="R66" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3943,33 +4142,36 @@
         <v>SG6</v>
       </c>
       <c r="H67" t="str">
-        <v>file</v>
+        <v>66</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J67" t="str">
+        <v/>
+      </c>
+      <c r="K67" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K67" t="str">
+      <c r="L67" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L67" t="str">
-        <v/>
-      </c>
       <c r="M67" t="str">
+        <v/>
+      </c>
+      <c r="N67" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N67" t="str">
+      <c r="O67" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P67" t="str">
+      <c r="Q67" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q67" t="str">
+      <c r="R67" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3996,33 +4198,36 @@
         <v>SG1</v>
       </c>
       <c r="H68" t="str">
-        <v>file</v>
+        <v>67</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J68" t="str">
+        <v/>
+      </c>
+      <c r="K68" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K68" t="str">
+      <c r="L68" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L68" t="str">
-        <v/>
-      </c>
       <c r="M68" t="str">
+        <v/>
+      </c>
+      <c r="N68" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N68" t="str">
+      <c r="O68" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P68" t="str">
+      <c r="Q68" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q68" t="str">
+      <c r="R68" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4049,33 +4254,36 @@
         <v>SG2</v>
       </c>
       <c r="H69" t="str">
-        <v>file</v>
+        <v>68</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J69" t="str">
+        <v/>
+      </c>
+      <c r="K69" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K69" t="str">
+      <c r="L69" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L69" t="str">
-        <v/>
-      </c>
       <c r="M69" t="str">
+        <v/>
+      </c>
+      <c r="N69" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N69" t="str">
+      <c r="O69" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P69" t="str">
+      <c r="Q69" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q69" t="str">
+      <c r="R69" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4102,33 +4310,36 @@
         <v>SG3</v>
       </c>
       <c r="H70" t="str">
-        <v>file</v>
+        <v>69</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J70" t="str">
+        <v/>
+      </c>
+      <c r="K70" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K70" t="str">
+      <c r="L70" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L70" t="str">
-        <v/>
-      </c>
       <c r="M70" t="str">
+        <v/>
+      </c>
+      <c r="N70" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N70" t="str">
+      <c r="O70" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P70" t="str">
+      <c r="Q70" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q70" t="str">
+      <c r="R70" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4155,33 +4366,36 @@
         <v>SG4</v>
       </c>
       <c r="H71" t="str">
-        <v>file</v>
+        <v>70</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J71" t="str">
+        <v/>
+      </c>
+      <c r="K71" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K71" t="str">
+      <c r="L71" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L71" t="str">
-        <v/>
-      </c>
       <c r="M71" t="str">
+        <v/>
+      </c>
+      <c r="N71" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N71" t="str">
+      <c r="O71" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P71" t="str">
+      <c r="Q71" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q71" t="str">
+      <c r="R71" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4208,33 +4422,36 @@
         <v>SG5</v>
       </c>
       <c r="H72" t="str">
-        <v>file</v>
+        <v>71</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J72" t="str">
+        <v/>
+      </c>
+      <c r="K72" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K72" t="str">
+      <c r="L72" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P72" t="str">
+      <c r="Q72" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q72" t="str">
+      <c r="R72" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4261,33 +4478,36 @@
         <v>SG6</v>
       </c>
       <c r="H73" t="str">
-        <v>file</v>
+        <v>72</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J73" t="str">
+        <v/>
+      </c>
+      <c r="K73" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K73" t="str">
+      <c r="L73" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L73" t="str">
-        <v/>
-      </c>
       <c r="M73" t="str">
+        <v/>
+      </c>
+      <c r="N73" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N73" t="str">
+      <c r="O73" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P73" t="str">
+      <c r="Q73" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q73" t="str">
+      <c r="R73" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4314,33 +4534,36 @@
         <v>SG1</v>
       </c>
       <c r="H74" t="str">
-        <v>file</v>
+        <v>73</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J74" t="str">
+        <v/>
+      </c>
+      <c r="K74" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K74" t="str">
+      <c r="L74" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L74" t="str">
-        <v/>
-      </c>
       <c r="M74" t="str">
+        <v/>
+      </c>
+      <c r="N74" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N74" t="str">
+      <c r="O74" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P74" t="str">
+      <c r="Q74" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q74" t="str">
+      <c r="R74" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4367,33 +4590,36 @@
         <v>SG2</v>
       </c>
       <c r="H75" t="str">
-        <v>file</v>
+        <v>74</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J75" t="str">
+        <v/>
+      </c>
+      <c r="K75" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K75" t="str">
+      <c r="L75" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L75" t="str">
-        <v/>
-      </c>
       <c r="M75" t="str">
+        <v/>
+      </c>
+      <c r="N75" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N75" t="str">
+      <c r="O75" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P75" t="str">
+      <c r="Q75" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q75" t="str">
+      <c r="R75" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4420,33 +4646,36 @@
         <v>SG3</v>
       </c>
       <c r="H76" t="str">
-        <v>file</v>
+        <v>75</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J76" t="str">
+        <v/>
+      </c>
+      <c r="K76" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K76" t="str">
+      <c r="L76" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L76" t="str">
-        <v/>
-      </c>
       <c r="M76" t="str">
+        <v/>
+      </c>
+      <c r="N76" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N76" t="str">
+      <c r="O76" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P76" t="str">
+      <c r="Q76" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q76" t="str">
+      <c r="R76" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4473,33 +4702,36 @@
         <v>SG4</v>
       </c>
       <c r="H77" t="str">
-        <v>file</v>
+        <v>76</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J77" t="str">
+        <v/>
+      </c>
+      <c r="K77" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K77" t="str">
+      <c r="L77" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L77" t="str">
-        <v/>
-      </c>
       <c r="M77" t="str">
+        <v/>
+      </c>
+      <c r="N77" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N77" t="str">
+      <c r="O77" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P77" t="str">
+      <c r="Q77" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q77" t="str">
+      <c r="R77" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4526,33 +4758,36 @@
         <v>SG5</v>
       </c>
       <c r="H78" t="str">
-        <v>file</v>
+        <v>77</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J78" t="str">
+        <v/>
+      </c>
+      <c r="K78" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K78" t="str">
+      <c r="L78" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L78" t="str">
-        <v/>
-      </c>
       <c r="M78" t="str">
+        <v/>
+      </c>
+      <c r="N78" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N78" t="str">
+      <c r="O78" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P78" t="str">
+      <c r="Q78" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q78" t="str">
+      <c r="R78" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4579,33 +4814,36 @@
         <v>SG6</v>
       </c>
       <c r="H79" t="str">
-        <v>file</v>
+        <v>78</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J79" t="str">
+        <v/>
+      </c>
+      <c r="K79" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K79" t="str">
+      <c r="L79" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P79" t="str">
+      <c r="Q79" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q79" t="str">
+      <c r="R79" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4632,33 +4870,36 @@
         <v>SG1</v>
       </c>
       <c r="H80" t="str">
-        <v>file</v>
+        <v>79</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J80" t="str">
+        <v/>
+      </c>
+      <c r="K80" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K80" t="str">
+      <c r="L80" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L80" t="str">
-        <v/>
-      </c>
       <c r="M80" t="str">
+        <v/>
+      </c>
+      <c r="N80" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N80" t="str">
+      <c r="O80" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P80" t="str">
+      <c r="Q80" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q80" t="str">
+      <c r="R80" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4685,33 +4926,36 @@
         <v>SG2</v>
       </c>
       <c r="H81" t="str">
-        <v>file</v>
+        <v>80</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J81" t="str">
+        <v/>
+      </c>
+      <c r="K81" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K81" t="str">
+      <c r="L81" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L81" t="str">
-        <v/>
-      </c>
       <c r="M81" t="str">
+        <v/>
+      </c>
+      <c r="N81" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N81" t="str">
+      <c r="O81" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P81" t="str">
+      <c r="Q81" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q81" t="str">
+      <c r="R81" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4738,33 +4982,36 @@
         <v>SG3</v>
       </c>
       <c r="H82" t="str">
-        <v>file</v>
+        <v>81</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J82" t="str">
+        <v/>
+      </c>
+      <c r="K82" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K82" t="str">
+      <c r="L82" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L82" t="str">
-        <v/>
-      </c>
       <c r="M82" t="str">
+        <v/>
+      </c>
+      <c r="N82" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N82" t="str">
+      <c r="O82" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P82" t="str">
+      <c r="Q82" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q82" t="str">
+      <c r="R82" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4791,33 +5038,36 @@
         <v>SG4</v>
       </c>
       <c r="H83" t="str">
-        <v>file</v>
+        <v>82</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J83" t="str">
+        <v/>
+      </c>
+      <c r="K83" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K83" t="str">
+      <c r="L83" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L83" t="str">
-        <v/>
-      </c>
       <c r="M83" t="str">
+        <v/>
+      </c>
+      <c r="N83" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N83" t="str">
+      <c r="O83" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P83" t="str">
+      <c r="Q83" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q83" t="str">
+      <c r="R83" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4844,33 +5094,36 @@
         <v>SG5</v>
       </c>
       <c r="H84" t="str">
-        <v>file</v>
+        <v>83</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J84" t="str">
+        <v/>
+      </c>
+      <c r="K84" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K84" t="str">
+      <c r="L84" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L84" t="str">
-        <v/>
-      </c>
       <c r="M84" t="str">
+        <v/>
+      </c>
+      <c r="N84" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N84" t="str">
+      <c r="O84" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P84" t="str">
+      <c r="Q84" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q84" t="str">
+      <c r="R84" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4897,33 +5150,36 @@
         <v>SG6</v>
       </c>
       <c r="H85" t="str">
-        <v>file</v>
+        <v>84</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J85" t="str">
+        <v/>
+      </c>
+      <c r="K85" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K85" t="str">
+      <c r="L85" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L85" t="str">
-        <v/>
-      </c>
       <c r="M85" t="str">
+        <v/>
+      </c>
+      <c r="N85" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N85" t="str">
+      <c r="O85" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P85" t="str">
+      <c r="Q85" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q85" t="str">
+      <c r="R85" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4950,33 +5206,36 @@
         <v>SG1</v>
       </c>
       <c r="H86" t="str">
-        <v>file</v>
+        <v>85</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J86" t="str">
+        <v/>
+      </c>
+      <c r="K86" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K86" t="str">
+      <c r="L86" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P86" t="str">
+      <c r="Q86" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q86" t="str">
+      <c r="R86" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5003,33 +5262,36 @@
         <v>SG2</v>
       </c>
       <c r="H87" t="str">
-        <v>file</v>
+        <v>86</v>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J87" t="str">
+        <v/>
+      </c>
+      <c r="K87" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K87" t="str">
+      <c r="L87" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L87" t="str">
-        <v/>
-      </c>
       <c r="M87" t="str">
+        <v/>
+      </c>
+      <c r="N87" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N87" t="str">
+      <c r="O87" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P87" t="str">
+      <c r="Q87" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q87" t="str">
+      <c r="R87" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5056,33 +5318,36 @@
         <v>SG3</v>
       </c>
       <c r="H88" t="str">
-        <v>file</v>
+        <v>87</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J88" t="str">
+        <v/>
+      </c>
+      <c r="K88" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K88" t="str">
+      <c r="L88" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L88" t="str">
-        <v/>
-      </c>
       <c r="M88" t="str">
+        <v/>
+      </c>
+      <c r="N88" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N88" t="str">
+      <c r="O88" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P88" t="str">
+      <c r="Q88" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q88" t="str">
+      <c r="R88" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5109,33 +5374,36 @@
         <v>SG4</v>
       </c>
       <c r="H89" t="str">
-        <v>file</v>
+        <v>88</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J89" t="str">
+        <v/>
+      </c>
+      <c r="K89" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K89" t="str">
+      <c r="L89" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L89" t="str">
-        <v/>
-      </c>
       <c r="M89" t="str">
+        <v/>
+      </c>
+      <c r="N89" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N89" t="str">
+      <c r="O89" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P89" t="str">
+      <c r="Q89" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q89" t="str">
+      <c r="R89" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5162,33 +5430,36 @@
         <v>SG5</v>
       </c>
       <c r="H90" t="str">
-        <v>file</v>
+        <v>89</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J90" t="str">
+        <v/>
+      </c>
+      <c r="K90" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K90" t="str">
+      <c r="L90" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L90" t="str">
-        <v/>
-      </c>
       <c r="M90" t="str">
+        <v/>
+      </c>
+      <c r="N90" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N90" t="str">
+      <c r="O90" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P90" t="str">
+      <c r="Q90" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q90" t="str">
+      <c r="R90" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5215,33 +5486,36 @@
         <v>SG6</v>
       </c>
       <c r="H91" t="str">
-        <v>file</v>
+        <v>90</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J91" t="str">
+        <v/>
+      </c>
+      <c r="K91" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K91" t="str">
+      <c r="L91" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L91" t="str">
-        <v/>
-      </c>
       <c r="M91" t="str">
+        <v/>
+      </c>
+      <c r="N91" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N91" t="str">
+      <c r="O91" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O91" t="str">
+      <c r="P91" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P91" t="str">
+      <c r="Q91" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q91" t="str">
+      <c r="R91" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5268,33 +5542,36 @@
         <v>SG1</v>
       </c>
       <c r="H92" t="str">
-        <v>file</v>
+        <v>91</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J92" t="str">
+        <v/>
+      </c>
+      <c r="K92" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K92" t="str">
+      <c r="L92" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L92" t="str">
-        <v/>
-      </c>
       <c r="M92" t="str">
+        <v/>
+      </c>
+      <c r="N92" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N92" t="str">
+      <c r="O92" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P92" t="str">
+      <c r="Q92" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q92" t="str">
+      <c r="R92" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5321,33 +5598,36 @@
         <v>SG2</v>
       </c>
       <c r="H93" t="str">
-        <v>file</v>
+        <v>92</v>
       </c>
       <c r="I93" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J93" t="str">
+        <v/>
+      </c>
+      <c r="K93" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K93" t="str">
+      <c r="L93" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L93" t="str">
+      <c r="M93" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N93" t="str">
+      <c r="O93" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O93" t="str">
+      <c r="P93" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P93" t="str">
+      <c r="Q93" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q93" t="str">
+      <c r="R93" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5374,33 +5654,36 @@
         <v>SG3</v>
       </c>
       <c r="H94" t="str">
-        <v>file</v>
+        <v>93</v>
       </c>
       <c r="I94" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J94" t="str">
+        <v/>
+      </c>
+      <c r="K94" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K94" t="str">
+      <c r="L94" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L94" t="str">
-        <v/>
-      </c>
       <c r="M94" t="str">
+        <v/>
+      </c>
+      <c r="N94" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N94" t="str">
+      <c r="O94" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O94" t="str">
+      <c r="P94" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P94" t="str">
+      <c r="Q94" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q94" t="str">
+      <c r="R94" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5427,33 +5710,36 @@
         <v>SG4</v>
       </c>
       <c r="H95" t="str">
-        <v>file</v>
+        <v>94</v>
       </c>
       <c r="I95" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J95" t="str">
+        <v/>
+      </c>
+      <c r="K95" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K95" t="str">
+      <c r="L95" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L95" t="str">
-        <v/>
-      </c>
       <c r="M95" t="str">
+        <v/>
+      </c>
+      <c r="N95" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N95" t="str">
+      <c r="O95" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O95" t="str">
+      <c r="P95" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P95" t="str">
+      <c r="Q95" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q95" t="str">
+      <c r="R95" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5480,33 +5766,36 @@
         <v>SG5</v>
       </c>
       <c r="H96" t="str">
-        <v>file</v>
+        <v>95</v>
       </c>
       <c r="I96" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J96" t="str">
+        <v/>
+      </c>
+      <c r="K96" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K96" t="str">
+      <c r="L96" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L96" t="str">
-        <v/>
-      </c>
       <c r="M96" t="str">
+        <v/>
+      </c>
+      <c r="N96" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N96" t="str">
+      <c r="O96" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O96" t="str">
+      <c r="P96" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P96" t="str">
+      <c r="Q96" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q96" t="str">
+      <c r="R96" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5533,33 +5822,36 @@
         <v>SG6</v>
       </c>
       <c r="H97" t="str">
-        <v>file</v>
+        <v>96</v>
       </c>
       <c r="I97" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J97" t="str">
+        <v/>
+      </c>
+      <c r="K97" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K97" t="str">
+      <c r="L97" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L97" t="str">
-        <v/>
-      </c>
       <c r="M97" t="str">
+        <v/>
+      </c>
+      <c r="N97" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N97" t="str">
+      <c r="O97" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O97" t="str">
+      <c r="P97" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P97" t="str">
+      <c r="Q97" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q97" t="str">
+      <c r="R97" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5586,33 +5878,36 @@
         <v>SG1</v>
       </c>
       <c r="H98" t="str">
-        <v>file</v>
+        <v>97</v>
       </c>
       <c r="I98" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K98" t="str">
+      <c r="L98" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L98" t="str">
-        <v/>
-      </c>
       <c r="M98" t="str">
+        <v/>
+      </c>
+      <c r="N98" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N98" t="str">
+      <c r="O98" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O98" t="str">
+      <c r="P98" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P98" t="str">
+      <c r="Q98" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q98" t="str">
+      <c r="R98" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5639,33 +5934,36 @@
         <v>SG2</v>
       </c>
       <c r="H99" t="str">
-        <v>file</v>
+        <v>98</v>
       </c>
       <c r="I99" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K99" t="str">
+      <c r="L99" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
       <c r="M99" t="str">
+        <v/>
+      </c>
+      <c r="N99" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N99" t="str">
+      <c r="O99" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O99" t="str">
+      <c r="P99" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P99" t="str">
+      <c r="Q99" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q99" t="str">
+      <c r="R99" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5692,33 +5990,36 @@
         <v>SG3</v>
       </c>
       <c r="H100" t="str">
-        <v>file</v>
+        <v>99</v>
       </c>
       <c r="I100" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K100" t="str">
+      <c r="L100" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L100" t="str">
+      <c r="M100" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N100" t="str">
+      <c r="O100" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O100" t="str">
+      <c r="P100" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P100" t="str">
+      <c r="Q100" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q100" t="str">
+      <c r="R100" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5745,33 +6046,36 @@
         <v>SG4</v>
       </c>
       <c r="H101" t="str">
-        <v>file</v>
+        <v>100</v>
       </c>
       <c r="I101" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K101" t="str">
+      <c r="L101" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L101" t="str">
-        <v/>
-      </c>
       <c r="M101" t="str">
+        <v/>
+      </c>
+      <c r="N101" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N101" t="str">
+      <c r="O101" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O101" t="str">
+      <c r="P101" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P101" t="str">
+      <c r="Q101" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q101" t="str">
+      <c r="R101" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5798,33 +6102,36 @@
         <v>SG5</v>
       </c>
       <c r="H102" t="str">
-        <v>file</v>
+        <v>101</v>
       </c>
       <c r="I102" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K102" t="str">
+      <c r="L102" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
       <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N102" t="str">
+      <c r="O102" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P102" t="str">
+      <c r="Q102" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q102" t="str">
+      <c r="R102" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5851,33 +6158,36 @@
         <v>SG6</v>
       </c>
       <c r="H103" t="str">
-        <v>file</v>
+        <v>102</v>
       </c>
       <c r="I103" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K103" t="str">
+      <c r="L103" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L103" t="str">
-        <v/>
-      </c>
       <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N103" t="str">
+      <c r="O103" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O103" t="str">
+      <c r="P103" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P103" t="str">
+      <c r="Q103" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q103" t="str">
+      <c r="R103" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5904,33 +6214,36 @@
         <v>SG1</v>
       </c>
       <c r="H104" t="str">
-        <v>file</v>
+        <v>103</v>
       </c>
       <c r="I104" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K104" t="str">
+      <c r="L104" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L104" t="str">
-        <v/>
-      </c>
       <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N104" t="str">
+      <c r="O104" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O104" t="str">
+      <c r="P104" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P104" t="str">
+      <c r="Q104" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q104" t="str">
+      <c r="R104" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5957,33 +6270,36 @@
         <v>SG2</v>
       </c>
       <c r="H105" t="str">
-        <v>file</v>
+        <v>104</v>
       </c>
       <c r="I105" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K105" t="str">
+      <c r="L105" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L105" t="str">
-        <v/>
-      </c>
       <c r="M105" t="str">
+        <v/>
+      </c>
+      <c r="N105" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N105" t="str">
+      <c r="O105" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O105" t="str">
+      <c r="P105" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P105" t="str">
+      <c r="Q105" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q105" t="str">
+      <c r="R105" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6010,33 +6326,36 @@
         <v>SG3</v>
       </c>
       <c r="H106" t="str">
-        <v>file</v>
+        <v>105</v>
       </c>
       <c r="I106" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K106" t="str">
+      <c r="L106" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L106" t="str">
-        <v/>
-      </c>
       <c r="M106" t="str">
+        <v/>
+      </c>
+      <c r="N106" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N106" t="str">
+      <c r="O106" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O106" t="str">
+      <c r="P106" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P106" t="str">
+      <c r="Q106" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q106" t="str">
+      <c r="R106" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6063,33 +6382,36 @@
         <v>SG4</v>
       </c>
       <c r="H107" t="str">
-        <v>file</v>
+        <v>106</v>
       </c>
       <c r="I107" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K107" t="str">
+      <c r="L107" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L107" t="str">
+      <c r="M107" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N107" t="str">
+      <c r="O107" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O107" t="str">
+      <c r="P107" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P107" t="str">
+      <c r="Q107" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q107" t="str">
+      <c r="R107" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6116,33 +6438,36 @@
         <v>SG5</v>
       </c>
       <c r="H108" t="str">
-        <v>file</v>
+        <v>107</v>
       </c>
       <c r="I108" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K108" t="str">
+      <c r="L108" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L108" t="str">
-        <v/>
-      </c>
       <c r="M108" t="str">
+        <v/>
+      </c>
+      <c r="N108" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N108" t="str">
+      <c r="O108" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O108" t="str">
+      <c r="P108" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P108" t="str">
+      <c r="Q108" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q108" t="str">
+      <c r="R108" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6169,33 +6494,36 @@
         <v>SG6</v>
       </c>
       <c r="H109" t="str">
-        <v>file</v>
+        <v>108</v>
       </c>
       <c r="I109" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K109" t="str">
+      <c r="L109" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L109" t="str">
-        <v/>
-      </c>
       <c r="M109" t="str">
+        <v/>
+      </c>
+      <c r="N109" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N109" t="str">
+      <c r="O109" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O109" t="str">
+      <c r="P109" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P109" t="str">
+      <c r="Q109" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q109" t="str">
+      <c r="R109" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6222,33 +6550,36 @@
         <v>SG1</v>
       </c>
       <c r="H110" t="str">
-        <v>file</v>
+        <v>109</v>
       </c>
       <c r="I110" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K110" t="str">
+      <c r="L110" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L110" t="str">
-        <v/>
-      </c>
       <c r="M110" t="str">
+        <v/>
+      </c>
+      <c r="N110" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N110" t="str">
+      <c r="O110" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O110" t="str">
+      <c r="P110" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P110" t="str">
+      <c r="Q110" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q110" t="str">
+      <c r="R110" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6275,33 +6606,36 @@
         <v>SG2</v>
       </c>
       <c r="H111" t="str">
-        <v>file</v>
+        <v>110</v>
       </c>
       <c r="I111" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K111" t="str">
+      <c r="L111" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L111" t="str">
-        <v/>
-      </c>
       <c r="M111" t="str">
+        <v/>
+      </c>
+      <c r="N111" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N111" t="str">
+      <c r="O111" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O111" t="str">
+      <c r="P111" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P111" t="str">
+      <c r="Q111" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q111" t="str">
+      <c r="R111" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6328,33 +6662,36 @@
         <v>SG3</v>
       </c>
       <c r="H112" t="str">
-        <v>file</v>
+        <v>111</v>
       </c>
       <c r="I112" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K112" t="str">
+      <c r="L112" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L112" t="str">
-        <v/>
-      </c>
       <c r="M112" t="str">
+        <v/>
+      </c>
+      <c r="N112" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N112" t="str">
+      <c r="O112" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O112" t="str">
+      <c r="P112" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P112" t="str">
+      <c r="Q112" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q112" t="str">
+      <c r="R112" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6381,33 +6718,36 @@
         <v>SG4</v>
       </c>
       <c r="H113" t="str">
-        <v>file</v>
+        <v>112</v>
       </c>
       <c r="I113" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K113" t="str">
+      <c r="L113" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L113" t="str">
-        <v/>
-      </c>
       <c r="M113" t="str">
+        <v/>
+      </c>
+      <c r="N113" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N113" t="str">
+      <c r="O113" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O113" t="str">
+      <c r="P113" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P113" t="str">
+      <c r="Q113" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q113" t="str">
+      <c r="R113" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6434,33 +6774,36 @@
         <v>SG5</v>
       </c>
       <c r="H114" t="str">
-        <v>file</v>
+        <v>113</v>
       </c>
       <c r="I114" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K114" t="str">
+      <c r="L114" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L114" t="str">
+      <c r="M114" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N114" t="str">
+      <c r="O114" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O114" t="str">
+      <c r="P114" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P114" t="str">
+      <c r="Q114" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q114" t="str">
+      <c r="R114" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6487,33 +6830,36 @@
         <v>SG6</v>
       </c>
       <c r="H115" t="str">
-        <v>file</v>
+        <v>114</v>
       </c>
       <c r="I115" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K115" t="str">
+      <c r="L115" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L115" t="str">
-        <v/>
-      </c>
       <c r="M115" t="str">
+        <v/>
+      </c>
+      <c r="N115" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N115" t="str">
+      <c r="O115" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O115" t="str">
+      <c r="P115" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P115" t="str">
+      <c r="Q115" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q115" t="str">
+      <c r="R115" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6540,33 +6886,36 @@
         <v>SG1</v>
       </c>
       <c r="H116" t="str">
-        <v>file</v>
+        <v>115</v>
       </c>
       <c r="I116" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K116" t="str">
+      <c r="L116" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L116" t="str">
-        <v/>
-      </c>
       <c r="M116" t="str">
+        <v/>
+      </c>
+      <c r="N116" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N116" t="str">
+      <c r="O116" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O116" t="str">
+      <c r="P116" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P116" t="str">
+      <c r="Q116" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q116" t="str">
+      <c r="R116" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6593,33 +6942,36 @@
         <v>SG2</v>
       </c>
       <c r="H117" t="str">
-        <v>file</v>
+        <v>116</v>
       </c>
       <c r="I117" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K117" t="str">
+      <c r="L117" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L117" t="str">
-        <v/>
-      </c>
       <c r="M117" t="str">
+        <v/>
+      </c>
+      <c r="N117" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N117" t="str">
+      <c r="O117" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O117" t="str">
+      <c r="P117" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P117" t="str">
+      <c r="Q117" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q117" t="str">
+      <c r="R117" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6646,33 +6998,36 @@
         <v>SG3</v>
       </c>
       <c r="H118" t="str">
-        <v>file</v>
+        <v>117</v>
       </c>
       <c r="I118" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K118" t="str">
+      <c r="L118" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L118" t="str">
-        <v/>
-      </c>
       <c r="M118" t="str">
+        <v/>
+      </c>
+      <c r="N118" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N118" t="str">
+      <c r="O118" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O118" t="str">
+      <c r="P118" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P118" t="str">
+      <c r="Q118" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q118" t="str">
+      <c r="R118" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6699,33 +7054,36 @@
         <v>SG4</v>
       </c>
       <c r="H119" t="str">
-        <v>file</v>
+        <v>118</v>
       </c>
       <c r="I119" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K119" t="str">
+      <c r="L119" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L119" t="str">
-        <v/>
-      </c>
       <c r="M119" t="str">
+        <v/>
+      </c>
+      <c r="N119" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N119" t="str">
+      <c r="O119" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O119" t="str">
+      <c r="P119" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P119" t="str">
+      <c r="Q119" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q119" t="str">
+      <c r="R119" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6752,33 +7110,36 @@
         <v>SG5</v>
       </c>
       <c r="H120" t="str">
-        <v>file</v>
+        <v>119</v>
       </c>
       <c r="I120" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K120" t="str">
+      <c r="L120" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L120" t="str">
-        <v/>
-      </c>
       <c r="M120" t="str">
+        <v/>
+      </c>
+      <c r="N120" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N120" t="str">
+      <c r="O120" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O120" t="str">
+      <c r="P120" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P120" t="str">
+      <c r="Q120" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q120" t="str">
+      <c r="R120" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6805,33 +7166,36 @@
         <v>SG6</v>
       </c>
       <c r="H121" t="str">
-        <v>file</v>
+        <v>120</v>
       </c>
       <c r="I121" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K121" t="str">
+      <c r="L121" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L121" t="str">
+      <c r="M121" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N121" t="str">
+      <c r="O121" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O121" t="str">
+      <c r="P121" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P121" t="str">
+      <c r="Q121" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q121" t="str">
+      <c r="R121" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6858,33 +7222,36 @@
         <v>SG1</v>
       </c>
       <c r="H122" t="str">
-        <v>file</v>
+        <v>121</v>
       </c>
       <c r="I122" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K122" t="str">
+      <c r="L122" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L122" t="str">
-        <v/>
-      </c>
       <c r="M122" t="str">
+        <v/>
+      </c>
+      <c r="N122" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N122" t="str">
+      <c r="O122" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O122" t="str">
+      <c r="P122" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P122" t="str">
+      <c r="Q122" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q122" t="str">
+      <c r="R122" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6911,33 +7278,36 @@
         <v>SG2</v>
       </c>
       <c r="H123" t="str">
-        <v>file</v>
+        <v>122</v>
       </c>
       <c r="I123" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K123" t="str">
+      <c r="L123" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L123" t="str">
-        <v/>
-      </c>
       <c r="M123" t="str">
+        <v/>
+      </c>
+      <c r="N123" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N123" t="str">
+      <c r="O123" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O123" t="str">
+      <c r="P123" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P123" t="str">
+      <c r="Q123" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q123" t="str">
+      <c r="R123" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6964,33 +7334,36 @@
         <v>SG3</v>
       </c>
       <c r="H124" t="str">
-        <v>file</v>
+        <v>123</v>
       </c>
       <c r="I124" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K124" t="str">
+      <c r="L124" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L124" t="str">
-        <v/>
-      </c>
       <c r="M124" t="str">
+        <v/>
+      </c>
+      <c r="N124" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N124" t="str">
+      <c r="O124" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O124" t="str">
+      <c r="P124" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P124" t="str">
+      <c r="Q124" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q124" t="str">
+      <c r="R124" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7017,33 +7390,36 @@
         <v>SG4</v>
       </c>
       <c r="H125" t="str">
-        <v>file</v>
+        <v>124</v>
       </c>
       <c r="I125" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K125" t="str">
+      <c r="L125" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L125" t="str">
-        <v/>
-      </c>
       <c r="M125" t="str">
+        <v/>
+      </c>
+      <c r="N125" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N125" t="str">
+      <c r="O125" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O125" t="str">
+      <c r="P125" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P125" t="str">
+      <c r="Q125" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q125" t="str">
+      <c r="R125" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7070,33 +7446,36 @@
         <v>SG5</v>
       </c>
       <c r="H126" t="str">
-        <v>file</v>
+        <v>125</v>
       </c>
       <c r="I126" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K126" t="str">
+      <c r="L126" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L126" t="str">
-        <v/>
-      </c>
       <c r="M126" t="str">
+        <v/>
+      </c>
+      <c r="N126" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N126" t="str">
+      <c r="O126" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O126" t="str">
+      <c r="P126" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P126" t="str">
+      <c r="Q126" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q126" t="str">
+      <c r="R126" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7123,33 +7502,36 @@
         <v>SG6</v>
       </c>
       <c r="H127" t="str">
-        <v>file</v>
+        <v>126</v>
       </c>
       <c r="I127" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K127" t="str">
+      <c r="L127" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L127" t="str">
-        <v/>
-      </c>
       <c r="M127" t="str">
+        <v/>
+      </c>
+      <c r="N127" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N127" t="str">
+      <c r="O127" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O127" t="str">
+      <c r="P127" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P127" t="str">
+      <c r="Q127" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q127" t="str">
+      <c r="R127" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7176,33 +7558,36 @@
         <v>SG1</v>
       </c>
       <c r="H128" t="str">
-        <v>file</v>
+        <v>127</v>
       </c>
       <c r="I128" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K128" t="str">
+      <c r="L128" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L128" t="str">
+      <c r="M128" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N128" t="str">
+      <c r="O128" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O128" t="str">
+      <c r="P128" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P128" t="str">
+      <c r="Q128" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q128" t="str">
+      <c r="R128" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7229,33 +7614,36 @@
         <v>SG2</v>
       </c>
       <c r="H129" t="str">
-        <v>file</v>
+        <v>128</v>
       </c>
       <c r="I129" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K129" t="str">
+      <c r="L129" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L129" t="str">
-        <v/>
-      </c>
       <c r="M129" t="str">
+        <v/>
+      </c>
+      <c r="N129" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N129" t="str">
+      <c r="O129" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O129" t="str">
+      <c r="P129" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P129" t="str">
+      <c r="Q129" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q129" t="str">
+      <c r="R129" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7282,33 +7670,36 @@
         <v>SG3</v>
       </c>
       <c r="H130" t="str">
-        <v>file</v>
+        <v>129</v>
       </c>
       <c r="I130" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K130" t="str">
+      <c r="L130" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L130" t="str">
-        <v/>
-      </c>
       <c r="M130" t="str">
+        <v/>
+      </c>
+      <c r="N130" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N130" t="str">
+      <c r="O130" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O130" t="str">
+      <c r="P130" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P130" t="str">
+      <c r="Q130" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q130" t="str">
+      <c r="R130" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7335,33 +7726,36 @@
         <v>SG4</v>
       </c>
       <c r="H131" t="str">
-        <v>file</v>
+        <v>130</v>
       </c>
       <c r="I131" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K131" t="str">
+      <c r="L131" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L131" t="str">
-        <v/>
-      </c>
       <c r="M131" t="str">
+        <v/>
+      </c>
+      <c r="N131" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N131" t="str">
+      <c r="O131" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O131" t="str">
+      <c r="P131" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P131" t="str">
+      <c r="Q131" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q131" t="str">
+      <c r="R131" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7388,33 +7782,36 @@
         <v>SG5</v>
       </c>
       <c r="H132" t="str">
-        <v>file</v>
+        <v>131</v>
       </c>
       <c r="I132" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K132" t="str">
+      <c r="L132" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L132" t="str">
-        <v/>
-      </c>
       <c r="M132" t="str">
+        <v/>
+      </c>
+      <c r="N132" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N132" t="str">
+      <c r="O132" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O132" t="str">
+      <c r="P132" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P132" t="str">
+      <c r="Q132" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q132" t="str">
+      <c r="R132" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7441,33 +7838,36 @@
         <v>SG6</v>
       </c>
       <c r="H133" t="str">
-        <v>file</v>
+        <v>132</v>
       </c>
       <c r="I133" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K133" t="str">
+      <c r="L133" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L133" t="str">
-        <v/>
-      </c>
       <c r="M133" t="str">
+        <v/>
+      </c>
+      <c r="N133" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N133" t="str">
+      <c r="O133" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O133" t="str">
+      <c r="P133" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P133" t="str">
+      <c r="Q133" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q133" t="str">
+      <c r="R133" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7494,33 +7894,36 @@
         <v>SG1</v>
       </c>
       <c r="H134" t="str">
-        <v>file</v>
+        <v>133</v>
       </c>
       <c r="I134" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K134" t="str">
+      <c r="L134" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L134" t="str">
-        <v/>
-      </c>
       <c r="M134" t="str">
+        <v/>
+      </c>
+      <c r="N134" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N134" t="str">
+      <c r="O134" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O134" t="str">
+      <c r="P134" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P134" t="str">
+      <c r="Q134" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q134" t="str">
+      <c r="R134" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7547,33 +7950,36 @@
         <v>SG2</v>
       </c>
       <c r="H135" t="str">
-        <v>file</v>
+        <v>134</v>
       </c>
       <c r="I135" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K135" t="str">
+      <c r="L135" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L135" t="str">
+      <c r="M135" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N135" t="str">
+      <c r="O135" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O135" t="str">
+      <c r="P135" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P135" t="str">
+      <c r="Q135" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q135" t="str">
+      <c r="R135" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7600,33 +8006,36 @@
         <v>SG3</v>
       </c>
       <c r="H136" t="str">
-        <v>file</v>
+        <v>135</v>
       </c>
       <c r="I136" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K136" t="str">
+      <c r="L136" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L136" t="str">
-        <v/>
-      </c>
       <c r="M136" t="str">
+        <v/>
+      </c>
+      <c r="N136" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N136" t="str">
+      <c r="O136" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O136" t="str">
+      <c r="P136" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P136" t="str">
+      <c r="Q136" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q136" t="str">
+      <c r="R136" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7653,33 +8062,36 @@
         <v>SG4</v>
       </c>
       <c r="H137" t="str">
-        <v>file</v>
+        <v>136</v>
       </c>
       <c r="I137" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K137" t="str">
+      <c r="L137" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L137" t="str">
-        <v/>
-      </c>
       <c r="M137" t="str">
+        <v/>
+      </c>
+      <c r="N137" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N137" t="str">
+      <c r="O137" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O137" t="str">
+      <c r="P137" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P137" t="str">
+      <c r="Q137" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q137" t="str">
+      <c r="R137" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7706,33 +8118,36 @@
         <v>SG5</v>
       </c>
       <c r="H138" t="str">
-        <v>file</v>
+        <v>137</v>
       </c>
       <c r="I138" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K138" t="str">
+      <c r="L138" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L138" t="str">
-        <v/>
-      </c>
       <c r="M138" t="str">
+        <v/>
+      </c>
+      <c r="N138" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N138" t="str">
+      <c r="O138" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O138" t="str">
+      <c r="P138" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P138" t="str">
+      <c r="Q138" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q138" t="str">
+      <c r="R138" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7759,33 +8174,36 @@
         <v>SG6</v>
       </c>
       <c r="H139" t="str">
-        <v>file</v>
+        <v>138</v>
       </c>
       <c r="I139" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J139" t="str">
+        <v/>
+      </c>
+      <c r="K139" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K139" t="str">
+      <c r="L139" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L139" t="str">
-        <v/>
-      </c>
       <c r="M139" t="str">
+        <v/>
+      </c>
+      <c r="N139" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N139" t="str">
+      <c r="O139" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O139" t="str">
+      <c r="P139" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P139" t="str">
+      <c r="Q139" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q139" t="str">
+      <c r="R139" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7812,33 +8230,36 @@
         <v>SG1</v>
       </c>
       <c r="H140" t="str">
-        <v>file</v>
+        <v>139</v>
       </c>
       <c r="I140" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J140" t="str">
+        <v/>
+      </c>
+      <c r="K140" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K140" t="str">
+      <c r="L140" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L140" t="str">
-        <v/>
-      </c>
       <c r="M140" t="str">
+        <v/>
+      </c>
+      <c r="N140" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N140" t="str">
+      <c r="O140" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O140" t="str">
+      <c r="P140" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P140" t="str">
+      <c r="Q140" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q140" t="str">
+      <c r="R140" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7865,33 +8286,36 @@
         <v>SG2</v>
       </c>
       <c r="H141" t="str">
-        <v>file</v>
+        <v>140</v>
       </c>
       <c r="I141" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J141" t="str">
+        <v/>
+      </c>
+      <c r="K141" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K141" t="str">
+      <c r="L141" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L141" t="str">
-        <v/>
-      </c>
       <c r="M141" t="str">
+        <v/>
+      </c>
+      <c r="N141" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N141" t="str">
+      <c r="O141" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O141" t="str">
+      <c r="P141" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P141" t="str">
+      <c r="Q141" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q141" t="str">
+      <c r="R141" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7918,33 +8342,36 @@
         <v>SG3</v>
       </c>
       <c r="H142" t="str">
-        <v>file</v>
+        <v>141</v>
       </c>
       <c r="I142" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J142" t="str">
+        <v/>
+      </c>
+      <c r="K142" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K142" t="str">
+      <c r="L142" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L142" t="str">
+      <c r="M142" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N142" t="str">
+      <c r="O142" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O142" t="str">
+      <c r="P142" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P142" t="str">
+      <c r="Q142" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q142" t="str">
+      <c r="R142" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7971,33 +8398,36 @@
         <v>SG4</v>
       </c>
       <c r="H143" t="str">
-        <v>file</v>
+        <v>142</v>
       </c>
       <c r="I143" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J143" t="str">
+        <v/>
+      </c>
+      <c r="K143" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K143" t="str">
+      <c r="L143" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L143" t="str">
-        <v/>
-      </c>
       <c r="M143" t="str">
+        <v/>
+      </c>
+      <c r="N143" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N143" t="str">
+      <c r="O143" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O143" t="str">
+      <c r="P143" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P143" t="str">
+      <c r="Q143" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q143" t="str">
+      <c r="R143" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8024,33 +8454,36 @@
         <v>SG5</v>
       </c>
       <c r="H144" t="str">
-        <v>file</v>
+        <v>143</v>
       </c>
       <c r="I144" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J144" t="str">
+        <v/>
+      </c>
+      <c r="K144" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K144" t="str">
+      <c r="L144" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L144" t="str">
-        <v/>
-      </c>
       <c r="M144" t="str">
+        <v/>
+      </c>
+      <c r="N144" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N144" t="str">
+      <c r="O144" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O144" t="str">
+      <c r="P144" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P144" t="str">
+      <c r="Q144" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q144" t="str">
+      <c r="R144" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8077,33 +8510,36 @@
         <v>SG6</v>
       </c>
       <c r="H145" t="str">
-        <v>file</v>
+        <v>144</v>
       </c>
       <c r="I145" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J145" t="str">
+        <v/>
+      </c>
+      <c r="K145" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K145" t="str">
+      <c r="L145" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L145" t="str">
-        <v/>
-      </c>
       <c r="M145" t="str">
+        <v/>
+      </c>
+      <c r="N145" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N145" t="str">
+      <c r="O145" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O145" t="str">
+      <c r="P145" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P145" t="str">
+      <c r="Q145" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q145" t="str">
+      <c r="R145" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8130,33 +8566,36 @@
         <v>SG1</v>
       </c>
       <c r="H146" t="str">
-        <v>file</v>
+        <v>145</v>
       </c>
       <c r="I146" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J146" t="str">
+        <v/>
+      </c>
+      <c r="K146" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K146" t="str">
+      <c r="L146" t="str">
         <v>CL G1</v>
       </c>
-      <c r="L146" t="str">
-        <v/>
-      </c>
       <c r="M146" t="str">
+        <v/>
+      </c>
+      <c r="N146" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N146" t="str">
+      <c r="O146" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O146" t="str">
+      <c r="P146" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P146" t="str">
+      <c r="Q146" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q146" t="str">
+      <c r="R146" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8183,33 +8622,36 @@
         <v>SG2</v>
       </c>
       <c r="H147" t="str">
-        <v>file</v>
+        <v>146</v>
       </c>
       <c r="I147" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J147" t="str">
+        <v/>
+      </c>
+      <c r="K147" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K147" t="str">
+      <c r="L147" t="str">
         <v>ML G2</v>
       </c>
-      <c r="L147" t="str">
-        <v/>
-      </c>
       <c r="M147" t="str">
+        <v/>
+      </c>
+      <c r="N147" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N147" t="str">
+      <c r="O147" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O147" t="str">
+      <c r="P147" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P147" t="str">
+      <c r="Q147" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q147" t="str">
+      <c r="R147" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8236,33 +8678,36 @@
         <v>SG3</v>
       </c>
       <c r="H148" t="str">
-        <v>file</v>
+        <v>147</v>
       </c>
       <c r="I148" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J148" t="str">
+        <v/>
+      </c>
+      <c r="K148" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K148" t="str">
+      <c r="L148" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L148" t="str">
-        <v/>
-      </c>
       <c r="M148" t="str">
+        <v/>
+      </c>
+      <c r="N148" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N148" t="str">
+      <c r="O148" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O148" t="str">
+      <c r="P148" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P148" t="str">
+      <c r="Q148" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q148" t="str">
+      <c r="R148" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8289,33 +8734,36 @@
         <v>SG4</v>
       </c>
       <c r="H149" t="str">
-        <v>file</v>
+        <v>148</v>
       </c>
       <c r="I149" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J149" t="str">
+        <v/>
+      </c>
+      <c r="K149" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K149" t="str">
+      <c r="L149" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L149" t="str">
+      <c r="M149" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N149" t="str">
+      <c r="O149" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O149" t="str">
+      <c r="P149" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P149" t="str">
+      <c r="Q149" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q149" t="str">
+      <c r="R149" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8342,33 +8790,36 @@
         <v>SG5</v>
       </c>
       <c r="H150" t="str">
-        <v>file</v>
+        <v>149</v>
       </c>
       <c r="I150" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J150" t="str">
+        <v/>
+      </c>
+      <c r="K150" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K150" t="str">
+      <c r="L150" t="str">
         <v>ML G1</v>
       </c>
-      <c r="L150" t="str">
-        <v/>
-      </c>
       <c r="M150" t="str">
+        <v/>
+      </c>
+      <c r="N150" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N150" t="str">
+      <c r="O150" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O150" t="str">
+      <c r="P150" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P150" t="str">
+      <c r="Q150" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q150" t="str">
+      <c r="R150" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8395,33 +8846,36 @@
         <v>SG6</v>
       </c>
       <c r="H151" t="str">
-        <v>file</v>
+        <v>150</v>
       </c>
       <c r="I151" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J151" t="str">
+        <v/>
+      </c>
+      <c r="K151" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K151" t="str">
+      <c r="L151" t="str">
         <v>TL G2</v>
       </c>
-      <c r="L151" t="str">
-        <v/>
-      </c>
       <c r="M151" t="str">
+        <v/>
+      </c>
+      <c r="N151" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N151" t="str">
+      <c r="O151" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O151" t="str">
+      <c r="P151" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P151" t="str">
+      <c r="Q151" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q151" t="str">
+      <c r="R151" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8448,33 +8902,36 @@
         <v>SG1</v>
       </c>
       <c r="H152" t="str">
-        <v>file</v>
+        <v>151</v>
       </c>
       <c r="I152" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J152" t="str">
+        <v/>
+      </c>
+      <c r="K152" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K152" t="str">
+      <c r="L152" t="str">
         <v>CL G3</v>
       </c>
-      <c r="L152" t="str">
-        <v/>
-      </c>
       <c r="M152" t="str">
+        <v/>
+      </c>
+      <c r="N152" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N152" t="str">
+      <c r="O152" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O152" t="str">
+      <c r="P152" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P152" t="str">
+      <c r="Q152" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q152" t="str">
+      <c r="R152" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8501,33 +8958,36 @@
         <v>SG2</v>
       </c>
       <c r="H153" t="str">
-        <v>file</v>
+        <v>152</v>
       </c>
       <c r="I153" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J153" t="str">
+        <v/>
+      </c>
+      <c r="K153" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K153" t="str">
+      <c r="L153" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L153" t="str">
-        <v/>
-      </c>
       <c r="M153" t="str">
+        <v/>
+      </c>
+      <c r="N153" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N153" t="str">
+      <c r="O153" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O153" t="str">
+      <c r="P153" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P153" t="str">
+      <c r="Q153" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q153" t="str">
+      <c r="R153" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8554,33 +9014,36 @@
         <v>SG3</v>
       </c>
       <c r="H154" t="str">
-        <v>file</v>
+        <v>153</v>
       </c>
       <c r="I154" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J154" t="str">
+        <v/>
+      </c>
+      <c r="K154" t="str">
         <v>EL G1</v>
       </c>
-      <c r="K154" t="str">
+      <c r="L154" t="str">
         <v>TL G1</v>
       </c>
-      <c r="L154" t="str">
-        <v/>
-      </c>
       <c r="M154" t="str">
+        <v/>
+      </c>
+      <c r="N154" t="str">
         <v>MA G1</v>
       </c>
-      <c r="N154" t="str">
+      <c r="O154" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="O154" t="str">
+      <c r="P154" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="P154" t="str">
+      <c r="Q154" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="Q154" t="str">
+      <c r="R154" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8607,33 +9070,36 @@
         <v>SG4</v>
       </c>
       <c r="H155" t="str">
-        <v>file</v>
+        <v>154</v>
       </c>
       <c r="I155" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J155" t="str">
+        <v/>
+      </c>
+      <c r="K155" t="str">
         <v>EL G2</v>
       </c>
-      <c r="K155" t="str">
+      <c r="L155" t="str">
         <v>CL G2</v>
       </c>
-      <c r="L155" t="str">
-        <v/>
-      </c>
       <c r="M155" t="str">
+        <v/>
+      </c>
+      <c r="N155" t="str">
         <v>MA G2</v>
       </c>
-      <c r="N155" t="str">
+      <c r="O155" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="O155" t="str">
+      <c r="P155" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="P155" t="str">
+      <c r="Q155" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="Q155" t="str">
+      <c r="R155" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8660,33 +9126,36 @@
         <v>SG5</v>
       </c>
       <c r="H156" t="str">
-        <v>file</v>
+        <v>155</v>
       </c>
       <c r="I156" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J156" t="str">
+        <v/>
+      </c>
+      <c r="K156" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K156" t="str">
+      <c r="L156" t="str">
         <v>ML G3</v>
       </c>
-      <c r="L156" t="str">
+      <c r="M156" t="str">
         <v>MALAY</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O156" t="str">
+      <c r="P156" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P156" t="str">
+      <c r="Q156" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q156" t="str">
+      <c r="R156" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8713,39 +9182,42 @@
         <v>SG6</v>
       </c>
       <c r="H157" t="str">
-        <v>file</v>
+        <v>156</v>
       </c>
       <c r="I157" t="str">
-        <v/>
+        <v>file</v>
       </c>
       <c r="J157" t="str">
+        <v/>
+      </c>
+      <c r="K157" t="str">
         <v>EL G3</v>
       </c>
-      <c r="K157" t="str">
+      <c r="L157" t="str">
         <v>TL G3</v>
       </c>
-      <c r="L157" t="str">
-        <v/>
-      </c>
       <c r="M157" t="str">
+        <v/>
+      </c>
+      <c r="N157" t="str">
         <v>MA G3</v>
       </c>
-      <c r="N157" t="str">
+      <c r="O157" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="O157" t="str">
+      <c r="P157" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="P157" t="str">
+      <c r="Q157" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="Q157" t="str">
+      <c r="R157" t="str">
         <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:R157"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Groups" sheetId="2" r:id="rId2"/>
     <sheet name="Memberships" sheetId="3" r:id="rId3"/>
     <sheet name="Teachers" sheetId="4" r:id="rId4"/>
-    <sheet name="Sources" sheetId="5" r:id="rId5"/>
+    <sheet name="Subjects" sheetId="5" r:id="rId5"/>
+    <sheet name="Sources" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
@@ -14546,6 +14547,55 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A7"/>
+  <cols>
+    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Subject</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>English Language</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Geography</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>History</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Literature</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Mathematics</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Science</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A7"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F2"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>

--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Teachers" sheetId="4" r:id="rId4"/>
     <sheet name="Subjects" sheetId="5" r:id="rId5"/>
     <sheet name="Sources" sheetId="6" r:id="rId6"/>
+    <sheet name="Requests" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -402,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R157"/>
+  <dimension ref="A1:S157"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -414,7 +415,7 @@
     <col min="8" max="8" width="5.83203125" customWidth="1"/>
     <col min="9" max="9" width="8.83203125" customWidth="1"/>
     <col min="10" max="10" width="28.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="13" max="13" width="12.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
@@ -422,6 +423,7 @@
     <col min="16" max="16" width="12.83203125" customWidth="1"/>
     <col min="17" max="17" width="12.83203125" customWidth="1"/>
     <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,27 +458,30 @@
         <v>SourceName</v>
       </c>
       <c r="K1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="L1" t="str">
         <v>EL</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>MT</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>HMT</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>MA</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>SCI</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>HIST</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>GEOG</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>LIT</v>
       </c>
     </row>
@@ -512,27 +517,30 @@
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="R2" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R2" t="str">
+      <c r="S2" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -568,27 +576,30 @@
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
       <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O3" t="str">
+      <c r="P3" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P3" t="str">
+      <c r="Q3" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="R3" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R3" t="str">
+      <c r="S3" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -624,27 +635,30 @@
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L4" t="str">
+      <c r="M4" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O4" t="str">
+      <c r="P4" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P4" t="str">
+      <c r="Q4" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q4" t="str">
+      <c r="R4" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R4" t="str">
+      <c r="S4" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -680,27 +694,30 @@
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L5" t="str">
+      <c r="M5" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
       <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="R5" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R5" t="str">
+      <c r="S5" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -736,27 +753,30 @@
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L6" t="str">
+      <c r="M6" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
       <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="R6" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R6" t="str">
+      <c r="S6" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -792,27 +812,30 @@
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L7" t="str">
+      <c r="M7" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
       <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="R7" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R7" t="str">
+      <c r="S7" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -848,27 +871,30 @@
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L8" t="str">
+      <c r="M8" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
       <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O8" t="str">
+      <c r="P8" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P8" t="str">
+      <c r="Q8" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q8" t="str">
+      <c r="R8" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R8" t="str">
+      <c r="S8" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -904,27 +930,30 @@
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L9" t="str">
+      <c r="M9" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M9" t="str">
+      <c r="N9" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N9" t="str">
+      <c r="O9" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O9" t="str">
+      <c r="P9" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P9" t="str">
+      <c r="Q9" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q9" t="str">
+      <c r="R9" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R9" t="str">
+      <c r="S9" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -960,27 +989,30 @@
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L10" t="str">
+      <c r="M10" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
       <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O10" t="str">
+      <c r="P10" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P10" t="str">
+      <c r="Q10" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q10" t="str">
+      <c r="R10" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R10" t="str">
+      <c r="S10" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1016,27 +1048,30 @@
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L11" t="str">
+      <c r="M11" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M11" t="str">
-        <v/>
-      </c>
       <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O11" t="str">
+      <c r="P11" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P11" t="str">
+      <c r="Q11" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q11" t="str">
+      <c r="R11" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R11" t="str">
+      <c r="S11" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1072,27 +1107,30 @@
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L12" t="str">
+      <c r="M12" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M12" t="str">
-        <v/>
-      </c>
       <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O12" t="str">
+      <c r="P12" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P12" t="str">
+      <c r="Q12" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q12" t="str">
+      <c r="R12" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R12" t="str">
+      <c r="S12" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1128,27 +1166,30 @@
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L13" t="str">
+      <c r="M13" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
       <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O13" t="str">
+      <c r="P13" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P13" t="str">
+      <c r="Q13" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q13" t="str">
+      <c r="R13" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R13" t="str">
+      <c r="S13" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1184,27 +1225,30 @@
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L14" t="str">
+      <c r="M14" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M14" t="str">
-        <v/>
-      </c>
       <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O14" t="str">
+      <c r="P14" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P14" t="str">
+      <c r="Q14" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q14" t="str">
+      <c r="R14" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R14" t="str">
+      <c r="S14" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1240,27 +1284,30 @@
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L15" t="str">
+      <c r="M15" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M15" t="str">
-        <v/>
-      </c>
       <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O15" t="str">
+      <c r="P15" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P15" t="str">
+      <c r="Q15" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q15" t="str">
+      <c r="R15" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R15" t="str">
+      <c r="S15" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1296,27 +1343,30 @@
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L16" t="str">
+      <c r="M16" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M16" t="str">
+      <c r="N16" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N16" t="str">
+      <c r="O16" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O16" t="str">
+      <c r="P16" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P16" t="str">
+      <c r="Q16" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q16" t="str">
+      <c r="R16" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R16" t="str">
+      <c r="S16" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1352,27 +1402,30 @@
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L17" t="str">
+      <c r="M17" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M17" t="str">
-        <v/>
-      </c>
       <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O17" t="str">
+      <c r="P17" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P17" t="str">
+      <c r="Q17" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q17" t="str">
+      <c r="R17" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R17" t="str">
+      <c r="S17" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1408,27 +1461,30 @@
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L18" t="str">
+      <c r="M18" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M18" t="str">
-        <v/>
-      </c>
       <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O18" t="str">
+      <c r="P18" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P18" t="str">
+      <c r="Q18" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q18" t="str">
+      <c r="R18" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R18" t="str">
+      <c r="S18" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1464,27 +1520,30 @@
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L19" t="str">
+      <c r="M19" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M19" t="str">
-        <v/>
-      </c>
       <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O19" t="str">
+      <c r="P19" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P19" t="str">
+      <c r="Q19" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q19" t="str">
+      <c r="R19" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R19" t="str">
+      <c r="S19" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1520,27 +1579,30 @@
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L20" t="str">
+      <c r="M20" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M20" t="str">
-        <v/>
-      </c>
       <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O20" t="str">
+      <c r="P20" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P20" t="str">
+      <c r="Q20" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q20" t="str">
+      <c r="R20" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R20" t="str">
+      <c r="S20" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1576,27 +1638,30 @@
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L21" t="str">
+      <c r="M21" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M21" t="str">
-        <v/>
-      </c>
       <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O21" t="str">
+      <c r="P21" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P21" t="str">
+      <c r="Q21" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q21" t="str">
+      <c r="R21" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R21" t="str">
+      <c r="S21" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1632,27 +1697,30 @@
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L22" t="str">
+      <c r="M22" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M22" t="str">
-        <v/>
-      </c>
       <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O22" t="str">
+      <c r="P22" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P22" t="str">
+      <c r="Q22" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q22" t="str">
+      <c r="R22" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R22" t="str">
+      <c r="S22" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1688,27 +1756,30 @@
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L23" t="str">
+      <c r="M23" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M23" t="str">
+      <c r="N23" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N23" t="str">
+      <c r="O23" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O23" t="str">
+      <c r="P23" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P23" t="str">
+      <c r="Q23" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q23" t="str">
+      <c r="R23" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R23" t="str">
+      <c r="S23" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1744,27 +1815,30 @@
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L24" t="str">
+      <c r="M24" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M24" t="str">
-        <v/>
-      </c>
       <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O24" t="str">
+      <c r="P24" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P24" t="str">
+      <c r="Q24" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q24" t="str">
+      <c r="R24" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R24" t="str">
+      <c r="S24" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1800,27 +1874,30 @@
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L25" t="str">
+      <c r="M25" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M25" t="str">
-        <v/>
-      </c>
       <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O25" t="str">
+      <c r="P25" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P25" t="str">
+      <c r="Q25" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q25" t="str">
+      <c r="R25" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R25" t="str">
+      <c r="S25" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -1856,27 +1933,30 @@
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L26" t="str">
+      <c r="M26" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M26" t="str">
-        <v/>
-      </c>
       <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O26" t="str">
+      <c r="P26" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P26" t="str">
+      <c r="Q26" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q26" t="str">
+      <c r="R26" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R26" t="str">
+      <c r="S26" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -1912,27 +1992,30 @@
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L27" t="str">
+      <c r="M27" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M27" t="str">
-        <v/>
-      </c>
       <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O27" t="str">
+      <c r="P27" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P27" t="str">
+      <c r="Q27" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q27" t="str">
+      <c r="R27" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R27" t="str">
+      <c r="S27" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -1968,27 +2051,30 @@
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L28" t="str">
+      <c r="M28" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M28" t="str">
-        <v/>
-      </c>
       <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O28" t="str">
+      <c r="P28" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P28" t="str">
+      <c r="Q28" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q28" t="str">
+      <c r="R28" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R28" t="str">
+      <c r="S28" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2024,27 +2110,30 @@
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L29" t="str">
+      <c r="M29" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M29" t="str">
-        <v/>
-      </c>
       <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O29" t="str">
+      <c r="P29" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P29" t="str">
+      <c r="Q29" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q29" t="str">
+      <c r="R29" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R29" t="str">
+      <c r="S29" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2080,27 +2169,30 @@
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L30" t="str">
+      <c r="M30" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M30" t="str">
+      <c r="N30" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N30" t="str">
+      <c r="O30" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O30" t="str">
+      <c r="P30" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P30" t="str">
+      <c r="Q30" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q30" t="str">
+      <c r="R30" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R30" t="str">
+      <c r="S30" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2136,27 +2228,30 @@
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L31" t="str">
+      <c r="M31" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M31" t="str">
-        <v/>
-      </c>
       <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O31" t="str">
+      <c r="P31" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P31" t="str">
+      <c r="Q31" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q31" t="str">
+      <c r="R31" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R31" t="str">
+      <c r="S31" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2192,27 +2287,30 @@
         <v/>
       </c>
       <c r="K32" t="str">
+        <v/>
+      </c>
+      <c r="L32" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L32" t="str">
+      <c r="M32" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M32" t="str">
-        <v/>
-      </c>
       <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O32" t="str">
+      <c r="P32" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P32" t="str">
+      <c r="Q32" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q32" t="str">
+      <c r="R32" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R32" t="str">
+      <c r="S32" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2248,27 +2346,30 @@
         <v/>
       </c>
       <c r="K33" t="str">
+        <v/>
+      </c>
+      <c r="L33" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L33" t="str">
+      <c r="M33" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M33" t="str">
-        <v/>
-      </c>
       <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O33" t="str">
+      <c r="P33" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P33" t="str">
+      <c r="Q33" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q33" t="str">
+      <c r="R33" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R33" t="str">
+      <c r="S33" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2304,27 +2405,30 @@
         <v/>
       </c>
       <c r="K34" t="str">
+        <v/>
+      </c>
+      <c r="L34" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L34" t="str">
+      <c r="M34" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M34" t="str">
-        <v/>
-      </c>
       <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O34" t="str">
+      <c r="P34" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P34" t="str">
+      <c r="Q34" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q34" t="str">
+      <c r="R34" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R34" t="str">
+      <c r="S34" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2360,27 +2464,30 @@
         <v/>
       </c>
       <c r="K35" t="str">
+        <v/>
+      </c>
+      <c r="L35" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L35" t="str">
+      <c r="M35" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M35" t="str">
-        <v/>
-      </c>
       <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O35" t="str">
+      <c r="P35" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P35" t="str">
+      <c r="Q35" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q35" t="str">
+      <c r="R35" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R35" t="str">
+      <c r="S35" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2416,27 +2523,30 @@
         <v/>
       </c>
       <c r="K36" t="str">
+        <v/>
+      </c>
+      <c r="L36" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L36" t="str">
+      <c r="M36" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M36" t="str">
-        <v/>
-      </c>
       <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O36" t="str">
+      <c r="P36" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P36" t="str">
+      <c r="Q36" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q36" t="str">
+      <c r="R36" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R36" t="str">
+      <c r="S36" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2472,27 +2582,30 @@
         <v/>
       </c>
       <c r="K37" t="str">
+        <v/>
+      </c>
+      <c r="L37" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L37" t="str">
+      <c r="M37" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M37" t="str">
+      <c r="N37" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N37" t="str">
+      <c r="O37" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O37" t="str">
+      <c r="P37" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P37" t="str">
+      <c r="Q37" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q37" t="str">
+      <c r="R37" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R37" t="str">
+      <c r="S37" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2528,27 +2641,30 @@
         <v/>
       </c>
       <c r="K38" t="str">
+        <v/>
+      </c>
+      <c r="L38" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L38" t="str">
+      <c r="M38" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M38" t="str">
-        <v/>
-      </c>
       <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O38" t="str">
+      <c r="P38" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P38" t="str">
+      <c r="Q38" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q38" t="str">
+      <c r="R38" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R38" t="str">
+      <c r="S38" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2584,27 +2700,30 @@
         <v/>
       </c>
       <c r="K39" t="str">
+        <v/>
+      </c>
+      <c r="L39" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L39" t="str">
+      <c r="M39" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M39" t="str">
-        <v/>
-      </c>
       <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O39" t="str">
+      <c r="P39" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P39" t="str">
+      <c r="Q39" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q39" t="str">
+      <c r="R39" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R39" t="str">
+      <c r="S39" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2640,27 +2759,30 @@
         <v/>
       </c>
       <c r="K40" t="str">
+        <v/>
+      </c>
+      <c r="L40" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L40" t="str">
+      <c r="M40" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
       <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O40" t="str">
+      <c r="P40" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P40" t="str">
+      <c r="Q40" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q40" t="str">
+      <c r="R40" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R40" t="str">
+      <c r="S40" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2696,27 +2818,30 @@
         <v/>
       </c>
       <c r="K41" t="str">
+        <v/>
+      </c>
+      <c r="L41" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L41" t="str">
+      <c r="M41" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M41" t="str">
-        <v/>
-      </c>
       <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O41" t="str">
+      <c r="P41" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P41" t="str">
+      <c r="Q41" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q41" t="str">
+      <c r="R41" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R41" t="str">
+      <c r="S41" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2752,27 +2877,30 @@
         <v/>
       </c>
       <c r="K42" t="str">
+        <v/>
+      </c>
+      <c r="L42" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L42" t="str">
+      <c r="M42" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M42" t="str">
-        <v/>
-      </c>
       <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O42" t="str">
+      <c r="P42" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P42" t="str">
+      <c r="Q42" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q42" t="str">
+      <c r="R42" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R42" t="str">
+      <c r="S42" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -2808,27 +2936,30 @@
         <v/>
       </c>
       <c r="K43" t="str">
+        <v/>
+      </c>
+      <c r="L43" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L43" t="str">
+      <c r="M43" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M43" t="str">
-        <v/>
-      </c>
       <c r="N43" t="str">
+        <v/>
+      </c>
+      <c r="O43" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O43" t="str">
+      <c r="P43" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P43" t="str">
+      <c r="Q43" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q43" t="str">
+      <c r="R43" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R43" t="str">
+      <c r="S43" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -2864,27 +2995,30 @@
         <v/>
       </c>
       <c r="K44" t="str">
+        <v/>
+      </c>
+      <c r="L44" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L44" t="str">
+      <c r="M44" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M44" t="str">
+      <c r="N44" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N44" t="str">
+      <c r="O44" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O44" t="str">
+      <c r="P44" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P44" t="str">
+      <c r="Q44" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q44" t="str">
+      <c r="R44" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R44" t="str">
+      <c r="S44" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2920,27 +3054,30 @@
         <v/>
       </c>
       <c r="K45" t="str">
+        <v/>
+      </c>
+      <c r="L45" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L45" t="str">
+      <c r="M45" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M45" t="str">
-        <v/>
-      </c>
       <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O45" t="str">
+      <c r="P45" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P45" t="str">
+      <c r="Q45" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q45" t="str">
+      <c r="R45" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R45" t="str">
+      <c r="S45" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -2976,27 +3113,30 @@
         <v/>
       </c>
       <c r="K46" t="str">
+        <v/>
+      </c>
+      <c r="L46" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L46" t="str">
+      <c r="M46" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M46" t="str">
-        <v/>
-      </c>
       <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O46" t="str">
+      <c r="P46" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P46" t="str">
+      <c r="Q46" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q46" t="str">
+      <c r="R46" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R46" t="str">
+      <c r="S46" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3032,27 +3172,30 @@
         <v/>
       </c>
       <c r="K47" t="str">
+        <v/>
+      </c>
+      <c r="L47" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L47" t="str">
+      <c r="M47" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M47" t="str">
-        <v/>
-      </c>
       <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O47" t="str">
+      <c r="P47" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P47" t="str">
+      <c r="Q47" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q47" t="str">
+      <c r="R47" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R47" t="str">
+      <c r="S47" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3088,27 +3231,30 @@
         <v/>
       </c>
       <c r="K48" t="str">
+        <v/>
+      </c>
+      <c r="L48" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L48" t="str">
+      <c r="M48" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M48" t="str">
-        <v/>
-      </c>
       <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O48" t="str">
+      <c r="P48" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P48" t="str">
+      <c r="Q48" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q48" t="str">
+      <c r="R48" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R48" t="str">
+      <c r="S48" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3144,27 +3290,30 @@
         <v/>
       </c>
       <c r="K49" t="str">
+        <v/>
+      </c>
+      <c r="L49" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L49" t="str">
+      <c r="M49" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M49" t="str">
-        <v/>
-      </c>
       <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O49" t="str">
+      <c r="P49" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P49" t="str">
+      <c r="Q49" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q49" t="str">
+      <c r="R49" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R49" t="str">
+      <c r="S49" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3200,27 +3349,30 @@
         <v/>
       </c>
       <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L50" t="str">
+      <c r="M50" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
       <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O50" t="str">
+      <c r="P50" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P50" t="str">
+      <c r="Q50" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q50" t="str">
+      <c r="R50" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R50" t="str">
+      <c r="S50" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3256,27 +3408,30 @@
         <v/>
       </c>
       <c r="K51" t="str">
+        <v/>
+      </c>
+      <c r="L51" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L51" t="str">
+      <c r="M51" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M51" t="str">
+      <c r="N51" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N51" t="str">
+      <c r="O51" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O51" t="str">
+      <c r="P51" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P51" t="str">
+      <c r="Q51" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q51" t="str">
+      <c r="R51" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R51" t="str">
+      <c r="S51" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3312,27 +3467,30 @@
         <v/>
       </c>
       <c r="K52" t="str">
+        <v/>
+      </c>
+      <c r="L52" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L52" t="str">
+      <c r="M52" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M52" t="str">
-        <v/>
-      </c>
       <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O52" t="str">
+      <c r="P52" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P52" t="str">
+      <c r="Q52" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q52" t="str">
+      <c r="R52" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R52" t="str">
+      <c r="S52" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3368,27 +3526,30 @@
         <v/>
       </c>
       <c r="K53" t="str">
+        <v/>
+      </c>
+      <c r="L53" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L53" t="str">
+      <c r="M53" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M53" t="str">
-        <v/>
-      </c>
       <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O53" t="str">
+      <c r="P53" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P53" t="str">
+      <c r="Q53" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q53" t="str">
+      <c r="R53" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R53" t="str">
+      <c r="S53" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3424,27 +3585,30 @@
         <v/>
       </c>
       <c r="K54" t="str">
+        <v/>
+      </c>
+      <c r="L54" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L54" t="str">
+      <c r="M54" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M54" t="str">
-        <v/>
-      </c>
       <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O54" t="str">
+      <c r="P54" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P54" t="str">
+      <c r="Q54" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q54" t="str">
+      <c r="R54" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R54" t="str">
+      <c r="S54" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3480,27 +3644,30 @@
         <v/>
       </c>
       <c r="K55" t="str">
+        <v/>
+      </c>
+      <c r="L55" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L55" t="str">
+      <c r="M55" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M55" t="str">
-        <v/>
-      </c>
       <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O55" t="str">
+      <c r="P55" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P55" t="str">
+      <c r="Q55" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q55" t="str">
+      <c r="R55" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R55" t="str">
+      <c r="S55" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3536,27 +3703,30 @@
         <v/>
       </c>
       <c r="K56" t="str">
+        <v/>
+      </c>
+      <c r="L56" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L56" t="str">
+      <c r="M56" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M56" t="str">
-        <v/>
-      </c>
       <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O56" t="str">
+      <c r="P56" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P56" t="str">
+      <c r="Q56" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q56" t="str">
+      <c r="R56" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R56" t="str">
+      <c r="S56" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3592,27 +3762,30 @@
         <v/>
       </c>
       <c r="K57" t="str">
+        <v/>
+      </c>
+      <c r="L57" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L57" t="str">
+      <c r="M57" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M57" t="str">
-        <v/>
-      </c>
       <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O57" t="str">
+      <c r="P57" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P57" t="str">
+      <c r="Q57" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q57" t="str">
+      <c r="R57" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R57" t="str">
+      <c r="S57" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3648,27 +3821,30 @@
         <v/>
       </c>
       <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L58" t="str">
+      <c r="M58" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M58" t="str">
+      <c r="N58" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N58" t="str">
+      <c r="O58" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O58" t="str">
+      <c r="P58" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P58" t="str">
+      <c r="Q58" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q58" t="str">
+      <c r="R58" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R58" t="str">
+      <c r="S58" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3704,27 +3880,30 @@
         <v/>
       </c>
       <c r="K59" t="str">
+        <v/>
+      </c>
+      <c r="L59" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L59" t="str">
+      <c r="M59" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M59" t="str">
-        <v/>
-      </c>
       <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O59" t="str">
+      <c r="P59" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P59" t="str">
+      <c r="Q59" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q59" t="str">
+      <c r="R59" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R59" t="str">
+      <c r="S59" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3760,27 +3939,30 @@
         <v/>
       </c>
       <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L60" t="str">
+      <c r="M60" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M60" t="str">
-        <v/>
-      </c>
       <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O60" t="str">
+      <c r="P60" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P60" t="str">
+      <c r="Q60" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q60" t="str">
+      <c r="R60" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R60" t="str">
+      <c r="S60" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3816,27 +3998,30 @@
         <v/>
       </c>
       <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L61" t="str">
+      <c r="M61" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M61" t="str">
-        <v/>
-      </c>
       <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O61" t="str">
+      <c r="P61" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P61" t="str">
+      <c r="Q61" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q61" t="str">
+      <c r="R61" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R61" t="str">
+      <c r="S61" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -3872,27 +4057,30 @@
         <v/>
       </c>
       <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L62" t="str">
+      <c r="M62" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M62" t="str">
-        <v/>
-      </c>
       <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O62" t="str">
+      <c r="P62" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P62" t="str">
+      <c r="Q62" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q62" t="str">
+      <c r="R62" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R62" t="str">
+      <c r="S62" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -3928,27 +4116,30 @@
         <v/>
       </c>
       <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L63" t="str">
+      <c r="M63" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M63" t="str">
-        <v/>
-      </c>
       <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O63" t="str">
+      <c r="P63" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P63" t="str">
+      <c r="Q63" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q63" t="str">
+      <c r="R63" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R63" t="str">
+      <c r="S63" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -3984,27 +4175,30 @@
         <v/>
       </c>
       <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L64" t="str">
+      <c r="M64" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M64" t="str">
-        <v/>
-      </c>
       <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O64" t="str">
+      <c r="P64" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P64" t="str">
+      <c r="Q64" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q64" t="str">
+      <c r="R64" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R64" t="str">
+      <c r="S64" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4040,27 +4234,30 @@
         <v/>
       </c>
       <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L65" t="str">
+      <c r="M65" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M65" t="str">
+      <c r="N65" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N65" t="str">
+      <c r="O65" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O65" t="str">
+      <c r="P65" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P65" t="str">
+      <c r="Q65" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q65" t="str">
+      <c r="R65" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R65" t="str">
+      <c r="S65" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4096,27 +4293,30 @@
         <v/>
       </c>
       <c r="K66" t="str">
+        <v/>
+      </c>
+      <c r="L66" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L66" t="str">
+      <c r="M66" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M66" t="str">
-        <v/>
-      </c>
       <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O66" t="str">
+      <c r="P66" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P66" t="str">
+      <c r="Q66" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q66" t="str">
+      <c r="R66" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R66" t="str">
+      <c r="S66" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4152,27 +4352,30 @@
         <v/>
       </c>
       <c r="K67" t="str">
+        <v/>
+      </c>
+      <c r="L67" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L67" t="str">
+      <c r="M67" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M67" t="str">
-        <v/>
-      </c>
       <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O67" t="str">
+      <c r="P67" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P67" t="str">
+      <c r="Q67" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q67" t="str">
+      <c r="R67" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R67" t="str">
+      <c r="S67" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4208,27 +4411,30 @@
         <v/>
       </c>
       <c r="K68" t="str">
+        <v/>
+      </c>
+      <c r="L68" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L68" t="str">
+      <c r="M68" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M68" t="str">
-        <v/>
-      </c>
       <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O68" t="str">
+      <c r="P68" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P68" t="str">
+      <c r="Q68" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q68" t="str">
+      <c r="R68" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R68" t="str">
+      <c r="S68" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4264,27 +4470,30 @@
         <v/>
       </c>
       <c r="K69" t="str">
+        <v/>
+      </c>
+      <c r="L69" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L69" t="str">
+      <c r="M69" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M69" t="str">
-        <v/>
-      </c>
       <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O69" t="str">
+      <c r="P69" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P69" t="str">
+      <c r="Q69" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q69" t="str">
+      <c r="R69" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R69" t="str">
+      <c r="S69" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4320,27 +4529,30 @@
         <v/>
       </c>
       <c r="K70" t="str">
+        <v/>
+      </c>
+      <c r="L70" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L70" t="str">
+      <c r="M70" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M70" t="str">
-        <v/>
-      </c>
       <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O70" t="str">
+      <c r="P70" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P70" t="str">
+      <c r="Q70" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q70" t="str">
+      <c r="R70" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R70" t="str">
+      <c r="S70" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4376,27 +4588,30 @@
         <v/>
       </c>
       <c r="K71" t="str">
+        <v/>
+      </c>
+      <c r="L71" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L71" t="str">
+      <c r="M71" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M71" t="str">
-        <v/>
-      </c>
       <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O71" t="str">
+      <c r="P71" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P71" t="str">
+      <c r="Q71" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q71" t="str">
+      <c r="R71" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R71" t="str">
+      <c r="S71" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4432,27 +4647,30 @@
         <v/>
       </c>
       <c r="K72" t="str">
+        <v/>
+      </c>
+      <c r="L72" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L72" t="str">
+      <c r="M72" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M72" t="str">
+      <c r="N72" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N72" t="str">
+      <c r="O72" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O72" t="str">
+      <c r="P72" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P72" t="str">
+      <c r="Q72" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q72" t="str">
+      <c r="R72" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R72" t="str">
+      <c r="S72" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4488,27 +4706,30 @@
         <v/>
       </c>
       <c r="K73" t="str">
+        <v/>
+      </c>
+      <c r="L73" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L73" t="str">
+      <c r="M73" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M73" t="str">
-        <v/>
-      </c>
       <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O73" t="str">
+      <c r="P73" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P73" t="str">
+      <c r="Q73" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q73" t="str">
+      <c r="R73" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R73" t="str">
+      <c r="S73" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4544,27 +4765,30 @@
         <v/>
       </c>
       <c r="K74" t="str">
+        <v/>
+      </c>
+      <c r="L74" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L74" t="str">
+      <c r="M74" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M74" t="str">
-        <v/>
-      </c>
       <c r="N74" t="str">
+        <v/>
+      </c>
+      <c r="O74" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O74" t="str">
+      <c r="P74" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P74" t="str">
+      <c r="Q74" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q74" t="str">
+      <c r="R74" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R74" t="str">
+      <c r="S74" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4600,27 +4824,30 @@
         <v/>
       </c>
       <c r="K75" t="str">
+        <v/>
+      </c>
+      <c r="L75" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L75" t="str">
+      <c r="M75" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M75" t="str">
-        <v/>
-      </c>
       <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O75" t="str">
+      <c r="P75" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P75" t="str">
+      <c r="Q75" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q75" t="str">
+      <c r="R75" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R75" t="str">
+      <c r="S75" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4656,27 +4883,30 @@
         <v/>
       </c>
       <c r="K76" t="str">
+        <v/>
+      </c>
+      <c r="L76" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L76" t="str">
+      <c r="M76" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M76" t="str">
-        <v/>
-      </c>
       <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O76" t="str">
+      <c r="P76" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P76" t="str">
+      <c r="Q76" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q76" t="str">
+      <c r="R76" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R76" t="str">
+      <c r="S76" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4712,27 +4942,30 @@
         <v/>
       </c>
       <c r="K77" t="str">
+        <v/>
+      </c>
+      <c r="L77" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L77" t="str">
+      <c r="M77" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M77" t="str">
-        <v/>
-      </c>
       <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O77" t="str">
+      <c r="P77" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P77" t="str">
+      <c r="Q77" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q77" t="str">
+      <c r="R77" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R77" t="str">
+      <c r="S77" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4768,27 +5001,30 @@
         <v/>
       </c>
       <c r="K78" t="str">
+        <v/>
+      </c>
+      <c r="L78" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L78" t="str">
+      <c r="M78" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M78" t="str">
-        <v/>
-      </c>
       <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O78" t="str">
+      <c r="P78" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P78" t="str">
+      <c r="Q78" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q78" t="str">
+      <c r="R78" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R78" t="str">
+      <c r="S78" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -4824,27 +5060,30 @@
         <v/>
       </c>
       <c r="K79" t="str">
+        <v/>
+      </c>
+      <c r="L79" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L79" t="str">
+      <c r="M79" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M79" t="str">
+      <c r="N79" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N79" t="str">
+      <c r="O79" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O79" t="str">
+      <c r="P79" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P79" t="str">
+      <c r="Q79" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q79" t="str">
+      <c r="R79" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R79" t="str">
+      <c r="S79" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -4880,27 +5119,30 @@
         <v/>
       </c>
       <c r="K80" t="str">
+        <v/>
+      </c>
+      <c r="L80" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L80" t="str">
+      <c r="M80" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M80" t="str">
-        <v/>
-      </c>
       <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O80" t="str">
+      <c r="P80" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P80" t="str">
+      <c r="Q80" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q80" t="str">
+      <c r="R80" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R80" t="str">
+      <c r="S80" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4936,27 +5178,30 @@
         <v/>
       </c>
       <c r="K81" t="str">
+        <v/>
+      </c>
+      <c r="L81" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L81" t="str">
+      <c r="M81" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M81" t="str">
-        <v/>
-      </c>
       <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O81" t="str">
+      <c r="P81" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P81" t="str">
+      <c r="Q81" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q81" t="str">
+      <c r="R81" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R81" t="str">
+      <c r="S81" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -4992,27 +5237,30 @@
         <v/>
       </c>
       <c r="K82" t="str">
+        <v/>
+      </c>
+      <c r="L82" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L82" t="str">
+      <c r="M82" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M82" t="str">
-        <v/>
-      </c>
       <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O82" t="str">
+      <c r="P82" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P82" t="str">
+      <c r="Q82" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q82" t="str">
+      <c r="R82" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R82" t="str">
+      <c r="S82" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5048,27 +5296,30 @@
         <v/>
       </c>
       <c r="K83" t="str">
+        <v/>
+      </c>
+      <c r="L83" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L83" t="str">
+      <c r="M83" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M83" t="str">
-        <v/>
-      </c>
       <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O83" t="str">
+      <c r="P83" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P83" t="str">
+      <c r="Q83" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q83" t="str">
+      <c r="R83" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R83" t="str">
+      <c r="S83" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5104,27 +5355,30 @@
         <v/>
       </c>
       <c r="K84" t="str">
+        <v/>
+      </c>
+      <c r="L84" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L84" t="str">
+      <c r="M84" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M84" t="str">
-        <v/>
-      </c>
       <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O84" t="str">
+      <c r="P84" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P84" t="str">
+      <c r="Q84" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q84" t="str">
+      <c r="R84" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R84" t="str">
+      <c r="S84" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5160,27 +5414,30 @@
         <v/>
       </c>
       <c r="K85" t="str">
+        <v/>
+      </c>
+      <c r="L85" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L85" t="str">
+      <c r="M85" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M85" t="str">
-        <v/>
-      </c>
       <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O85" t="str">
+      <c r="P85" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P85" t="str">
+      <c r="Q85" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q85" t="str">
+      <c r="R85" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R85" t="str">
+      <c r="S85" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5216,27 +5473,30 @@
         <v/>
       </c>
       <c r="K86" t="str">
+        <v/>
+      </c>
+      <c r="L86" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L86" t="str">
+      <c r="M86" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M86" t="str">
+      <c r="N86" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N86" t="str">
+      <c r="O86" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O86" t="str">
+      <c r="P86" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P86" t="str">
+      <c r="Q86" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q86" t="str">
+      <c r="R86" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R86" t="str">
+      <c r="S86" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5272,27 +5532,30 @@
         <v/>
       </c>
       <c r="K87" t="str">
+        <v/>
+      </c>
+      <c r="L87" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L87" t="str">
+      <c r="M87" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M87" t="str">
-        <v/>
-      </c>
       <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O87" t="str">
+      <c r="P87" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P87" t="str">
+      <c r="Q87" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q87" t="str">
+      <c r="R87" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R87" t="str">
+      <c r="S87" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5328,27 +5591,30 @@
         <v/>
       </c>
       <c r="K88" t="str">
+        <v/>
+      </c>
+      <c r="L88" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L88" t="str">
+      <c r="M88" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M88" t="str">
-        <v/>
-      </c>
       <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O88" t="str">
+      <c r="P88" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P88" t="str">
+      <c r="Q88" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q88" t="str">
+      <c r="R88" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R88" t="str">
+      <c r="S88" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5384,27 +5650,30 @@
         <v/>
       </c>
       <c r="K89" t="str">
+        <v/>
+      </c>
+      <c r="L89" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L89" t="str">
+      <c r="M89" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M89" t="str">
-        <v/>
-      </c>
       <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O89" t="str">
+      <c r="P89" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P89" t="str">
+      <c r="Q89" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q89" t="str">
+      <c r="R89" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R89" t="str">
+      <c r="S89" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5440,27 +5709,30 @@
         <v/>
       </c>
       <c r="K90" t="str">
+        <v/>
+      </c>
+      <c r="L90" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L90" t="str">
+      <c r="M90" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M90" t="str">
-        <v/>
-      </c>
       <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O90" t="str">
+      <c r="P90" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P90" t="str">
+      <c r="Q90" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q90" t="str">
+      <c r="R90" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R90" t="str">
+      <c r="S90" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5496,27 +5768,30 @@
         <v/>
       </c>
       <c r="K91" t="str">
+        <v/>
+      </c>
+      <c r="L91" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L91" t="str">
+      <c r="M91" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M91" t="str">
-        <v/>
-      </c>
       <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O91" t="str">
+      <c r="P91" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P91" t="str">
+      <c r="Q91" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q91" t="str">
+      <c r="R91" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R91" t="str">
+      <c r="S91" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5552,27 +5827,30 @@
         <v/>
       </c>
       <c r="K92" t="str">
+        <v/>
+      </c>
+      <c r="L92" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L92" t="str">
+      <c r="M92" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M92" t="str">
-        <v/>
-      </c>
       <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O92" t="str">
+      <c r="P92" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P92" t="str">
+      <c r="Q92" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q92" t="str">
+      <c r="R92" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R92" t="str">
+      <c r="S92" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5608,27 +5886,30 @@
         <v/>
       </c>
       <c r="K93" t="str">
+        <v/>
+      </c>
+      <c r="L93" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L93" t="str">
+      <c r="M93" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M93" t="str">
+      <c r="N93" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N93" t="str">
+      <c r="O93" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O93" t="str">
+      <c r="P93" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P93" t="str">
+      <c r="Q93" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q93" t="str">
+      <c r="R93" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R93" t="str">
+      <c r="S93" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5664,27 +5945,30 @@
         <v/>
       </c>
       <c r="K94" t="str">
+        <v/>
+      </c>
+      <c r="L94" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L94" t="str">
+      <c r="M94" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M94" t="str">
-        <v/>
-      </c>
       <c r="N94" t="str">
+        <v/>
+      </c>
+      <c r="O94" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O94" t="str">
+      <c r="P94" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P94" t="str">
+      <c r="Q94" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q94" t="str">
+      <c r="R94" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R94" t="str">
+      <c r="S94" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5720,27 +6004,30 @@
         <v/>
       </c>
       <c r="K95" t="str">
+        <v/>
+      </c>
+      <c r="L95" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L95" t="str">
+      <c r="M95" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M95" t="str">
-        <v/>
-      </c>
       <c r="N95" t="str">
+        <v/>
+      </c>
+      <c r="O95" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O95" t="str">
+      <c r="P95" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P95" t="str">
+      <c r="Q95" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q95" t="str">
+      <c r="R95" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R95" t="str">
+      <c r="S95" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -5776,27 +6063,30 @@
         <v/>
       </c>
       <c r="K96" t="str">
+        <v/>
+      </c>
+      <c r="L96" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L96" t="str">
+      <c r="M96" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M96" t="str">
-        <v/>
-      </c>
       <c r="N96" t="str">
+        <v/>
+      </c>
+      <c r="O96" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O96" t="str">
+      <c r="P96" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P96" t="str">
+      <c r="Q96" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q96" t="str">
+      <c r="R96" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R96" t="str">
+      <c r="S96" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5832,27 +6122,30 @@
         <v/>
       </c>
       <c r="K97" t="str">
+        <v/>
+      </c>
+      <c r="L97" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L97" t="str">
+      <c r="M97" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M97" t="str">
-        <v/>
-      </c>
       <c r="N97" t="str">
+        <v/>
+      </c>
+      <c r="O97" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O97" t="str">
+      <c r="P97" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P97" t="str">
+      <c r="Q97" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q97" t="str">
+      <c r="R97" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R97" t="str">
+      <c r="S97" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -5888,27 +6181,30 @@
         <v/>
       </c>
       <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L98" t="str">
+      <c r="M98" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M98" t="str">
-        <v/>
-      </c>
       <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O98" t="str">
+      <c r="P98" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P98" t="str">
+      <c r="Q98" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q98" t="str">
+      <c r="R98" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R98" t="str">
+      <c r="S98" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -5944,27 +6240,30 @@
         <v/>
       </c>
       <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L99" t="str">
+      <c r="M99" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M99" t="str">
-        <v/>
-      </c>
       <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O99" t="str">
+      <c r="P99" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P99" t="str">
+      <c r="Q99" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q99" t="str">
+      <c r="R99" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R99" t="str">
+      <c r="S99" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6000,27 +6299,30 @@
         <v/>
       </c>
       <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L100" t="str">
+      <c r="M100" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M100" t="str">
+      <c r="N100" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N100" t="str">
+      <c r="O100" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O100" t="str">
+      <c r="P100" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P100" t="str">
+      <c r="Q100" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q100" t="str">
+      <c r="R100" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R100" t="str">
+      <c r="S100" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6056,27 +6358,30 @@
         <v/>
       </c>
       <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L101" t="str">
+      <c r="M101" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M101" t="str">
-        <v/>
-      </c>
       <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O101" t="str">
+      <c r="P101" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P101" t="str">
+      <c r="Q101" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q101" t="str">
+      <c r="R101" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R101" t="str">
+      <c r="S101" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6112,27 +6417,30 @@
         <v/>
       </c>
       <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L102" t="str">
+      <c r="M102" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M102" t="str">
-        <v/>
-      </c>
       <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O102" t="str">
+      <c r="P102" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P102" t="str">
+      <c r="Q102" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q102" t="str">
+      <c r="R102" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R102" t="str">
+      <c r="S102" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6168,27 +6476,30 @@
         <v/>
       </c>
       <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L103" t="str">
+      <c r="M103" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M103" t="str">
-        <v/>
-      </c>
       <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O103" t="str">
+      <c r="P103" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P103" t="str">
+      <c r="Q103" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q103" t="str">
+      <c r="R103" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R103" t="str">
+      <c r="S103" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6224,27 +6535,30 @@
         <v/>
       </c>
       <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L104" t="str">
+      <c r="M104" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M104" t="str">
-        <v/>
-      </c>
       <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O104" t="str">
+      <c r="P104" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P104" t="str">
+      <c r="Q104" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q104" t="str">
+      <c r="R104" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R104" t="str">
+      <c r="S104" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6280,27 +6594,30 @@
         <v/>
       </c>
       <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L105" t="str">
+      <c r="M105" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M105" t="str">
-        <v/>
-      </c>
       <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O105" t="str">
+      <c r="P105" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P105" t="str">
+      <c r="Q105" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q105" t="str">
+      <c r="R105" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R105" t="str">
+      <c r="S105" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6336,27 +6653,30 @@
         <v/>
       </c>
       <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L106" t="str">
+      <c r="M106" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M106" t="str">
-        <v/>
-      </c>
       <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O106" t="str">
+      <c r="P106" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P106" t="str">
+      <c r="Q106" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q106" t="str">
+      <c r="R106" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R106" t="str">
+      <c r="S106" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6392,27 +6712,30 @@
         <v/>
       </c>
       <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L107" t="str">
+      <c r="M107" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M107" t="str">
+      <c r="N107" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N107" t="str">
+      <c r="O107" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O107" t="str">
+      <c r="P107" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P107" t="str">
+      <c r="Q107" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q107" t="str">
+      <c r="R107" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R107" t="str">
+      <c r="S107" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6448,27 +6771,30 @@
         <v/>
       </c>
       <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L108" t="str">
+      <c r="M108" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M108" t="str">
-        <v/>
-      </c>
       <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O108" t="str">
+      <c r="P108" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P108" t="str">
+      <c r="Q108" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q108" t="str">
+      <c r="R108" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R108" t="str">
+      <c r="S108" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6504,27 +6830,30 @@
         <v/>
       </c>
       <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L109" t="str">
+      <c r="M109" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M109" t="str">
-        <v/>
-      </c>
       <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O109" t="str">
+      <c r="P109" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P109" t="str">
+      <c r="Q109" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q109" t="str">
+      <c r="R109" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R109" t="str">
+      <c r="S109" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6560,27 +6889,30 @@
         <v/>
       </c>
       <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L110" t="str">
+      <c r="M110" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M110" t="str">
-        <v/>
-      </c>
       <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O110" t="str">
+      <c r="P110" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P110" t="str">
+      <c r="Q110" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q110" t="str">
+      <c r="R110" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R110" t="str">
+      <c r="S110" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6616,27 +6948,30 @@
         <v/>
       </c>
       <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L111" t="str">
+      <c r="M111" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M111" t="str">
-        <v/>
-      </c>
       <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O111" t="str">
+      <c r="P111" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P111" t="str">
+      <c r="Q111" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q111" t="str">
+      <c r="R111" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R111" t="str">
+      <c r="S111" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6672,27 +7007,30 @@
         <v/>
       </c>
       <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L112" t="str">
+      <c r="M112" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M112" t="str">
-        <v/>
-      </c>
       <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O112" t="str">
+      <c r="P112" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P112" t="str">
+      <c r="Q112" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q112" t="str">
+      <c r="R112" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R112" t="str">
+      <c r="S112" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6728,27 +7066,30 @@
         <v/>
       </c>
       <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L113" t="str">
+      <c r="M113" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M113" t="str">
-        <v/>
-      </c>
       <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O113" t="str">
+      <c r="P113" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P113" t="str">
+      <c r="Q113" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q113" t="str">
+      <c r="R113" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R113" t="str">
+      <c r="S113" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6784,27 +7125,30 @@
         <v/>
       </c>
       <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L114" t="str">
+      <c r="M114" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M114" t="str">
+      <c r="N114" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N114" t="str">
+      <c r="O114" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O114" t="str">
+      <c r="P114" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P114" t="str">
+      <c r="Q114" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q114" t="str">
+      <c r="R114" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R114" t="str">
+      <c r="S114" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -6840,27 +7184,30 @@
         <v/>
       </c>
       <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L115" t="str">
+      <c r="M115" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M115" t="str">
-        <v/>
-      </c>
       <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O115" t="str">
+      <c r="P115" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P115" t="str">
+      <c r="Q115" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q115" t="str">
+      <c r="R115" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R115" t="str">
+      <c r="S115" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -6896,27 +7243,30 @@
         <v/>
       </c>
       <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L116" t="str">
+      <c r="M116" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M116" t="str">
-        <v/>
-      </c>
       <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O116" t="str">
+      <c r="P116" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P116" t="str">
+      <c r="Q116" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q116" t="str">
+      <c r="R116" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R116" t="str">
+      <c r="S116" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -6952,27 +7302,30 @@
         <v/>
       </c>
       <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L117" t="str">
+      <c r="M117" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M117" t="str">
-        <v/>
-      </c>
       <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O117" t="str">
+      <c r="P117" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P117" t="str">
+      <c r="Q117" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q117" t="str">
+      <c r="R117" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R117" t="str">
+      <c r="S117" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7008,27 +7361,30 @@
         <v/>
       </c>
       <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L118" t="str">
+      <c r="M118" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M118" t="str">
-        <v/>
-      </c>
       <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O118" t="str">
+      <c r="P118" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P118" t="str">
+      <c r="Q118" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q118" t="str">
+      <c r="R118" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R118" t="str">
+      <c r="S118" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7064,27 +7420,30 @@
         <v/>
       </c>
       <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L119" t="str">
+      <c r="M119" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M119" t="str">
-        <v/>
-      </c>
       <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O119" t="str">
+      <c r="P119" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P119" t="str">
+      <c r="Q119" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q119" t="str">
+      <c r="R119" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R119" t="str">
+      <c r="S119" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7120,27 +7479,30 @@
         <v/>
       </c>
       <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L120" t="str">
+      <c r="M120" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M120" t="str">
-        <v/>
-      </c>
       <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O120" t="str">
+      <c r="P120" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P120" t="str">
+      <c r="Q120" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q120" t="str">
+      <c r="R120" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R120" t="str">
+      <c r="S120" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7176,27 +7538,30 @@
         <v/>
       </c>
       <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L121" t="str">
+      <c r="M121" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M121" t="str">
+      <c r="N121" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N121" t="str">
+      <c r="O121" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O121" t="str">
+      <c r="P121" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P121" t="str">
+      <c r="Q121" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q121" t="str">
+      <c r="R121" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R121" t="str">
+      <c r="S121" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7232,27 +7597,30 @@
         <v/>
       </c>
       <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L122" t="str">
+      <c r="M122" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M122" t="str">
-        <v/>
-      </c>
       <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O122" t="str">
+      <c r="P122" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P122" t="str">
+      <c r="Q122" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q122" t="str">
+      <c r="R122" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R122" t="str">
+      <c r="S122" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7288,27 +7656,30 @@
         <v/>
       </c>
       <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L123" t="str">
+      <c r="M123" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M123" t="str">
-        <v/>
-      </c>
       <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O123" t="str">
+      <c r="P123" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P123" t="str">
+      <c r="Q123" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q123" t="str">
+      <c r="R123" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R123" t="str">
+      <c r="S123" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7344,27 +7715,30 @@
         <v/>
       </c>
       <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L124" t="str">
+      <c r="M124" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M124" t="str">
-        <v/>
-      </c>
       <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O124" t="str">
+      <c r="P124" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P124" t="str">
+      <c r="Q124" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q124" t="str">
+      <c r="R124" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R124" t="str">
+      <c r="S124" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7400,27 +7774,30 @@
         <v/>
       </c>
       <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L125" t="str">
+      <c r="M125" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M125" t="str">
-        <v/>
-      </c>
       <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O125" t="str">
+      <c r="P125" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P125" t="str">
+      <c r="Q125" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q125" t="str">
+      <c r="R125" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R125" t="str">
+      <c r="S125" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7456,27 +7833,30 @@
         <v/>
       </c>
       <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L126" t="str">
+      <c r="M126" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M126" t="str">
-        <v/>
-      </c>
       <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O126" t="str">
+      <c r="P126" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P126" t="str">
+      <c r="Q126" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q126" t="str">
+      <c r="R126" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R126" t="str">
+      <c r="S126" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7512,27 +7892,30 @@
         <v/>
       </c>
       <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L127" t="str">
+      <c r="M127" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M127" t="str">
-        <v/>
-      </c>
       <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O127" t="str">
+      <c r="P127" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P127" t="str">
+      <c r="Q127" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q127" t="str">
+      <c r="R127" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R127" t="str">
+      <c r="S127" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7568,27 +7951,30 @@
         <v/>
       </c>
       <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L128" t="str">
+      <c r="M128" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M128" t="str">
+      <c r="N128" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N128" t="str">
+      <c r="O128" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O128" t="str">
+      <c r="P128" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P128" t="str">
+      <c r="Q128" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q128" t="str">
+      <c r="R128" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R128" t="str">
+      <c r="S128" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7624,27 +8010,30 @@
         <v/>
       </c>
       <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L129" t="str">
+      <c r="M129" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M129" t="str">
-        <v/>
-      </c>
       <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O129" t="str">
+      <c r="P129" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P129" t="str">
+      <c r="Q129" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q129" t="str">
+      <c r="R129" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R129" t="str">
+      <c r="S129" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7680,27 +8069,30 @@
         <v/>
       </c>
       <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L130" t="str">
+      <c r="M130" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M130" t="str">
-        <v/>
-      </c>
       <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O130" t="str">
+      <c r="P130" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P130" t="str">
+      <c r="Q130" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q130" t="str">
+      <c r="R130" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R130" t="str">
+      <c r="S130" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7736,27 +8128,30 @@
         <v/>
       </c>
       <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L131" t="str">
+      <c r="M131" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M131" t="str">
-        <v/>
-      </c>
       <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O131" t="str">
+      <c r="P131" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P131" t="str">
+      <c r="Q131" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q131" t="str">
+      <c r="R131" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R131" t="str">
+      <c r="S131" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -7792,27 +8187,30 @@
         <v/>
       </c>
       <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L132" t="str">
+      <c r="M132" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M132" t="str">
-        <v/>
-      </c>
       <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O132" t="str">
+      <c r="P132" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P132" t="str">
+      <c r="Q132" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q132" t="str">
+      <c r="R132" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R132" t="str">
+      <c r="S132" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7848,27 +8246,30 @@
         <v/>
       </c>
       <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L133" t="str">
+      <c r="M133" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M133" t="str">
-        <v/>
-      </c>
       <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O133" t="str">
+      <c r="P133" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P133" t="str">
+      <c r="Q133" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q133" t="str">
+      <c r="R133" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R133" t="str">
+      <c r="S133" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -7904,27 +8305,30 @@
         <v/>
       </c>
       <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L134" t="str">
+      <c r="M134" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M134" t="str">
-        <v/>
-      </c>
       <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O134" t="str">
+      <c r="P134" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P134" t="str">
+      <c r="Q134" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q134" t="str">
+      <c r="R134" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R134" t="str">
+      <c r="S134" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -7960,27 +8364,30 @@
         <v/>
       </c>
       <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L135" t="str">
+      <c r="M135" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M135" t="str">
+      <c r="N135" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N135" t="str">
+      <c r="O135" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O135" t="str">
+      <c r="P135" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P135" t="str">
+      <c r="Q135" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q135" t="str">
+      <c r="R135" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R135" t="str">
+      <c r="S135" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8016,27 +8423,30 @@
         <v/>
       </c>
       <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L136" t="str">
+      <c r="M136" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M136" t="str">
-        <v/>
-      </c>
       <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O136" t="str">
+      <c r="P136" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P136" t="str">
+      <c r="Q136" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q136" t="str">
+      <c r="R136" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R136" t="str">
+      <c r="S136" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8072,27 +8482,30 @@
         <v/>
       </c>
       <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L137" t="str">
+      <c r="M137" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M137" t="str">
-        <v/>
-      </c>
       <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O137" t="str">
+      <c r="P137" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P137" t="str">
+      <c r="Q137" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q137" t="str">
+      <c r="R137" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R137" t="str">
+      <c r="S137" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8128,27 +8541,30 @@
         <v/>
       </c>
       <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L138" t="str">
+      <c r="M138" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M138" t="str">
-        <v/>
-      </c>
       <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O138" t="str">
+      <c r="P138" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P138" t="str">
+      <c r="Q138" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q138" t="str">
+      <c r="R138" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R138" t="str">
+      <c r="S138" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8184,27 +8600,30 @@
         <v/>
       </c>
       <c r="K139" t="str">
+        <v/>
+      </c>
+      <c r="L139" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L139" t="str">
+      <c r="M139" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M139" t="str">
-        <v/>
-      </c>
       <c r="N139" t="str">
+        <v/>
+      </c>
+      <c r="O139" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O139" t="str">
+      <c r="P139" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P139" t="str">
+      <c r="Q139" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q139" t="str">
+      <c r="R139" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R139" t="str">
+      <c r="S139" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8240,27 +8659,30 @@
         <v/>
       </c>
       <c r="K140" t="str">
+        <v/>
+      </c>
+      <c r="L140" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L140" t="str">
+      <c r="M140" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M140" t="str">
-        <v/>
-      </c>
       <c r="N140" t="str">
+        <v/>
+      </c>
+      <c r="O140" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O140" t="str">
+      <c r="P140" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P140" t="str">
+      <c r="Q140" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q140" t="str">
+      <c r="R140" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R140" t="str">
+      <c r="S140" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8296,27 +8718,30 @@
         <v/>
       </c>
       <c r="K141" t="str">
+        <v/>
+      </c>
+      <c r="L141" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L141" t="str">
+      <c r="M141" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M141" t="str">
-        <v/>
-      </c>
       <c r="N141" t="str">
+        <v/>
+      </c>
+      <c r="O141" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O141" t="str">
+      <c r="P141" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P141" t="str">
+      <c r="Q141" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q141" t="str">
+      <c r="R141" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R141" t="str">
+      <c r="S141" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8352,27 +8777,30 @@
         <v/>
       </c>
       <c r="K142" t="str">
+        <v/>
+      </c>
+      <c r="L142" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L142" t="str">
+      <c r="M142" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M142" t="str">
+      <c r="N142" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N142" t="str">
+      <c r="O142" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O142" t="str">
+      <c r="P142" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P142" t="str">
+      <c r="Q142" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q142" t="str">
+      <c r="R142" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R142" t="str">
+      <c r="S142" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8408,27 +8836,30 @@
         <v/>
       </c>
       <c r="K143" t="str">
+        <v/>
+      </c>
+      <c r="L143" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L143" t="str">
+      <c r="M143" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M143" t="str">
-        <v/>
-      </c>
       <c r="N143" t="str">
+        <v/>
+      </c>
+      <c r="O143" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O143" t="str">
+      <c r="P143" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P143" t="str">
+      <c r="Q143" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q143" t="str">
+      <c r="R143" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R143" t="str">
+      <c r="S143" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8464,27 +8895,30 @@
         <v/>
       </c>
       <c r="K144" t="str">
+        <v/>
+      </c>
+      <c r="L144" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L144" t="str">
+      <c r="M144" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M144" t="str">
-        <v/>
-      </c>
       <c r="N144" t="str">
+        <v/>
+      </c>
+      <c r="O144" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O144" t="str">
+      <c r="P144" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P144" t="str">
+      <c r="Q144" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q144" t="str">
+      <c r="R144" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R144" t="str">
+      <c r="S144" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8520,27 +8954,30 @@
         <v/>
       </c>
       <c r="K145" t="str">
+        <v/>
+      </c>
+      <c r="L145" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L145" t="str">
+      <c r="M145" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M145" t="str">
-        <v/>
-      </c>
       <c r="N145" t="str">
+        <v/>
+      </c>
+      <c r="O145" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O145" t="str">
+      <c r="P145" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P145" t="str">
+      <c r="Q145" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q145" t="str">
+      <c r="R145" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R145" t="str">
+      <c r="S145" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8576,27 +9013,30 @@
         <v/>
       </c>
       <c r="K146" t="str">
+        <v/>
+      </c>
+      <c r="L146" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L146" t="str">
+      <c r="M146" t="str">
         <v>CL G1</v>
       </c>
-      <c r="M146" t="str">
-        <v/>
-      </c>
       <c r="N146" t="str">
+        <v/>
+      </c>
+      <c r="O146" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O146" t="str">
+      <c r="P146" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P146" t="str">
+      <c r="Q146" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q146" t="str">
+      <c r="R146" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R146" t="str">
+      <c r="S146" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8632,27 +9072,30 @@
         <v/>
       </c>
       <c r="K147" t="str">
+        <v/>
+      </c>
+      <c r="L147" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L147" t="str">
+      <c r="M147" t="str">
         <v>ML G2</v>
       </c>
-      <c r="M147" t="str">
-        <v/>
-      </c>
       <c r="N147" t="str">
+        <v/>
+      </c>
+      <c r="O147" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O147" t="str">
+      <c r="P147" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P147" t="str">
+      <c r="Q147" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q147" t="str">
+      <c r="R147" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R147" t="str">
+      <c r="S147" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8688,27 +9131,30 @@
         <v/>
       </c>
       <c r="K148" t="str">
+        <v/>
+      </c>
+      <c r="L148" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L148" t="str">
+      <c r="M148" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M148" t="str">
-        <v/>
-      </c>
       <c r="N148" t="str">
+        <v/>
+      </c>
+      <c r="O148" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O148" t="str">
+      <c r="P148" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P148" t="str">
+      <c r="Q148" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q148" t="str">
+      <c r="R148" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R148" t="str">
+      <c r="S148" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8744,27 +9190,30 @@
         <v/>
       </c>
       <c r="K149" t="str">
+        <v/>
+      </c>
+      <c r="L149" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L149" t="str">
+      <c r="M149" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M149" t="str">
+      <c r="N149" t="str">
         <v>CHINESE</v>
       </c>
-      <c r="N149" t="str">
+      <c r="O149" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O149" t="str">
+      <c r="P149" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P149" t="str">
+      <c r="Q149" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q149" t="str">
+      <c r="R149" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R149" t="str">
+      <c r="S149" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8800,27 +9249,30 @@
         <v/>
       </c>
       <c r="K150" t="str">
+        <v/>
+      </c>
+      <c r="L150" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L150" t="str">
+      <c r="M150" t="str">
         <v>ML G1</v>
       </c>
-      <c r="M150" t="str">
-        <v/>
-      </c>
       <c r="N150" t="str">
+        <v/>
+      </c>
+      <c r="O150" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O150" t="str">
+      <c r="P150" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P150" t="str">
+      <c r="Q150" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q150" t="str">
+      <c r="R150" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R150" t="str">
+      <c r="S150" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -8856,27 +9308,30 @@
         <v/>
       </c>
       <c r="K151" t="str">
+        <v/>
+      </c>
+      <c r="L151" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L151" t="str">
+      <c r="M151" t="str">
         <v>TL G2</v>
       </c>
-      <c r="M151" t="str">
-        <v/>
-      </c>
       <c r="N151" t="str">
+        <v/>
+      </c>
+      <c r="O151" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O151" t="str">
+      <c r="P151" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P151" t="str">
+      <c r="Q151" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q151" t="str">
+      <c r="R151" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R151" t="str">
+      <c r="S151" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -8912,27 +9367,30 @@
         <v/>
       </c>
       <c r="K152" t="str">
+        <v/>
+      </c>
+      <c r="L152" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L152" t="str">
+      <c r="M152" t="str">
         <v>CL G3</v>
       </c>
-      <c r="M152" t="str">
-        <v/>
-      </c>
       <c r="N152" t="str">
+        <v/>
+      </c>
+      <c r="O152" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O152" t="str">
+      <c r="P152" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P152" t="str">
+      <c r="Q152" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q152" t="str">
+      <c r="R152" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R152" t="str">
+      <c r="S152" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -8968,27 +9426,30 @@
         <v/>
       </c>
       <c r="K153" t="str">
+        <v/>
+      </c>
+      <c r="L153" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L153" t="str">
+      <c r="M153" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M153" t="str">
-        <v/>
-      </c>
       <c r="N153" t="str">
+        <v/>
+      </c>
+      <c r="O153" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O153" t="str">
+      <c r="P153" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P153" t="str">
+      <c r="Q153" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q153" t="str">
+      <c r="R153" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R153" t="str">
+      <c r="S153" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -9024,27 +9485,30 @@
         <v/>
       </c>
       <c r="K154" t="str">
+        <v/>
+      </c>
+      <c r="L154" t="str">
         <v>EL G1</v>
       </c>
-      <c r="L154" t="str">
+      <c r="M154" t="str">
         <v>TL G1</v>
       </c>
-      <c r="M154" t="str">
-        <v/>
-      </c>
       <c r="N154" t="str">
+        <v/>
+      </c>
+      <c r="O154" t="str">
         <v>MA G1</v>
       </c>
-      <c r="O154" t="str">
+      <c r="P154" t="str">
         <v>SCI G1</v>
       </c>
-      <c r="P154" t="str">
+      <c r="Q154" t="str">
         <v>HIST G1</v>
       </c>
-      <c r="Q154" t="str">
+      <c r="R154" t="str">
         <v>GEOG G1</v>
       </c>
-      <c r="R154" t="str">
+      <c r="S154" t="str">
         <v>LIT G1</v>
       </c>
     </row>
@@ -9080,27 +9544,30 @@
         <v/>
       </c>
       <c r="K155" t="str">
+        <v/>
+      </c>
+      <c r="L155" t="str">
         <v>EL G2</v>
       </c>
-      <c r="L155" t="str">
+      <c r="M155" t="str">
         <v>CL G2</v>
       </c>
-      <c r="M155" t="str">
-        <v/>
-      </c>
       <c r="N155" t="str">
+        <v/>
+      </c>
+      <c r="O155" t="str">
         <v>MA G2</v>
       </c>
-      <c r="O155" t="str">
+      <c r="P155" t="str">
         <v>SCI G2</v>
       </c>
-      <c r="P155" t="str">
+      <c r="Q155" t="str">
         <v>HIST G2</v>
       </c>
-      <c r="Q155" t="str">
+      <c r="R155" t="str">
         <v>GEOG G2</v>
       </c>
-      <c r="R155" t="str">
+      <c r="S155" t="str">
         <v>LIT G2</v>
       </c>
     </row>
@@ -9136,27 +9603,30 @@
         <v/>
       </c>
       <c r="K156" t="str">
+        <v/>
+      </c>
+      <c r="L156" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L156" t="str">
+      <c r="M156" t="str">
         <v>ML G3</v>
       </c>
-      <c r="M156" t="str">
+      <c r="N156" t="str">
         <v>MALAY</v>
       </c>
-      <c r="N156" t="str">
+      <c r="O156" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O156" t="str">
+      <c r="P156" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P156" t="str">
+      <c r="Q156" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q156" t="str">
+      <c r="R156" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R156" t="str">
+      <c r="S156" t="str">
         <v>LIT G3</v>
       </c>
     </row>
@@ -9192,33 +9662,36 @@
         <v/>
       </c>
       <c r="K157" t="str">
+        <v/>
+      </c>
+      <c r="L157" t="str">
         <v>EL G3</v>
       </c>
-      <c r="L157" t="str">
+      <c r="M157" t="str">
         <v>TL G3</v>
       </c>
-      <c r="M157" t="str">
-        <v/>
-      </c>
       <c r="N157" t="str">
+        <v/>
+      </c>
+      <c r="O157" t="str">
         <v>MA G3</v>
       </c>
-      <c r="O157" t="str">
+      <c r="P157" t="str">
         <v>SCI G3</v>
       </c>
-      <c r="P157" t="str">
+      <c r="Q157" t="str">
         <v>HIST G3</v>
       </c>
-      <c r="Q157" t="str">
+      <c r="R157" t="str">
         <v>GEOG G3</v>
       </c>
-      <c r="R157" t="str">
+      <c r="S157" t="str">
         <v>LIT G3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:R157"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S157"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -14651,4 +15124,63 @@
     <ignoredError numberStoredAsText="1" sqref="A1:F2"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K1"/>
+  <cols>
+    <col min="1" max="1" width="14.83203125" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="3" width="24.83203125" customWidth="1"/>
+    <col min="4" max="4" width="16.83203125" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="6" max="6" width="28.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>RequestID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Made</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Teacher</v>
+      </c>
+      <c r="D1" t="str">
+        <v>GroupCode</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Action</v>
+      </c>
+      <c r="F1" t="str">
+        <v>StudentName</v>
+      </c>
+      <c r="G1" t="str">
+        <v>StudentID</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Reason</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Status</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Decided</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Note</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:K1"/>
+  </ignoredErrors>
+</worksheet>
 </file>
--- a/sample/namelist.xlsx
+++ b/sample/namelist.xlsx
@@ -9757,7 +9757,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -9786,7 +9786,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -9815,7 +9815,7 @@
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -9844,7 +9844,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -9873,7 +9873,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -9902,7 +9902,7 @@
         <v>1</v>
       </c>
       <c r="F7" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -9931,7 +9931,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -9960,7 +9960,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -9989,7 +9989,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -10018,7 +10018,7 @@
         <v>1</v>
       </c>
       <c r="F11" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -10047,7 +10047,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <v>EL=</v>
+        <v>EL</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -10076,7 +10076,7 @@
         <v>1</v>
       </c>
       <c r="F13" t="str">
-        <v>MA=</v>
+        <v>MA</v>
       </c>
       <c r="G13" t="str">
         <v/>
